--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R96b765a9d9dc4e93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="单币测算" sheetId="2" r:id="R57dd9c4cd02349d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全Quote预算" sheetId="3" r:id="R188a5d39cb1d4558"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选中Quote曲线" sheetId="4" r:id="Rb8d713ca8d9340c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="5" r:id="R6b34ddec61354312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R81efb20ad7014217"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="单币测算" sheetId="2" r:id="Race44d43fd85422b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全Quote预算" sheetId="3" r:id="R5d5f64c74dea4a1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选中Quote曲线" sheetId="4" r:id="Rf2ab475e3ee74623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="5" r:id="R32cccb051ed843c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="14">
+  <x:numFmts count="15">
     <x:numFmt numFmtId="200" formatCode="@"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00000000"/>
     <x:numFmt numFmtId="202" formatCode="0.0000x"/>
@@ -32,6 +32,7 @@
     <x:numFmt numFmtId="211" formatCode="0.0%"/>
     <x:numFmt numFmtId="212" formatCode="General"/>
     <x:numFmt numFmtId="213" formatCode="0.000000"/>
+    <x:numFmt numFmtId="214" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </x:numFmts>
   <x:fonts count="31">
     <x:font>
@@ -646,7 +647,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="516">
+  <x:cellXfs count="520">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2017,6 +2018,16 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="213" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="214" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -11021,7 +11032,7 @@
         <x:v>说明</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="20" customHeight="1">
+    <x:row r="9" ht="36" customHeight="1">
       <x:c r="C9" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -11072,19 +11083,19 @@
       <x:c r="Q9" s="39" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R9" s="33" t="str">
+      <x:c r="R9" s="518" t="str">
         <x:v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</x:v>
       </x:c>
       <x:c r="S9" s="515"/>
-      <x:c r="T9" s="6" t="n">
+      <x:c r="T9" s="516" t="n">
         <x:v>46282.368501157405</x:v>
       </x:c>
-      <x:c r="U9" s="6"/>
-      <x:c r="V9" s="6" t="str">
+      <x:c r="U9" s="517"/>
+      <x:c r="V9" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="20" customHeight="1">
+    <x:row r="10" ht="36" customHeight="1">
       <x:c r="C10" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -11135,23 +11146,23 @@
       <x:c r="Q10" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R10" s="35" t="str">
+      <x:c r="R10" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</x:v>
       </x:c>
       <x:c r="S10" s="515" t="n">
         <x:v>333.84044118382997</x:v>
       </x:c>
-      <x:c r="T10" s="6" t="n">
+      <x:c r="T10" s="516" t="n">
         <x:v>46282.36820370371</x:v>
       </x:c>
-      <x:c r="U10" s="6" t="str">
+      <x:c r="U10" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x8bb3514e2204e1cdf3ac149efee7ff04d91b719f</x:v>
       </x:c>
-      <x:c r="V10" s="6" t="str">
+      <x:c r="V10" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="20" customHeight="1">
+    <x:row r="11" ht="36" customHeight="1">
       <x:c r="C11" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -11202,19 +11213,19 @@
       <x:c r="Q11" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R11" s="35" t="str">
+      <x:c r="R11" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</x:v>
       </x:c>
       <x:c r="S11" s="515"/>
-      <x:c r="T11" s="6" t="n">
+      <x:c r="T11" s="516" t="n">
         <x:v>46282.36820842593</x:v>
       </x:c>
-      <x:c r="U11" s="6"/>
-      <x:c r="V11" s="6" t="str">
+      <x:c r="U11" s="517"/>
+      <x:c r="V11" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="20" customHeight="1">
+    <x:row r="12" ht="36" customHeight="1">
       <x:c r="C12" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -11265,19 +11276,19 @@
       <x:c r="Q12" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R12" s="35" t="str">
+      <x:c r="R12" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x86923f96303D656E4aa86D9d42D1e57ad2023fdC</x:v>
       </x:c>
       <x:c r="S12" s="515"/>
-      <x:c r="T12" s="6" t="n">
+      <x:c r="T12" s="516" t="n">
         <x:v>46282.368211388886</x:v>
       </x:c>
-      <x:c r="U12" s="6"/>
-      <x:c r="V12" s="6" t="str">
+      <x:c r="U12" s="517"/>
+      <x:c r="V12" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="20" customHeight="1">
+    <x:row r="13" ht="36" customHeight="1">
       <x:c r="C13" s="26" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -11328,19 +11339,19 @@
       <x:c r="Q13" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R13" s="35" t="str">
+      <x:c r="R13" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x12f190a9F9d7D37a250758b26824B97CE941bF54</x:v>
       </x:c>
       <x:c r="S13" s="515"/>
-      <x:c r="T13" s="6" t="n">
+      <x:c r="T13" s="516" t="n">
         <x:v>46282.368217152776</x:v>
       </x:c>
-      <x:c r="U13" s="6"/>
-      <x:c r="V13" s="6" t="str">
+      <x:c r="U13" s="517"/>
+      <x:c r="V13" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="20" customHeight="1">
+    <x:row r="14" ht="36" customHeight="1">
       <x:c r="C14" s="26" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -11391,19 +11402,19 @@
       <x:c r="Q14" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R14" s="35" t="str">
+      <x:c r="R14" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xad25ac6c84d497db898fa1e8387bf6af3532a1c4</x:v>
       </x:c>
       <x:c r="S14" s="515"/>
-      <x:c r="T14" s="6" t="n">
+      <x:c r="T14" s="516" t="n">
         <x:v>46282.36822626158</x:v>
       </x:c>
-      <x:c r="U14" s="6"/>
-      <x:c r="V14" s="6" t="str">
+      <x:c r="U14" s="517"/>
+      <x:c r="V14" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="20" customHeight="1">
+    <x:row r="15" ht="36" customHeight="1">
       <x:c r="C15" s="26" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -11454,19 +11465,19 @@
       <x:c r="Q15" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R15" s="35" t="str">
+      <x:c r="R15" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x48E39E56aCdbA37b09020C0b734A613C9a2f100A</x:v>
       </x:c>
       <x:c r="S15" s="515"/>
-      <x:c r="T15" s="6" t="n">
+      <x:c r="T15" s="516" t="n">
         <x:v>46282.368228761574</x:v>
       </x:c>
-      <x:c r="U15" s="6"/>
-      <x:c r="V15" s="6" t="str">
+      <x:c r="U15" s="517"/>
+      <x:c r="V15" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="20" customHeight="1">
+    <x:row r="16" ht="36" customHeight="1">
       <x:c r="C16" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -11517,19 +11528,19 @@
       <x:c r="Q16" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R16" s="35" t="str">
+      <x:c r="R16" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x822cc93ffd030293e9842c30bbd678f530701867</x:v>
       </x:c>
       <x:c r="S16" s="515"/>
-      <x:c r="T16" s="6" t="n">
+      <x:c r="T16" s="516" t="n">
         <x:v>46282.36823450231</x:v>
       </x:c>
-      <x:c r="U16" s="6"/>
-      <x:c r="V16" s="6" t="str">
+      <x:c r="U16" s="517"/>
+      <x:c r="V16" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="20" customHeight="1">
+    <x:row r="17" ht="36" customHeight="1">
       <x:c r="C17" s="26" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -11580,19 +11591,19 @@
       <x:c r="Q17" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R17" s="35" t="str">
+      <x:c r="R17" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xcef9027c7d6985b85f0ba431125073529a947a68</x:v>
       </x:c>
       <x:c r="S17" s="515"/>
-      <x:c r="T17" s="6" t="n">
+      <x:c r="T17" s="516" t="n">
         <x:v>46282.36824038195</x:v>
       </x:c>
-      <x:c r="U17" s="6"/>
-      <x:c r="V17" s="6" t="str">
+      <x:c r="U17" s="517"/>
+      <x:c r="V17" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="20" customHeight="1">
+    <x:row r="18" ht="36" customHeight="1">
       <x:c r="C18" s="26" t="n">
         <x:v>10</x:v>
       </x:c>
@@ -11643,23 +11654,23 @@
       <x:c r="Q18" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R18" s="35" t="str">
+      <x:c r="R18" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</x:v>
       </x:c>
       <x:c r="S18" s="515" t="n">
         <x:v>168.78684455476264</x:v>
       </x:c>
-      <x:c r="T18" s="6" t="n">
+      <x:c r="T18" s="516" t="n">
         <x:v>46282.368246273145</x:v>
       </x:c>
-      <x:c r="U18" s="6" t="str">
+      <x:c r="U18" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x6707aeac7d0e519b083219d27bb427364363183a</x:v>
       </x:c>
-      <x:c r="V18" s="6" t="str">
+      <x:c r="V18" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="20" customHeight="1">
+    <x:row r="19" ht="36" customHeight="1">
       <x:c r="C19" s="26" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -11710,19 +11721,19 @@
       <x:c r="Q19" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R19" s="35" t="str">
+      <x:c r="R19" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x4EA005168D7F09a7A0Ba9D1DEf21a479950E44C2</x:v>
       </x:c>
       <x:c r="S19" s="515"/>
-      <x:c r="T19" s="6" t="n">
+      <x:c r="T19" s="516" t="n">
         <x:v>46282.368252002314</x:v>
       </x:c>
-      <x:c r="U19" s="6"/>
-      <x:c r="V19" s="6" t="str">
+      <x:c r="U19" s="517"/>
+      <x:c r="V19" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="20" customHeight="1">
+    <x:row r="20" ht="36" customHeight="1">
       <x:c r="C20" s="26" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -11773,23 +11784,23 @@
       <x:c r="Q20" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R20" s="35" t="str">
+      <x:c r="R20" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</x:v>
       </x:c>
       <x:c r="S20" s="515" t="n">
         <x:v>83.35251668951989</x:v>
       </x:c>
-      <x:c r="T20" s="6" t="n">
+      <x:c r="T20" s="516" t="n">
         <x:v>46282.36825775463</x:v>
       </x:c>
-      <x:c r="U20" s="6" t="str">
+      <x:c r="U20" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x754ddd4bf8e8635b4301a7f4af2ea7a82ab6cea7</x:v>
       </x:c>
-      <x:c r="V20" s="6" t="str">
+      <x:c r="V20" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="20" customHeight="1">
+    <x:row r="21" ht="36" customHeight="1">
       <x:c r="C21" s="26" t="n">
         <x:v>13</x:v>
       </x:c>
@@ -11840,19 +11851,19 @@
       <x:c r="Q21" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R21" s="35" t="str">
+      <x:c r="R21" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x941AE714EC6D8130c7B75d67160Ca08f1e7d11Dd</x:v>
       </x:c>
       <x:c r="S21" s="515"/>
-      <x:c r="T21" s="6" t="n">
+      <x:c r="T21" s="516" t="n">
         <x:v>46282.36826351852</x:v>
       </x:c>
-      <x:c r="U21" s="6"/>
-      <x:c r="V21" s="6" t="str">
+      <x:c r="U21" s="517"/>
+      <x:c r="V21" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="20" customHeight="1">
+    <x:row r="22" ht="36" customHeight="1">
       <x:c r="C22" s="26" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -11903,23 +11914,23 @@
       <x:c r="Q22" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R22" s="35" t="str">
+      <x:c r="R22" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</x:v>
       </x:c>
       <x:c r="S22" s="515" t="n">
         <x:v>8.607488515008058</x:v>
       </x:c>
-      <x:c r="T22" s="6" t="n">
+      <x:c r="T22" s="516" t="n">
         <x:v>46282.36826935185</x:v>
       </x:c>
-      <x:c r="U22" s="6" t="str">
+      <x:c r="U22" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x81b4caac5d313ea0c831c4d16f8c23937602dcf1</x:v>
       </x:c>
-      <x:c r="V22" s="6" t="str">
+      <x:c r="V22" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="20" customHeight="1">
+    <x:row r="23" ht="36" customHeight="1">
       <x:c r="C23" s="26" t="n">
         <x:v>15</x:v>
       </x:c>
@@ -11970,19 +11981,19 @@
       <x:c r="Q23" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R23" s="35" t="str">
+      <x:c r="R23" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x25c288e6d899b9bc30160965ad9644c67e73be0c</x:v>
       </x:c>
       <x:c r="S23" s="515"/>
-      <x:c r="T23" s="6" t="n">
+      <x:c r="T23" s="516" t="n">
         <x:v>46282.36827517361</x:v>
       </x:c>
-      <x:c r="U23" s="6"/>
-      <x:c r="V23" s="6" t="str">
+      <x:c r="U23" s="517"/>
+      <x:c r="V23" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="20" customHeight="1">
+    <x:row r="24" ht="36" customHeight="1">
       <x:c r="C24" s="26" t="n">
         <x:v>16</x:v>
       </x:c>
@@ -12033,19 +12044,19 @@
       <x:c r="Q24" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R24" s="35" t="str">
+      <x:c r="R24" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x41F4267525a8AFf329540eF24fD83d9044758B33</x:v>
       </x:c>
       <x:c r="S24" s="515"/>
-      <x:c r="T24" s="6" t="n">
+      <x:c r="T24" s="516" t="n">
         <x:v>46282.3682809375</x:v>
       </x:c>
-      <x:c r="U24" s="6"/>
-      <x:c r="V24" s="6" t="str">
+      <x:c r="U24" s="517"/>
+      <x:c r="V24" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="20" customHeight="1">
+    <x:row r="25" ht="36" customHeight="1">
       <x:c r="C25" s="26" t="n">
         <x:v>17</x:v>
       </x:c>
@@ -12096,23 +12107,23 @@
       <x:c r="Q25" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R25" s="35" t="str">
+      <x:c r="R25" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</x:v>
       </x:c>
       <x:c r="S25" s="515" t="n">
         <x:v>396.83524666459823</x:v>
       </x:c>
-      <x:c r="T25" s="6" t="n">
+      <x:c r="T25" s="516" t="n">
         <x:v>46282.36829019676</x:v>
       </x:c>
-      <x:c r="U25" s="6" t="str">
+      <x:c r="U25" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x98996e833ea35ec17c3645ca7b6dd40d188564c4</x:v>
       </x:c>
-      <x:c r="V25" s="6" t="str">
+      <x:c r="V25" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="20" customHeight="1">
+    <x:row r="26" ht="36" customHeight="1">
       <x:c r="C26" s="26" t="n">
         <x:v>18</x:v>
       </x:c>
@@ -12163,19 +12174,19 @@
       <x:c r="Q26" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R26" s="35" t="str">
+      <x:c r="R26" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x1b0E319c6A659F002271B69dB8A7df2F911c153E</x:v>
       </x:c>
       <x:c r="S26" s="515"/>
-      <x:c r="T26" s="6" t="n">
+      <x:c r="T26" s="516" t="n">
         <x:v>46282.36829252315</x:v>
       </x:c>
-      <x:c r="U26" s="6"/>
-      <x:c r="V26" s="6" t="str">
+      <x:c r="U26" s="517"/>
+      <x:c r="V26" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="20" customHeight="1">
+    <x:row r="27" ht="36" customHeight="1">
       <x:c r="C27" s="26" t="n">
         <x:v>19</x:v>
       </x:c>
@@ -12226,23 +12237,23 @@
       <x:c r="Q27" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R27" s="35" t="str">
+      <x:c r="R27" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</x:v>
       </x:c>
       <x:c r="S27" s="515" t="n">
         <x:v>343.71903556093804</x:v>
       </x:c>
-      <x:c r="T27" s="6" t="n">
+      <x:c r="T27" s="516" t="n">
         <x:v>46282.36829837963</x:v>
       </x:c>
-      <x:c r="U27" s="6" t="str">
+      <x:c r="U27" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x8c2b4303fa0b99d07a5d3e9411497a277e65b673</x:v>
       </x:c>
-      <x:c r="V27" s="6" t="str">
+      <x:c r="V27" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="20" customHeight="1">
+    <x:row r="28" ht="36" customHeight="1">
       <x:c r="C28" s="26" t="n">
         <x:v>20</x:v>
       </x:c>
@@ -12293,23 +12304,23 @@
       <x:c r="Q28" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R28" s="35" t="str">
+      <x:c r="R28" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</x:v>
       </x:c>
       <x:c r="S28" s="515" t="n">
         <x:v>28.304625023770683</x:v>
       </x:c>
-      <x:c r="T28" s="6" t="n">
+      <x:c r="T28" s="516" t="n">
         <x:v>46282.368304166666</x:v>
       </x:c>
-      <x:c r="U28" s="6" t="str">
+      <x:c r="U28" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0xd10e6245961d697d975963682ece9979e9917fbc</x:v>
       </x:c>
-      <x:c r="V28" s="6" t="str">
+      <x:c r="V28" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="20" customHeight="1">
+    <x:row r="29" ht="36" customHeight="1">
       <x:c r="C29" s="26" t="n">
         <x:v>21</x:v>
       </x:c>
@@ -12360,19 +12371,19 @@
       <x:c r="Q29" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R29" s="35" t="str">
+      <x:c r="R29" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x980dcf6766fa79f5cf0c4aadb3ab477ff15a9619</x:v>
       </x:c>
       <x:c r="S29" s="515"/>
-      <x:c r="T29" s="6" t="n">
+      <x:c r="T29" s="516" t="n">
         <x:v>46282.36830994213</x:v>
       </x:c>
-      <x:c r="U29" s="6"/>
-      <x:c r="V29" s="6" t="str">
+      <x:c r="U29" s="517"/>
+      <x:c r="V29" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="20" customHeight="1">
+    <x:row r="30" ht="36" customHeight="1">
       <x:c r="C30" s="26" t="n">
         <x:v>22</x:v>
       </x:c>
@@ -12423,19 +12434,19 @@
       <x:c r="Q30" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R30" s="35" t="str">
+      <x:c r="R30" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xacef2e09adb47ad6abebad9ff06689e60615c2b6</x:v>
       </x:c>
       <x:c r="S30" s="515"/>
-      <x:c r="T30" s="6" t="n">
+      <x:c r="T30" s="516" t="n">
         <x:v>46282.36831733796</x:v>
       </x:c>
-      <x:c r="U30" s="6"/>
-      <x:c r="V30" s="6" t="str">
+      <x:c r="U30" s="517"/>
+      <x:c r="V30" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="20" customHeight="1">
+    <x:row r="31" ht="36" customHeight="1">
       <x:c r="C31" s="26" t="n">
         <x:v>23</x:v>
       </x:c>
@@ -12486,19 +12497,19 @@
       <x:c r="Q31" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R31" s="35" t="str">
+      <x:c r="R31" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x03DfbBE0AC4E7bCDaFd08eD41A400326B77D8c80</x:v>
       </x:c>
       <x:c r="S31" s="515"/>
-      <x:c r="T31" s="6" t="n">
+      <x:c r="T31" s="516" t="n">
         <x:v>46282.36832488426</x:v>
       </x:c>
-      <x:c r="U31" s="6"/>
-      <x:c r="V31" s="6" t="str">
+      <x:c r="U31" s="517"/>
+      <x:c r="V31" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="20" customHeight="1">
+    <x:row r="32" ht="36" customHeight="1">
       <x:c r="C32" s="26" t="n">
         <x:v>24</x:v>
       </x:c>
@@ -12549,23 +12560,23 @@
       <x:c r="Q32" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R32" s="35" t="str">
+      <x:c r="R32" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</x:v>
       </x:c>
       <x:c r="S32" s="515" t="n">
         <x:v>1143.244622821855</x:v>
       </x:c>
-      <x:c r="T32" s="6" t="n">
+      <x:c r="T32" s="516" t="n">
         <x:v>46282.36832918981</x:v>
       </x:c>
-      <x:c r="U32" s="6" t="str">
+      <x:c r="U32" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x666ba98ab094793e276215448f2485fd8e3c3ce5</x:v>
       </x:c>
-      <x:c r="V32" s="6" t="str">
+      <x:c r="V32" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="20" customHeight="1">
+    <x:row r="33" ht="36" customHeight="1">
       <x:c r="C33" s="26" t="n">
         <x:v>25</x:v>
       </x:c>
@@ -12616,19 +12627,19 @@
       <x:c r="Q33" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R33" s="35" t="str">
+      <x:c r="R33" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x4e62068525Ab11FE768e29dfD00ef909B9803016</x:v>
       </x:c>
       <x:c r="S33" s="515"/>
-      <x:c r="T33" s="6" t="n">
+      <x:c r="T33" s="516" t="n">
         <x:v>46282.36833318287</x:v>
       </x:c>
-      <x:c r="U33" s="6"/>
-      <x:c r="V33" s="6" t="str">
+      <x:c r="U33" s="517"/>
+      <x:c r="V33" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="20" customHeight="1">
+    <x:row r="34" ht="36" customHeight="1">
       <x:c r="C34" s="26" t="n">
         <x:v>26</x:v>
       </x:c>
@@ -12679,23 +12690,23 @@
       <x:c r="Q34" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R34" s="35" t="str">
+      <x:c r="R34" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</x:v>
       </x:c>
       <x:c r="S34" s="515" t="n">
         <x:v>681.5229249447019</x:v>
       </x:c>
-      <x:c r="T34" s="6" t="n">
+      <x:c r="T34" s="516" t="n">
         <x:v>46282.368339849534</x:v>
       </x:c>
-      <x:c r="U34" s="6" t="str">
+      <x:c r="U34" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0xa4bdb396a69617eb7f70e2cc1ef526f7340b1b0d</x:v>
       </x:c>
-      <x:c r="V34" s="6" t="str">
+      <x:c r="V34" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="20" customHeight="1">
+    <x:row r="35" ht="36" customHeight="1">
       <x:c r="C35" s="26" t="n">
         <x:v>27</x:v>
       </x:c>
@@ -12746,19 +12757,19 @@
       <x:c r="Q35" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R35" s="35" t="str">
+      <x:c r="R35" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x43B07D15cE533bEc5476d70C22a78a1B2B662155</x:v>
       </x:c>
       <x:c r="S35" s="515"/>
-      <x:c r="T35" s="6" t="n">
+      <x:c r="T35" s="516" t="n">
         <x:v>46282.36834631945</x:v>
       </x:c>
-      <x:c r="U35" s="6"/>
-      <x:c r="V35" s="6" t="str">
+      <x:c r="U35" s="517"/>
+      <x:c r="V35" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="20" customHeight="1">
+    <x:row r="36" ht="36" customHeight="1">
       <x:c r="C36" s="26" t="n">
         <x:v>28</x:v>
       </x:c>
@@ -12809,19 +12820,19 @@
       <x:c r="Q36" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R36" s="35" t="str">
+      <x:c r="R36" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x62fd0668e10D8B72339BE2DCF7643001688ff13B</x:v>
       </x:c>
       <x:c r="S36" s="515"/>
-      <x:c r="T36" s="6" t="n">
+      <x:c r="T36" s="516" t="n">
         <x:v>46282.368350543984</x:v>
       </x:c>
-      <x:c r="U36" s="6"/>
-      <x:c r="V36" s="6" t="str">
+      <x:c r="U36" s="517"/>
+      <x:c r="V36" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="20" customHeight="1">
+    <x:row r="37" ht="36" customHeight="1">
       <x:c r="C37" s="26" t="n">
         <x:v>29</x:v>
       </x:c>
@@ -12872,19 +12883,19 @@
       <x:c r="Q37" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R37" s="35" t="str">
+      <x:c r="R37" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xe93237C50D904957Cf27E7B1133b510C669c2e74</x:v>
       </x:c>
       <x:c r="S37" s="515"/>
-      <x:c r="T37" s="6" t="n">
+      <x:c r="T37" s="516" t="n">
         <x:v>46282.368356956016</x:v>
       </x:c>
-      <x:c r="U37" s="6"/>
-      <x:c r="V37" s="6" t="str">
+      <x:c r="U37" s="517"/>
+      <x:c r="V37" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="20" customHeight="1">
+    <x:row r="38" ht="36" customHeight="1">
       <x:c r="C38" s="26" t="n">
         <x:v>30</x:v>
       </x:c>
@@ -12935,23 +12946,23 @@
       <x:c r="Q38" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R38" s="35" t="str">
+      <x:c r="R38" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</x:v>
       </x:c>
       <x:c r="S38" s="515" t="n">
         <x:v>128.77203166755078</x:v>
       </x:c>
-      <x:c r="T38" s="6" t="n">
+      <x:c r="T38" s="516" t="n">
         <x:v>46282.368362835645</x:v>
       </x:c>
-      <x:c r="U38" s="6" t="str">
+      <x:c r="U38" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x70504a6fafdbfb75fe971faa4dd716e79ac5624c</x:v>
       </x:c>
-      <x:c r="V38" s="6" t="str">
+      <x:c r="V38" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="20" customHeight="1">
+    <x:row r="39" ht="36" customHeight="1">
       <x:c r="C39" s="26" t="n">
         <x:v>31</x:v>
       </x:c>
@@ -13002,23 +13013,23 @@
       <x:c r="Q39" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R39" s="35" t="str">
+      <x:c r="R39" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</x:v>
       </x:c>
       <x:c r="S39" s="515" t="n">
         <x:v>940.8085033979563</x:v>
       </x:c>
-      <x:c r="T39" s="6" t="n">
+      <x:c r="T39" s="516" t="n">
         <x:v>46282.36836875</x:v>
       </x:c>
-      <x:c r="U39" s="6" t="str">
+      <x:c r="U39" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x301f48ec369bb3bfa0bc04d44a79037aa0ee2340</x:v>
       </x:c>
-      <x:c r="V39" s="6" t="str">
+      <x:c r="V39" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="20" customHeight="1">
+    <x:row r="40" ht="36" customHeight="1">
       <x:c r="C40" s="26" t="n">
         <x:v>32</x:v>
       </x:c>
@@ -13069,19 +13080,19 @@
       <x:c r="Q40" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R40" s="35" t="str">
+      <x:c r="R40" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xe0444ef8bf4ed74f74fd73686e2ddf4c1c5591e8</x:v>
       </x:c>
       <x:c r="S40" s="515"/>
-      <x:c r="T40" s="6" t="n">
+      <x:c r="T40" s="516" t="n">
         <x:v>46282.36837949074</x:v>
       </x:c>
-      <x:c r="U40" s="6"/>
-      <x:c r="V40" s="6" t="str">
+      <x:c r="U40" s="517"/>
+      <x:c r="V40" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="20" customHeight="1">
+    <x:row r="41" ht="36" customHeight="1">
       <x:c r="C41" s="26" t="n">
         <x:v>33</x:v>
       </x:c>
@@ -13132,19 +13143,19 @@
       <x:c r="Q41" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R41" s="35" t="str">
+      <x:c r="R41" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x408c14038a04f7bd235329e26d2bf569ee20e250</x:v>
       </x:c>
       <x:c r="S41" s="515"/>
-      <x:c r="T41" s="6" t="n">
+      <x:c r="T41" s="516" t="n">
         <x:v>46282.36838523148</x:v>
       </x:c>
-      <x:c r="U41" s="6"/>
-      <x:c r="V41" s="6" t="str">
+      <x:c r="U41" s="517"/>
+      <x:c r="V41" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="20" customHeight="1">
+    <x:row r="42" ht="36" customHeight="1">
       <x:c r="C42" s="26" t="n">
         <x:v>34</x:v>
       </x:c>
@@ -13195,23 +13206,23 @@
       <x:c r="Q42" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R42" s="35" t="str">
+      <x:c r="R42" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</x:v>
       </x:c>
       <x:c r="S42" s="515" t="n">
         <x:v>217.12890214486603</x:v>
       </x:c>
-      <x:c r="T42" s="6" t="n">
+      <x:c r="T42" s="516" t="n">
         <x:v>46282.36837377315</x:v>
       </x:c>
-      <x:c r="U42" s="6" t="str">
+      <x:c r="U42" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x62ab521f71431f78ac374cdbadc6cda3c8916b6c</x:v>
       </x:c>
-      <x:c r="V42" s="6" t="str">
+      <x:c r="V42" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="20" customHeight="1">
+    <x:row r="43" ht="36" customHeight="1">
       <x:c r="C43" s="26" t="n">
         <x:v>35</x:v>
       </x:c>
@@ -13262,19 +13273,19 @@
       <x:c r="Q43" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R43" s="35" t="str">
+      <x:c r="R43" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x7066A64c24e4206CD62E83bf198c1E7EB361F51e</x:v>
       </x:c>
       <x:c r="S43" s="515"/>
-      <x:c r="T43" s="6" t="n">
+      <x:c r="T43" s="516" t="n">
         <x:v>46282.3683928125</x:v>
       </x:c>
-      <x:c r="U43" s="6"/>
-      <x:c r="V43" s="6" t="str">
+      <x:c r="U43" s="517"/>
+      <x:c r="V43" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="20" customHeight="1">
+    <x:row r="44" ht="36" customHeight="1">
       <x:c r="C44" s="26" t="n">
         <x:v>36</x:v>
       </x:c>
@@ -13325,19 +13336,19 @@
       <x:c r="Q44" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R44" s="35" t="str">
+      <x:c r="R44" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x894E1EC2D74FFE5AEF8Dc8A9e84686acCB964F2A</x:v>
       </x:c>
       <x:c r="S44" s="515"/>
-      <x:c r="T44" s="6" t="n">
+      <x:c r="T44" s="516" t="n">
         <x:v>46282.36839777778</x:v>
       </x:c>
-      <x:c r="U44" s="6"/>
-      <x:c r="V44" s="6" t="str">
+      <x:c r="U44" s="517"/>
+      <x:c r="V44" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="20" customHeight="1">
+    <x:row r="45" ht="36" customHeight="1">
       <x:c r="C45" s="26" t="n">
         <x:v>37</x:v>
       </x:c>
@@ -13388,23 +13399,23 @@
       <x:c r="Q45" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R45" s="35" t="str">
+      <x:c r="R45" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</x:v>
       </x:c>
       <x:c r="S45" s="515" t="n">
         <x:v>710.5882117442176</x:v>
       </x:c>
-      <x:c r="T45" s="6" t="n">
+      <x:c r="T45" s="516" t="n">
         <x:v>46282.36840363426</x:v>
       </x:c>
-      <x:c r="U45" s="6" t="str">
+      <x:c r="U45" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0xa40d00a55d43ba2d188039dcf88bd68f4f133e78</x:v>
       </x:c>
-      <x:c r="V45" s="6" t="str">
+      <x:c r="V45" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="20" customHeight="1">
+    <x:row r="46" ht="36" customHeight="1">
       <x:c r="C46" s="26" t="n">
         <x:v>38</x:v>
       </x:c>
@@ -13455,23 +13466,23 @@
       <x:c r="Q46" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R46" s="35" t="str">
+      <x:c r="R46" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</x:v>
       </x:c>
       <x:c r="S46" s="515" t="n">
         <x:v>48.151892146167164</x:v>
       </x:c>
-      <x:c r="T46" s="6" t="n">
+      <x:c r="T46" s="516" t="n">
         <x:v>46282.368411539355</x:v>
       </x:c>
-      <x:c r="U46" s="6" t="str">
+      <x:c r="U46" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x6d25417718a8d6c529130a8ccc4bfbf0a18219d3</x:v>
       </x:c>
-      <x:c r="V46" s="6" t="str">
+      <x:c r="V46" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="20" customHeight="1">
+    <x:row r="47" ht="36" customHeight="1">
       <x:c r="C47" s="26" t="n">
         <x:v>39</x:v>
       </x:c>
@@ -13522,23 +13533,23 @@
       <x:c r="Q47" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R47" s="35" t="str">
+      <x:c r="R47" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</x:v>
       </x:c>
       <x:c r="S47" s="515" t="n">
         <x:v>159.20150530961936</x:v>
       </x:c>
-      <x:c r="T47" s="6" t="n">
+      <x:c r="T47" s="516" t="n">
         <x:v>46282.368414351855</x:v>
       </x:c>
-      <x:c r="U47" s="6" t="str">
+      <x:c r="U47" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0xa541143f20d7b0643123064abf25f423e375b531</x:v>
       </x:c>
-      <x:c r="V47" s="6" t="str">
+      <x:c r="V47" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="20" customHeight="1">
+    <x:row r="48" ht="36" customHeight="1">
       <x:c r="C48" s="26" t="n">
         <x:v>40</x:v>
       </x:c>
@@ -13589,19 +13600,19 @@
       <x:c r="Q48" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R48" s="35" t="str">
+      <x:c r="R48" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xB1BF26c1D20ff267A4f93550d1E0d06ac40a114B</x:v>
       </x:c>
       <x:c r="S48" s="515"/>
-      <x:c r="T48" s="6" t="n">
+      <x:c r="T48" s="516" t="n">
         <x:v>46282.3684209375</x:v>
       </x:c>
-      <x:c r="U48" s="6"/>
-      <x:c r="V48" s="6" t="str">
+      <x:c r="U48" s="517"/>
+      <x:c r="V48" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="20" customHeight="1">
+    <x:row r="49" ht="36" customHeight="1">
       <x:c r="C49" s="26" t="n">
         <x:v>41</x:v>
       </x:c>
@@ -13652,23 +13663,23 @@
       <x:c r="Q49" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R49" s="35" t="str">
+      <x:c r="R49" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</x:v>
       </x:c>
       <x:c r="S49" s="515" t="n">
         <x:v>101.55835576951948</x:v>
       </x:c>
-      <x:c r="T49" s="6" t="n">
+      <x:c r="T49" s="516" t="n">
         <x:v>46282.36842652778</x:v>
       </x:c>
-      <x:c r="U49" s="6" t="str">
+      <x:c r="U49" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0x7f310e3d05e575bd449e4484ef5da15863ea43b1</x:v>
       </x:c>
-      <x:c r="V49" s="6" t="str">
+      <x:c r="V49" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="20" customHeight="1">
+    <x:row r="50" ht="36" customHeight="1">
       <x:c r="C50" s="26" t="n">
         <x:v>42</x:v>
       </x:c>
@@ -13719,19 +13730,19 @@
       <x:c r="Q50" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R50" s="35" t="str">
+      <x:c r="R50" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xf53f66751b1eff985311b693531e3290f600c410</x:v>
       </x:c>
       <x:c r="S50" s="515"/>
-      <x:c r="T50" s="6" t="n">
+      <x:c r="T50" s="516" t="n">
         <x:v>46282.3684325463</x:v>
       </x:c>
-      <x:c r="U50" s="6"/>
-      <x:c r="V50" s="6" t="str">
+      <x:c r="U50" s="517"/>
+      <x:c r="V50" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="20" customHeight="1">
+    <x:row r="51" ht="36" customHeight="1">
       <x:c r="C51" s="26" t="n">
         <x:v>43</x:v>
       </x:c>
@@ -13782,19 +13793,19 @@
       <x:c r="Q51" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R51" s="35" t="str">
+      <x:c r="R51" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x84CAb63bc87912E71ad199ff14A0bA45de68FeF8</x:v>
       </x:c>
       <x:c r="S51" s="515"/>
-      <x:c r="T51" s="6" t="n">
+      <x:c r="T51" s="516" t="n">
         <x:v>46282.36843747685</x:v>
       </x:c>
-      <x:c r="U51" s="6"/>
-      <x:c r="V51" s="6" t="str">
+      <x:c r="U51" s="517"/>
+      <x:c r="V51" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="20" customHeight="1">
+    <x:row r="52" ht="36" customHeight="1">
       <x:c r="C52" s="26" t="n">
         <x:v>44</x:v>
       </x:c>
@@ -13845,19 +13856,19 @@
       <x:c r="Q52" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R52" s="35" t="str">
+      <x:c r="R52" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x411efb0e7f985935daec3d4c3ebaea0d0ad7d89f</x:v>
       </x:c>
       <x:c r="S52" s="515"/>
-      <x:c r="T52" s="6" t="n">
+      <x:c r="T52" s="516" t="n">
         <x:v>46282.36844511574</x:v>
       </x:c>
-      <x:c r="U52" s="6"/>
-      <x:c r="V52" s="6" t="str">
+      <x:c r="U52" s="517"/>
+      <x:c r="V52" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="20" customHeight="1">
+    <x:row r="53" ht="36" customHeight="1">
       <x:c r="C53" s="26" t="n">
         <x:v>45</x:v>
       </x:c>
@@ -13908,19 +13919,19 @@
       <x:c r="Q53" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R53" s="35" t="str">
+      <x:c r="R53" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xF6589F11Bc40b669e584073F428B05562F568733</x:v>
       </x:c>
       <x:c r="S53" s="515"/>
-      <x:c r="T53" s="6" t="n">
+      <x:c r="T53" s="516" t="n">
         <x:v>46282.36845233796</x:v>
       </x:c>
-      <x:c r="U53" s="6"/>
-      <x:c r="V53" s="6" t="str">
+      <x:c r="U53" s="517"/>
+      <x:c r="V53" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="20" customHeight="1">
+    <x:row r="54" ht="36" customHeight="1">
       <x:c r="C54" s="26" t="n">
         <x:v>46</x:v>
       </x:c>
@@ -13971,19 +13982,19 @@
       <x:c r="Q54" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R54" s="35" t="str">
+      <x:c r="R54" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xB90A19fF0Af67f7779afF50A882A9CfF42446400</x:v>
       </x:c>
       <x:c r="S54" s="515"/>
-      <x:c r="T54" s="6" t="n">
+      <x:c r="T54" s="516" t="n">
         <x:v>46282.36845486111</x:v>
       </x:c>
-      <x:c r="U54" s="6"/>
-      <x:c r="V54" s="6" t="str">
+      <x:c r="U54" s="517"/>
+      <x:c r="V54" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="20" customHeight="1">
+    <x:row r="55" ht="36" customHeight="1">
       <x:c r="C55" s="26" t="n">
         <x:v>47</x:v>
       </x:c>
@@ -14034,23 +14045,23 @@
       <x:c r="Q55" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R55" s="35" t="str">
+      <x:c r="R55" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</x:v>
       </x:c>
       <x:c r="S55" s="515" t="n">
         <x:v>153.1452363556294</x:v>
       </x:c>
-      <x:c r="T55" s="6" t="n">
+      <x:c r="T55" s="516" t="n">
         <x:v>46282.3684615625</x:v>
       </x:c>
-      <x:c r="U55" s="6" t="str">
+      <x:c r="U55" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0xc3c9f0171490ef0f4536fe493f3b0ebb5ee0cb5e</x:v>
       </x:c>
-      <x:c r="V55" s="6" t="str">
+      <x:c r="V55" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="20" customHeight="1">
+    <x:row r="56" ht="36" customHeight="1">
       <x:c r="C56" s="26" t="n">
         <x:v>48</x:v>
       </x:c>
@@ -14101,23 +14112,23 @@
       <x:c r="Q56" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R56" s="35" t="str">
+      <x:c r="R56" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</x:v>
       </x:c>
       <x:c r="S56" s="515" t="n">
         <x:v>760.2113839039964</x:v>
       </x:c>
-      <x:c r="T56" s="6" t="n">
+      <x:c r="T56" s="516" t="n">
         <x:v>46282.368470127316</x:v>
       </x:c>
-      <x:c r="U56" s="6" t="str">
+      <x:c r="U56" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0xddcbba3666f578e3f09516f21ff85bfee859ab5e</x:v>
       </x:c>
-      <x:c r="V56" s="6" t="str">
+      <x:c r="V56" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="20" customHeight="1">
+    <x:row r="57" ht="36" customHeight="1">
       <x:c r="C57" s="26" t="n">
         <x:v>49</x:v>
       </x:c>
@@ -14168,23 +14179,23 @@
       <x:c r="Q57" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R57" s="35" t="str">
+      <x:c r="R57" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</x:v>
       </x:c>
       <x:c r="S57" s="515" t="n">
         <x:v>363.286058871218</x:v>
       </x:c>
-      <x:c r="T57" s="6" t="n">
+      <x:c r="T57" s="516" t="n">
         <x:v>46282.368473194445</x:v>
       </x:c>
-      <x:c r="U57" s="6" t="str">
+      <x:c r="U57" s="517" t="str">
         <x:v>https://dexscreener.com/robinhood/0xa953ca88ff430e9487c60ca34d757414f4efda07</x:v>
       </x:c>
-      <x:c r="V57" s="6" t="str">
+      <x:c r="V57" s="517" t="str">
         <x:v>Quote 代币池价；可手动更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="20" customHeight="1">
+    <x:row r="58" ht="36" customHeight="1">
       <x:c r="C58" s="26" t="n">
         <x:v>50</x:v>
       </x:c>
@@ -14235,19 +14246,19 @@
       <x:c r="Q58" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R58" s="35" t="str">
+      <x:c r="R58" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x58FfE4a942d3885bAa22D7520691F611EF09e7AA</x:v>
       </x:c>
       <x:c r="S58" s="515"/>
-      <x:c r="T58" s="6" t="n">
+      <x:c r="T58" s="516" t="n">
         <x:v>46282.36847894676</x:v>
       </x:c>
-      <x:c r="U58" s="6"/>
-      <x:c r="V58" s="6" t="str">
+      <x:c r="U58" s="517"/>
+      <x:c r="V58" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="20" customHeight="1">
+    <x:row r="59" ht="36" customHeight="1">
       <x:c r="C59" s="26" t="n">
         <x:v>51</x:v>
       </x:c>
@@ -14298,19 +14309,19 @@
       <x:c r="Q59" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R59" s="35" t="str">
+      <x:c r="R59" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x5e81213613b6B86EaB4c6c50d718d34359459786</x:v>
       </x:c>
       <x:c r="S59" s="515"/>
-      <x:c r="T59" s="6" t="n">
+      <x:c r="T59" s="516" t="n">
         <x:v>46282.36848482639</x:v>
       </x:c>
-      <x:c r="U59" s="6"/>
-      <x:c r="V59" s="6" t="str">
+      <x:c r="U59" s="517"/>
+      <x:c r="V59" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="20" customHeight="1">
+    <x:row r="60" ht="36" customHeight="1">
       <x:c r="C60" s="26" t="n">
         <x:v>52</x:v>
       </x:c>
@@ -14361,19 +14372,19 @@
       <x:c r="Q60" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R60" s="35" t="str">
+      <x:c r="R60" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xf23250dac154d05bb671cb0d0ebef3c635c79ce2</x:v>
       </x:c>
       <x:c r="S60" s="515"/>
-      <x:c r="T60" s="6" t="n">
+      <x:c r="T60" s="516" t="n">
         <x:v>46282.36849291667</x:v>
       </x:c>
-      <x:c r="U60" s="6"/>
-      <x:c r="V60" s="6" t="str">
+      <x:c r="U60" s="517"/>
+      <x:c r="V60" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="20" customHeight="1">
+    <x:row r="61" ht="36" customHeight="1">
       <x:c r="C61" s="26" t="n">
         <x:v>53</x:v>
       </x:c>
@@ -14424,19 +14435,19 @@
       <x:c r="Q61" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R61" s="35" t="str">
+      <x:c r="R61" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xa30FA36Db767ad9eD3f7a60fC79526fB4d56D344</x:v>
       </x:c>
       <x:c r="S61" s="515"/>
-      <x:c r="T61" s="6" t="n">
+      <x:c r="T61" s="516" t="n">
         <x:v>46282.368495393515</x:v>
       </x:c>
-      <x:c r="U61" s="6"/>
-      <x:c r="V61" s="6" t="str">
+      <x:c r="U61" s="517"/>
+      <x:c r="V61" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="20" customHeight="1">
+    <x:row r="62" ht="36" customHeight="1">
       <x:c r="C62" s="26" t="n">
         <x:v>54</x:v>
       </x:c>
@@ -14487,15 +14498,15 @@
       <x:c r="Q62" s="40" t="str">
         <x:v>Approved / Native</x:v>
       </x:c>
-      <x:c r="R62" s="35" t="str">
+      <x:c r="R62" s="519" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x9e7ABD3C9139D14E4c86DcE0e455AAB7A0C2FB3E</x:v>
       </x:c>
       <x:c r="S62" s="515"/>
-      <x:c r="T62" s="6" t="n">
+      <x:c r="T62" s="516" t="n">
         <x:v>46282.368501157405</x:v>
       </x:c>
-      <x:c r="U62" s="6"/>
-      <x:c r="V62" s="6" t="str">
+      <x:c r="U62" s="517"/>
+      <x:c r="V62" s="517" t="str">
         <x:v>暂无合格池价；可手动输入</x:v>
       </x:c>
     </x:row>

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R88c0330aa756435a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R0a1c5690fff84951"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rda86b20109df4d7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Ra4b1910f27474888"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,7 +27,7 @@
     <x:numFmt numFmtId="209" formatCode="0.000000E+00"/>
     <x:numFmt numFmtId="210" formatCode="0.0000000000"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -79,8 +79,13 @@
       <x:name val="Arial"/>
     </x:font>
     <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF667085"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
       <x:b/>
-      <x:sz val="13"/>
+      <x:sz val="12"/>
       <x:color rgb="FF365F20"/>
       <x:name val="Arial"/>
     </x:font>
@@ -110,12 +115,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE8F3DD"/>
+        <x:fgColor rgb="FFEAF3FA"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFEAF3FA"/>
+        <x:fgColor rgb="FFE8F3DD"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -153,7 +158,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="102">
+  <x:cellXfs count="104">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -324,10 +329,19 @@
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="208" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="206" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -363,19 +377,16 @@
     <x:xf numFmtId="205" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="208" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -405,22 +416,22 @@
     <x:xf numFmtId="210" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="11" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="208" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -701,3251 +712,3301 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="2" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="2" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="21" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="21" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="25" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="21" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="2"/>
-      <x:c r="B1" s="2"/>
-      <x:c r="C1" s="2"/>
-      <x:c r="D1" s="2"/>
-      <x:c r="E1" s="2"/>
-      <x:c r="F1" s="2"/>
-      <x:c r="G1" s="2"/>
-      <x:c r="H1" s="2"/>
-      <x:c r="I1" s="2"/>
-      <x:c r="J1" s="2"/>
-      <x:c r="K1" s="2"/>
-      <x:c r="L1" s="2"/>
-    </x:row>
-    <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="2"/>
-      <x:c r="B2" s="2"/>
-      <x:c r="C2" s="4" t="str">
-        <x:v>Pons V2 控筹模型</x:v>
-      </x:c>
-      <x:c r="D2" s="3"/>
-      <x:c r="E2" s="3"/>
-      <x:c r="F2" s="3"/>
-      <x:c r="G2" s="3"/>
-      <x:c r="H2" s="3"/>
-      <x:c r="I2" s="3"/>
-      <x:c r="J2" s="3"/>
-      <x:c r="K2" s="3"/>
-      <x:c r="L2" s="3"/>
-    </x:row>
-    <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="2"/>
-      <x:c r="B3" s="2"/>
-      <x:c r="C3" s="5" t="str">
-        <x:v>蓝色格可编辑。Quote / USDT 资金不含 Gas，Gas 单独以 ETH 计价。</x:v>
-      </x:c>
-      <x:c r="D3" s="5"/>
-      <x:c r="E3" s="5"/>
-      <x:c r="F3" s="5"/>
-      <x:c r="G3" s="5"/>
-      <x:c r="H3" s="5"/>
-      <x:c r="I3" s="5"/>
-      <x:c r="J3" s="5"/>
-      <x:c r="K3" s="5"/>
-      <x:c r="L3" s="5"/>
-    </x:row>
-    <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="2"/>
-      <x:c r="B4" s="2"/>
-      <x:c r="C4" s="2"/>
-      <x:c r="D4" s="2"/>
-      <x:c r="E4" s="2"/>
-      <x:c r="F4" s="2"/>
-      <x:c r="G4" s="2"/>
-      <x:c r="H4" s="2"/>
-      <x:c r="I4" s="2"/>
-      <x:c r="J4" s="2"/>
-      <x:c r="K4" s="2"/>
-      <x:c r="L4" s="2"/>
-    </x:row>
-    <x:row r="5" ht="27" customHeight="1">
-      <x:c r="A5" s="2"/>
-      <x:c r="B5" s="2"/>
-      <x:c r="C5" s="8" t="str">
-        <x:v>一、可编辑参数</x:v>
-      </x:c>
-      <x:c r="D5" s="8"/>
-      <x:c r="E5" s="8"/>
-      <x:c r="F5" s="8"/>
-      <x:c r="G5" s="8"/>
-      <x:c r="H5" s="8"/>
-      <x:c r="I5" s="8"/>
-      <x:c r="J5" s="8"/>
-      <x:c r="K5" s="8"/>
-      <x:c r="L5" s="8"/>
-    </x:row>
-    <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="2"/>
-      <x:c r="B6" s="2"/>
-      <x:c r="C6" s="48" t="str">
-        <x:v>交易参数</x:v>
-      </x:c>
-      <x:c r="D6" s="2"/>
-      <x:c r="E6" s="2"/>
-      <x:c r="F6" s="48" t="str">
-        <x:v>地址与 Gas</x:v>
-      </x:c>
-      <x:c r="G6" s="2"/>
-      <x:c r="H6" s="2"/>
-      <x:c r="I6" s="48" t="str">
-        <x:v>平台设置</x:v>
-      </x:c>
-      <x:c r="J6" s="2"/>
-      <x:c r="K6" s="2"/>
-      <x:c r="L6" s="2"/>
-    </x:row>
-    <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="2"/>
-      <x:c r="B7" s="2"/>
-      <x:c r="C7" s="35" t="str">
-        <x:v>Quote</x:v>
-      </x:c>
-      <x:c r="D7" s="51" t="str">
-        <x:v>SLV</x:v>
-      </x:c>
-      <x:c r="E7" s="2"/>
-      <x:c r="F7" s="35" t="str">
-        <x:v>内盘套数</x:v>
-      </x:c>
-      <x:c r="G7" s="51" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H7" s="2"/>
-      <x:c r="I7" s="35" t="str">
-        <x:v>Creator Tax</x:v>
-      </x:c>
-      <x:c r="J7" s="53" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="2"/>
-      <x:c r="L7" s="2"/>
-    </x:row>
-    <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="2"/>
-      <x:c r="B8" s="2"/>
-      <x:c r="C8" s="35" t="str">
-        <x:v>目标控筹率</x:v>
-      </x:c>
-      <x:c r="D8" s="53" t="n">
-        <x:v>0.9</x:v>
-      </x:c>
-      <x:c r="E8" s="35" t="str">
-        <x:v>预算沿用 +1%</x:v>
-      </x:c>
-      <x:c r="F8" s="35" t="str">
-        <x:v>内盘地址 / 套</x:v>
-      </x:c>
-      <x:c r="G8" s="51" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H8" s="2"/>
-      <x:c r="I8" s="35" t="str">
-        <x:v>滑点假设</x:v>
-      </x:c>
-      <x:c r="J8" s="53" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="35" t="str">
-        <x:v>现有预算未计滑点</x:v>
-      </x:c>
-      <x:c r="L8" s="35"/>
-    </x:row>
-    <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="2"/>
-      <x:c r="B9" s="2"/>
-      <x:c r="C9" s="35" t="str">
-        <x:v>手动价格 / USDT</x:v>
-      </x:c>
-      <x:c r="D9" s="54"/>
-      <x:c r="E9" s="35" t="str">
-        <x:v>留空用日更价</x:v>
-      </x:c>
-      <x:c r="F9" s="35" t="str">
-        <x:v>外盘地址数</x:v>
-      </x:c>
-      <x:c r="G9" s="51" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H9" s="2"/>
-      <x:c r="I9" s="35" t="str">
-        <x:v>Snipe Tax 豁免</x:v>
-      </x:c>
-      <x:c r="J9" s="51" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="K9" s="35"/>
-      <x:c r="L9" s="35"/>
-    </x:row>
-    <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="2"/>
-      <x:c r="B10" s="2"/>
-      <x:c r="C10" s="35" t="str">
-        <x:v>资金预留 / Quote</x:v>
-      </x:c>
-      <x:c r="D10" s="54" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="35" t="str">
-        <x:v>Holder 地址数</x:v>
-      </x:c>
-      <x:c r="G10" s="51" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H10" s="2"/>
-      <x:c r="I10" s="35" t="str">
-        <x:v>Buyback enabled</x:v>
-      </x:c>
-      <x:c r="J10" s="51" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="K10" s="35" t="str">
-        <x:v>不抵扣回购收益</x:v>
-      </x:c>
-      <x:c r="L10" s="35"/>
-    </x:row>
-    <x:row r="11" ht="38" customHeight="1">
-      <x:c r="A11" s="2"/>
-      <x:c r="B11" s="2"/>
-      <x:c r="C11" s="2"/>
-      <x:c r="D11" s="2"/>
-      <x:c r="E11" s="2"/>
-      <x:c r="F11" s="35" t="str">
-        <x:v>单地址 Gas / ETH</x:v>
-      </x:c>
-      <x:c r="G11" s="54" t="n">
-        <x:v>0.005</x:v>
-      </x:c>
-      <x:c r="H11" s="2"/>
-      <x:c r="I11" s="35" t="str">
-        <x:v>Creator recipient</x:v>
-      </x:c>
-      <x:c r="J11" s="52"/>
-      <x:c r="K11" s="35" t="str">
-        <x:v>仅记录收款地址，不抵扣分红收益</x:v>
-      </x:c>
-      <x:c r="L11" s="35"/>
-    </x:row>
-    <x:row r="12" ht="38" customHeight="1">
-      <x:c r="A12" s="2"/>
-      <x:c r="B12" s="2"/>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="2"/>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
-      <x:c r="G12" s="2"/>
-      <x:c r="H12" s="2"/>
-      <x:c r="I12" s="2"/>
-      <x:c r="J12" s="2"/>
-      <x:c r="K12" s="35"/>
-      <x:c r="L12" s="35"/>
-    </x:row>
-    <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="2"/>
-      <x:c r="B13" s="2"/>
-      <x:c r="C13" s="55" t="str">
-        <x:v>手动价格只用于 USDT 换算，不改变 Quote 控筹预算。清空覆盖格后恢复自动取价。</x:v>
-      </x:c>
-      <x:c r="D13" s="55"/>
-      <x:c r="E13" s="55"/>
-      <x:c r="F13" s="55"/>
-      <x:c r="G13" s="55"/>
-      <x:c r="H13" s="55"/>
-      <x:c r="I13" s="55"/>
-      <x:c r="J13" s="55"/>
-      <x:c r="K13" s="55"/>
-      <x:c r="L13" s="55"/>
-    </x:row>
-    <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="2"/>
-      <x:c r="B14" s="2"/>
-      <x:c r="C14" s="2"/>
-      <x:c r="D14" s="2"/>
-      <x:c r="E14" s="2"/>
-      <x:c r="F14" s="2"/>
-      <x:c r="G14" s="2"/>
-      <x:c r="H14" s="2"/>
-      <x:c r="I14" s="2"/>
-      <x:c r="J14" s="2"/>
-      <x:c r="K14" s="2"/>
-      <x:c r="L14" s="2"/>
-    </x:row>
-    <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="2"/>
-      <x:c r="B15" s="2"/>
-      <x:c r="C15" s="2"/>
-      <x:c r="D15" s="2"/>
-      <x:c r="E15" s="2"/>
-      <x:c r="F15" s="2"/>
-      <x:c r="G15" s="2"/>
-      <x:c r="H15" s="2"/>
-      <x:c r="I15" s="2"/>
-      <x:c r="J15" s="2"/>
-      <x:c r="K15" s="2"/>
-      <x:c r="L15" s="2"/>
-    </x:row>
-    <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="2"/>
-      <x:c r="B16" s="2"/>
-      <x:c r="C16" s="2"/>
-      <x:c r="D16" s="2"/>
-      <x:c r="E16" s="2"/>
-      <x:c r="F16" s="2"/>
-      <x:c r="G16" s="2"/>
-      <x:c r="H16" s="2"/>
-      <x:c r="I16" s="2"/>
-      <x:c r="J16" s="2"/>
-      <x:c r="K16" s="2"/>
-      <x:c r="L16" s="2"/>
-    </x:row>
-    <x:row r="17" ht="27" customHeight="1">
-      <x:c r="A17" s="2"/>
-      <x:c r="B17" s="2"/>
-      <x:c r="C17" s="8" t="str">
-        <x:v>二、测算结果</x:v>
-      </x:c>
-      <x:c r="D17" s="8"/>
-      <x:c r="E17" s="8"/>
-      <x:c r="F17" s="8"/>
-      <x:c r="G17" s="8"/>
-      <x:c r="H17" s="8"/>
-      <x:c r="I17" s="8"/>
-      <x:c r="J17" s="8"/>
-      <x:c r="K17" s="8"/>
-      <x:c r="L17" s="8"/>
-    </x:row>
-    <x:row r="18" ht="38" customHeight="1">
-      <x:c r="A18" s="2"/>
-      <x:c r="B18" s="2"/>
-      <x:c r="C18" s="35" t="str">
-        <x:v>建议总资金 / Quote</x:v>
-      </x:c>
-      <x:c r="D18" s="71" t="n">
-        <x:f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($D$21="","",SUM($D$21,$G$21,$J$21,$D$22)))</x:f>
-        <x:v>15773.425525779472</x:v>
-      </x:c>
-      <x:c r="E18" s="57" t="str">
-        <x:f>$D$7</x:f>
-        <x:v>SLV</x:v>
-      </x:c>
-      <x:c r="F18" s="35" t="str">
-        <x:v>折合 USDT（不含 Gas）</x:v>
-      </x:c>
-      <x:c r="G18" s="71" t="str">
-        <x:f>IF(OR($D$18="",$D$24=""),"",$D$18*$D$24)</x:f>
-      </x:c>
-      <x:c r="H18" s="57" t="str">
-        <x:v>USDT</x:v>
-      </x:c>
-      <x:c r="I18" s="35" t="str">
-        <x:v>Gas 储备 / ETH</x:v>
-      </x:c>
-      <x:c r="J18" s="71" t="n">
-        <x:f>$G$22*MAX(0,$G$11)</x:f>
-        <x:v>0.61</x:v>
-      </x:c>
-      <x:c r="K18" s="57" t="str">
-        <x:v>ETH</x:v>
-      </x:c>
-      <x:c r="L18" s="57"/>
-    </x:row>
-    <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="2"/>
-      <x:c r="B19" s="2"/>
-      <x:c r="C19" s="2"/>
-      <x:c r="D19" s="2"/>
-      <x:c r="E19" s="2"/>
-      <x:c r="F19" s="2"/>
-      <x:c r="G19" s="2"/>
-      <x:c r="H19" s="2"/>
-      <x:c r="I19" s="2"/>
-      <x:c r="J19" s="2"/>
-      <x:c r="K19" s="2"/>
-      <x:c r="L19" s="2"/>
-    </x:row>
-    <x:row r="20" ht="26" customHeight="1">
-      <x:c r="A20" s="2"/>
-      <x:c r="B20" s="2"/>
-      <x:c r="C20" s="2"/>
-      <x:c r="D20" s="2"/>
-      <x:c r="E20" s="2"/>
-      <x:c r="F20" s="2"/>
-      <x:c r="G20" s="2"/>
-      <x:c r="H20" s="2"/>
-      <x:c r="I20" s="2"/>
-      <x:c r="J20" s="2"/>
-      <x:c r="K20" s="2"/>
-      <x:c r="L20" s="2"/>
-    </x:row>
-    <x:row r="21" ht="26" customHeight="1">
-      <x:c r="A21" s="2"/>
-      <x:c r="B21" s="2"/>
-      <x:c r="C21" s="35" t="str">
-        <x:v>理论累计投入 / Quote</x:v>
-      </x:c>
-      <x:c r="D21" s="58" t="n">
-        <x:f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$35="","",$J$31+$J$35))</x:f>
-        <x:v>5520.084846424523</x:v>
-      </x:c>
-      <x:c r="E21" s="2"/>
-      <x:c r="F21" s="35" t="str">
-        <x:v>额外内盘资金 / Quote</x:v>
-      </x:c>
-      <x:c r="G21" s="58" t="n">
-        <x:f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$31="","",$J$31*MAX(0,$G$7-1)))</x:f>
-        <x:v>174.54190618125045</x:v>
-      </x:c>
-      <x:c r="H21" s="2"/>
-      <x:c r="I21" s="35" t="str">
-        <x:v>洗筹预算 / Quote</x:v>
-      </x:c>
-      <x:c r="J21" s="58" t="n">
-        <x:f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$36="","",$J$36*($G$32+$J$7)*2))</x:f>
-        <x:v>10073.7987731737</x:v>
-      </x:c>
-      <x:c r="K21" s="2"/>
-      <x:c r="L21" s="2"/>
-    </x:row>
-    <x:row r="22" ht="26" customHeight="1">
-      <x:c r="A22" s="2"/>
-      <x:c r="B22" s="2"/>
-      <x:c r="C22" s="35" t="str">
-        <x:v>资金预留 / Quote</x:v>
-      </x:c>
-      <x:c r="D22" s="58" t="n">
-        <x:f>$D$10</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E22" s="2"/>
-      <x:c r="F22" s="35" t="str">
-        <x:v>地址总数</x:v>
-      </x:c>
-      <x:c r="G22" s="61" t="n">
-        <x:f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</x:f>
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H22" s="2"/>
-      <x:c r="I22" s="35" t="str">
-        <x:v>预算使用控筹率</x:v>
-      </x:c>
-      <x:c r="J22" s="59" t="n">
-        <x:f>$D$8+1%</x:f>
-        <x:v>0.91</x:v>
-      </x:c>
-      <x:c r="K22" s="2"/>
-      <x:c r="L22" s="2"/>
-    </x:row>
-    <x:row r="23" ht="40" customHeight="1">
-      <x:c r="A23" s="2"/>
-      <x:c r="B23" s="2"/>
-      <x:c r="C23" s="35" t="str">
-        <x:v>目标是否可达</x:v>
-      </x:c>
-      <x:c r="D23" s="63" t="str">
-        <x:f>IF($J$41&lt;&gt;"参数有效",$J$41,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$43),"Creator Tax无效",IF($J$22&gt;=$G$23,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</x:f>
-        <x:v>可达</x:v>
-      </x:c>
-      <x:c r="E23" s="2"/>
-      <x:c r="F23" s="35" t="str">
-        <x:v>当前控筹上限</x:v>
-      </x:c>
-      <x:c r="G23" s="60" t="n">
-        <x:f>MIN(1-$G$41/$D$35,$G$33+(1-$G$32-$J$7)*$G$38/$D$35)</x:f>
-        <x:v>0.916326530612245</x:v>
-      </x:c>
-      <x:c r="H23" s="2"/>
-      <x:c r="I23" s="35" t="str">
-        <x:v>资金口径</x:v>
-      </x:c>
-      <x:c r="J23" s="58" t="str">
-        <x:v>Quote 预算 + 单独 Gas</x:v>
-      </x:c>
-      <x:c r="K23" s="2"/>
-      <x:c r="L23" s="2"/>
-    </x:row>
-    <x:row r="24" ht="40" customHeight="1">
-      <x:c r="A24" s="2"/>
-      <x:c r="B24" s="2"/>
-      <x:c r="C24" s="35" t="str">
-        <x:v>使用价格 / USDT</x:v>
-      </x:c>
-      <x:c r="D24" s="58" t="str">
-        <x:f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</x:f>
-      </x:c>
-      <x:c r="E24" s="2"/>
-      <x:c r="F24" s="35" t="str">
-        <x:v>行情时间 / UTC</x:v>
-      </x:c>
-      <x:c r="G24" s="62" t="n">
-        <x:f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</x:f>
-        <x:v>46283.229019363425</x:v>
-      </x:c>
-      <x:c r="H24" s="2"/>
-      <x:c r="I24" s="35" t="str">
-        <x:v>价格状态</x:v>
-      </x:c>
-      <x:c r="J24" s="58" t="str">
-        <x:f>IF($D$9&lt;&gt;"",IF($D$24="","手动价格无效","手动价格"),IF($D$24="","缺少价格","每日行情"))</x:f>
-        <x:v>缺少价格</x:v>
-      </x:c>
-      <x:c r="K24" s="2"/>
-      <x:c r="L24" s="2"/>
-    </x:row>
-    <x:row r="25" ht="26" customHeight="1">
-      <x:c r="A25" s="2"/>
-      <x:c r="B25" s="2"/>
-      <x:c r="C25" s="35" t="str">
-        <x:v>价格采用方式</x:v>
-      </x:c>
-      <x:c r="D25" s="58" t="str">
-        <x:f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</x:f>
-        <x:v>每日行情</x:v>
-      </x:c>
-      <x:c r="E25" s="2"/>
-      <x:c r="F25" s="2"/>
-      <x:c r="G25" s="58"/>
-      <x:c r="H25" s="2"/>
-      <x:c r="I25" s="2" t="str">
-        <x:v>价格缺失时 USDT 结果留空</x:v>
-      </x:c>
-      <x:c r="J25" s="58"/>
-      <x:c r="K25" s="2"/>
-      <x:c r="L25" s="2"/>
-    </x:row>
-    <x:row r="26" ht="26" customHeight="1">
-      <x:c r="A26" s="2"/>
-      <x:c r="B26" s="2"/>
-      <x:c r="C26" s="2"/>
-      <x:c r="D26" s="2"/>
-      <x:c r="E26" s="2"/>
-      <x:c r="F26" s="2"/>
-      <x:c r="G26" s="2"/>
-      <x:c r="H26" s="2"/>
-      <x:c r="I26" s="2"/>
-      <x:c r="J26" s="2"/>
-      <x:c r="K26" s="2"/>
-      <x:c r="L26" s="2"/>
-    </x:row>
-    <x:row r="27" ht="26" customHeight="1">
-      <x:c r="A27" s="2"/>
-      <x:c r="B27" s="2"/>
-      <x:c r="C27" s="2"/>
-      <x:c r="D27" s="2"/>
-      <x:c r="E27" s="2"/>
-      <x:c r="F27" s="2"/>
-      <x:c r="G27" s="2"/>
-      <x:c r="H27" s="2"/>
-      <x:c r="I27" s="2"/>
-      <x:c r="J27" s="2"/>
-      <x:c r="K27" s="2"/>
-      <x:c r="L27" s="2"/>
-    </x:row>
-    <x:row r="28" ht="26" customHeight="1">
-      <x:c r="A28" s="2"/>
-      <x:c r="B28" s="2"/>
-      <x:c r="C28" s="2"/>
-      <x:c r="D28" s="2"/>
-      <x:c r="E28" s="2"/>
-      <x:c r="F28" s="2"/>
-      <x:c r="G28" s="2"/>
-      <x:c r="H28" s="2"/>
-      <x:c r="I28" s="2"/>
-      <x:c r="J28" s="2"/>
-      <x:c r="K28" s="2"/>
-      <x:c r="L28" s="2"/>
-    </x:row>
-    <x:row r="29" ht="27" customHeight="1">
-      <x:c r="A29" s="2"/>
-      <x:c r="B29" s="2"/>
-      <x:c r="C29" s="8" t="str">
-        <x:v>三、模型信息与计算口径</x:v>
-      </x:c>
-      <x:c r="D29" s="8"/>
-      <x:c r="E29" s="8"/>
-      <x:c r="F29" s="8"/>
-      <x:c r="G29" s="8"/>
-      <x:c r="H29" s="8"/>
-      <x:c r="I29" s="8"/>
-      <x:c r="J29" s="8"/>
-      <x:c r="K29" s="8"/>
-      <x:c r="L29" s="8"/>
-    </x:row>
-    <x:row r="30" ht="26" customHeight="1">
-      <x:c r="A30" s="2"/>
-      <x:c r="B30" s="2"/>
-      <x:c r="C30" s="48" t="str">
-        <x:v>Quote 信息</x:v>
-      </x:c>
-      <x:c r="D30" s="2"/>
-      <x:c r="E30" s="2"/>
-      <x:c r="F30" s="48" t="str">
-        <x:v>协议与曲线参数</x:v>
-      </x:c>
-      <x:c r="G30" s="2"/>
-      <x:c r="H30" s="2"/>
-      <x:c r="I30" s="48" t="str">
-        <x:v>预算中间计算</x:v>
-      </x:c>
-      <x:c r="J30" s="2"/>
-      <x:c r="K30" s="2"/>
-      <x:c r="L30" s="2"/>
-    </x:row>
-    <x:row r="31" ht="36" customHeight="1">
-      <x:c r="A31" s="2"/>
-      <x:c r="B31" s="2"/>
-      <x:c r="C31" s="35" t="str">
-        <x:v>Quote 名称</x:v>
-      </x:c>
-      <x:c r="D31" s="63" t="str">
-        <x:f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</x:f>
-        <x:v>iShares Silver Trust</x:v>
-      </x:c>
-      <x:c r="E31" s="35"/>
-      <x:c r="F31" s="35" t="str">
-        <x:v>内盘基础费</x:v>
-      </x:c>
-      <x:c r="G31" s="60" t="n">
-        <x:f>1%</x:f>
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="H31" s="2"/>
-      <x:c r="I31" s="35" t="str">
-        <x:v>一套内盘打满 / Quote</x:v>
-      </x:c>
-      <x:c r="J31" s="58" t="n">
-        <x:f>IF(1-$G$31-$J$7&gt;0,$G$34/(1-$G$31-$J$7),"")</x:f>
-        <x:v>174.54190618125045</x:v>
-      </x:c>
-      <x:c r="K31" s="2"/>
-      <x:c r="L31" s="2"/>
-    </x:row>
-    <x:row r="32" ht="36" customHeight="1">
-      <x:c r="A32" s="2"/>
-      <x:c r="B32" s="2"/>
-      <x:c r="C32" s="35" t="str">
-        <x:v>Quote 合约</x:v>
-      </x:c>
-      <x:c r="D32" s="66" t="str">
-        <x:f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</x:f>
-        <x:v>​0x411efb0e7f985935daec3d4c3ebaea0d0ad7d89f</x:v>
-      </x:c>
-      <x:c r="E32" s="35"/>
-      <x:c r="F32" s="35" t="str">
-        <x:v>外盘 Hook 费</x:v>
-      </x:c>
-      <x:c r="G32" s="60" t="n">
-        <x:f>1%</x:f>
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="H32" s="2"/>
-      <x:c r="I32" s="35" t="str">
-        <x:v>目标+1% Pool TOKEN</x:v>
-      </x:c>
-      <x:c r="J32" s="68" t="n">
-        <x:f>IF($J$22&lt;$G$23,$D$35*(1-$J$22)-$G$41,"")</x:f>
-        <x:v>8367346.938775495</x:v>
-      </x:c>
-      <x:c r="K32" s="2"/>
-      <x:c r="L32" s="2"/>
-    </x:row>
-    <x:row r="33" ht="26" customHeight="1">
-      <x:c r="A33" s="2"/>
-      <x:c r="B33" s="2"/>
-      <x:c r="C33" s="2"/>
-      <x:c r="D33" s="63"/>
-      <x:c r="E33" s="35"/>
-      <x:c r="F33" s="35" t="str">
-        <x:v>毕业控筹率</x:v>
-      </x:c>
-      <x:c r="G33" s="60" t="n">
-        <x:f>$G$34/($G$36+$G$34)</x:f>
-        <x:v>0.7142857142857143</x:v>
-      </x:c>
-      <x:c r="H33" s="2"/>
-      <x:c r="I33" s="35" t="str">
-        <x:v>目标+1% Pool Quote</x:v>
-      </x:c>
-      <x:c r="J33" s="58" t="n">
-        <x:f>IF($J$32="","",$G$40/$J$32)</x:f>
-        <x:v>4214.548466327764</x:v>
-      </x:c>
-      <x:c r="K33" s="2"/>
-      <x:c r="L33" s="2"/>
-    </x:row>
-    <x:row r="34" ht="26" customHeight="1">
-      <x:c r="A34" s="2"/>
-      <x:c r="B34" s="2"/>
-      <x:c r="C34" s="35" t="str">
-        <x:v>Decimals</x:v>
-      </x:c>
-      <x:c r="D34" s="64" t="n">
-        <x:f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,4,FALSE)</x:f>
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E34" s="2"/>
-      <x:c r="F34" s="35" t="str">
-        <x:v>毕业真实 Quote</x:v>
-      </x:c>
-      <x:c r="G34" s="58" t="n">
-        <x:f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</x:f>
-        <x:v>172.79648711943796</x:v>
-      </x:c>
-      <x:c r="H34" s="2"/>
-      <x:c r="I34" s="35" t="str">
-        <x:v>外盘净增加 / Quote</x:v>
-      </x:c>
-      <x:c r="J34" s="58" t="n">
-        <x:f>IF($J$33="","",MAX(0,$J$33-$G$34))</x:f>
-        <x:v>4041.751979208326</x:v>
-      </x:c>
-      <x:c r="K34" s="2"/>
-      <x:c r="L34" s="2"/>
-    </x:row>
-    <x:row r="35" ht="26" customHeight="1">
-      <x:c r="A35" s="2"/>
-      <x:c r="B35" s="2"/>
-      <x:c r="C35" s="35" t="str">
-        <x:v>总供应量</x:v>
-      </x:c>
-      <x:c r="D35" s="61" t="n">
-        <x:f>1000000000</x:f>
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="E35" s="2"/>
-      <x:c r="F35" s="35" t="str">
-        <x:v>内盘初始 TOKEN</x:v>
-      </x:c>
-      <x:c r="G35" s="68" t="n">
-        <x:f>$D$35</x:f>
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="H35" s="2"/>
-      <x:c r="I35" s="35" t="str">
-        <x:v>外盘含费投入 / Quote</x:v>
-      </x:c>
-      <x:c r="J35" s="58" t="n">
-        <x:f>IF($J$32="","",$G$40/($G$38-MAX(0,($J$22-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>5345.542940243272</x:v>
-      </x:c>
-      <x:c r="K35" s="2"/>
-      <x:c r="L35" s="2"/>
-    </x:row>
-    <x:row r="36" ht="36" customHeight="1">
-      <x:c r="A36" s="2"/>
-      <x:c r="B36" s="2"/>
-      <x:c r="C36" s="35" t="str">
-        <x:v>协议参数证据</x:v>
-      </x:c>
-      <x:c r="D36" s="69" t="n">
-        <x:f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</x:f>
-        <x:v>54430299</x:v>
-      </x:c>
-      <x:c r="E36" s="35"/>
-      <x:c r="F36" s="35" t="str">
-        <x:v>phantom Quote</x:v>
-      </x:c>
-      <x:c r="G36" s="58" t="n">
-        <x:f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</x:f>
-        <x:v>69.11859484777517</x:v>
-      </x:c>
-      <x:c r="H36" s="2"/>
-      <x:c r="I36" s="35" t="str">
-        <x:v>目标+1% FDV / Quote</x:v>
-      </x:c>
-      <x:c r="J36" s="58" t="n">
-        <x:f>IF($J$33="","",$J$33/$J$32*$D$35)</x:f>
-        <x:v>503689.93865868496</x:v>
-      </x:c>
-      <x:c r="K36" s="2"/>
-      <x:c r="L36" s="2"/>
-    </x:row>
-    <x:row r="37" ht="26" customHeight="1">
-      <x:c r="A37" s="2"/>
-      <x:c r="B37" s="2"/>
-      <x:c r="C37" s="35" t="str">
-        <x:v>外盘机制</x:v>
-      </x:c>
-      <x:c r="D37" s="63" t="str">
-        <x:v>Uniswap V4 / exact-input</x:v>
-      </x:c>
-      <x:c r="E37" s="35"/>
-      <x:c r="F37" s="35" t="str">
-        <x:v>内盘 k</x:v>
-      </x:c>
-      <x:c r="G37" s="65" t="n">
-        <x:f>$G$36*$D$35</x:f>
-        <x:v>69118594847.77518</x:v>
-      </x:c>
-      <x:c r="H37" s="2"/>
-      <x:c r="I37" s="35" t="str">
-        <x:v>洗筹单边费率</x:v>
-      </x:c>
-      <x:c r="J37" s="60" t="n">
-        <x:f>$G$32+$J$7</x:f>
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K37" s="2"/>
-      <x:c r="L37" s="2"/>
-    </x:row>
-    <x:row r="38" ht="36" customHeight="1">
-      <x:c r="A38" s="2"/>
-      <x:c r="B38" s="2"/>
-      <x:c r="C38" s="35" t="str">
-        <x:v>费用方向</x:v>
-      </x:c>
-      <x:c r="D38" s="63" t="str">
-        <x:v>Hook + Creator Tax 从 Meme 输出扣除</x:v>
-      </x:c>
-      <x:c r="E38" s="35"/>
-      <x:c r="F38" s="35" t="str">
-        <x:v>外盘初始 TOKEN</x:v>
-      </x:c>
-      <x:c r="G38" s="68" t="n">
-        <x:f>$D$35*$G$36*$G$34/($G$36+$G$34)^2</x:f>
-        <x:v>204081632.65306124</x:v>
-      </x:c>
-      <x:c r="H38" s="2"/>
-      <x:c r="I38" s="35" t="str">
-        <x:v>预算缓冲</x:v>
-      </x:c>
-      <x:c r="J38" s="59" t="n">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K38" s="2"/>
-      <x:c r="L38" s="2"/>
-    </x:row>
-    <x:row r="39" ht="36" customHeight="1">
-      <x:c r="A39" s="2"/>
-      <x:c r="B39" s="2"/>
-      <x:c r="C39" s="35" t="str">
-        <x:v>洗筹口径</x:v>
-      </x:c>
-      <x:c r="D39" s="63" t="str">
-        <x:v>目标+1% FDV ×（Hook + Creator Tax）×2</x:v>
-      </x:c>
-      <x:c r="E39" s="35"/>
-      <x:c r="F39" s="35" t="str">
-        <x:v>外盘初始 Quote</x:v>
-      </x:c>
-      <x:c r="G39" s="58" t="n">
-        <x:f>$G$34</x:f>
-        <x:v>172.79648711943796</x:v>
-      </x:c>
-      <x:c r="H39" s="2"/>
-      <x:c r="I39" s="35" t="str">
-        <x:v>分红与回购口径</x:v>
-      </x:c>
-      <x:c r="J39" s="70" t="str">
-        <x:v>不抵扣分红 / 回购收益</x:v>
-      </x:c>
-      <x:c r="K39" s="35"/>
-      <x:c r="L39" s="35"/>
-    </x:row>
-    <x:row r="40" ht="26" customHeight="1">
-      <x:c r="A40" s="2"/>
-      <x:c r="B40" s="2"/>
-      <x:c r="C40" s="2"/>
-      <x:c r="D40" s="63"/>
-      <x:c r="E40" s="35"/>
-      <x:c r="F40" s="35" t="str">
-        <x:v>外盘 k</x:v>
-      </x:c>
-      <x:c r="G40" s="65" t="n">
-        <x:f>$G$38*$G$34</x:f>
-        <x:v>35264589208.04857</x:v>
-      </x:c>
-      <x:c r="H40" s="2"/>
-      <x:c r="I40" s="2"/>
-      <x:c r="J40" s="63"/>
-      <x:c r="K40" s="35"/>
-      <x:c r="L40" s="35"/>
-    </x:row>
-    <x:row r="41" ht="36" customHeight="1">
-      <x:c r="A41" s="2"/>
-      <x:c r="B41" s="2"/>
-      <x:c r="C41" s="2"/>
-      <x:c r="D41" s="58"/>
-      <x:c r="E41" s="2"/>
-      <x:c r="F41" s="35" t="str">
-        <x:v>Locker TOKEN</x:v>
-      </x:c>
-      <x:c r="G41" s="68" t="n">
-        <x:f>$D$35*$G$36^2/($G$36+$G$34)^2</x:f>
-        <x:v>81632653.06122448</x:v>
-      </x:c>
-      <x:c r="H41" s="2"/>
-      <x:c r="I41" s="35" t="str">
-        <x:v>输入检查</x:v>
-      </x:c>
-      <x:c r="J41" s="63" t="str">
-        <x:f>IF(COUNT($D$8,$D$10,$G$7:$G$11,$J$7:$J$8)&lt;&gt;9,"缺少或非数值参数",IF(OR($G$7&lt;1,$G$8&lt;0,$G$9&lt;0,$G$10&lt;0,$G$11&lt;0,$D$10&lt;0,$G$7&lt;&gt;INT($G$7),$G$8&lt;&gt;INT($G$8),$G$9&lt;&gt;INT($G$9),$G$10&lt;&gt;INT($G$10)),"地址/Gas/预留参数无效",IF(OR($J$8&lt;0,$J$8&gt;1,AND($J$9&lt;&gt;"是",$J$9&lt;&gt;"否"),AND($J$10&lt;&gt;"是",$J$10&lt;&gt;"否")),"平台设置无效","参数有效")))</x:f>
-        <x:v>参数有效</x:v>
-      </x:c>
-      <x:c r="K41" s="35"/>
-      <x:c r="L41" s="35"/>
-    </x:row>
-    <x:row r="42" ht="36" customHeight="1">
-      <x:c r="A42" s="2"/>
-      <x:c r="B42" s="2"/>
-      <x:c r="C42" s="2"/>
-      <x:c r="D42" s="58"/>
-      <x:c r="E42" s="2"/>
-      <x:c r="F42" s="35" t="str">
-        <x:v>Snipe 窗口</x:v>
-      </x:c>
-      <x:c r="G42" s="70" t="str">
-        <x:v>3 秒；默认豁免或避开</x:v>
-      </x:c>
-      <x:c r="H42" s="2"/>
-      <x:c r="I42" s="2"/>
-      <x:c r="J42" s="58"/>
-      <x:c r="K42" s="2"/>
-      <x:c r="L42" s="2"/>
-    </x:row>
-    <x:row r="43" ht="36" customHeight="1">
-      <x:c r="A43" s="2"/>
-      <x:c r="B43" s="2"/>
-      <x:c r="C43" s="2"/>
-      <x:c r="D43" s="58"/>
-      <x:c r="E43" s="2"/>
-      <x:c r="F43" s="35" t="str">
-        <x:v>Creator Tax 上限</x:v>
-      </x:c>
-      <x:c r="G43" s="60" t="n">
-        <x:f>10%</x:f>
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="H43" s="2"/>
-      <x:c r="I43" s="2"/>
-      <x:c r="J43" s="58"/>
-      <x:c r="K43" s="2"/>
-      <x:c r="L43" s="2"/>
-    </x:row>
-    <x:row r="44" ht="26" customHeight="1">
-      <x:c r="A44" s="2"/>
-      <x:c r="B44" s="2"/>
-      <x:c r="C44" s="2"/>
-      <x:c r="D44" s="2"/>
-      <x:c r="E44" s="2"/>
-      <x:c r="F44" s="2"/>
-      <x:c r="G44" s="2"/>
-      <x:c r="H44" s="2"/>
-      <x:c r="I44" s="2"/>
-      <x:c r="J44" s="2"/>
-      <x:c r="K44" s="2"/>
-      <x:c r="L44" s="2"/>
-    </x:row>
-    <x:row r="45" ht="26" customHeight="1">
-      <x:c r="A45" s="2"/>
-      <x:c r="B45" s="2"/>
-      <x:c r="C45" s="2"/>
-      <x:c r="D45" s="2"/>
-      <x:c r="E45" s="2"/>
-      <x:c r="F45" s="2"/>
-      <x:c r="G45" s="2"/>
-      <x:c r="H45" s="2"/>
-      <x:c r="I45" s="2"/>
-      <x:c r="J45" s="2"/>
-      <x:c r="K45" s="2"/>
-      <x:c r="L45" s="2"/>
-    </x:row>
-    <x:row r="46" ht="26" customHeight="1">
-      <x:c r="A46" s="2"/>
-      <x:c r="B46" s="2"/>
-      <x:c r="C46" s="2"/>
-      <x:c r="D46" s="2"/>
-      <x:c r="E46" s="2"/>
-      <x:c r="F46" s="2"/>
-      <x:c r="G46" s="2"/>
-      <x:c r="H46" s="2"/>
-      <x:c r="I46" s="2"/>
-      <x:c r="J46" s="2"/>
-      <x:c r="K46" s="2"/>
-      <x:c r="L46" s="2"/>
-    </x:row>
-    <x:row r="47" ht="27" customHeight="1">
-      <x:c r="A47" s="2"/>
-      <x:c r="B47" s="2"/>
-      <x:c r="C47" s="8" t="str">
-        <x:v>内盘曲线</x:v>
-      </x:c>
-      <x:c r="D47" s="8"/>
-      <x:c r="E47" s="8"/>
-      <x:c r="F47" s="8"/>
-      <x:c r="G47" s="8"/>
-      <x:c r="H47" s="8"/>
-      <x:c r="I47" s="8"/>
-      <x:c r="J47" s="8"/>
-      <x:c r="K47" s="8"/>
-      <x:c r="L47" s="8"/>
-    </x:row>
-    <x:row r="48" ht="38" customHeight="1">
-      <x:c r="A48" s="2"/>
-      <x:c r="B48" s="2"/>
-      <x:c r="C48" s="75" t="str">
-        <x:v>控筹率</x:v>
-      </x:c>
-      <x:c r="D48" s="75" t="str">
-        <x:v>pooled TOKEN</x:v>
-      </x:c>
-      <x:c r="E48" s="75" t="str">
-        <x:v>pooled Quote</x:v>
-      </x:c>
-      <x:c r="F48" s="75" t="str">
-        <x:v>价格 / Quote</x:v>
-      </x:c>
-      <x:c r="G48" s="75" t="str">
-        <x:v>价格 / USDT</x:v>
-      </x:c>
-      <x:c r="H48" s="75" t="str">
-        <x:v>市值 / Quote</x:v>
-      </x:c>
-      <x:c r="I48" s="75" t="str">
-        <x:v>市值 / USDT</x:v>
-      </x:c>
-      <x:c r="J48" s="75" t="str">
-        <x:v>区间净投入
-/ Quote</x:v>
-      </x:c>
-      <x:c r="K48" s="75" t="str">
-        <x:v>区间含费
-/ Quote</x:v>
-      </x:c>
-      <x:c r="L48" s="75" t="str">
-        <x:v>理论累计所需
-/ Quote</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="26" customHeight="1">
-      <x:c r="A49" s="2"/>
-      <x:c r="B49" s="2"/>
-      <x:c r="C49" s="76" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D49" s="79" t="n">
-        <x:f>$D$35*(1-C49)</x:f>
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="E49" s="26" t="n">
-        <x:f>$G$37/D49</x:f>
-        <x:v>69.11859484777517</x:v>
-      </x:c>
-      <x:c r="F49" s="82" t="n">
-        <x:f>IF(OR(D49="",E49=""),"",E49/D49)</x:f>
-        <x:v>6.911859484777517e-8</x:v>
-      </x:c>
-      <x:c r="G49" s="82" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F49))),"",F49*$D$24)</x:f>
-      </x:c>
-      <x:c r="H49" s="26" t="n">
-        <x:f>IF(NOT(ISNUMBER(F49)),"",F49*$D$35)</x:f>
-        <x:v>69.11859484777517</x:v>
-      </x:c>
-      <x:c r="I49" s="26" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H49))),"",H49*$D$24)</x:f>
-      </x:c>
-      <x:c r="J49" s="26" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K49" s="26" t="n">
-        <x:f>J49/(1-$G$31-$J$7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L49" s="88" t="n">
-        <x:f>SUM($K$49:K49)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="26" customHeight="1">
-      <x:c r="A50" s="2"/>
-      <x:c r="B50" s="2"/>
-      <x:c r="C50" s="77" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="D50" s="80" t="n">
-        <x:f>$D$35*(1-C50)</x:f>
-        <x:v>900000000</x:v>
-      </x:c>
-      <x:c r="E50" s="27" t="n">
-        <x:f>$G$37/D50</x:f>
-        <x:v>76.7984387197502</x:v>
-      </x:c>
-      <x:c r="F50" s="83" t="n">
-        <x:f>IF(OR(D50="",E50=""),"",E50/D50)</x:f>
-        <x:v>8.533159857750022e-8</x:v>
-      </x:c>
-      <x:c r="G50" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F50))),"",F50*$D$24)</x:f>
-      </x:c>
-      <x:c r="H50" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F50)),"",F50*$D$35)</x:f>
-        <x:v>85.33159857750022</x:v>
-      </x:c>
-      <x:c r="I50" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H50))),"",H50*$D$24)</x:f>
-      </x:c>
-      <x:c r="J50" s="27" t="n">
-        <x:f>E50-E49</x:f>
-        <x:v>7.679843871975024</x:v>
-      </x:c>
-      <x:c r="K50" s="27" t="n">
-        <x:f>J50/(1-$G$31-$J$7)</x:f>
-        <x:v>7.757418052500024</x:v>
-      </x:c>
-      <x:c r="L50" s="89" t="n">
-        <x:f>SUM($K$49:K50)</x:f>
-        <x:v>7.757418052500024</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="26" customHeight="1">
-      <x:c r="A51" s="2"/>
-      <x:c r="B51" s="2"/>
-      <x:c r="C51" s="77" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="D51" s="80" t="n">
-        <x:f>$D$35*(1-C51)</x:f>
-        <x:v>800000000</x:v>
-      </x:c>
-      <x:c r="E51" s="27" t="n">
-        <x:f>$G$37/D51</x:f>
-        <x:v>86.39824355971898</x:v>
-      </x:c>
-      <x:c r="F51" s="83" t="n">
-        <x:f>IF(OR(D51="",E51=""),"",E51/D51)</x:f>
-        <x:v>1.0799780444964873e-7</x:v>
-      </x:c>
-      <x:c r="G51" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F51))),"",F51*$D$24)</x:f>
-      </x:c>
-      <x:c r="H51" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F51)),"",F51*$D$35)</x:f>
-        <x:v>107.99780444964873</x:v>
-      </x:c>
-      <x:c r="I51" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H51))),"",H51*$D$24)</x:f>
-      </x:c>
-      <x:c r="J51" s="27" t="n">
-        <x:f>E51-E50</x:f>
-        <x:v>9.599804839968783</x:v>
-      </x:c>
-      <x:c r="K51" s="27" t="n">
-        <x:f>J51/(1-$G$31-$J$7)</x:f>
-        <x:v>9.696772565625034</x:v>
-      </x:c>
-      <x:c r="L51" s="89" t="n">
-        <x:f>SUM($K$49:K51)</x:f>
-        <x:v>17.454190618125057</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" ht="26" customHeight="1">
-      <x:c r="A52" s="2"/>
-      <x:c r="B52" s="2"/>
-      <x:c r="C52" s="77" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="D52" s="80" t="n">
-        <x:f>$D$35*(1-C52)</x:f>
-        <x:v>700000000</x:v>
-      </x:c>
-      <x:c r="E52" s="27" t="n">
-        <x:f>$G$37/D52</x:f>
-        <x:v>98.74084978253596</x:v>
-      </x:c>
-      <x:c r="F52" s="83" t="n">
-        <x:f>IF(OR(D52="",E52=""),"",E52/D52)</x:f>
-        <x:v>1.4105835683219424e-7</x:v>
-      </x:c>
-      <x:c r="G52" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F52))),"",F52*$D$24)</x:f>
-      </x:c>
-      <x:c r="H52" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F52)),"",F52*$D$35)</x:f>
-        <x:v>141.05835683219425</x:v>
-      </x:c>
-      <x:c r="I52" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H52))),"",H52*$D$24)</x:f>
-      </x:c>
-      <x:c r="J52" s="27" t="n">
-        <x:f>E52-E51</x:f>
-        <x:v>12.342606222816983</x:v>
-      </x:c>
-      <x:c r="K52" s="27" t="n">
-        <x:f>J52/(1-$G$31-$J$7)</x:f>
-        <x:v>12.467279012946447</x:v>
-      </x:c>
-      <x:c r="L52" s="89" t="n">
-        <x:f>SUM($K$49:K52)</x:f>
-        <x:v>29.921469631071503</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="26" customHeight="1">
-      <x:c r="A53" s="2"/>
-      <x:c r="B53" s="2"/>
-      <x:c r="C53" s="77" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="D53" s="80" t="n">
-        <x:f>$D$35*(1-C53)</x:f>
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="E53" s="27" t="n">
-        <x:f>$G$37/D53</x:f>
-        <x:v>115.1976580796253</x:v>
-      </x:c>
-      <x:c r="F53" s="83" t="n">
-        <x:f>IF(OR(D53="",E53=""),"",E53/D53)</x:f>
-        <x:v>1.919960967993755e-7</x:v>
-      </x:c>
-      <x:c r="G53" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F53))),"",F53*$D$24)</x:f>
-      </x:c>
-      <x:c r="H53" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F53)),"",F53*$D$35)</x:f>
-        <x:v>191.99609679937552</x:v>
-      </x:c>
-      <x:c r="I53" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H53))),"",H53*$D$24)</x:f>
-      </x:c>
-      <x:c r="J53" s="27" t="n">
-        <x:f>E53-E52</x:f>
-        <x:v>16.45680829708934</x:v>
-      </x:c>
-      <x:c r="K53" s="27" t="n">
-        <x:f>J53/(1-$G$31-$J$7)</x:f>
-        <x:v>16.623038683928623</x:v>
-      </x:c>
-      <x:c r="L53" s="89" t="n">
-        <x:f>SUM($K$49:K53)</x:f>
-        <x:v>46.54450831500013</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" ht="26" customHeight="1">
-      <x:c r="A54" s="2"/>
-      <x:c r="B54" s="2"/>
-      <x:c r="C54" s="77" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="D54" s="80" t="n">
-        <x:f>$D$35*(1-C54)</x:f>
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="E54" s="27" t="n">
-        <x:f>$G$37/D54</x:f>
-        <x:v>138.23718969555034</x:v>
-      </x:c>
-      <x:c r="F54" s="83" t="n">
-        <x:f>IF(OR(D54="",E54=""),"",E54/D54)</x:f>
-        <x:v>2.7647437939110067e-7</x:v>
-      </x:c>
-      <x:c r="G54" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F54))),"",F54*$D$24)</x:f>
-      </x:c>
-      <x:c r="H54" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F54)),"",F54*$D$35)</x:f>
-        <x:v>276.4743793911007</x:v>
-      </x:c>
-      <x:c r="I54" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H54))),"",H54*$D$24)</x:f>
-      </x:c>
-      <x:c r="J54" s="27" t="n">
-        <x:f>E54-E53</x:f>
-        <x:v>23.039531615925043</x:v>
-      </x:c>
-      <x:c r="K54" s="27" t="n">
-        <x:f>J54/(1-$G$31-$J$7)</x:f>
-        <x:v>23.272254157500043</x:v>
-      </x:c>
-      <x:c r="L54" s="89" t="n">
-        <x:f>SUM($K$49:K54)</x:f>
-        <x:v>69.81676247250017</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" ht="26" customHeight="1">
-      <x:c r="A55" s="2"/>
-      <x:c r="B55" s="2"/>
-      <x:c r="C55" s="77" t="n">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="D55" s="80" t="n">
-        <x:f>$D$35*(1-C55)</x:f>
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="E55" s="27" t="n">
-        <x:f>$G$37/D55</x:f>
-        <x:v>172.79648711943796</x:v>
-      </x:c>
-      <x:c r="F55" s="83" t="n">
-        <x:f>IF(OR(D55="",E55=""),"",E55/D55)</x:f>
-        <x:v>4.319912177985949e-7</x:v>
-      </x:c>
-      <x:c r="G55" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F55))),"",F55*$D$24)</x:f>
-      </x:c>
-      <x:c r="H55" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F55)),"",F55*$D$35)</x:f>
-        <x:v>431.9912177985949</x:v>
-      </x:c>
-      <x:c r="I55" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H55))),"",H55*$D$24)</x:f>
-      </x:c>
-      <x:c r="J55" s="27" t="n">
-        <x:f>E55-E54</x:f>
-        <x:v>34.559297423887614</x:v>
-      </x:c>
-      <x:c r="K55" s="27" t="n">
-        <x:f>J55/(1-$G$31-$J$7)</x:f>
-        <x:v>34.908381236250115</x:v>
-      </x:c>
-      <x:c r="L55" s="89" t="n">
-        <x:f>SUM($K$49:K55)</x:f>
-        <x:v>104.7251437087503</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="26" customHeight="1">
-      <x:c r="A56" s="2"/>
-      <x:c r="B56" s="2"/>
-      <x:c r="C56" s="77" t="n">
-        <x:v>0.7</x:v>
-      </x:c>
-      <x:c r="D56" s="80" t="n">
-        <x:f>$D$35*(1-C56)</x:f>
-        <x:v>300000000.00000006</x:v>
-      </x:c>
-      <x:c r="E56" s="27" t="n">
-        <x:f>$G$37/D56</x:f>
-        <x:v>230.39531615925054</x:v>
-      </x:c>
-      <x:c r="F56" s="83" t="n">
-        <x:f>IF(OR(D56="",E56=""),"",E56/D56)</x:f>
-        <x:v>7.679843871975016e-7</x:v>
-      </x:c>
-      <x:c r="G56" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F56))),"",F56*$D$24)</x:f>
-      </x:c>
-      <x:c r="H56" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F56)),"",F56*$D$35)</x:f>
-        <x:v>767.9843871975016</x:v>
-      </x:c>
-      <x:c r="I56" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H56))),"",H56*$D$24)</x:f>
-      </x:c>
-      <x:c r="J56" s="27" t="n">
-        <x:f>E56-E55</x:f>
-        <x:v>57.598829039812586</x:v>
-      </x:c>
-      <x:c r="K56" s="27" t="n">
-        <x:f>J56/(1-$G$31-$J$7)</x:f>
-        <x:v>58.18063539375009</x:v>
-      </x:c>
-      <x:c r="L56" s="89" t="n">
-        <x:f>SUM($K$49:K56)</x:f>
-        <x:v>162.9057791025004</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="26" customHeight="1">
-      <x:c r="A57" s="2"/>
-      <x:c r="B57" s="2"/>
-      <x:c r="C57" s="91" t="n">
-        <x:f>$G$33</x:f>
-        <x:v>0.7142857142857143</x:v>
-      </x:c>
-      <x:c r="D57" s="92" t="n">
-        <x:f>$D$35*(1-C57)</x:f>
-        <x:v>285714285.7142857</x:v>
-      </x:c>
-      <x:c r="E57" s="93" t="n">
-        <x:f>$G$37/D57</x:f>
-        <x:v>241.91508196721315</x:v>
-      </x:c>
-      <x:c r="F57" s="94" t="n">
-        <x:f>IF(OR(D57="",E57=""),"",E57/D57)</x:f>
-        <x:v>8.467027868852461e-7</x:v>
-      </x:c>
-      <x:c r="G57" s="94" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F57))),"",F57*$D$24)</x:f>
-      </x:c>
-      <x:c r="H57" s="93" t="n">
-        <x:f>IF(NOT(ISNUMBER(F57)),"",F57*$D$35)</x:f>
-        <x:v>846.7027868852462</x:v>
-      </x:c>
-      <x:c r="I57" s="93" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H57))),"",H57*$D$24)</x:f>
-      </x:c>
-      <x:c r="J57" s="93" t="n">
-        <x:f>E57-E56</x:f>
-        <x:v>11.519765807962614</x:v>
-      </x:c>
-      <x:c r="K57" s="93" t="n">
-        <x:f>J57/(1-$G$31-$J$7)</x:f>
-        <x:v>11.636127078750116</x:v>
-      </x:c>
-      <x:c r="L57" s="90" t="n">
-        <x:f>SUM($K$49:K57)</x:f>
-        <x:v>174.5419061812505</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="26" customHeight="1">
-      <x:c r="A58" s="2"/>
-      <x:c r="B58" s="2"/>
-      <x:c r="C58" s="2"/>
-      <x:c r="D58" s="2"/>
-      <x:c r="E58" s="2"/>
-      <x:c r="F58" s="2"/>
-      <x:c r="G58" s="2"/>
-      <x:c r="H58" s="2"/>
-      <x:c r="I58" s="2"/>
-      <x:c r="J58" s="2"/>
-      <x:c r="K58" s="2"/>
-      <x:c r="L58" s="2"/>
-    </x:row>
-    <x:row r="59" ht="26" customHeight="1">
-      <x:c r="A59" s="2"/>
-      <x:c r="B59" s="2"/>
-      <x:c r="C59" s="2"/>
-      <x:c r="D59" s="2"/>
-      <x:c r="E59" s="2"/>
-      <x:c r="F59" s="2"/>
-      <x:c r="G59" s="2"/>
-      <x:c r="H59" s="2"/>
-      <x:c r="I59" s="2"/>
-      <x:c r="J59" s="2"/>
-      <x:c r="K59" s="2"/>
-      <x:c r="L59" s="2"/>
-    </x:row>
-    <x:row r="60" ht="27" customHeight="1">
-      <x:c r="A60" s="2"/>
-      <x:c r="B60" s="2"/>
-      <x:c r="C60" s="8" t="str">
-        <x:v>外盘曲线</x:v>
-      </x:c>
-      <x:c r="D60" s="8"/>
-      <x:c r="E60" s="8"/>
-      <x:c r="F60" s="8"/>
-      <x:c r="G60" s="8"/>
-      <x:c r="H60" s="8"/>
-      <x:c r="I60" s="8"/>
-      <x:c r="J60" s="8"/>
-      <x:c r="K60" s="8"/>
-      <x:c r="L60" s="8"/>
-    </x:row>
-    <x:row r="61" ht="38" customHeight="1">
-      <x:c r="A61" s="2"/>
-      <x:c r="B61" s="2"/>
-      <x:c r="C61" s="75" t="str">
-        <x:v>控筹率</x:v>
-      </x:c>
-      <x:c r="D61" s="75" t="str">
-        <x:v>pooled TOKEN</x:v>
-      </x:c>
-      <x:c r="E61" s="75" t="str">
-        <x:v>pooled Quote</x:v>
-      </x:c>
-      <x:c r="F61" s="75" t="str">
-        <x:v>价格 / Quote</x:v>
-      </x:c>
-      <x:c r="G61" s="75" t="str">
-        <x:v>价格 / USDT</x:v>
-      </x:c>
-      <x:c r="H61" s="75" t="str">
-        <x:v>市值 / Quote</x:v>
-      </x:c>
-      <x:c r="I61" s="75" t="str">
-        <x:v>市值 / USDT</x:v>
-      </x:c>
-      <x:c r="J61" s="75" t="str">
-        <x:v>外盘净投入
-/ Quote</x:v>
-      </x:c>
-      <x:c r="K61" s="75" t="str">
-        <x:v>外盘含费
-/ Quote</x:v>
-      </x:c>
-      <x:c r="L61" s="75" t="str">
-        <x:v>理论累计所需
-/ Quote</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="26" customHeight="1">
-      <x:c r="A62" s="2"/>
-      <x:c r="B62" s="2"/>
-      <x:c r="C62" s="95" t="n">
-        <x:f>$G$33</x:f>
-        <x:v>0.7142857142857143</x:v>
-      </x:c>
-      <x:c r="D62" s="96" t="n">
-        <x:f>$G$38</x:f>
-        <x:v>204081632.65306124</x:v>
-      </x:c>
-      <x:c r="E62" s="97" t="n">
-        <x:f>$G$34</x:f>
-        <x:v>172.79648711943796</x:v>
-      </x:c>
-      <x:c r="F62" s="98" t="n">
-        <x:f>IF(OR(D62="",E62=""),"",E62/D62)</x:f>
-        <x:v>8.467027868852459e-7</x:v>
-      </x:c>
-      <x:c r="G62" s="98" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F62))),"",F62*$D$24)</x:f>
-      </x:c>
-      <x:c r="H62" s="97" t="n">
-        <x:f>IF(NOT(ISNUMBER(F62)),"",F62*$D$35)</x:f>
-        <x:v>846.7027868852459</x:v>
-      </x:c>
-      <x:c r="I62" s="97" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H62))),"",H62*$D$24)</x:f>
-      </x:c>
-      <x:c r="J62" s="97" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K62" s="97" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L62" s="88" t="n">
-        <x:f>$J$31</x:f>
-        <x:v>174.54190618125045</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="26" customHeight="1">
-      <x:c r="A63" s="2"/>
-      <x:c r="B63" s="2"/>
-      <x:c r="C63" s="77" t="n">
-        <x:v>0.75</x:v>
-      </x:c>
-      <x:c r="D63" s="80" t="n">
-        <x:f>IF(C63&lt;$G$23,$D$35*(1-C63)-$G$41,"")</x:f>
-        <x:v>168367346.93877554</x:v>
-      </x:c>
-      <x:c r="E63" s="27" t="n">
-        <x:f>IF(D63="","",$G$40/D63)</x:f>
-        <x:v>209.45028741750056</x:v>
-      </x:c>
-      <x:c r="F63" s="83" t="n">
-        <x:f>IF(OR(D63="",E63=""),"",E63/D63)</x:f>
-        <x:v>0.0000012440077676918213</x:v>
-      </x:c>
-      <x:c r="G63" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F63))),"",F63*$D$24)</x:f>
-      </x:c>
-      <x:c r="H63" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F63)),"",F63*$D$35)</x:f>
-        <x:v>1244.0077676918213</x:v>
-      </x:c>
-      <x:c r="I63" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H63))),"",H63*$D$24)</x:f>
-      </x:c>
-      <x:c r="J63" s="27" t="n">
-        <x:f>IF(E63="","",MAX(0,E63-$G$34))</x:f>
-        <x:v>36.653800298062606</x:v>
-      </x:c>
-      <x:c r="K63" s="27" t="n">
-        <x:f>IF(D63="","",$G$40/($G$38-MAX(0,(C63-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>37.103540179020456</x:v>
-      </x:c>
-      <x:c r="L63" s="89" t="n">
-        <x:f>IF(K63="","",$J$31+K63)</x:f>
-        <x:v>211.6454463602709</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="26" customHeight="1">
-      <x:c r="A64" s="2"/>
-      <x:c r="B64" s="2"/>
-      <x:c r="C64" s="77" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="D64" s="80" t="n">
-        <x:f>IF(C64&lt;$G$23,$D$35*(1-C64)-$G$41,"")</x:f>
-        <x:v>118367346.9387755</x:v>
-      </x:c>
-      <x:c r="E64" s="27" t="n">
-        <x:f>IF(D64="","",$G$40/D64)</x:f>
-        <x:v>297.9249777921345</x:v>
-      </x:c>
-      <x:c r="F64" s="83" t="n">
-        <x:f>IF(OR(D64="",E64=""),"",E64/D64)</x:f>
-        <x:v>0.0000025169523985887227</x:v>
-      </x:c>
-      <x:c r="G64" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F64))),"",F64*$D$24)</x:f>
-      </x:c>
-      <x:c r="H64" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F64)),"",F64*$D$35)</x:f>
-        <x:v>2516.9523985887226</x:v>
-      </x:c>
-      <x:c r="I64" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H64))),"",H64*$D$24)</x:f>
-      </x:c>
-      <x:c r="J64" s="27" t="n">
-        <x:f>IF(E64="","",MAX(0,E64-$G$34))</x:f>
-        <x:v>125.12849067269653</x:v>
-      </x:c>
-      <x:c r="K64" s="27" t="n">
-        <x:f>IF(D64="","",$G$40/($G$38-MAX(0,(C64-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>127.32372735116493</x:v>
-      </x:c>
-      <x:c r="L64" s="89" t="n">
-        <x:f>IF(K64="","",$J$31+K64)</x:f>
-        <x:v>301.86563353241536</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="26" customHeight="1">
-      <x:c r="A65" s="2"/>
-      <x:c r="B65" s="2"/>
-      <x:c r="C65" s="77" t="n">
-        <x:v>0.82</x:v>
-      </x:c>
-      <x:c r="D65" s="80" t="n">
-        <x:f>IF(C65&lt;$G$23,$D$35*(1-C65)-$G$41,"")</x:f>
-        <x:v>98367346.93877558</x:v>
-      </x:c>
-      <x:c r="E65" s="27" t="n">
-        <x:f>IF(D65="","",$G$40/D65)</x:f>
-        <x:v>358.4989359324437</x:v>
-      </x:c>
-      <x:c r="F65" s="83" t="n">
-        <x:f>IF(OR(D65="",E65=""),"",E65/D65)</x:f>
-        <x:v>0.000003644491257404508</x:v>
-      </x:c>
-      <x:c r="G65" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F65))),"",F65*$D$24)</x:f>
-      </x:c>
-      <x:c r="H65" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F65)),"",F65*$D$35)</x:f>
-        <x:v>3644.4912574045084</x:v>
-      </x:c>
-      <x:c r="I65" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H65))),"",H65*$D$24)</x:f>
-      </x:c>
-      <x:c r="J65" s="27" t="n">
-        <x:f>IF(E65="","",MAX(0,E65-$G$34))</x:f>
-        <x:v>185.70244881300576</x:v>
-      </x:c>
-      <x:c r="K65" s="27" t="n">
-        <x:f>IF(D65="","",$G$40/($G$38-MAX(0,(C65-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>189.63682272853552</x:v>
-      </x:c>
-      <x:c r="L65" s="89" t="n">
-        <x:f>IF(K65="","",$J$31+K65)</x:f>
-        <x:v>364.17872890978595</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="26" customHeight="1">
-      <x:c r="A66" s="2"/>
-      <x:c r="B66" s="2"/>
-      <x:c r="C66" s="77" t="n">
-        <x:v>0.84</x:v>
-      </x:c>
-      <x:c r="D66" s="80" t="n">
-        <x:f>IF(C66&lt;$G$23,$D$35*(1-C66)-$G$41,"")</x:f>
-        <x:v>78367346.93877555</x:v>
-      </x:c>
-      <x:c r="E66" s="27" t="n">
-        <x:f>IF(D66="","",$G$40/D66)</x:f>
-        <x:v>449.99085187353614</x:v>
-      </x:c>
-      <x:c r="F66" s="83" t="n">
-        <x:f>IF(OR(D66="",E66=""),"",E66/D66)</x:f>
-        <x:v>0.000005742070766094599</x:v>
-      </x:c>
-      <x:c r="G66" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F66))),"",F66*$D$24)</x:f>
-      </x:c>
-      <x:c r="H66" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F66)),"",F66*$D$35)</x:f>
-        <x:v>5742.070766094599</x:v>
-      </x:c>
-      <x:c r="I66" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H66))),"",H66*$D$24)</x:f>
-      </x:c>
-      <x:c r="J66" s="27" t="n">
-        <x:f>IF(E66="","",MAX(0,E66-$G$34))</x:f>
-        <x:v>277.19436475409816</x:v>
-      </x:c>
-      <x:c r="K66" s="27" t="n">
-        <x:f>IF(D66="","",$G$40/($G$38-MAX(0,(C66-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>284.6059787849564</x:v>
-      </x:c>
-      <x:c r="L66" s="89" t="n">
-        <x:f>IF(K66="","",$J$31+K66)</x:f>
-        <x:v>459.14788496620685</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="26" customHeight="1">
-      <x:c r="A67" s="2"/>
-      <x:c r="B67" s="2"/>
-      <x:c r="C67" s="77" t="n">
-        <x:v>0.86</x:v>
-      </x:c>
-      <x:c r="D67" s="80" t="n">
-        <x:f>IF(C67&lt;$G$23,$D$35*(1-C67)-$G$41,"")</x:f>
-        <x:v>58367346.938775524</x:v>
-      </x:c>
-      <x:c r="E67" s="27" t="n">
-        <x:f>IF(D67="","",$G$40/D67)</x:f>
-        <x:v>604.1835213966361</x:v>
-      </x:c>
-      <x:c r="F67" s="83" t="n">
-        <x:f>IF(OR(D67="",E67=""),"",E67/D67)</x:f>
-        <x:v>0.00001035139599595635</x:v>
-      </x:c>
-      <x:c r="G67" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F67))),"",F67*$D$24)</x:f>
-      </x:c>
-      <x:c r="H67" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F67)),"",F67*$D$35)</x:f>
-        <x:v>10351.39599595635</x:v>
-      </x:c>
-      <x:c r="I67" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H67))),"",H67*$D$24)</x:f>
-      </x:c>
-      <x:c r="J67" s="27" t="n">
-        <x:f>IF(E67="","",MAX(0,E67-$G$34))</x:f>
-        <x:v>431.38703427719815</x:v>
-      </x:c>
-      <x:c r="K67" s="27" t="n">
-        <x:f>IF(D67="","",$G$40/($G$38-MAX(0,(C67-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>447.0169992872412</x:v>
-      </x:c>
-      <x:c r="L67" s="89" t="n">
-        <x:f>IF(K67="","",$J$31+K67)</x:f>
-        <x:v>621.5589054684917</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="26" customHeight="1">
-      <x:c r="A68" s="2"/>
-      <x:c r="B68" s="2"/>
-      <x:c r="C68" s="77" t="n">
-        <x:v>0.88</x:v>
-      </x:c>
-      <x:c r="D68" s="80" t="n">
-        <x:f>IF(C68&lt;$G$23,$D$35*(1-C68)-$G$41,"")</x:f>
-        <x:v>38367346.938775524</x:v>
-      </x:c>
-      <x:c r="E68" s="27" t="n">
-        <x:f>IF(D68="","",$G$40/D68)</x:f>
-        <x:v>919.1302506353081</x:v>
-      </x:c>
-      <x:c r="F68" s="83" t="n">
-        <x:f>IF(OR(D68="",E68=""),"",E68/D68)</x:f>
-        <x:v>0.000023956054404856426</x:v>
-      </x:c>
-      <x:c r="G68" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F68))),"",F68*$D$24)</x:f>
-      </x:c>
-      <x:c r="H68" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F68)),"",F68*$D$35)</x:f>
-        <x:v>23956.054404856426</x:v>
-      </x:c>
-      <x:c r="I68" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H68))),"",H68*$D$24)</x:f>
-      </x:c>
-      <x:c r="J68" s="27" t="n">
-        <x:f>IF(E68="","",MAX(0,E68-$G$34))</x:f>
-        <x:v>746.3337635158701</x:v>
-      </x:c>
-      <x:c r="K68" s="27" t="n">
-        <x:f>IF(D68="","",$G$40/($G$38-MAX(0,(C68-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>788.2626266347389</x:v>
-      </x:c>
-      <x:c r="L68" s="89" t="n">
-        <x:f>IF(K68="","",$J$31+K68)</x:f>
-        <x:v>962.8045328159894</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" ht="26" customHeight="1">
-      <x:c r="A69" s="2"/>
-      <x:c r="B69" s="2"/>
-      <x:c r="C69" s="77" t="n">
-        <x:v>0.89</x:v>
-      </x:c>
-      <x:c r="D69" s="80" t="n">
-        <x:f>IF(C69&lt;$G$23,$D$35*(1-C69)-$G$41,"")</x:f>
-        <x:v>28367346.93877551</x:v>
-      </x:c>
-      <x:c r="E69" s="27" t="n">
-        <x:f>IF(D69="","",$G$40/D69)</x:f>
-        <x:v>1243.1401951038704</x:v>
-      </x:c>
-      <x:c r="F69" s="83" t="n">
-        <x:f>IF(OR(D69="",E69=""),"",E69/D69)</x:f>
-        <x:v>0.00004382292774107169</x:v>
-      </x:c>
-      <x:c r="G69" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F69))),"",F69*$D$24)</x:f>
-      </x:c>
-      <x:c r="H69" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F69)),"",F69*$D$35)</x:f>
-        <x:v>43822.92774107169</x:v>
-      </x:c>
-      <x:c r="I69" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H69))),"",H69*$D$24)</x:f>
-      </x:c>
-      <x:c r="J69" s="27" t="n">
-        <x:f>IF(E69="","",MAX(0,E69-$G$34))</x:f>
-        <x:v>1070.3437079844325</x:v>
-      </x:c>
-      <x:c r="K69" s="27" t="n">
-        <x:f>IF(D69="","",$G$40/($G$38-MAX(0,(C69-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>1153.31608844834</x:v>
-      </x:c>
-      <x:c r="L69" s="89" t="n">
-        <x:f>IF(K69="","",$J$31+K69)</x:f>
-        <x:v>1327.8579946295904</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" ht="26" customHeight="1">
-      <x:c r="A70" s="2"/>
-      <x:c r="B70" s="2"/>
-      <x:c r="C70" s="77" t="n">
-        <x:v>0.9</x:v>
-      </x:c>
-      <x:c r="D70" s="80" t="n">
-        <x:f>IF(C70&lt;$G$23,$D$35*(1-C70)-$G$41,"")</x:f>
-        <x:v>18367346.93877551</x:v>
-      </x:c>
-      <x:c r="E70" s="27" t="n">
-        <x:f>IF(D70="","",$G$40/D70)</x:f>
-        <x:v>1919.9609679937555</x:v>
-      </x:c>
-      <x:c r="F70" s="83" t="n">
-        <x:f>IF(OR(D70="",E70=""),"",E70/D70)</x:f>
-        <x:v>0.0001045312082574378</x:v>
-      </x:c>
-      <x:c r="G70" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F70))),"",F70*$D$24)</x:f>
-      </x:c>
-      <x:c r="H70" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F70)),"",F70*$D$35)</x:f>
-        <x:v>104531.2082574378</x:v>
-      </x:c>
-      <x:c r="I70" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H70))),"",H70*$D$24)</x:f>
-      </x:c>
-      <x:c r="J70" s="27" t="n">
-        <x:f>IF(E70="","",MAX(0,E70-$G$34))</x:f>
-        <x:v>1747.1644808743176</x:v>
-      </x:c>
-      <x:c r="K70" s="27" t="n">
-        <x:f>IF(D70="","",$G$40/($G$38-MAX(0,(C70-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>1965.5600409836077</x:v>
-      </x:c>
-      <x:c r="L70" s="89" t="n">
-        <x:f>IF(K70="","",$J$31+K70)</x:f>
-        <x:v>2140.1019471648583</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" ht="26" customHeight="1">
-      <x:c r="A71" s="2"/>
-      <x:c r="B71" s="2"/>
-      <x:c r="C71" s="77" t="n">
-        <x:v>0.905</x:v>
-      </x:c>
-      <x:c r="D71" s="80" t="n">
-        <x:f>IF(C71&lt;$G$23,$D$35*(1-C71)-$G$41,"")</x:f>
-        <x:v>13367346.938775495</x:v>
-      </x:c>
-      <x:c r="E71" s="27" t="n">
-        <x:f>IF(D71="","",$G$40/D71)</x:f>
-        <x:v>2638.1143071669953</x:v>
-      </x:c>
-      <x:c r="F71" s="83" t="n">
-        <x:f>IF(OR(D71="",E71=""),"",E71/D71)</x:f>
-        <x:v>0.00019735511610867622</x:v>
-      </x:c>
-      <x:c r="G71" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F71))),"",F71*$D$24)</x:f>
-      </x:c>
-      <x:c r="H71" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F71)),"",F71*$D$35)</x:f>
-        <x:v>197355.11610867621</x:v>
-      </x:c>
-      <x:c r="I71" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H71))),"",H71*$D$24)</x:f>
-      </x:c>
-      <x:c r="J71" s="27" t="n">
-        <x:f>IF(E71="","",MAX(0,E71-$G$34))</x:f>
-        <x:v>2465.3178200475572</x:v>
-      </x:c>
-      <x:c r="K71" s="27" t="n">
-        <x:f>IF(D71="","",$G$40/($G$38-MAX(0,(C71-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>2909.51922906513</x:v>
-      </x:c>
-      <x:c r="L71" s="89" t="n">
-        <x:f>IF(K71="","",$J$31+K71)</x:f>
-        <x:v>3084.06113524638</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" ht="26" customHeight="1">
-      <x:c r="A72" s="2"/>
-      <x:c r="B72" s="2"/>
-      <x:c r="C72" s="77" t="n">
-        <x:v>0.91</x:v>
-      </x:c>
-      <x:c r="D72" s="80" t="n">
-        <x:f>IF(C72&lt;$G$23,$D$35*(1-C72)-$G$41,"")</x:f>
-        <x:v>8367346.938775495</x:v>
-      </x:c>
-      <x:c r="E72" s="27" t="n">
-        <x:f>IF(D72="","",$G$40/D72)</x:f>
-        <x:v>4214.548466327764</x:v>
-      </x:c>
-      <x:c r="F72" s="83" t="n">
-        <x:f>IF(OR(D72="",E72=""),"",E72/D72)</x:f>
-        <x:v>0.0005036899386586849</x:v>
-      </x:c>
-      <x:c r="G72" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F72))),"",F72*$D$24)</x:f>
-      </x:c>
-      <x:c r="H72" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F72)),"",F72*$D$35)</x:f>
-        <x:v>503689.93865868496</x:v>
-      </x:c>
-      <x:c r="I72" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H72))),"",H72*$D$24)</x:f>
-      </x:c>
-      <x:c r="J72" s="27" t="n">
-        <x:f>IF(E72="","",MAX(0,E72-$G$34))</x:f>
-        <x:v>4041.751979208326</x:v>
-      </x:c>
-      <x:c r="K72" s="27" t="n">
-        <x:f>IF(D72="","",$G$40/($G$38-MAX(0,(C72-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>5345.542940243272</x:v>
-      </x:c>
-      <x:c r="L72" s="89" t="n">
-        <x:f>IF(K72="","",$J$31+K72)</x:f>
-        <x:v>5520.084846424523</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="26" customHeight="1">
-      <x:c r="A73" s="2"/>
-      <x:c r="B73" s="2"/>
-      <x:c r="C73" s="77" t="n">
-        <x:v>0.915</x:v>
-      </x:c>
-      <x:c r="D73" s="80" t="n">
-        <x:f>IF(C73&lt;$G$23,$D$35*(1-C73)-$G$41,"")</x:f>
-        <x:v>3367346.9387754947</x:v>
-      </x:c>
-      <x:c r="E73" s="27" t="n">
-        <x:f>IF(D73="","",$G$40/D73)</x:f>
-        <x:v>10472.514370875078</x:v>
-      </x:c>
-      <x:c r="F73" s="83" t="n">
-        <x:f>IF(OR(D73="",E73=""),"",E73/D73)</x:f>
-        <x:v>0.0031100194192295832</x:v>
-      </x:c>
-      <x:c r="G73" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F73))),"",F73*$D$24)</x:f>
-      </x:c>
-      <x:c r="H73" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F73)),"",F73*$D$35)</x:f>
-        <x:v>3110019.4192295833</x:v>
-      </x:c>
-      <x:c r="I73" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H73))),"",H73*$D$24)</x:f>
-      </x:c>
-      <x:c r="J73" s="27" t="n">
-        <x:f>IF(E73="","",MAX(0,E73-$G$34))</x:f>
-        <x:v>10299.71788375564</x:v>
-      </x:c>
-      <x:c r="K73" s="27" t="n">
-        <x:f>IF(D73="","",$G$40/($G$38-MAX(0,(C73-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-        <x:v>26145.43770491818</x:v>
-      </x:c>
-      <x:c r="L73" s="89" t="n">
-        <x:f>IF(K73="","",$J$31+K73)</x:f>
-        <x:v>26319.97961109943</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="26" customHeight="1">
-      <x:c r="A74" s="2"/>
-      <x:c r="B74" s="2"/>
-      <x:c r="C74" s="77" t="n">
-        <x:v>0.918</x:v>
-      </x:c>
-      <x:c r="D74" s="80" t="str">
-        <x:f>IF(C74&lt;$G$23,$D$35*(1-C74)-$G$41,"")</x:f>
-      </x:c>
-      <x:c r="E74" s="27" t="str">
-        <x:f>IF(D74="","",$G$40/D74)</x:f>
-      </x:c>
-      <x:c r="F74" s="83" t="str">
-        <x:f>IF(OR(D74="",E74=""),"",E74/D74)</x:f>
-      </x:c>
-      <x:c r="G74" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F74))),"",F74*$D$24)</x:f>
-      </x:c>
-      <x:c r="H74" s="27" t="str">
-        <x:f>IF(NOT(ISNUMBER(F74)),"",F74*$D$35)</x:f>
-      </x:c>
-      <x:c r="I74" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H74))),"",H74*$D$24)</x:f>
-      </x:c>
-      <x:c r="J74" s="27" t="str">
-        <x:f>IF(E74="","",MAX(0,E74-$G$34))</x:f>
-      </x:c>
-      <x:c r="K74" s="27" t="str">
-        <x:f>IF(D74="","",$G$40/($G$38-MAX(0,(C74-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-      </x:c>
-      <x:c r="L74" s="89" t="str">
-        <x:f>IF(K74="","",$J$31+K74)</x:f>
-      </x:c>
-    </x:row>
-    <x:row r="75" ht="26" customHeight="1">
-      <x:c r="A75" s="2"/>
-      <x:c r="B75" s="2"/>
-      <x:c r="C75" s="78" t="n">
-        <x:v>0.9183673469387755</x:v>
-      </x:c>
-      <x:c r="D75" s="81" t="str">
-        <x:f>IF(C75&lt;$G$23,$D$35*(1-C75)-$G$41,"")</x:f>
-      </x:c>
-      <x:c r="E75" s="28" t="str">
-        <x:f>IF(D75="","",$G$40/D75)</x:f>
-      </x:c>
-      <x:c r="F75" s="84" t="str">
-        <x:f>IF(OR(D75="",E75=""),"",E75/D75)</x:f>
-      </x:c>
-      <x:c r="G75" s="84" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F75))),"",F75*$D$24)</x:f>
-      </x:c>
-      <x:c r="H75" s="28" t="str">
-        <x:f>IF(NOT(ISNUMBER(F75)),"",F75*$D$35)</x:f>
-      </x:c>
-      <x:c r="I75" s="28" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H75))),"",H75*$D$24)</x:f>
-      </x:c>
-      <x:c r="J75" s="28" t="str">
-        <x:f>IF(E75="","",MAX(0,E75-$G$34))</x:f>
-      </x:c>
-      <x:c r="K75" s="28" t="str">
-        <x:f>IF(D75="","",$G$40/($G$38-MAX(0,(C75-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</x:f>
-      </x:c>
-      <x:c r="L75" s="90" t="str">
-        <x:f>IF(K75="","",$J$31+K75)</x:f>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="26" customHeight="1">
-      <x:c r="A76" s="2"/>
-      <x:c r="B76" s="2"/>
-      <x:c r="C76" s="2"/>
-      <x:c r="D76" s="2"/>
-      <x:c r="E76" s="2"/>
-      <x:c r="F76" s="2"/>
-      <x:c r="G76" s="2"/>
-      <x:c r="H76" s="2"/>
-      <x:c r="I76" s="2"/>
-      <x:c r="J76" s="2"/>
-      <x:c r="K76" s="2"/>
-      <x:c r="L76" s="2"/>
-    </x:row>
-    <x:row r="77" ht="26" customHeight="1">
-      <x:c r="A77" s="2"/>
-      <x:c r="B77" s="2"/>
-      <x:c r="C77" s="2"/>
-      <x:c r="D77" s="2"/>
-      <x:c r="E77" s="2"/>
-      <x:c r="F77" s="2"/>
-      <x:c r="G77" s="2"/>
-      <x:c r="H77" s="2"/>
-      <x:c r="I77" s="2"/>
-      <x:c r="J77" s="2"/>
-      <x:c r="K77" s="2"/>
-      <x:c r="L77" s="2"/>
-    </x:row>
-    <x:row r="78" ht="27" customHeight="1">
-      <x:c r="A78" s="2"/>
-      <x:c r="B78" s="2"/>
-      <x:c r="C78" s="100" t="str">
-        <x:v>外盘回落参考</x:v>
-      </x:c>
-      <x:c r="D78" s="100"/>
-      <x:c r="E78" s="100"/>
-      <x:c r="F78" s="100"/>
-      <x:c r="G78" s="100"/>
-      <x:c r="H78" s="100"/>
-      <x:c r="I78" s="100"/>
-      <x:c r="J78" s="100"/>
-      <x:c r="K78" s="100"/>
-      <x:c r="L78" s="100"/>
-    </x:row>
-    <x:row r="79" ht="38" customHeight="1">
-      <x:c r="A79" s="2"/>
-      <x:c r="B79" s="2"/>
-      <x:c r="C79" s="75" t="str">
-        <x:v>控筹率</x:v>
-      </x:c>
-      <x:c r="D79" s="75" t="str">
-        <x:v>pooled TOKEN</x:v>
-      </x:c>
-      <x:c r="E79" s="75" t="str">
-        <x:v>pooled Quote</x:v>
-      </x:c>
-      <x:c r="F79" s="75" t="str">
-        <x:v>价格 / Quote</x:v>
-      </x:c>
-      <x:c r="G79" s="75" t="str">
-        <x:v>价格 / USDT</x:v>
-      </x:c>
-      <x:c r="H79" s="75" t="str">
-        <x:v>市值 / Quote</x:v>
-      </x:c>
-      <x:c r="I79" s="75" t="str">
-        <x:v>市值 / USDT</x:v>
-      </x:c>
-      <x:c r="J79" s="75" t="str">
-        <x:v>较毕业点回撤</x:v>
-      </x:c>
-      <x:c r="K79" s="75" t="str"/>
-      <x:c r="L79" s="75" t="str"/>
-    </x:row>
-    <x:row r="80" ht="26" customHeight="1">
-      <x:c r="A80" s="2"/>
-      <x:c r="B80" s="2"/>
-      <x:c r="C80" s="95" t="n">
-        <x:v>0.7142857142857143</x:v>
-      </x:c>
-      <x:c r="D80" s="96" t="n">
-        <x:f>$D$35*(1-C80)-$G$41</x:f>
-        <x:v>204081632.6530612</x:v>
-      </x:c>
-      <x:c r="E80" s="97" t="n">
-        <x:f>$G$40/D80</x:f>
-        <x:v>172.79648711943798</x:v>
-      </x:c>
-      <x:c r="F80" s="98" t="n">
-        <x:f>IF(OR(D80="",E80=""),"",E80/D80)</x:f>
-        <x:v>8.467027868852462e-7</x:v>
-      </x:c>
-      <x:c r="G80" s="98" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F80))),"",F80*$D$24)</x:f>
-      </x:c>
-      <x:c r="H80" s="97" t="n">
-        <x:f>IF(NOT(ISNUMBER(F80)),"",F80*$D$35)</x:f>
-        <x:v>846.7027868852463</x:v>
-      </x:c>
-      <x:c r="I80" s="97" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H80))),"",H80*$D$24)</x:f>
-      </x:c>
-      <x:c r="J80" s="95" t="n">
-        <x:f>IF($H$80&gt;0,1-H80/$H$80,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K80" s="97"/>
-      <x:c r="L80" s="97"/>
-    </x:row>
-    <x:row r="81" ht="26" customHeight="1">
-      <x:c r="A81" s="2"/>
-      <x:c r="B81" s="2"/>
-      <x:c r="C81" s="77" t="n">
-        <x:v>0.7</x:v>
-      </x:c>
-      <x:c r="D81" s="80" t="n">
-        <x:f>$D$35*(1-C81)-$G$41</x:f>
-        <x:v>218367346.9387756</x:v>
-      </x:c>
-      <x:c r="E81" s="27" t="n">
-        <x:f>$G$40/D81</x:f>
-        <x:v>161.49204403685786</x:v>
-      </x:c>
-      <x:c r="F81" s="83" t="n">
-        <x:f>IF(OR(D81="",E81=""),"",E81/D81)</x:f>
-        <x:v>7.395430054024329e-7</x:v>
-      </x:c>
-      <x:c r="G81" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F81))),"",F81*$D$24)</x:f>
-      </x:c>
-      <x:c r="H81" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F81)),"",F81*$D$35)</x:f>
-        <x:v>739.5430054024329</x:v>
-      </x:c>
-      <x:c r="I81" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H81))),"",H81*$D$24)</x:f>
-      </x:c>
-      <x:c r="J81" s="77" t="n">
-        <x:f>IF($H$80&gt;0,1-H81/$H$80,0)</x:f>
-        <x:v>0.12656127172678933</x:v>
-      </x:c>
-      <x:c r="K81" s="27"/>
-      <x:c r="L81" s="27"/>
-    </x:row>
-    <x:row r="82" ht="26" customHeight="1">
-      <x:c r="A82" s="2"/>
-      <x:c r="B82" s="2"/>
-      <x:c r="C82" s="77" t="n">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="D82" s="80" t="n">
-        <x:f>$D$35*(1-C82)-$G$41</x:f>
-        <x:v>318367346.93877554</x:v>
-      </x:c>
-      <x:c r="E82" s="27" t="n">
-        <x:f>$G$40/D82</x:f>
-        <x:v>110.76697892271665</x:v>
-      </x:c>
-      <x:c r="F82" s="83" t="n">
-        <x:f>IF(OR(D82="",E82=""),"",E82/D82)</x:f>
-        <x:v>3.479219209751997e-7</x:v>
-      </x:c>
-      <x:c r="G82" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F82))),"",F82*$D$24)</x:f>
-      </x:c>
-      <x:c r="H82" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F82)),"",F82*$D$35)</x:f>
-        <x:v>347.9219209751997</x:v>
-      </x:c>
-      <x:c r="I82" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H82))),"",H82*$D$24)</x:f>
-      </x:c>
-      <x:c r="J82" s="77" t="n">
-        <x:f>IF($H$80&gt;0,1-H82/$H$80,0)</x:f>
-        <x:v>0.5890861275476661</x:v>
-      </x:c>
-      <x:c r="K82" s="27"/>
-      <x:c r="L82" s="27"/>
-    </x:row>
-    <x:row r="83" ht="26" customHeight="1">
-      <x:c r="A83" s="2"/>
-      <x:c r="B83" s="2"/>
-      <x:c r="C83" s="77" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="D83" s="80" t="n">
-        <x:f>$D$35*(1-C83)-$G$41</x:f>
-        <x:v>418367346.93877554</x:v>
-      </x:c>
-      <x:c r="E83" s="27" t="n">
-        <x:f>$G$40/D83</x:f>
-        <x:v>84.29096932655511</x:v>
-      </x:c>
-      <x:c r="F83" s="83" t="n">
-        <x:f>IF(OR(D83="",E83=""),"",E83/D83)</x:f>
-        <x:v>2.0147597546347317e-7</x:v>
-      </x:c>
-      <x:c r="G83" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F83))),"",F83*$D$24)</x:f>
-      </x:c>
-      <x:c r="H83" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F83)),"",F83*$D$35)</x:f>
-        <x:v>201.47597546347316</x:v>
-      </x:c>
-      <x:c r="I83" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H83))),"",H83*$D$24)</x:f>
-      </x:c>
-      <x:c r="J83" s="77" t="n">
-        <x:f>IF($H$80&gt;0,1-H83/$H$80,0)</x:f>
-        <x:v>0.7620464009518144</x:v>
-      </x:c>
-      <x:c r="K83" s="27"/>
-      <x:c r="L83" s="27"/>
-    </x:row>
-    <x:row r="84" ht="26" customHeight="1">
-      <x:c r="A84" s="2"/>
-      <x:c r="B84" s="2"/>
-      <x:c r="C84" s="77" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="D84" s="80" t="n">
-        <x:f>$D$35*(1-C84)-$G$41</x:f>
-        <x:v>518367346.93877554</x:v>
-      </x:c>
-      <x:c r="E84" s="27" t="n">
-        <x:f>$G$40/D84</x:f>
-        <x:v>68.03011303914882</x:v>
-      </x:c>
-      <x:c r="F84" s="83" t="n">
-        <x:f>IF(OR(D84="",E84=""),"",E84/D84)</x:f>
-        <x:v>1.3123919444560203e-7</x:v>
-      </x:c>
-      <x:c r="G84" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F84))),"",F84*$D$24)</x:f>
-      </x:c>
-      <x:c r="H84" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F84)),"",F84*$D$35)</x:f>
-        <x:v>131.23919444560204</x:v>
-      </x:c>
-      <x:c r="I84" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H84))),"",H84*$D$24)</x:f>
-      </x:c>
-      <x:c r="J84" s="77" t="n">
-        <x:f>IF($H$80&gt;0,1-H84/$H$80,0)</x:f>
-        <x:v>0.84499968999938</x:v>
-      </x:c>
-      <x:c r="K84" s="27"/>
-      <x:c r="L84" s="27"/>
-    </x:row>
-    <x:row r="85" ht="26" customHeight="1">
-      <x:c r="A85" s="2"/>
-      <x:c r="B85" s="2"/>
-      <x:c r="C85" s="77" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="D85" s="80" t="n">
-        <x:f>$D$35*(1-C85)-$G$41</x:f>
-        <x:v>618367346.9387755</x:v>
-      </x:c>
-      <x:c r="E85" s="27" t="n">
-        <x:f>$G$40/D85</x:f>
-        <x:v>57.028543603774914</x:v>
-      </x:c>
-      <x:c r="F85" s="83" t="n">
-        <x:f>IF(OR(D85="",E85=""),"",E85/D85)</x:f>
-        <x:v>9.222437744504854e-8</x:v>
-      </x:c>
-      <x:c r="G85" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F85))),"",F85*$D$24)</x:f>
-      </x:c>
-      <x:c r="H85" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F85)),"",F85*$D$35)</x:f>
-        <x:v>92.22437744504853</x:v>
-      </x:c>
-      <x:c r="I85" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H85))),"",H85*$D$24)</x:f>
-      </x:c>
-      <x:c r="J85" s="77" t="n">
-        <x:f>IF($H$80&gt;0,1-H85/$H$80,0)</x:f>
-        <x:v>0.8910782167325644</x:v>
-      </x:c>
-      <x:c r="K85" s="27"/>
-      <x:c r="L85" s="27"/>
-    </x:row>
-    <x:row r="86" ht="26" customHeight="1">
-      <x:c r="A86" s="2"/>
-      <x:c r="B86" s="2"/>
-      <x:c r="C86" s="77" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="D86" s="80" t="n">
-        <x:f>$D$35*(1-C86)-$G$41</x:f>
-        <x:v>718367346.9387755</x:v>
-      </x:c>
-      <x:c r="E86" s="27" t="n">
-        <x:f>$G$40/D86</x:f>
-        <x:v>49.089911113476695</x:v>
-      </x:c>
-      <x:c r="F86" s="83" t="n">
-        <x:f>IF(OR(D86="",E86=""),"",E86/D86)</x:f>
-        <x:v>6.833538762955562e-8</x:v>
-      </x:c>
-      <x:c r="G86" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F86))),"",F86*$D$24)</x:f>
-      </x:c>
-      <x:c r="H86" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F86)),"",F86*$D$35)</x:f>
-        <x:v>68.33538762955563</x:v>
-      </x:c>
-      <x:c r="I86" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H86))),"",H86*$D$24)</x:f>
-      </x:c>
-      <x:c r="J86" s="77" t="n">
-        <x:f>IF($H$80&gt;0,1-H86/$H$80,0)</x:f>
-        <x:v>0.9192923553719008</x:v>
-      </x:c>
-      <x:c r="K86" s="27"/>
-      <x:c r="L86" s="27"/>
-    </x:row>
-    <x:row r="87" ht="26" customHeight="1">
-      <x:c r="A87" s="2"/>
-      <x:c r="B87" s="2"/>
-      <x:c r="C87" s="77" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="D87" s="80" t="n">
-        <x:f>$D$35*(1-C87)-$G$41</x:f>
-        <x:v>818367346.9387755</x:v>
-      </x:c>
-      <x:c r="E87" s="27" t="n">
-        <x:f>$G$40/D87</x:f>
-        <x:v>43.09139329661795</x:v>
-      </x:c>
-      <x:c r="F87" s="83" t="n">
-        <x:f>IF(OR(D87="",E87=""),"",E87/D87)</x:f>
-        <x:v>5.265531849212667e-8</x:v>
-      </x:c>
-      <x:c r="G87" s="83" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F87))),"",F87*$D$24)</x:f>
-      </x:c>
-      <x:c r="H87" s="27" t="n">
-        <x:f>IF(NOT(ISNUMBER(F87)),"",F87*$D$35)</x:f>
-        <x:v>52.65531849212667</x:v>
-      </x:c>
-      <x:c r="I87" s="27" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H87))),"",H87*$D$24)</x:f>
-      </x:c>
-      <x:c r="J87" s="77" t="n">
-        <x:f>IF($H$80&gt;0,1-H87/$H$80,0)</x:f>
-        <x:v>0.9378113320190795</x:v>
-      </x:c>
-      <x:c r="K87" s="27"/>
-      <x:c r="L87" s="27"/>
-    </x:row>
-    <x:row r="88" ht="26" customHeight="1">
-      <x:c r="A88" s="2"/>
-      <x:c r="B88" s="2"/>
-      <x:c r="C88" s="78" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D88" s="81" t="n">
-        <x:f>$D$35*(1-C88)-$G$41</x:f>
-        <x:v>918367346.9387755</x:v>
-      </x:c>
-      <x:c r="E88" s="28" t="n">
-        <x:f>$G$40/D88</x:f>
-        <x:v>38.399219359875104</x:v>
-      </x:c>
-      <x:c r="F88" s="84" t="n">
-        <x:f>IF(OR(D88="",E88=""),"",E88/D88)</x:f>
-        <x:v>4.181248330297511e-8</x:v>
-      </x:c>
-      <x:c r="G88" s="84" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(F88))),"",F88*$D$24)</x:f>
-      </x:c>
-      <x:c r="H88" s="28" t="n">
-        <x:f>IF(NOT(ISNUMBER(F88)),"",F88*$D$35)</x:f>
-        <x:v>41.81248330297511</x:v>
-      </x:c>
-      <x:c r="I88" s="28" t="str">
-        <x:f>IF(OR($D$24="",NOT(ISNUMBER(H88))),"",H88*$D$24)</x:f>
-      </x:c>
-      <x:c r="J88" s="78" t="n">
-        <x:f>IF($H$80&gt;0,1-H88/$H$80,0)</x:f>
-        <x:v>0.9506172839506173</x:v>
-      </x:c>
-      <x:c r="K88" s="101" t="str">
-        <x:v>沉没成本 / Quote</x:v>
-      </x:c>
-      <x:c r="L88" s="28" t="n">
-        <x:f>E88</x:f>
-        <x:v>38.399219359875104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="26" customHeight="1">
-      <x:c r="A89" s="2"/>
-      <x:c r="B89" s="2"/>
-      <x:c r="C89" s="2"/>
-      <x:c r="D89" s="2"/>
-      <x:c r="E89" s="2"/>
-      <x:c r="F89" s="2"/>
-      <x:c r="G89" s="2"/>
-      <x:c r="H89" s="2"/>
-      <x:c r="I89" s="2"/>
-      <x:c r="J89" s="2"/>
-      <x:c r="K89" s="2"/>
-      <x:c r="L89" s="2"/>
-    </x:row>
-    <x:row r="90" ht="26" customHeight="1">
-      <x:c r="A90" s="2"/>
-      <x:c r="B90" s="2"/>
-      <x:c r="C90" s="2"/>
-      <x:c r="D90" s="2"/>
-      <x:c r="E90" s="2"/>
-      <x:c r="F90" s="2"/>
-      <x:c r="G90" s="2"/>
-      <x:c r="H90" s="2"/>
-      <x:c r="I90" s="2"/>
-      <x:c r="J90" s="2"/>
-      <x:c r="K90" s="2"/>
-      <x:c r="L90" s="2"/>
-    </x:row>
-    <x:row r="91" ht="26" customHeight="1">
-      <x:c r="A91" s="2"/>
-      <x:c r="B91" s="2"/>
-      <x:c r="C91" s="2"/>
-      <x:c r="D91" s="2"/>
-      <x:c r="E91" s="2"/>
-      <x:c r="F91" s="2"/>
-      <x:c r="G91" s="2"/>
-      <x:c r="H91" s="2"/>
-      <x:c r="I91" s="2"/>
-      <x:c r="J91" s="2"/>
-      <x:c r="K91" s="2"/>
-      <x:c r="L91" s="2"/>
-    </x:row>
-    <x:row r="92" ht="26" customHeight="1">
-      <x:c r="A92" s="2"/>
-      <x:c r="B92" s="2"/>
-      <x:c r="C92" s="2"/>
-      <x:c r="D92" s="2"/>
-      <x:c r="E92" s="2"/>
-      <x:c r="F92" s="2"/>
-      <x:c r="G92" s="2"/>
-      <x:c r="H92" s="2"/>
-      <x:c r="I92" s="2"/>
-      <x:c r="J92" s="2"/>
-      <x:c r="K92" s="2"/>
-      <x:c r="L92" s="2"/>
-    </x:row>
-    <x:row r="93" ht="26" customHeight="1">
-      <x:c r="A93" s="2"/>
-      <x:c r="B93" s="2"/>
-      <x:c r="C93" s="2"/>
-      <x:c r="D93" s="2"/>
-      <x:c r="E93" s="2"/>
-      <x:c r="F93" s="2"/>
-      <x:c r="G93" s="2"/>
-      <x:c r="H93" s="2"/>
-      <x:c r="I93" s="2"/>
-      <x:c r="J93" s="2"/>
-      <x:c r="K93" s="2"/>
-      <x:c r="L93" s="2"/>
-    </x:row>
-    <x:row r="94" ht="26" customHeight="1">
-      <x:c r="A94" s="2"/>
-      <x:c r="B94" s="2"/>
-      <x:c r="C94" s="2"/>
-      <x:c r="D94" s="2"/>
-      <x:c r="E94" s="2"/>
-      <x:c r="F94" s="2"/>
-      <x:c r="G94" s="2"/>
-      <x:c r="H94" s="2"/>
-      <x:c r="I94" s="2"/>
-      <x:c r="J94" s="2"/>
-      <x:c r="K94" s="2"/>
-      <x:c r="L94" s="2"/>
-    </x:row>
-    <x:row r="95" ht="26" customHeight="1">
-      <x:c r="A95" s="2"/>
-      <x:c r="B95" s="2"/>
-      <x:c r="C95" s="2"/>
-      <x:c r="D95" s="2"/>
-      <x:c r="E95" s="2"/>
-      <x:c r="F95" s="2"/>
-      <x:c r="G95" s="2"/>
-      <x:c r="H95" s="2"/>
-      <x:c r="I95" s="2"/>
-      <x:c r="J95" s="2"/>
-      <x:c r="K95" s="2"/>
-      <x:c r="L95" s="2"/>
-    </x:row>
-    <x:row r="96" ht="26" customHeight="1">
-      <x:c r="A96" s="2"/>
-      <x:c r="B96" s="2"/>
-      <x:c r="C96" s="2"/>
-      <x:c r="D96" s="2"/>
-      <x:c r="E96" s="2"/>
-      <x:c r="F96" s="2"/>
-      <x:c r="G96" s="2"/>
-      <x:c r="H96" s="2"/>
-      <x:c r="I96" s="2"/>
-      <x:c r="J96" s="2"/>
-      <x:c r="K96" s="2"/>
-      <x:c r="L96" s="2"/>
-    </x:row>
-    <x:row r="97" ht="26" customHeight="1">
-      <x:c r="A97" s="2"/>
-      <x:c r="B97" s="2"/>
-      <x:c r="C97" s="2"/>
-      <x:c r="D97" s="2"/>
-      <x:c r="E97" s="2"/>
-      <x:c r="F97" s="2"/>
-      <x:c r="G97" s="2"/>
-      <x:c r="H97" s="2"/>
-      <x:c r="I97" s="2"/>
-      <x:c r="J97" s="2"/>
-      <x:c r="K97" s="2"/>
-      <x:c r="L97" s="2"/>
-    </x:row>
-    <x:row r="98" ht="26" customHeight="1">
-      <x:c r="A98" s="2"/>
-      <x:c r="B98" s="2"/>
-      <x:c r="C98" s="2"/>
-      <x:c r="D98" s="2"/>
-      <x:c r="E98" s="2"/>
-      <x:c r="F98" s="2"/>
-      <x:c r="G98" s="2"/>
-      <x:c r="H98" s="2"/>
-      <x:c r="I98" s="2"/>
-      <x:c r="J98" s="2"/>
-      <x:c r="K98" s="2"/>
-      <x:c r="L98" s="2"/>
-    </x:row>
-    <x:row r="99" ht="26" customHeight="1">
-      <x:c r="A99" s="2"/>
-      <x:c r="B99" s="2"/>
-      <x:c r="C99" s="2"/>
-      <x:c r="D99" s="2"/>
-      <x:c r="E99" s="2"/>
-      <x:c r="F99" s="2"/>
-      <x:c r="G99" s="2"/>
-      <x:c r="H99" s="2"/>
-      <x:c r="I99" s="2"/>
-      <x:c r="J99" s="2"/>
-      <x:c r="K99" s="2"/>
-      <x:c r="L99" s="2"/>
-    </x:row>
-    <x:row r="100" ht="26" customHeight="1">
-      <x:c r="A100" s="2"/>
-      <x:c r="B100" s="2"/>
-      <x:c r="C100" s="2"/>
-      <x:c r="D100" s="2"/>
-      <x:c r="E100" s="2"/>
-      <x:c r="F100" s="2"/>
-      <x:c r="G100" s="2"/>
-      <x:c r="H100" s="2"/>
-      <x:c r="I100" s="2"/>
-      <x:c r="J100" s="2"/>
-      <x:c r="K100" s="2"/>
-      <x:c r="L100" s="2"/>
-    </x:row>
-    <x:row r="101" ht="26" customHeight="1">
-      <x:c r="A101" s="2"/>
-      <x:c r="B101" s="2"/>
-      <x:c r="C101" s="2"/>
-      <x:c r="D101" s="2"/>
-      <x:c r="E101" s="2"/>
-      <x:c r="F101" s="2"/>
-      <x:c r="G101" s="2"/>
-      <x:c r="H101" s="2"/>
-      <x:c r="I101" s="2"/>
-      <x:c r="J101" s="2"/>
-      <x:c r="K101" s="2"/>
-      <x:c r="L101" s="2"/>
-    </x:row>
-    <x:row r="102" ht="26" customHeight="1">
-      <x:c r="A102" s="2"/>
-      <x:c r="B102" s="2"/>
-      <x:c r="C102" s="2"/>
-      <x:c r="D102" s="2"/>
-      <x:c r="E102" s="2"/>
-      <x:c r="F102" s="2"/>
-      <x:c r="G102" s="2"/>
-      <x:c r="H102" s="2"/>
-      <x:c r="I102" s="2"/>
-      <x:c r="J102" s="2"/>
-      <x:c r="K102" s="2"/>
-      <x:c r="L102" s="2"/>
-    </x:row>
-    <x:row r="103" ht="26" customHeight="1">
-      <x:c r="A103" s="2"/>
-      <x:c r="B103" s="2"/>
-      <x:c r="C103" s="2"/>
-      <x:c r="D103" s="2"/>
-      <x:c r="E103" s="2"/>
-      <x:c r="F103" s="2"/>
-      <x:c r="G103" s="2"/>
-      <x:c r="H103" s="2"/>
-      <x:c r="I103" s="2"/>
-      <x:c r="J103" s="2"/>
-      <x:c r="K103" s="2"/>
-      <x:c r="L103" s="2"/>
-    </x:row>
-    <x:row r="104" ht="26" customHeight="1">
-      <x:c r="A104" s="2"/>
-      <x:c r="B104" s="2"/>
-      <x:c r="C104" s="2"/>
-      <x:c r="D104" s="2"/>
-      <x:c r="E104" s="2"/>
-      <x:c r="F104" s="2"/>
-      <x:c r="G104" s="2"/>
-      <x:c r="H104" s="2"/>
-      <x:c r="I104" s="2"/>
-      <x:c r="J104" s="2"/>
-      <x:c r="K104" s="2"/>
-      <x:c r="L104" s="2"/>
-    </x:row>
-    <x:row r="105" ht="26" customHeight="1">
-      <x:c r="A105" s="2"/>
-      <x:c r="B105" s="2"/>
-      <x:c r="C105" s="2"/>
-      <x:c r="D105" s="2"/>
-      <x:c r="E105" s="2"/>
-      <x:c r="F105" s="2"/>
-      <x:c r="G105" s="2"/>
-      <x:c r="H105" s="2"/>
-      <x:c r="I105" s="2"/>
-      <x:c r="J105" s="2"/>
-      <x:c r="K105" s="2"/>
-      <x:c r="L105" s="2"/>
-    </x:row>
-    <x:row r="106" ht="26" customHeight="1">
-      <x:c r="A106" s="2"/>
-      <x:c r="B106" s="2"/>
-      <x:c r="C106" s="2"/>
-      <x:c r="D106" s="2"/>
-      <x:c r="E106" s="2"/>
-      <x:c r="F106" s="2"/>
-      <x:c r="G106" s="2"/>
-      <x:c r="H106" s="2"/>
-      <x:c r="I106" s="2"/>
-      <x:c r="J106" s="2"/>
-      <x:c r="K106" s="2"/>
-      <x:c r="L106" s="2"/>
-    </x:row>
-    <x:row r="107" ht="26" customHeight="1">
-      <x:c r="A107" s="2"/>
-      <x:c r="B107" s="2"/>
-      <x:c r="C107" s="2"/>
-      <x:c r="D107" s="2"/>
-      <x:c r="E107" s="2"/>
-      <x:c r="F107" s="2"/>
-      <x:c r="G107" s="2"/>
-      <x:c r="H107" s="2"/>
-      <x:c r="I107" s="2"/>
-      <x:c r="J107" s="2"/>
-      <x:c r="K107" s="2"/>
-      <x:c r="L107" s="2"/>
-    </x:row>
-    <x:row r="108" ht="26" customHeight="1">
-      <x:c r="A108" s="2"/>
-      <x:c r="B108" s="2"/>
-      <x:c r="C108" s="2"/>
-      <x:c r="D108" s="2"/>
-      <x:c r="E108" s="2"/>
-      <x:c r="F108" s="2"/>
-      <x:c r="G108" s="2"/>
-      <x:c r="H108" s="2"/>
-      <x:c r="I108" s="2"/>
-      <x:c r="J108" s="2"/>
-      <x:c r="K108" s="2"/>
-      <x:c r="L108" s="2"/>
-    </x:row>
-    <x:row r="109" ht="26" customHeight="1">
-      <x:c r="A109" s="2"/>
-      <x:c r="B109" s="2"/>
-      <x:c r="C109" s="2"/>
-      <x:c r="D109" s="2"/>
-      <x:c r="E109" s="2"/>
-      <x:c r="F109" s="2"/>
-      <x:c r="G109" s="2"/>
-      <x:c r="H109" s="2"/>
-      <x:c r="I109" s="2"/>
-      <x:c r="J109" s="2"/>
-      <x:c r="K109" s="2"/>
-      <x:c r="L109" s="2"/>
-    </x:row>
-    <x:row r="110" ht="26" customHeight="1">
-      <x:c r="A110" s="2"/>
-      <x:c r="B110" s="2"/>
-      <x:c r="C110" s="2"/>
-      <x:c r="D110" s="2"/>
-      <x:c r="E110" s="2"/>
-      <x:c r="F110" s="2"/>
-      <x:c r="G110" s="2"/>
-      <x:c r="H110" s="2"/>
-      <x:c r="I110" s="2"/>
-      <x:c r="J110" s="2"/>
-      <x:c r="K110" s="2"/>
-      <x:c r="L110" s="2"/>
-    </x:row>
-    <x:row r="111" ht="26" customHeight="1">
-      <x:c r="A111" s="2"/>
-      <x:c r="B111" s="2"/>
-      <x:c r="C111" s="2"/>
-      <x:c r="D111" s="2"/>
-      <x:c r="E111" s="2"/>
-      <x:c r="F111" s="2"/>
-      <x:c r="G111" s="2"/>
-      <x:c r="H111" s="2"/>
-      <x:c r="I111" s="2"/>
-      <x:c r="J111" s="2"/>
-      <x:c r="K111" s="2"/>
-      <x:c r="L111" s="2"/>
-    </x:row>
-    <x:row r="112" ht="26" customHeight="1">
-      <x:c r="A112" s="2"/>
-      <x:c r="B112" s="2"/>
-      <x:c r="C112" s="2"/>
-      <x:c r="D112" s="2"/>
-      <x:c r="E112" s="2"/>
-      <x:c r="F112" s="2"/>
-      <x:c r="G112" s="2"/>
-      <x:c r="H112" s="2"/>
-      <x:c r="I112" s="2"/>
-      <x:c r="J112" s="2"/>
-      <x:c r="K112" s="2"/>
-      <x:c r="L112" s="2"/>
-    </x:row>
-    <x:row r="113" ht="26" customHeight="1">
-      <x:c r="A113" s="2"/>
-      <x:c r="B113" s="2"/>
-      <x:c r="C113" s="2"/>
-      <x:c r="D113" s="2"/>
-      <x:c r="E113" s="2"/>
-      <x:c r="F113" s="2"/>
-      <x:c r="G113" s="2"/>
-      <x:c r="H113" s="2"/>
-      <x:c r="I113" s="2"/>
-      <x:c r="J113" s="2"/>
-      <x:c r="K113" s="2"/>
-      <x:c r="L113" s="2"/>
-    </x:row>
-    <x:row r="114" ht="26" customHeight="1">
-      <x:c r="A114" s="2"/>
-      <x:c r="B114" s="2"/>
-      <x:c r="C114" s="2"/>
-      <x:c r="D114" s="2"/>
-      <x:c r="E114" s="2"/>
-      <x:c r="F114" s="2"/>
-      <x:c r="G114" s="2"/>
-      <x:c r="H114" s="2"/>
-      <x:c r="I114" s="2"/>
-      <x:c r="J114" s="2"/>
-      <x:c r="K114" s="2"/>
-      <x:c r="L114" s="2"/>
-    </x:row>
-    <x:row r="115" ht="26" customHeight="1">
-      <x:c r="A115" s="2"/>
-      <x:c r="B115" s="2"/>
-      <x:c r="C115" s="2"/>
-      <x:c r="D115" s="2"/>
-      <x:c r="E115" s="2"/>
-      <x:c r="F115" s="2"/>
-      <x:c r="G115" s="2"/>
-      <x:c r="H115" s="2"/>
-      <x:c r="I115" s="2"/>
-      <x:c r="J115" s="2"/>
-      <x:c r="K115" s="2"/>
-      <x:c r="L115" s="2"/>
-    </x:row>
-    <x:row r="116" ht="26" customHeight="1">
-      <x:c r="A116" s="2"/>
-      <x:c r="B116" s="2"/>
-      <x:c r="C116" s="2"/>
-      <x:c r="D116" s="2"/>
-      <x:c r="E116" s="2"/>
-      <x:c r="F116" s="2"/>
-      <x:c r="G116" s="2"/>
-      <x:c r="H116" s="2"/>
-      <x:c r="I116" s="2"/>
-      <x:c r="J116" s="2"/>
-      <x:c r="K116" s="2"/>
-      <x:c r="L116" s="2"/>
-    </x:row>
-    <x:row r="117" ht="26" customHeight="1">
-      <x:c r="A117" s="2"/>
-      <x:c r="B117" s="2"/>
-      <x:c r="C117" s="2"/>
-      <x:c r="D117" s="2"/>
-      <x:c r="E117" s="2"/>
-      <x:c r="F117" s="2"/>
-      <x:c r="G117" s="2"/>
-      <x:c r="H117" s="2"/>
-      <x:c r="I117" s="2"/>
-      <x:c r="J117" s="2"/>
-      <x:c r="K117" s="2"/>
-      <x:c r="L117" s="2"/>
-    </x:row>
-    <x:row r="118" ht="26" customHeight="1">
-      <x:c r="A118" s="2"/>
-      <x:c r="B118" s="2"/>
-      <x:c r="C118" s="2"/>
-      <x:c r="D118" s="2"/>
-      <x:c r="E118" s="2"/>
-      <x:c r="F118" s="2"/>
-      <x:c r="G118" s="2"/>
-      <x:c r="H118" s="2"/>
-      <x:c r="I118" s="2"/>
-      <x:c r="J118" s="2"/>
-      <x:c r="K118" s="2"/>
-      <x:c r="L118" s="2"/>
-    </x:row>
-    <x:row r="119" ht="26" customHeight="1">
-      <x:c r="A119" s="2"/>
-      <x:c r="B119" s="2"/>
-      <x:c r="C119" s="2"/>
-      <x:c r="D119" s="2"/>
-      <x:c r="E119" s="2"/>
-      <x:c r="F119" s="2"/>
-      <x:c r="G119" s="2"/>
-      <x:c r="H119" s="2"/>
-      <x:c r="I119" s="2"/>
-      <x:c r="J119" s="2"/>
-      <x:c r="K119" s="2"/>
-      <x:c r="L119" s="2"/>
-    </x:row>
-    <x:row r="120" ht="26" customHeight="1">
-      <x:c r="A120" s="2"/>
-      <x:c r="B120" s="2"/>
-      <x:c r="C120" s="2"/>
-      <x:c r="D120" s="2"/>
-      <x:c r="E120" s="2"/>
-      <x:c r="F120" s="2"/>
-      <x:c r="G120" s="2"/>
-      <x:c r="H120" s="2"/>
-      <x:c r="I120" s="2"/>
-      <x:c r="J120" s="2"/>
-      <x:c r="K120" s="2"/>
-      <x:c r="L120" s="2"/>
-    </x:row>
-    <x:row r="121" ht="26" customHeight="1">
-      <x:c r="A121" s="2"/>
-      <x:c r="B121" s="2"/>
-      <x:c r="C121" s="2"/>
-      <x:c r="D121" s="2"/>
-      <x:c r="E121" s="2"/>
-      <x:c r="F121" s="2"/>
-      <x:c r="G121" s="2"/>
-      <x:c r="H121" s="2"/>
-      <x:c r="I121" s="2"/>
-      <x:c r="J121" s="2"/>
-      <x:c r="K121" s="2"/>
-      <x:c r="L121" s="2"/>
-    </x:row>
-    <x:row r="122" ht="26" customHeight="1">
-      <x:c r="A122" s="2"/>
-      <x:c r="B122" s="2"/>
-      <x:c r="C122" s="2"/>
-      <x:c r="D122" s="2"/>
-      <x:c r="E122" s="2"/>
-      <x:c r="F122" s="2"/>
-      <x:c r="G122" s="2"/>
-      <x:c r="H122" s="2"/>
-      <x:c r="I122" s="2"/>
-      <x:c r="J122" s="2"/>
-      <x:c r="K122" s="2"/>
-      <x:c r="L122" s="2"/>
-    </x:row>
-    <x:row r="123" ht="26" customHeight="1">
-      <x:c r="A123" s="2"/>
-      <x:c r="B123" s="2"/>
-      <x:c r="C123" s="2"/>
-      <x:c r="D123" s="2"/>
-      <x:c r="E123" s="2"/>
-      <x:c r="F123" s="2"/>
-      <x:c r="G123" s="2"/>
-      <x:c r="H123" s="2"/>
-      <x:c r="I123" s="2"/>
-      <x:c r="J123" s="2"/>
-      <x:c r="K123" s="2"/>
-      <x:c r="L123" s="2"/>
-    </x:row>
-    <x:row r="124" ht="26" customHeight="1">
-      <x:c r="A124" s="2"/>
-      <x:c r="B124" s="2"/>
-      <x:c r="C124" s="2"/>
-      <x:c r="D124" s="2"/>
-      <x:c r="E124" s="2"/>
-      <x:c r="F124" s="2"/>
-      <x:c r="G124" s="2"/>
-      <x:c r="H124" s="2"/>
-      <x:c r="I124" s="2"/>
-      <x:c r="J124" s="2"/>
-      <x:c r="K124" s="2"/>
-      <x:c r="L124" s="2"/>
-    </x:row>
-    <x:row r="125" ht="26" customHeight="1">
-      <x:c r="A125" s="2"/>
-      <x:c r="B125" s="2"/>
-      <x:c r="C125" s="2"/>
-      <x:c r="D125" s="2"/>
-      <x:c r="E125" s="2"/>
-      <x:c r="F125" s="2"/>
-      <x:c r="G125" s="2"/>
-      <x:c r="H125" s="2"/>
-      <x:c r="I125" s="2"/>
-      <x:c r="J125" s="2"/>
-      <x:c r="K125" s="2"/>
-      <x:c r="L125" s="2"/>
-    </x:row>
-    <x:row r="126" ht="26" customHeight="1">
-      <x:c r="A126" s="2"/>
-      <x:c r="B126" s="2"/>
-      <x:c r="C126" s="2"/>
-      <x:c r="D126" s="2"/>
-      <x:c r="E126" s="2"/>
-      <x:c r="F126" s="2"/>
-      <x:c r="G126" s="2"/>
-      <x:c r="H126" s="2"/>
-      <x:c r="I126" s="2"/>
-      <x:c r="J126" s="2"/>
-      <x:c r="K126" s="2"/>
-      <x:c r="L126" s="2"/>
-    </x:row>
-    <x:row r="127" ht="26" customHeight="1">
-      <x:c r="A127" s="2"/>
-      <x:c r="B127" s="2"/>
-      <x:c r="C127" s="2"/>
-      <x:c r="D127" s="2"/>
-      <x:c r="E127" s="2"/>
-      <x:c r="F127" s="2"/>
-      <x:c r="G127" s="2"/>
-      <x:c r="H127" s="2"/>
-      <x:c r="I127" s="2"/>
-      <x:c r="J127" s="2"/>
-      <x:c r="K127" s="2"/>
-      <x:c r="L127" s="2"/>
-    </x:row>
-    <x:row r="128" ht="26" customHeight="1">
-      <x:c r="A128" s="2"/>
-      <x:c r="B128" s="2"/>
-      <x:c r="C128" s="2"/>
-      <x:c r="D128" s="2"/>
-      <x:c r="E128" s="2"/>
-      <x:c r="F128" s="2"/>
-      <x:c r="G128" s="2"/>
-      <x:c r="H128" s="2"/>
-      <x:c r="I128" s="2"/>
-      <x:c r="J128" s="2"/>
-      <x:c r="K128" s="2"/>
-      <x:c r="L128" s="2"/>
-    </x:row>
-    <x:row r="129" ht="26" customHeight="1">
-      <x:c r="A129" s="2"/>
-      <x:c r="B129" s="2"/>
-      <x:c r="C129" s="2"/>
-      <x:c r="D129" s="2"/>
-      <x:c r="E129" s="2"/>
-      <x:c r="F129" s="2"/>
-      <x:c r="G129" s="2"/>
-      <x:c r="H129" s="2"/>
-      <x:c r="I129" s="2"/>
-      <x:c r="J129" s="2"/>
-      <x:c r="K129" s="2"/>
-      <x:c r="L129" s="2"/>
-    </x:row>
-    <x:row r="130" ht="26" customHeight="1">
-      <x:c r="A130" s="2"/>
-      <x:c r="B130" s="2"/>
-      <x:c r="C130" s="2"/>
-      <x:c r="D130" s="2"/>
-      <x:c r="E130" s="2"/>
-      <x:c r="F130" s="2"/>
-      <x:c r="G130" s="2"/>
-      <x:c r="H130" s="2"/>
-      <x:c r="I130" s="2"/>
-      <x:c r="J130" s="2"/>
-      <x:c r="K130" s="2"/>
-      <x:c r="L130" s="2"/>
-    </x:row>
-    <x:row r="131" ht="26" customHeight="1">
-      <x:c r="A131" s="2"/>
-      <x:c r="B131" s="2"/>
-      <x:c r="C131" s="2"/>
-      <x:c r="D131" s="2"/>
-      <x:c r="E131" s="2"/>
-      <x:c r="F131" s="2"/>
-      <x:c r="G131" s="2"/>
-      <x:c r="H131" s="2"/>
-      <x:c r="I131" s="2"/>
-      <x:c r="J131" s="2"/>
-      <x:c r="K131" s="2"/>
-      <x:c r="L131" s="2"/>
-    </x:row>
-    <x:row r="132" ht="26" customHeight="1">
-      <x:c r="A132" s="2"/>
-      <x:c r="B132" s="2"/>
-      <x:c r="C132" s="2"/>
-      <x:c r="D132" s="2"/>
-      <x:c r="E132" s="2"/>
-      <x:c r="F132" s="2"/>
-      <x:c r="G132" s="2"/>
-      <x:c r="H132" s="2"/>
-      <x:c r="I132" s="2"/>
-      <x:c r="J132" s="2"/>
-      <x:c r="K132" s="2"/>
-      <x:c r="L132" s="2"/>
-    </x:row>
-    <x:row r="133" ht="26" customHeight="1">
-      <x:c r="A133" s="2"/>
-      <x:c r="B133" s="2"/>
-      <x:c r="C133" s="2"/>
-      <x:c r="D133" s="2"/>
-      <x:c r="E133" s="2"/>
-      <x:c r="F133" s="2"/>
-      <x:c r="G133" s="2"/>
-      <x:c r="H133" s="2"/>
-      <x:c r="I133" s="2"/>
-      <x:c r="J133" s="2"/>
-      <x:c r="K133" s="2"/>
-      <x:c r="L133" s="2"/>
-    </x:row>
-    <x:row r="134" ht="26" customHeight="1">
-      <x:c r="A134" s="2"/>
-      <x:c r="B134" s="2"/>
-      <x:c r="C134" s="2"/>
-      <x:c r="D134" s="2"/>
-      <x:c r="E134" s="2"/>
-      <x:c r="F134" s="2"/>
-      <x:c r="G134" s="2"/>
-      <x:c r="H134" s="2"/>
-      <x:c r="I134" s="2"/>
-      <x:c r="J134" s="2"/>
-      <x:c r="K134" s="2"/>
-      <x:c r="L134" s="2"/>
-    </x:row>
-    <x:row r="135" ht="26" customHeight="1">
-      <x:c r="A135" s="2"/>
-      <x:c r="B135" s="2"/>
-      <x:c r="C135" s="2"/>
-      <x:c r="D135" s="2"/>
-      <x:c r="E135" s="2"/>
-      <x:c r="F135" s="2"/>
-      <x:c r="G135" s="2"/>
-      <x:c r="H135" s="2"/>
-      <x:c r="I135" s="2"/>
-      <x:c r="J135" s="2"/>
-      <x:c r="K135" s="2"/>
-      <x:c r="L135" s="2"/>
-    </x:row>
-    <x:row r="136" ht="26" customHeight="1">
-      <x:c r="A136" s="2"/>
-      <x:c r="B136" s="2"/>
-      <x:c r="C136" s="2"/>
-      <x:c r="D136" s="2"/>
-      <x:c r="E136" s="2"/>
-      <x:c r="F136" s="2"/>
-      <x:c r="G136" s="2"/>
-      <x:c r="H136" s="2"/>
-      <x:c r="I136" s="2"/>
-      <x:c r="J136" s="2"/>
-      <x:c r="K136" s="2"/>
-      <x:c r="L136" s="2"/>
-    </x:row>
-    <x:row r="137" ht="26" customHeight="1">
-      <x:c r="A137" s="2"/>
-      <x:c r="B137" s="2"/>
-      <x:c r="C137" s="2"/>
-      <x:c r="D137" s="2"/>
-      <x:c r="E137" s="2"/>
-      <x:c r="F137" s="2"/>
-      <x:c r="G137" s="2"/>
-      <x:c r="H137" s="2"/>
-      <x:c r="I137" s="2"/>
-      <x:c r="J137" s="2"/>
-      <x:c r="K137" s="2"/>
-      <x:c r="L137" s="2"/>
-    </x:row>
-    <x:row r="138" ht="26" customHeight="1">
-      <x:c r="A138" s="2"/>
-      <x:c r="B138" s="2"/>
-      <x:c r="C138" s="2"/>
-      <x:c r="D138" s="2"/>
-      <x:c r="E138" s="2"/>
-      <x:c r="F138" s="2"/>
-      <x:c r="G138" s="2"/>
-      <x:c r="H138" s="2"/>
-      <x:c r="I138" s="2"/>
-      <x:c r="J138" s="2"/>
-      <x:c r="K138" s="2"/>
-      <x:c r="L138" s="2"/>
-    </x:row>
-    <x:row r="139" ht="26" customHeight="1">
-      <x:c r="A139" s="2"/>
-      <x:c r="B139" s="2"/>
-      <x:c r="C139" s="2"/>
-      <x:c r="D139" s="2"/>
-      <x:c r="E139" s="2"/>
-      <x:c r="F139" s="2"/>
-      <x:c r="G139" s="2"/>
-      <x:c r="H139" s="2"/>
-      <x:c r="I139" s="2"/>
-      <x:c r="J139" s="2"/>
-      <x:c r="K139" s="2"/>
-      <x:c r="L139" s="2"/>
-    </x:row>
-    <x:row r="140" ht="26" customHeight="1">
-      <x:c r="A140" s="2"/>
-      <x:c r="B140" s="2"/>
-      <x:c r="C140" s="2"/>
-      <x:c r="D140" s="2"/>
-      <x:c r="E140" s="2"/>
-      <x:c r="F140" s="2"/>
-      <x:c r="G140" s="2"/>
-      <x:c r="H140" s="2"/>
-      <x:c r="I140" s="2"/>
-      <x:c r="J140" s="2"/>
-      <x:c r="K140" s="2"/>
-      <x:c r="L140" s="2"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="C3:L3"/>
-    <x:mergeCell ref="K8:L8"/>
-    <x:mergeCell ref="K10:L10"/>
-    <x:mergeCell ref="K11:L12"/>
-    <x:mergeCell ref="C13:L13"/>
-    <x:mergeCell ref="I25:L25"/>
-    <x:mergeCell ref="J23:L23"/>
-    <x:mergeCell ref="G24:H24"/>
-    <x:mergeCell ref="D32:E33"/>
-    <x:mergeCell ref="D31:E31"/>
-    <x:mergeCell ref="D36:E36"/>
-    <x:mergeCell ref="D37:E37"/>
-    <x:mergeCell ref="D38:E38"/>
-    <x:mergeCell ref="D39:E40"/>
-    <x:mergeCell ref="J39:L40"/>
-    <x:mergeCell ref="J24:L24"/>
-    <x:mergeCell ref="J41:L41"/>
-  </x:mergeCells>
-  <x:conditionalFormatting sqref="D23:D23">
-    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不可达"/>
-    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="无效"/>
-    <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="缺少"/>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J24:J24">
-    <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="缺少"/>
-  </x:conditionalFormatting>
-  <x:dataValidations count="13">
-    <x:dataValidation type="list" sqref="D7">
-      <x:formula1>'Quote参数'!$E$9:$E$62</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="D8">
-      <x:formula1>0</x:formula1>
-      <x:formula2>0.99</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="J7">
-      <x:formula1>0</x:formula1>
-      <x:formula2>0.1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" operator="between" sqref="J8">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="greaterThan" showErrorMessage="1" errorTitle="地址参数无效" error="输入非负整数；内盘套数至少为 1。" sqref="G7">
-      <x:formula1>0</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="greaterThan" showErrorMessage="1" errorTitle="地址参数无效" error="输入非负整数；内盘套数至少为 1。" sqref="G8">
-      <x:formula1>-1</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="greaterThan" showErrorMessage="1" errorTitle="地址参数无效" error="输入非负整数；内盘套数至少为 1。" sqref="G9">
-      <x:formula1>-1</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="greaterThan" showErrorMessage="1" errorTitle="地址参数无效" error="输入非负整数；内盘套数至少为 1。" sqref="G10">
-      <x:formula1>-1</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="between" showErrorMessage="1" errorTitle="参数无效" error="Gas 与资金预留不能为负数。" sqref="D10">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1e+307</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" errorStyle="stop" operator="between" showErrorMessage="1" errorTitle="参数无效" error="Gas 与资金预留不能为负数。" sqref="G11">
-      <x:formula1>0</x:formula1>
-      <x:formula2>1e+307</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThan" sqref="D9">
-      <x:formula1>0</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="J9">
-      <x:formula1>"是,否"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="J10">
-      <x:formula1>"是,否"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" showOutlineSymbols="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="2" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="2" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="21" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="25" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="21" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="17" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="4" t="str">
+        <v>Pons V2 控筹模型</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="5" t="str">
+        <v>蓝色格可编辑。Quote / USDT 资金不含 Gas，Gas 单独以 ETH 计价。</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" ht="6" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="8" t="str">
+        <v>一、可编辑参数</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="48" t="str">
+        <v>交易参数</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="48" t="str">
+        <v>地址与 Gas</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="48" t="str">
+        <v>平台设置</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="35" t="str">
+        <v>Quote</v>
+      </c>
+      <c r="D7" s="51" t="str">
+        <v>SLV</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="35" t="str">
+        <v>内盘套数</v>
+      </c>
+      <c r="G7" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="35" t="str">
+        <v>Creator Tax</v>
+      </c>
+      <c r="J7" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="35" t="str">
+        <v>目标控筹率</v>
+      </c>
+      <c r="D8" s="53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E8" s="35" t="str">
+        <v>预算沿用 +1%</v>
+      </c>
+      <c r="F8" s="35" t="str">
+        <v>内盘地址 / 套</v>
+      </c>
+      <c r="G8" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="35" t="str">
+        <v>滑点假设</v>
+      </c>
+      <c r="J8" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="35" t="str">
+        <v>现有预算未计滑点</v>
+      </c>
+      <c r="L8" s="35"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="35" t="str">
+        <v>手动价格 / USDT</v>
+      </c>
+      <c r="D9" s="54"/>
+      <c r="E9" s="35" t="str">
+        <v>留空用日更价</v>
+      </c>
+      <c r="F9" s="35" t="str">
+        <v>外盘地址数</v>
+      </c>
+      <c r="G9" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="35" t="str">
+        <v>Snipe Tax 豁免</v>
+      </c>
+      <c r="J9" s="51" t="str">
+        <v>是</v>
+      </c>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="35" t="str">
+        <v>Holder 地址数</v>
+      </c>
+      <c r="G10" s="51" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="35" t="str">
+        <v>Buyback enabled</v>
+      </c>
+      <c r="J10" s="51" t="str">
+        <v>否</v>
+      </c>
+      <c r="K10" s="35" t="str">
+        <v>不抵扣回购收益</v>
+      </c>
+      <c r="L10" s="35"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="35" t="str">
+        <v>单地址 Gas / ETH</v>
+      </c>
+      <c r="G11" s="54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="35" t="str">
+        <v>Creator recipient</v>
+      </c>
+      <c r="J11" s="52"/>
+      <c r="K11" s="35" t="str">
+        <v>仅记录收款地址，不抵扣分红收益</v>
+      </c>
+      <c r="L11" s="35"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="35" t="str">
+        <v>资金预留 / Quote</v>
+      </c>
+      <c r="G12" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="55" t="str">
+        <v>手动价格只用于 USDT 换算，不改变 Quote 控筹预算。清空覆盖格后恢复自动取价。</v>
+      </c>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+    </row>
+    <row r="14" ht="6" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" ht="6" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" ht="6" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="8" t="str">
+        <v>二、测算结果</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="35" t="str">
+        <v>建议总资金 / Quote</v>
+      </c>
+      <c r="D18" s="74" t="n">
+        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($D$21="","",SUM($D$21,$G$21,$J$21,$D$22)))</f>
+        <v>15773.425525779472</v>
+      </c>
+      <c r="E18" s="62" t="str">
+        <f>$D$7</f>
+        <v>SLV</v>
+      </c>
+      <c r="F18" s="35" t="str">
+        <v>折合 USDT（不含 Gas）</v>
+      </c>
+      <c r="G18" s="74" t="str">
+        <f>IF(OR($D$18="",$D$24=""),"",$D$18*$D$24)</f>
+      </c>
+      <c r="H18" s="62" t="str">
+        <v>USDT</v>
+      </c>
+      <c r="I18" s="35" t="str">
+        <v>Gas 储备 / ETH</v>
+      </c>
+      <c r="J18" s="74" t="n">
+        <f>$G$22*MAX(0,$G$11)</f>
+        <v>0.61</v>
+      </c>
+      <c r="K18" s="62" t="str">
+        <v>ETH</v>
+      </c>
+      <c r="L18" s="62"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="57" t="str">
+        <v>Quote 资金构成：预算控筹率理论资金 + 额外内盘资金 + 资金预留 + 洗筹损耗</v>
+      </c>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+    </row>
+    <row r="20" ht="6" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="35" t="str">
+        <f>"预算 "&amp;TEXT($J$22,"0%")&amp;" 理论资金 / Quote"</f>
+        <v>预算 91% 理论资金 / Quote</v>
+      </c>
+      <c r="D21" s="60" t="n">
+        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$35="","",$J$31+$J$35))</f>
+        <v>5520.084846424523</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="35" t="str">
+        <v>额外内盘资金 / Quote</v>
+      </c>
+      <c r="G21" s="60" t="n">
+        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$31="","",$J$31*MAX(0,$G$7-1)))</f>
+        <v>174.54190618125045</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="35" t="str">
+        <v>洗筹损耗 / Quote</v>
+      </c>
+      <c r="J21" s="60" t="n">
+        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$36="","",$J$36*($G$32+$J$7)*2))</f>
+        <v>10073.7987731737</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="35" t="str">
+        <v>资金预留 / Quote</v>
+      </c>
+      <c r="D22" s="60" t="n">
+        <f>$G$12</f>
+        <v>5</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="35" t="str">
+        <v>地址总数</v>
+      </c>
+      <c r="G22" s="64" t="n">
+        <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
+        <v>122</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="35" t="str">
+        <v>预算使用控筹率</v>
+      </c>
+      <c r="J22" s="59" t="n">
+        <f>$D$8+1%</f>
+        <v>0.91</v>
+      </c>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="35" t="str">
+        <v>目标是否可达</v>
+      </c>
+      <c r="D23" s="66" t="str">
+        <f>IF($J$41&lt;&gt;"参数有效",$J$41,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$43),"Creator Tax无效",IF($J$22&gt;=$G$23,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</f>
+        <v>可达</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="35" t="str">
+        <v>当前控筹上限</v>
+      </c>
+      <c r="G23" s="63" t="n">
+        <f>MIN(1-$G$41/$D$35,$G$33+(1-$G$32-$J$7)*$G$38/$D$35)</f>
+        <v>0.916326530612245</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="35" t="str">
+        <v>资金口径</v>
+      </c>
+      <c r="J23" s="60" t="str">
+        <v>Quote 预算 + 单独 Gas</v>
+      </c>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="35" t="str">
+        <v>使用价格 / USDT</v>
+      </c>
+      <c r="D24" s="60" t="str">
+        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="35" t="str">
+        <v>行情时间 / UTC</v>
+      </c>
+      <c r="G24" s="65" t="n">
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
+        <v>46283.229019363425</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="35" t="str">
+        <v>价格状态</v>
+      </c>
+      <c r="J24" s="60" t="str">
+        <f>IF($D$9&lt;&gt;"",IF($D$24="","手动价格无效","手动价格"),IF($D$24="","缺少价格","每日行情"))</f>
+        <v>缺少价格</v>
+      </c>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="35" t="str">
+        <v>价格采用方式</v>
+      </c>
+      <c r="D25" s="60" t="str">
+        <f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</f>
+        <v>每日行情</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="str">
+        <v>价格缺失时 USDT 结果留空</v>
+      </c>
+      <c r="J25" s="60"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="35" t="str">
+        <v>内盘基础手续费</v>
+      </c>
+      <c r="D26" s="59" t="n">
+        <f>$G$31</f>
+        <v>0.01</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="35" t="str">
+        <v>外盘 Hook 手续费</v>
+      </c>
+      <c r="G26" s="59" t="n">
+        <f>$G$32</f>
+        <v>0.01</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="35" t="str">
+        <v>洗筹双边总费率</v>
+      </c>
+      <c r="J26" s="59" t="n">
+        <f>SUM(G27,J27)</f>
+        <v>0.02</v>
+      </c>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="35" t="str">
+        <v>内盘买入含税费率</v>
+      </c>
+      <c r="D27" s="59" t="n">
+        <f>$G$31+$J$7</f>
+        <v>0.01</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="35" t="str">
+        <v>外盘买入含税费率</v>
+      </c>
+      <c r="G27" s="59" t="n">
+        <f>$G$32+$J$7</f>
+        <v>0.01</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="35" t="str">
+        <v>外盘卖出含税费率</v>
+      </c>
+      <c r="J27" s="59" t="n">
+        <f>$G$32+$J$7</f>
+        <v>0.01</v>
+      </c>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="35" t="str">
+        <v>沉没成本 / Quote</v>
+      </c>
+      <c r="D28" s="60" t="n">
+        <f>E88</f>
+        <v>38.399219359875104</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="35" t="str">
+        <v>一套内盘打满 / Quote</v>
+      </c>
+      <c r="G28" s="60" t="n">
+        <f>$J$31</f>
+        <v>174.54190618125045</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="58" t="str">
+        <v>费率为预算加总口径；双边合计用于 FDV 洗筹预算。沉没成本与一套打满仅作参考，不重复计入总额。</v>
+      </c>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" collapsed="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="8" t="str">
+        <v>三、模型信息与计算口径（默认折叠，点左侧 + 展开）</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="48" t="str">
+        <v>Quote 信息</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="48" t="str">
+        <v>协议与曲线参数</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="48" t="str">
+        <v>预算中间计算</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="35" t="str">
+        <v>Quote 名称</v>
+      </c>
+      <c r="D31" s="66" t="str">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</f>
+        <v>iShares Silver Trust</v>
+      </c>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35" t="str">
+        <v>内盘基础费</v>
+      </c>
+      <c r="G31" s="63" t="n">
+        <f>1%</f>
+        <v>0.01</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="35" t="str">
+        <v>一套内盘打满 / Quote</v>
+      </c>
+      <c r="J31" s="60" t="n">
+        <f>IF(1-$G$31-$J$7&gt;0,$G$34/(1-$G$31-$J$7),"")</f>
+        <v>174.54190618125045</v>
+      </c>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="35" t="str">
+        <v>Quote 合约</v>
+      </c>
+      <c r="D32" s="69" t="str">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</f>
+        <v>​0x411efb0e7f985935daec3d4c3ebaea0d0ad7d89f</v>
+      </c>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35" t="str">
+        <v>外盘 Hook 费</v>
+      </c>
+      <c r="G32" s="63" t="n">
+        <f>1%</f>
+        <v>0.01</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="35" t="str">
+        <v>目标+1% Pool TOKEN</v>
+      </c>
+      <c r="J32" s="71" t="n">
+        <f>IF($J$22&lt;$G$23,$D$35*(1-$J$22)-$G$41,"")</f>
+        <v>8367346.938775495</v>
+      </c>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35" t="str">
+        <v>毕业控筹率</v>
+      </c>
+      <c r="G33" s="63" t="n">
+        <f>$G$34/($G$36+$G$34)</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="H33" s="2"/>
+      <c r="I33" s="35" t="str">
+        <v>目标+1% Pool Quote</v>
+      </c>
+      <c r="J33" s="60" t="n">
+        <f>IF($J$32="","",$G$40/$J$32)</f>
+        <v>4214.548466327764</v>
+      </c>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="35" t="str">
+        <v>Decimals</v>
+      </c>
+      <c r="D34" s="67" t="n">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,4,FALSE)</f>
+        <v>18</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="35" t="str">
+        <v>毕业真实 Quote</v>
+      </c>
+      <c r="G34" s="60" t="n">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</f>
+        <v>172.79648711943796</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="35" t="str">
+        <v>外盘净增加 / Quote</v>
+      </c>
+      <c r="J34" s="60" t="n">
+        <f>IF($J$33="","",MAX(0,$J$33-$G$34))</f>
+        <v>4041.751979208326</v>
+      </c>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="35" t="str">
+        <v>总供应量</v>
+      </c>
+      <c r="D35" s="64" t="n">
+        <f>1000000000</f>
+        <v>1000000000</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="35" t="str">
+        <v>内盘初始 TOKEN</v>
+      </c>
+      <c r="G35" s="71" t="n">
+        <f>$D$35</f>
+        <v>1000000000</v>
+      </c>
+      <c r="H35" s="2"/>
+      <c r="I35" s="35" t="str">
+        <v>外盘含费投入 / Quote</v>
+      </c>
+      <c r="J35" s="60" t="n">
+        <f>IF($J$32="","",$G$40/($G$38-MAX(0,($J$22-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>5345.542940243272</v>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="35" t="str">
+        <v>协议参数证据</v>
+      </c>
+      <c r="D36" s="72" t="n">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</f>
+        <v>54430299</v>
+      </c>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35" t="str">
+        <v>phantom Quote</v>
+      </c>
+      <c r="G36" s="60" t="n">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</f>
+        <v>69.11859484777517</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="35" t="str">
+        <v>目标+1% FDV / Quote</v>
+      </c>
+      <c r="J36" s="60" t="n">
+        <f>IF($J$33="","",$J$33/$J$32*$D$35)</f>
+        <v>503689.93865868496</v>
+      </c>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="35" t="str">
+        <v>外盘机制</v>
+      </c>
+      <c r="D37" s="66" t="str">
+        <v>Uniswap V4 / exact-input</v>
+      </c>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35" t="str">
+        <v>内盘 k</v>
+      </c>
+      <c r="G37" s="68" t="n">
+        <f>$G$36*$D$35</f>
+        <v>69118594847.77518</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="35" t="str">
+        <v>洗筹单边费率</v>
+      </c>
+      <c r="J37" s="63" t="n">
+        <f>$G$32+$J$7</f>
+        <v>0.01</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="35" t="str">
+        <v>费用方向</v>
+      </c>
+      <c r="D38" s="66" t="str">
+        <v>Hook + Creator Tax 从 Meme 输出扣除</v>
+      </c>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35" t="str">
+        <v>外盘初始 TOKEN</v>
+      </c>
+      <c r="G38" s="71" t="n">
+        <f>$D$35*$G$36*$G$34/($G$36+$G$34)^2</f>
+        <v>204081632.65306124</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="35" t="str">
+        <v>预算缓冲</v>
+      </c>
+      <c r="J38" s="59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="35" t="str">
+        <v>洗筹口径</v>
+      </c>
+      <c r="D39" s="66" t="str">
+        <v>目标+1% FDV ×（Hook + Creator Tax）×2</v>
+      </c>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35" t="str">
+        <v>外盘初始 Quote</v>
+      </c>
+      <c r="G39" s="60" t="n">
+        <f>$G$34</f>
+        <v>172.79648711943796</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="35" t="str">
+        <v>分红与回购口径</v>
+      </c>
+      <c r="J39" s="73" t="str">
+        <v>不抵扣分红 / 回购收益</v>
+      </c>
+      <c r="K39" s="35"/>
+      <c r="L39" s="35"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35" t="str">
+        <v>外盘 k</v>
+      </c>
+      <c r="G40" s="68" t="n">
+        <f>$G$38*$G$34</f>
+        <v>35264589208.04857</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="66"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
+    </row>
+    <row r="41" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="35" t="str">
+        <v>Locker TOKEN</v>
+      </c>
+      <c r="G41" s="71" t="n">
+        <f>$D$35*$G$36^2/($G$36+$G$34)^2</f>
+        <v>81632653.06122448</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="35" t="str">
+        <v>输入检查</v>
+      </c>
+      <c r="J41" s="66" t="str">
+        <f>IF(COUNT($D$8,$G$7:$G$12,$J$7:$J$8)&lt;&gt;9,"缺少或非数值参数",IF(OR($G$7&lt;1,$G$8&lt;0,$G$9&lt;0,$G$10&lt;0,$G$11&lt;0,$G$12&lt;0,$G$7&lt;&gt;INT($G$7),$G$8&lt;&gt;INT($G$8),$G$9&lt;&gt;INT($G$9),$G$10&lt;&gt;INT($G$10)),"地址/Gas/预留参数无效",IF(OR($J$8&lt;0,$J$8&gt;1,AND($J$9&lt;&gt;"是",$J$9&lt;&gt;"否"),AND($J$10&lt;&gt;"是",$J$10&lt;&gt;"否")),"平台设置无效","参数有效")))</f>
+        <v>参数有效</v>
+      </c>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+    </row>
+    <row r="42" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="35" t="str">
+        <v>Snipe 窗口</v>
+      </c>
+      <c r="G42" s="73" t="str">
+        <v>3 秒；默认豁免或避开</v>
+      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="60"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="35" t="str">
+        <v>Creator Tax 上限</v>
+      </c>
+      <c r="G43" s="63" t="n">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="60"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+    </row>
+    <row r="46" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="8" t="str">
+        <v>内盘曲线</v>
+      </c>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="77" t="str">
+        <v>控筹率</v>
+      </c>
+      <c r="D48" s="77" t="str">
+        <v>pooled TOKEN</v>
+      </c>
+      <c r="E48" s="77" t="str">
+        <v>pooled Quote</v>
+      </c>
+      <c r="F48" s="77" t="str">
+        <v>价格 / Quote</v>
+      </c>
+      <c r="G48" s="77" t="str">
+        <v>价格 / USDT</v>
+      </c>
+      <c r="H48" s="77" t="str">
+        <v>市值 / Quote</v>
+      </c>
+      <c r="I48" s="77" t="str">
+        <v>市值 / USDT</v>
+      </c>
+      <c r="J48" s="77" t="str">
+        <v>区间净投入
+/ Quote</v>
+      </c>
+      <c r="K48" s="77" t="str">
+        <v>区间含费
+/ Quote</v>
+      </c>
+      <c r="L48" s="77" t="str">
+        <v>理论累计所需
+/ Quote</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="81" t="n">
+        <f>$D$35*(1-C49)</f>
+        <v>1000000000</v>
+      </c>
+      <c r="E49" s="26" t="n">
+        <f>$G$37/D49</f>
+        <v>69.11859484777517</v>
+      </c>
+      <c r="F49" s="84" t="n">
+        <f>IF(OR(D49="",E49=""),"",E49/D49)</f>
+        <v>6.911859484777517e-8</v>
+      </c>
+      <c r="G49" s="84" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F49))),"",F49*$D$24)</f>
+      </c>
+      <c r="H49" s="26" t="n">
+        <f>IF(NOT(ISNUMBER(F49)),"",F49*$D$35)</f>
+        <v>69.11859484777517</v>
+      </c>
+      <c r="I49" s="26" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H49))),"",H49*$D$24)</f>
+      </c>
+      <c r="J49" s="26" t="n">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="26" t="n">
+        <f>J49/(1-$G$31-$J$7)</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="90" t="n">
+        <f>SUM($K$49:K49)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D50" s="82" t="n">
+        <f>$D$35*(1-C50)</f>
+        <v>900000000</v>
+      </c>
+      <c r="E50" s="27" t="n">
+        <f>$G$37/D50</f>
+        <v>76.7984387197502</v>
+      </c>
+      <c r="F50" s="85" t="n">
+        <f>IF(OR(D50="",E50=""),"",E50/D50)</f>
+        <v>8.533159857750022e-8</v>
+      </c>
+      <c r="G50" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F50))),"",F50*$D$24)</f>
+      </c>
+      <c r="H50" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F50)),"",F50*$D$35)</f>
+        <v>85.33159857750022</v>
+      </c>
+      <c r="I50" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H50))),"",H50*$D$24)</f>
+      </c>
+      <c r="J50" s="27" t="n">
+        <f>E50-E49</f>
+        <v>7.679843871975024</v>
+      </c>
+      <c r="K50" s="27" t="n">
+        <f>J50/(1-$G$31-$J$7)</f>
+        <v>7.757418052500024</v>
+      </c>
+      <c r="L50" s="91" t="n">
+        <f>SUM($K$49:K50)</f>
+        <v>7.757418052500024</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D51" s="82" t="n">
+        <f>$D$35*(1-C51)</f>
+        <v>800000000</v>
+      </c>
+      <c r="E51" s="27" t="n">
+        <f>$G$37/D51</f>
+        <v>86.39824355971898</v>
+      </c>
+      <c r="F51" s="85" t="n">
+        <f>IF(OR(D51="",E51=""),"",E51/D51)</f>
+        <v>1.0799780444964873e-7</v>
+      </c>
+      <c r="G51" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F51))),"",F51*$D$24)</f>
+      </c>
+      <c r="H51" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F51)),"",F51*$D$35)</f>
+        <v>107.99780444964873</v>
+      </c>
+      <c r="I51" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H51))),"",H51*$D$24)</f>
+      </c>
+      <c r="J51" s="27" t="n">
+        <f>E51-E50</f>
+        <v>9.599804839968783</v>
+      </c>
+      <c r="K51" s="27" t="n">
+        <f>J51/(1-$G$31-$J$7)</f>
+        <v>9.696772565625034</v>
+      </c>
+      <c r="L51" s="91" t="n">
+        <f>SUM($K$49:K51)</f>
+        <v>17.454190618125057</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D52" s="82" t="n">
+        <f>$D$35*(1-C52)</f>
+        <v>700000000</v>
+      </c>
+      <c r="E52" s="27" t="n">
+        <f>$G$37/D52</f>
+        <v>98.74084978253596</v>
+      </c>
+      <c r="F52" s="85" t="n">
+        <f>IF(OR(D52="",E52=""),"",E52/D52)</f>
+        <v>1.4105835683219424e-7</v>
+      </c>
+      <c r="G52" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F52))),"",F52*$D$24)</f>
+      </c>
+      <c r="H52" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F52)),"",F52*$D$35)</f>
+        <v>141.05835683219425</v>
+      </c>
+      <c r="I52" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H52))),"",H52*$D$24)</f>
+      </c>
+      <c r="J52" s="27" t="n">
+        <f>E52-E51</f>
+        <v>12.342606222816983</v>
+      </c>
+      <c r="K52" s="27" t="n">
+        <f>J52/(1-$G$31-$J$7)</f>
+        <v>12.467279012946447</v>
+      </c>
+      <c r="L52" s="91" t="n">
+        <f>SUM($K$49:K52)</f>
+        <v>29.921469631071503</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D53" s="82" t="n">
+        <f>$D$35*(1-C53)</f>
+        <v>600000000</v>
+      </c>
+      <c r="E53" s="27" t="n">
+        <f>$G$37/D53</f>
+        <v>115.1976580796253</v>
+      </c>
+      <c r="F53" s="85" t="n">
+        <f>IF(OR(D53="",E53=""),"",E53/D53)</f>
+        <v>1.919960967993755e-7</v>
+      </c>
+      <c r="G53" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F53))),"",F53*$D$24)</f>
+      </c>
+      <c r="H53" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F53)),"",F53*$D$35)</f>
+        <v>191.99609679937552</v>
+      </c>
+      <c r="I53" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H53))),"",H53*$D$24)</f>
+      </c>
+      <c r="J53" s="27" t="n">
+        <f>E53-E52</f>
+        <v>16.45680829708934</v>
+      </c>
+      <c r="K53" s="27" t="n">
+        <f>J53/(1-$G$31-$J$7)</f>
+        <v>16.623038683928623</v>
+      </c>
+      <c r="L53" s="91" t="n">
+        <f>SUM($K$49:K53)</f>
+        <v>46.54450831500013</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D54" s="82" t="n">
+        <f>$D$35*(1-C54)</f>
+        <v>500000000</v>
+      </c>
+      <c r="E54" s="27" t="n">
+        <f>$G$37/D54</f>
+        <v>138.23718969555034</v>
+      </c>
+      <c r="F54" s="85" t="n">
+        <f>IF(OR(D54="",E54=""),"",E54/D54)</f>
+        <v>2.7647437939110067e-7</v>
+      </c>
+      <c r="G54" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F54))),"",F54*$D$24)</f>
+      </c>
+      <c r="H54" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F54)),"",F54*$D$35)</f>
+        <v>276.4743793911007</v>
+      </c>
+      <c r="I54" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H54))),"",H54*$D$24)</f>
+      </c>
+      <c r="J54" s="27" t="n">
+        <f>E54-E53</f>
+        <v>23.039531615925043</v>
+      </c>
+      <c r="K54" s="27" t="n">
+        <f>J54/(1-$G$31-$J$7)</f>
+        <v>23.272254157500043</v>
+      </c>
+      <c r="L54" s="91" t="n">
+        <f>SUM($K$49:K54)</f>
+        <v>69.81676247250017</v>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D55" s="82" t="n">
+        <f>$D$35*(1-C55)</f>
+        <v>400000000</v>
+      </c>
+      <c r="E55" s="27" t="n">
+        <f>$G$37/D55</f>
+        <v>172.79648711943796</v>
+      </c>
+      <c r="F55" s="85" t="n">
+        <f>IF(OR(D55="",E55=""),"",E55/D55)</f>
+        <v>4.319912177985949e-7</v>
+      </c>
+      <c r="G55" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F55))),"",F55*$D$24)</f>
+      </c>
+      <c r="H55" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F55)),"",F55*$D$35)</f>
+        <v>431.9912177985949</v>
+      </c>
+      <c r="I55" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H55))),"",H55*$D$24)</f>
+      </c>
+      <c r="J55" s="27" t="n">
+        <f>E55-E54</f>
+        <v>34.559297423887614</v>
+      </c>
+      <c r="K55" s="27" t="n">
+        <f>J55/(1-$G$31-$J$7)</f>
+        <v>34.908381236250115</v>
+      </c>
+      <c r="L55" s="91" t="n">
+        <f>SUM($K$49:K55)</f>
+        <v>104.7251437087503</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="79" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D56" s="82" t="n">
+        <f>$D$35*(1-C56)</f>
+        <v>300000000.00000006</v>
+      </c>
+      <c r="E56" s="27" t="n">
+        <f>$G$37/D56</f>
+        <v>230.39531615925054</v>
+      </c>
+      <c r="F56" s="85" t="n">
+        <f>IF(OR(D56="",E56=""),"",E56/D56)</f>
+        <v>7.679843871975016e-7</v>
+      </c>
+      <c r="G56" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F56))),"",F56*$D$24)</f>
+      </c>
+      <c r="H56" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F56)),"",F56*$D$35)</f>
+        <v>767.9843871975016</v>
+      </c>
+      <c r="I56" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H56))),"",H56*$D$24)</f>
+      </c>
+      <c r="J56" s="27" t="n">
+        <f>E56-E55</f>
+        <v>57.598829039812586</v>
+      </c>
+      <c r="K56" s="27" t="n">
+        <f>J56/(1-$G$31-$J$7)</f>
+        <v>58.18063539375009</v>
+      </c>
+      <c r="L56" s="91" t="n">
+        <f>SUM($K$49:K56)</f>
+        <v>162.9057791025004</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="93" t="n">
+        <f>$G$33</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="D57" s="94" t="n">
+        <f>$D$35*(1-C57)</f>
+        <v>285714285.7142857</v>
+      </c>
+      <c r="E57" s="95" t="n">
+        <f>$G$37/D57</f>
+        <v>241.91508196721315</v>
+      </c>
+      <c r="F57" s="96" t="n">
+        <f>IF(OR(D57="",E57=""),"",E57/D57)</f>
+        <v>8.467027868852461e-7</v>
+      </c>
+      <c r="G57" s="96" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F57))),"",F57*$D$24)</f>
+      </c>
+      <c r="H57" s="95" t="n">
+        <f>IF(NOT(ISNUMBER(F57)),"",F57*$D$35)</f>
+        <v>846.7027868852462</v>
+      </c>
+      <c r="I57" s="95" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H57))),"",H57*$D$24)</f>
+      </c>
+      <c r="J57" s="95" t="n">
+        <f>E57-E56</f>
+        <v>11.519765807962614</v>
+      </c>
+      <c r="K57" s="95" t="n">
+        <f>J57/(1-$G$31-$J$7)</f>
+        <v>11.636127078750116</v>
+      </c>
+      <c r="L57" s="92" t="n">
+        <f>SUM($K$49:K57)</f>
+        <v>174.5419061812505</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="8" t="str">
+        <v>外盘曲线</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="77" t="str">
+        <v>控筹率</v>
+      </c>
+      <c r="D61" s="77" t="str">
+        <v>pooled TOKEN</v>
+      </c>
+      <c r="E61" s="77" t="str">
+        <v>pooled Quote</v>
+      </c>
+      <c r="F61" s="77" t="str">
+        <v>价格 / Quote</v>
+      </c>
+      <c r="G61" s="77" t="str">
+        <v>价格 / USDT</v>
+      </c>
+      <c r="H61" s="77" t="str">
+        <v>市值 / Quote</v>
+      </c>
+      <c r="I61" s="77" t="str">
+        <v>市值 / USDT</v>
+      </c>
+      <c r="J61" s="77" t="str">
+        <v>外盘净投入
+/ Quote</v>
+      </c>
+      <c r="K61" s="77" t="str">
+        <v>外盘含费
+/ Quote</v>
+      </c>
+      <c r="L61" s="77" t="str">
+        <v>理论累计所需
+/ Quote</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="97" t="n">
+        <f>$G$33</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="D62" s="98" t="n">
+        <f>$G$38</f>
+        <v>204081632.65306124</v>
+      </c>
+      <c r="E62" s="99" t="n">
+        <f>$G$34</f>
+        <v>172.79648711943796</v>
+      </c>
+      <c r="F62" s="100" t="n">
+        <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
+        <v>8.467027868852459e-7</v>
+      </c>
+      <c r="G62" s="100" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F62))),"",F62*$D$24)</f>
+      </c>
+      <c r="H62" s="99" t="n">
+        <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$35)</f>
+        <v>846.7027868852459</v>
+      </c>
+      <c r="I62" s="99" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H62))),"",H62*$D$24)</f>
+      </c>
+      <c r="J62" s="99" t="n">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="K62" s="99" t="n">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="L62" s="90" t="n">
+        <f>$J$31</f>
+        <v>174.54190618125045</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="79" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D63" s="82" t="n">
+        <f>IF(C63&lt;$G$23,$D$35*(1-C63)-$G$41,"")</f>
+        <v>168367346.93877554</v>
+      </c>
+      <c r="E63" s="27" t="n">
+        <f>IF(D63="","",$G$40/D63)</f>
+        <v>209.45028741750056</v>
+      </c>
+      <c r="F63" s="85" t="n">
+        <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
+        <v>0.0000012440077676918213</v>
+      </c>
+      <c r="G63" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F63))),"",F63*$D$24)</f>
+      </c>
+      <c r="H63" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$35)</f>
+        <v>1244.0077676918213</v>
+      </c>
+      <c r="I63" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H63))),"",H63*$D$24)</f>
+      </c>
+      <c r="J63" s="27" t="n">
+        <f>IF(E63="","",MAX(0,E63-$G$34))</f>
+        <v>36.653800298062606</v>
+      </c>
+      <c r="K63" s="27" t="n">
+        <f>IF(D63="","",$G$40/($G$38-MAX(0,(C63-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>37.103540179020456</v>
+      </c>
+      <c r="L63" s="91" t="n">
+        <f>IF(K63="","",$J$31+K63)</f>
+        <v>211.6454463602709</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="79" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D64" s="82" t="n">
+        <f>IF(C64&lt;$G$23,$D$35*(1-C64)-$G$41,"")</f>
+        <v>118367346.9387755</v>
+      </c>
+      <c r="E64" s="27" t="n">
+        <f>IF(D64="","",$G$40/D64)</f>
+        <v>297.9249777921345</v>
+      </c>
+      <c r="F64" s="85" t="n">
+        <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
+        <v>0.0000025169523985887227</v>
+      </c>
+      <c r="G64" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F64))),"",F64*$D$24)</f>
+      </c>
+      <c r="H64" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$35)</f>
+        <v>2516.9523985887226</v>
+      </c>
+      <c r="I64" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H64))),"",H64*$D$24)</f>
+      </c>
+      <c r="J64" s="27" t="n">
+        <f>IF(E64="","",MAX(0,E64-$G$34))</f>
+        <v>125.12849067269653</v>
+      </c>
+      <c r="K64" s="27" t="n">
+        <f>IF(D64="","",$G$40/($G$38-MAX(0,(C64-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>127.32372735116493</v>
+      </c>
+      <c r="L64" s="91" t="n">
+        <f>IF(K64="","",$J$31+K64)</f>
+        <v>301.86563353241536</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="79" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D65" s="82" t="n">
+        <f>IF(C65&lt;$G$23,$D$35*(1-C65)-$G$41,"")</f>
+        <v>98367346.93877558</v>
+      </c>
+      <c r="E65" s="27" t="n">
+        <f>IF(D65="","",$G$40/D65)</f>
+        <v>358.4989359324437</v>
+      </c>
+      <c r="F65" s="85" t="n">
+        <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
+        <v>0.000003644491257404508</v>
+      </c>
+      <c r="G65" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F65))),"",F65*$D$24)</f>
+      </c>
+      <c r="H65" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$35)</f>
+        <v>3644.4912574045084</v>
+      </c>
+      <c r="I65" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H65))),"",H65*$D$24)</f>
+      </c>
+      <c r="J65" s="27" t="n">
+        <f>IF(E65="","",MAX(0,E65-$G$34))</f>
+        <v>185.70244881300576</v>
+      </c>
+      <c r="K65" s="27" t="n">
+        <f>IF(D65="","",$G$40/($G$38-MAX(0,(C65-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>189.63682272853552</v>
+      </c>
+      <c r="L65" s="91" t="n">
+        <f>IF(K65="","",$J$31+K65)</f>
+        <v>364.17872890978595</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="79" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D66" s="82" t="n">
+        <f>IF(C66&lt;$G$23,$D$35*(1-C66)-$G$41,"")</f>
+        <v>78367346.93877555</v>
+      </c>
+      <c r="E66" s="27" t="n">
+        <f>IF(D66="","",$G$40/D66)</f>
+        <v>449.99085187353614</v>
+      </c>
+      <c r="F66" s="85" t="n">
+        <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
+        <v>0.000005742070766094599</v>
+      </c>
+      <c r="G66" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F66))),"",F66*$D$24)</f>
+      </c>
+      <c r="H66" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$35)</f>
+        <v>5742.070766094599</v>
+      </c>
+      <c r="I66" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H66))),"",H66*$D$24)</f>
+      </c>
+      <c r="J66" s="27" t="n">
+        <f>IF(E66="","",MAX(0,E66-$G$34))</f>
+        <v>277.19436475409816</v>
+      </c>
+      <c r="K66" s="27" t="n">
+        <f>IF(D66="","",$G$40/($G$38-MAX(0,(C66-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>284.6059787849564</v>
+      </c>
+      <c r="L66" s="91" t="n">
+        <f>IF(K66="","",$J$31+K66)</f>
+        <v>459.14788496620685</v>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="79" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D67" s="82" t="n">
+        <f>IF(C67&lt;$G$23,$D$35*(1-C67)-$G$41,"")</f>
+        <v>58367346.938775524</v>
+      </c>
+      <c r="E67" s="27" t="n">
+        <f>IF(D67="","",$G$40/D67)</f>
+        <v>604.1835213966361</v>
+      </c>
+      <c r="F67" s="85" t="n">
+        <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
+        <v>0.00001035139599595635</v>
+      </c>
+      <c r="G67" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F67))),"",F67*$D$24)</f>
+      </c>
+      <c r="H67" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$35)</f>
+        <v>10351.39599595635</v>
+      </c>
+      <c r="I67" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H67))),"",H67*$D$24)</f>
+      </c>
+      <c r="J67" s="27" t="n">
+        <f>IF(E67="","",MAX(0,E67-$G$34))</f>
+        <v>431.38703427719815</v>
+      </c>
+      <c r="K67" s="27" t="n">
+        <f>IF(D67="","",$G$40/($G$38-MAX(0,(C67-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>447.0169992872412</v>
+      </c>
+      <c r="L67" s="91" t="n">
+        <f>IF(K67="","",$J$31+K67)</f>
+        <v>621.5589054684917</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="79" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D68" s="82" t="n">
+        <f>IF(C68&lt;$G$23,$D$35*(1-C68)-$G$41,"")</f>
+        <v>38367346.938775524</v>
+      </c>
+      <c r="E68" s="27" t="n">
+        <f>IF(D68="","",$G$40/D68)</f>
+        <v>919.1302506353081</v>
+      </c>
+      <c r="F68" s="85" t="n">
+        <f>IF(OR(D68="",E68=""),"",E68/D68)</f>
+        <v>0.000023956054404856426</v>
+      </c>
+      <c r="G68" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F68))),"",F68*$D$24)</f>
+      </c>
+      <c r="H68" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F68)),"",F68*$D$35)</f>
+        <v>23956.054404856426</v>
+      </c>
+      <c r="I68" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H68))),"",H68*$D$24)</f>
+      </c>
+      <c r="J68" s="27" t="n">
+        <f>IF(E68="","",MAX(0,E68-$G$34))</f>
+        <v>746.3337635158701</v>
+      </c>
+      <c r="K68" s="27" t="n">
+        <f>IF(D68="","",$G$40/($G$38-MAX(0,(C68-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>788.2626266347389</v>
+      </c>
+      <c r="L68" s="91" t="n">
+        <f>IF(K68="","",$J$31+K68)</f>
+        <v>962.8045328159894</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="79" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D69" s="82" t="n">
+        <f>IF(C69&lt;$G$23,$D$35*(1-C69)-$G$41,"")</f>
+        <v>28367346.93877551</v>
+      </c>
+      <c r="E69" s="27" t="n">
+        <f>IF(D69="","",$G$40/D69)</f>
+        <v>1243.1401951038704</v>
+      </c>
+      <c r="F69" s="85" t="n">
+        <f>IF(OR(D69="",E69=""),"",E69/D69)</f>
+        <v>0.00004382292774107169</v>
+      </c>
+      <c r="G69" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F69))),"",F69*$D$24)</f>
+      </c>
+      <c r="H69" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F69)),"",F69*$D$35)</f>
+        <v>43822.92774107169</v>
+      </c>
+      <c r="I69" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H69))),"",H69*$D$24)</f>
+      </c>
+      <c r="J69" s="27" t="n">
+        <f>IF(E69="","",MAX(0,E69-$G$34))</f>
+        <v>1070.3437079844325</v>
+      </c>
+      <c r="K69" s="27" t="n">
+        <f>IF(D69="","",$G$40/($G$38-MAX(0,(C69-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>1153.31608844834</v>
+      </c>
+      <c r="L69" s="91" t="n">
+        <f>IF(K69="","",$J$31+K69)</f>
+        <v>1327.8579946295904</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D70" s="82" t="n">
+        <f>IF(C70&lt;$G$23,$D$35*(1-C70)-$G$41,"")</f>
+        <v>18367346.93877551</v>
+      </c>
+      <c r="E70" s="27" t="n">
+        <f>IF(D70="","",$G$40/D70)</f>
+        <v>1919.9609679937555</v>
+      </c>
+      <c r="F70" s="85" t="n">
+        <f>IF(OR(D70="",E70=""),"",E70/D70)</f>
+        <v>0.0001045312082574378</v>
+      </c>
+      <c r="G70" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F70))),"",F70*$D$24)</f>
+      </c>
+      <c r="H70" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F70)),"",F70*$D$35)</f>
+        <v>104531.2082574378</v>
+      </c>
+      <c r="I70" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H70))),"",H70*$D$24)</f>
+      </c>
+      <c r="J70" s="27" t="n">
+        <f>IF(E70="","",MAX(0,E70-$G$34))</f>
+        <v>1747.1644808743176</v>
+      </c>
+      <c r="K70" s="27" t="n">
+        <f>IF(D70="","",$G$40/($G$38-MAX(0,(C70-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>1965.5600409836077</v>
+      </c>
+      <c r="L70" s="91" t="n">
+        <f>IF(K70="","",$J$31+K70)</f>
+        <v>2140.1019471648583</v>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="79" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="D71" s="82" t="n">
+        <f>IF(C71&lt;$G$23,$D$35*(1-C71)-$G$41,"")</f>
+        <v>13367346.938775495</v>
+      </c>
+      <c r="E71" s="27" t="n">
+        <f>IF(D71="","",$G$40/D71)</f>
+        <v>2638.1143071669953</v>
+      </c>
+      <c r="F71" s="85" t="n">
+        <f>IF(OR(D71="",E71=""),"",E71/D71)</f>
+        <v>0.00019735511610867622</v>
+      </c>
+      <c r="G71" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F71))),"",F71*$D$24)</f>
+      </c>
+      <c r="H71" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F71)),"",F71*$D$35)</f>
+        <v>197355.11610867621</v>
+      </c>
+      <c r="I71" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H71))),"",H71*$D$24)</f>
+      </c>
+      <c r="J71" s="27" t="n">
+        <f>IF(E71="","",MAX(0,E71-$G$34))</f>
+        <v>2465.3178200475572</v>
+      </c>
+      <c r="K71" s="27" t="n">
+        <f>IF(D71="","",$G$40/($G$38-MAX(0,(C71-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>2909.51922906513</v>
+      </c>
+      <c r="L71" s="91" t="n">
+        <f>IF(K71="","",$J$31+K71)</f>
+        <v>3084.06113524638</v>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="79" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D72" s="82" t="n">
+        <f>IF(C72&lt;$G$23,$D$35*(1-C72)-$G$41,"")</f>
+        <v>8367346.938775495</v>
+      </c>
+      <c r="E72" s="27" t="n">
+        <f>IF(D72="","",$G$40/D72)</f>
+        <v>4214.548466327764</v>
+      </c>
+      <c r="F72" s="85" t="n">
+        <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
+        <v>0.0005036899386586849</v>
+      </c>
+      <c r="G72" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F72))),"",F72*$D$24)</f>
+      </c>
+      <c r="H72" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$35)</f>
+        <v>503689.93865868496</v>
+      </c>
+      <c r="I72" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H72))),"",H72*$D$24)</f>
+      </c>
+      <c r="J72" s="27" t="n">
+        <f>IF(E72="","",MAX(0,E72-$G$34))</f>
+        <v>4041.751979208326</v>
+      </c>
+      <c r="K72" s="27" t="n">
+        <f>IF(D72="","",$G$40/($G$38-MAX(0,(C72-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>5345.542940243272</v>
+      </c>
+      <c r="L72" s="91" t="n">
+        <f>IF(K72="","",$J$31+K72)</f>
+        <v>5520.084846424523</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="79" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="D73" s="82" t="n">
+        <f>IF(C73&lt;$G$23,$D$35*(1-C73)-$G$41,"")</f>
+        <v>3367346.9387754947</v>
+      </c>
+      <c r="E73" s="27" t="n">
+        <f>IF(D73="","",$G$40/D73)</f>
+        <v>10472.514370875078</v>
+      </c>
+      <c r="F73" s="85" t="n">
+        <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
+        <v>0.0031100194192295832</v>
+      </c>
+      <c r="G73" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F73))),"",F73*$D$24)</f>
+      </c>
+      <c r="H73" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$35)</f>
+        <v>3110019.4192295833</v>
+      </c>
+      <c r="I73" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H73))),"",H73*$D$24)</f>
+      </c>
+      <c r="J73" s="27" t="n">
+        <f>IF(E73="","",MAX(0,E73-$G$34))</f>
+        <v>10299.71788375564</v>
+      </c>
+      <c r="K73" s="27" t="n">
+        <f>IF(D73="","",$G$40/($G$38-MAX(0,(C73-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+        <v>26145.43770491818</v>
+      </c>
+      <c r="L73" s="91" t="n">
+        <f>IF(K73="","",$J$31+K73)</f>
+        <v>26319.97961109943</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="79" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="D74" s="82" t="str">
+        <f>IF(C74&lt;$G$23,$D$35*(1-C74)-$G$41,"")</f>
+      </c>
+      <c r="E74" s="27" t="str">
+        <f>IF(D74="","",$G$40/D74)</f>
+      </c>
+      <c r="F74" s="85" t="str">
+        <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
+      </c>
+      <c r="G74" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F74))),"",F74*$D$24)</f>
+      </c>
+      <c r="H74" s="27" t="str">
+        <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$35)</f>
+      </c>
+      <c r="I74" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H74))),"",H74*$D$24)</f>
+      </c>
+      <c r="J74" s="27" t="str">
+        <f>IF(E74="","",MAX(0,E74-$G$34))</f>
+      </c>
+      <c r="K74" s="27" t="str">
+        <f>IF(D74="","",$G$40/($G$38-MAX(0,(C74-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      </c>
+      <c r="L74" s="91" t="str">
+        <f>IF(K74="","",$J$31+K74)</f>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="80" t="n">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="D75" s="83" t="str">
+        <f>IF(C75&lt;$G$23,$D$35*(1-C75)-$G$41,"")</f>
+      </c>
+      <c r="E75" s="28" t="str">
+        <f>IF(D75="","",$G$40/D75)</f>
+      </c>
+      <c r="F75" s="86" t="str">
+        <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
+      </c>
+      <c r="G75" s="86" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F75))),"",F75*$D$24)</f>
+      </c>
+      <c r="H75" s="28" t="str">
+        <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$35)</f>
+      </c>
+      <c r="I75" s="28" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H75))),"",H75*$D$24)</f>
+      </c>
+      <c r="J75" s="28" t="str">
+        <f>IF(E75="","",MAX(0,E75-$G$34))</f>
+      </c>
+      <c r="K75" s="28" t="str">
+        <f>IF(D75="","",$G$40/($G$38-MAX(0,(C75-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      </c>
+      <c r="L75" s="92" t="str">
+        <f>IF(K75="","",$J$31+K75)</f>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="102" t="str">
+        <v>外盘回落参考</v>
+      </c>
+      <c r="D78" s="102"/>
+      <c r="E78" s="102"/>
+      <c r="F78" s="102"/>
+      <c r="G78" s="102"/>
+      <c r="H78" s="102"/>
+      <c r="I78" s="102"/>
+      <c r="J78" s="102"/>
+      <c r="K78" s="102"/>
+      <c r="L78" s="102"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="77" t="str">
+        <v>控筹率</v>
+      </c>
+      <c r="D79" s="77" t="str">
+        <v>pooled TOKEN</v>
+      </c>
+      <c r="E79" s="77" t="str">
+        <v>pooled Quote</v>
+      </c>
+      <c r="F79" s="77" t="str">
+        <v>价格 / Quote</v>
+      </c>
+      <c r="G79" s="77" t="str">
+        <v>价格 / USDT</v>
+      </c>
+      <c r="H79" s="77" t="str">
+        <v>市值 / Quote</v>
+      </c>
+      <c r="I79" s="77" t="str">
+        <v>市值 / USDT</v>
+      </c>
+      <c r="J79" s="77" t="str">
+        <v>较毕业点回撤</v>
+      </c>
+      <c r="K79" s="77" t="str"/>
+      <c r="L79" s="77" t="str"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="97" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="D80" s="98" t="n">
+        <f>$D$35*(1-C80)-$G$41</f>
+        <v>204081632.6530612</v>
+      </c>
+      <c r="E80" s="99" t="n">
+        <f>$G$40/D80</f>
+        <v>172.79648711943798</v>
+      </c>
+      <c r="F80" s="100" t="n">
+        <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
+        <v>8.467027868852462e-7</v>
+      </c>
+      <c r="G80" s="100" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F80))),"",F80*$D$24)</f>
+      </c>
+      <c r="H80" s="99" t="n">
+        <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$35)</f>
+        <v>846.7027868852463</v>
+      </c>
+      <c r="I80" s="99" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H80))),"",H80*$D$24)</f>
+      </c>
+      <c r="J80" s="97" t="n">
+        <f>IF($H$80&gt;0,1-H80/$H$80,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K80" s="99"/>
+      <c r="L80" s="99"/>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="79" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D81" s="82" t="n">
+        <f>$D$35*(1-C81)-$G$41</f>
+        <v>218367346.9387756</v>
+      </c>
+      <c r="E81" s="27" t="n">
+        <f>$G$40/D81</f>
+        <v>161.49204403685786</v>
+      </c>
+      <c r="F81" s="85" t="n">
+        <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
+        <v>7.395430054024329e-7</v>
+      </c>
+      <c r="G81" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F81))),"",F81*$D$24)</f>
+      </c>
+      <c r="H81" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$35)</f>
+        <v>739.5430054024329</v>
+      </c>
+      <c r="I81" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H81))),"",H81*$D$24)</f>
+      </c>
+      <c r="J81" s="79" t="n">
+        <f>IF($H$80&gt;0,1-H81/$H$80,0)</f>
+        <v>0.12656127172678933</v>
+      </c>
+      <c r="K81" s="27"/>
+      <c r="L81" s="27"/>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D82" s="82" t="n">
+        <f>$D$35*(1-C82)-$G$41</f>
+        <v>318367346.93877554</v>
+      </c>
+      <c r="E82" s="27" t="n">
+        <f>$G$40/D82</f>
+        <v>110.76697892271665</v>
+      </c>
+      <c r="F82" s="85" t="n">
+        <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
+        <v>3.479219209751997e-7</v>
+      </c>
+      <c r="G82" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F82))),"",F82*$D$24)</f>
+      </c>
+      <c r="H82" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$35)</f>
+        <v>347.9219209751997</v>
+      </c>
+      <c r="I82" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H82))),"",H82*$D$24)</f>
+      </c>
+      <c r="J82" s="79" t="n">
+        <f>IF($H$80&gt;0,1-H82/$H$80,0)</f>
+        <v>0.5890861275476661</v>
+      </c>
+      <c r="K82" s="27"/>
+      <c r="L82" s="27"/>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D83" s="82" t="n">
+        <f>$D$35*(1-C83)-$G$41</f>
+        <v>418367346.93877554</v>
+      </c>
+      <c r="E83" s="27" t="n">
+        <f>$G$40/D83</f>
+        <v>84.29096932655511</v>
+      </c>
+      <c r="F83" s="85" t="n">
+        <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
+        <v>2.0147597546347317e-7</v>
+      </c>
+      <c r="G83" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F83))),"",F83*$D$24)</f>
+      </c>
+      <c r="H83" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$35)</f>
+        <v>201.47597546347316</v>
+      </c>
+      <c r="I83" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H83))),"",H83*$D$24)</f>
+      </c>
+      <c r="J83" s="79" t="n">
+        <f>IF($H$80&gt;0,1-H83/$H$80,0)</f>
+        <v>0.7620464009518144</v>
+      </c>
+      <c r="K83" s="27"/>
+      <c r="L83" s="27"/>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D84" s="82" t="n">
+        <f>$D$35*(1-C84)-$G$41</f>
+        <v>518367346.93877554</v>
+      </c>
+      <c r="E84" s="27" t="n">
+        <f>$G$40/D84</f>
+        <v>68.03011303914882</v>
+      </c>
+      <c r="F84" s="85" t="n">
+        <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
+        <v>1.3123919444560203e-7</v>
+      </c>
+      <c r="G84" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F84))),"",F84*$D$24)</f>
+      </c>
+      <c r="H84" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$35)</f>
+        <v>131.23919444560204</v>
+      </c>
+      <c r="I84" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H84))),"",H84*$D$24)</f>
+      </c>
+      <c r="J84" s="79" t="n">
+        <f>IF($H$80&gt;0,1-H84/$H$80,0)</f>
+        <v>0.84499968999938</v>
+      </c>
+      <c r="K84" s="27"/>
+      <c r="L84" s="27"/>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D85" s="82" t="n">
+        <f>$D$35*(1-C85)-$G$41</f>
+        <v>618367346.9387755</v>
+      </c>
+      <c r="E85" s="27" t="n">
+        <f>$G$40/D85</f>
+        <v>57.028543603774914</v>
+      </c>
+      <c r="F85" s="85" t="n">
+        <f>IF(OR(D85="",E85=""),"",E85/D85)</f>
+        <v>9.222437744504854e-8</v>
+      </c>
+      <c r="G85" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F85))),"",F85*$D$24)</f>
+      </c>
+      <c r="H85" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F85)),"",F85*$D$35)</f>
+        <v>92.22437744504853</v>
+      </c>
+      <c r="I85" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H85))),"",H85*$D$24)</f>
+      </c>
+      <c r="J85" s="79" t="n">
+        <f>IF($H$80&gt;0,1-H85/$H$80,0)</f>
+        <v>0.8910782167325644</v>
+      </c>
+      <c r="K85" s="27"/>
+      <c r="L85" s="27"/>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D86" s="82" t="n">
+        <f>$D$35*(1-C86)-$G$41</f>
+        <v>718367346.9387755</v>
+      </c>
+      <c r="E86" s="27" t="n">
+        <f>$G$40/D86</f>
+        <v>49.089911113476695</v>
+      </c>
+      <c r="F86" s="85" t="n">
+        <f>IF(OR(D86="",E86=""),"",E86/D86)</f>
+        <v>6.833538762955562e-8</v>
+      </c>
+      <c r="G86" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F86))),"",F86*$D$24)</f>
+      </c>
+      <c r="H86" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F86)),"",F86*$D$35)</f>
+        <v>68.33538762955563</v>
+      </c>
+      <c r="I86" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H86))),"",H86*$D$24)</f>
+      </c>
+      <c r="J86" s="79" t="n">
+        <f>IF($H$80&gt;0,1-H86/$H$80,0)</f>
+        <v>0.9192923553719008</v>
+      </c>
+      <c r="K86" s="27"/>
+      <c r="L86" s="27"/>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D87" s="82" t="n">
+        <f>$D$35*(1-C87)-$G$41</f>
+        <v>818367346.9387755</v>
+      </c>
+      <c r="E87" s="27" t="n">
+        <f>$G$40/D87</f>
+        <v>43.09139329661795</v>
+      </c>
+      <c r="F87" s="85" t="n">
+        <f>IF(OR(D87="",E87=""),"",E87/D87)</f>
+        <v>5.265531849212667e-8</v>
+      </c>
+      <c r="G87" s="85" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F87))),"",F87*$D$24)</f>
+      </c>
+      <c r="H87" s="27" t="n">
+        <f>IF(NOT(ISNUMBER(F87)),"",F87*$D$35)</f>
+        <v>52.65531849212667</v>
+      </c>
+      <c r="I87" s="27" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H87))),"",H87*$D$24)</f>
+      </c>
+      <c r="J87" s="79" t="n">
+        <f>IF($H$80&gt;0,1-H87/$H$80,0)</f>
+        <v>0.9378113320190795</v>
+      </c>
+      <c r="K87" s="27"/>
+      <c r="L87" s="27"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="83" t="n">
+        <f>$D$35*(1-C88)-$G$41</f>
+        <v>918367346.9387755</v>
+      </c>
+      <c r="E88" s="28" t="n">
+        <f>$G$40/D88</f>
+        <v>38.399219359875104</v>
+      </c>
+      <c r="F88" s="86" t="n">
+        <f>IF(OR(D88="",E88=""),"",E88/D88)</f>
+        <v>4.181248330297511e-8</v>
+      </c>
+      <c r="G88" s="86" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(F88))),"",F88*$D$24)</f>
+      </c>
+      <c r="H88" s="28" t="n">
+        <f>IF(NOT(ISNUMBER(F88)),"",F88*$D$35)</f>
+        <v>41.81248330297511</v>
+      </c>
+      <c r="I88" s="28" t="str">
+        <f>IF(OR($D$24="",NOT(ISNUMBER(H88))),"",H88*$D$24)</f>
+      </c>
+      <c r="J88" s="80" t="n">
+        <f>IF($H$80&gt;0,1-H88/$H$80,0)</f>
+        <v>0.9506172839506173</v>
+      </c>
+      <c r="K88" s="103" t="str">
+        <v>沉没成本 / Quote</v>
+      </c>
+      <c r="L88" s="28" t="n">
+        <f>E88</f>
+        <v>38.399219359875104</v>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="2"/>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="2"/>
+      <c r="K116" s="2"/>
+      <c r="L116" s="2"/>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="2"/>
+      <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
+      <c r="J118" s="2"/>
+      <c r="K118" s="2"/>
+      <c r="L118" s="2"/>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
+      <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2"/>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+      <c r="I121" s="2"/>
+      <c r="J121" s="2"/>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
+      <c r="I123" s="2"/>
+      <c r="J123" s="2"/>
+      <c r="K123" s="2"/>
+      <c r="L123" s="2"/>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+      <c r="H124" s="2"/>
+      <c r="I124" s="2"/>
+      <c r="J124" s="2"/>
+      <c r="K124" s="2"/>
+      <c r="L124" s="2"/>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+      <c r="H125" s="2"/>
+      <c r="I125" s="2"/>
+      <c r="J125" s="2"/>
+      <c r="K125" s="2"/>
+      <c r="L125" s="2"/>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+      <c r="I126" s="2"/>
+      <c r="J126" s="2"/>
+      <c r="K126" s="2"/>
+      <c r="L126" s="2"/>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
+      <c r="J127" s="2"/>
+      <c r="K127" s="2"/>
+      <c r="L127" s="2"/>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+      <c r="H128" s="2"/>
+      <c r="I128" s="2"/>
+      <c r="J128" s="2"/>
+      <c r="K128" s="2"/>
+      <c r="L128" s="2"/>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+      <c r="I129" s="2"/>
+      <c r="J129" s="2"/>
+      <c r="K129" s="2"/>
+      <c r="L129" s="2"/>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+      <c r="H130" s="2"/>
+      <c r="I130" s="2"/>
+      <c r="J130" s="2"/>
+      <c r="K130" s="2"/>
+      <c r="L130" s="2"/>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
+      <c r="I131" s="2"/>
+      <c r="J131" s="2"/>
+      <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2"/>
+      <c r="I132" s="2"/>
+      <c r="J132" s="2"/>
+      <c r="K132" s="2"/>
+      <c r="L132" s="2"/>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+      <c r="I134" s="2"/>
+      <c r="J134" s="2"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+      <c r="I135" s="2"/>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="2"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2"/>
+      <c r="J137" s="2"/>
+      <c r="K137" s="2"/>
+      <c r="L137" s="2"/>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+      <c r="I138" s="2"/>
+      <c r="J138" s="2"/>
+      <c r="K138" s="2"/>
+      <c r="L138" s="2"/>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+      <c r="I139" s="2"/>
+      <c r="J139" s="2"/>
+      <c r="K139" s="2"/>
+      <c r="L139" s="2"/>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+      <c r="I140" s="2"/>
+      <c r="J140" s="2"/>
+      <c r="K140" s="2"/>
+      <c r="L140" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="C3:L3"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K11:L12"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="D32:E33"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E40"/>
+    <mergeCell ref="J39:L40"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="J41:L41"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D23:D23">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不可达"/>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="无效"/>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="缺少"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24:J24">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="缺少"/>
+  </conditionalFormatting>
+  <dataValidations count="13">
+    <dataValidation type="list" sqref="D7">
+      <formula1>'Quote参数'!$E$9:$E$62</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" sqref="D8">
+      <formula1>0</formula1>
+      <formula2>0.99</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" sqref="J7">
+      <formula1>0</formula1>
+      <formula2>0.1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" sqref="J8">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="whole" errorStyle="stop" operator="greaterThan" showErrorMessage="1" errorTitle="地址参数无效" error="输入非负整数；内盘套数至少为 1。" sqref="G7">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" errorStyle="stop" operator="greaterThan" showErrorMessage="1" errorTitle="地址参数无效" error="输入非负整数；内盘套数至少为 1。" sqref="G8">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation type="whole" errorStyle="stop" operator="greaterThan" showErrorMessage="1" errorTitle="地址参数无效" error="输入非负整数；内盘套数至少为 1。" sqref="G9">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation type="whole" errorStyle="stop" operator="greaterThan" showErrorMessage="1" errorTitle="地址参数无效" error="输入非负整数；内盘套数至少为 1。" sqref="G10">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="between" showErrorMessage="1" errorTitle="参数无效" error="Gas 与资金预留不能为负数。" sqref="G12">
+      <formula1>0</formula1>
+      <formula2>1e+307</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="between" showErrorMessage="1" errorTitle="参数无效" error="Gas 与资金预留不能为负数。" sqref="G11">
+      <formula1>0</formula1>
+      <formula2>1e+307</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" sqref="D9">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="J9">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="J10">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rda86b20109df4d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Ra4b1910f27474888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R8302c7757af445bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R6ca9761c17d04849"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -96,7 +96,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -126,6 +126,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF7D2638"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -158,7 +163,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="104">
+  <x:cellXfs count="126">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -467,11 +472,67 @@
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="23">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -515,6 +576,95 @@
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
@@ -766,7 +916,7 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="str">
-        <v>蓝色格可编辑。Quote / USDT 资金不含 Gas，Gas 单独以 ETH 计价。</v>
+        <v>蓝色格可编辑。Quote 资金与原生币 Gas 分开准备；总折算价值包含 Gas。</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -1035,7 +1185,7 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="8" t="str">
+      <c r="C17" s="9" t="str">
         <v>二、测算结果</v>
       </c>
       <c r="D17" s="8"/>
@@ -1051,2883 +1201,3081 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="35" t="str">
-        <v>建议总资金 / Quote</v>
-      </c>
-      <c r="D18" s="74" t="n">
-        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($D$21="","",SUM($D$21,$G$21,$J$21,$D$22)))</f>
+      <c r="C18" s="107" t="str">
+        <v>建议 Quote 资金</v>
+      </c>
+      <c r="D18" s="117" t="n">
+        <f>IF(ISNUMBER($D$26),(IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
         <v>15773.425525779472</v>
       </c>
       <c r="E18" s="62" t="str">
         <f>$D$7</f>
         <v>SLV</v>
       </c>
-      <c r="F18" s="35" t="str">
-        <v>折合 USDT（不含 Gas）</v>
-      </c>
-      <c r="G18" s="74" t="str">
-        <f>IF(OR($D$18="",$D$24=""),"",$D$18*$D$24)</f>
+      <c r="F18" s="107" t="str">
+        <v>原生币 Gas 储备</v>
+      </c>
+      <c r="G18" s="74" t="n">
+        <f>$D$32*MAX(0,$G$11)</f>
+        <v>0.61</v>
       </c>
       <c r="H18" s="62" t="str">
+        <v>ETH</v>
+      </c>
+      <c r="I18" s="107" t="str">
+        <v>总折算 / USDT</v>
+      </c>
+      <c r="J18" s="117" t="str">
+        <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
+      </c>
+      <c r="K18" s="62" t="str">
         <v>USDT</v>
       </c>
-      <c r="I18" s="35" t="str">
-        <v>Gas 储备 / ETH</v>
-      </c>
-      <c r="J18" s="74" t="n">
-        <f>$G$22*MAX(0,$G$11)</f>
-        <v>0.61</v>
-      </c>
-      <c r="K18" s="62" t="str">
-        <v>ETH</v>
-      </c>
       <c r="L18" s="62"/>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="57" t="str">
-        <v>Quote 资金构成：预算控筹率理论资金 + 额外内盘资金 + 资金预留 + 洗筹损耗</v>
-      </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
+      <c r="C19" s="107" t="str">
+        <v>Quote 折算 / USDT</v>
+      </c>
+      <c r="D19" s="118" t="str">
+        <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$33&gt;0,$D$18*$D$33,"")),"")</f>
+      </c>
+      <c r="E19" s="106" t="str">
+        <v>USDT</v>
+      </c>
+      <c r="F19" s="107" t="str">
+        <v>Gas 折算 / USDT</v>
+      </c>
+      <c r="G19" s="118" t="n">
+        <f>IF($G$18=0,0,IF($J$19="","",$G$18*$J$19))</f>
+        <v>1513.8558244080918</v>
+      </c>
+      <c r="H19" s="106" t="str">
+        <v>USDT</v>
+      </c>
+      <c r="I19" s="107" t="str">
+        <v>原生币价格 / USDT</v>
+      </c>
+      <c r="J19" s="119" t="n">
+        <f>IF($D$7="ETH",$D$33,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+        <v>2481.7308596853964</v>
+      </c>
+      <c r="K19" s="106"/>
+      <c r="L19" s="106"/>
     </row>
     <row r="20" ht="6" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="106"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="35" t="str">
-        <f>"预算 "&amp;TEXT($J$22,"0%")&amp;" 理论资金 / Quote"</f>
-        <v>预算 91% 理论资金 / Quote</v>
-      </c>
-      <c r="D21" s="60" t="n">
-        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$35="","",$J$31+$J$35))</f>
-        <v>5520.084846424523</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="35" t="str">
-        <v>额外内盘资金 / Quote</v>
-      </c>
-      <c r="G21" s="60" t="n">
-        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$31="","",$J$31*MAX(0,$G$7-1)))</f>
-        <v>174.54190618125045</v>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="35" t="str">
-        <v>洗筹损耗 / Quote</v>
-      </c>
-      <c r="J21" s="60" t="n">
-        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$36="","",$J$36*($G$32+$J$7)*2))</f>
-        <v>10073.7987731737</v>
-      </c>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
+      <c r="C21" s="76" t="str">
+        <v>Quote 资金构成</v>
+      </c>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="76" t="str">
+        <v>手续费</v>
+      </c>
+      <c r="J21" s="75"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="75"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="35" t="str">
-        <v>资金预留 / Quote</v>
-      </c>
-      <c r="D22" s="60" t="n">
-        <f>$G$12</f>
-        <v>5</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="35" t="str">
-        <v>地址总数</v>
-      </c>
-      <c r="G22" s="64" t="n">
-        <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
-        <v>122</v>
-      </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="35" t="str">
-        <v>预算使用控筹率</v>
-      </c>
-      <c r="J22" s="59" t="n">
-        <f>$D$8+1%</f>
-        <v>0.91</v>
-      </c>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
+      <c r="C22" s="106" t="str">
+        <f>"预算 "&amp;TEXT($D$31,"0%")&amp;" 理论资金"</f>
+        <v>预算 91% 理论资金</v>
+      </c>
+      <c r="D22" s="118" t="n">
+        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
+        <v>5520.084846424523</v>
+      </c>
+      <c r="E22" s="106" t="str">
+        <f>$D$7</f>
+        <v>SLV</v>
+      </c>
+      <c r="F22" s="106"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="115" t="str">
+        <v>内盘</v>
+      </c>
+      <c r="J22" s="116"/>
+      <c r="K22" s="116"/>
+      <c r="L22" s="116"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="35" t="str">
-        <v>目标是否可达</v>
-      </c>
-      <c r="D23" s="66" t="str">
-        <f>IF($J$41&lt;&gt;"参数有效",$J$41,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$43),"Creator Tax无效",IF($J$22&gt;=$G$23,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</f>
-        <v>可达</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="35" t="str">
-        <v>当前控筹上限</v>
-      </c>
-      <c r="G23" s="63" t="n">
-        <f>MIN(1-$G$41/$D$35,$G$33+(1-$G$32-$J$7)*$G$38/$D$35)</f>
-        <v>0.916326530612245</v>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="35" t="str">
-        <v>资金口径</v>
-      </c>
-      <c r="J23" s="60" t="str">
-        <v>Quote 预算 + 单独 Gas</v>
-      </c>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
+      <c r="C23" s="107" t="str">
+        <v>额外内盘资金</v>
+      </c>
+      <c r="D23" s="118" t="n">
+        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
+        <v>174.54190618125045</v>
+      </c>
+      <c r="E23" s="106" t="str">
+        <f>$D$7</f>
+        <v>SLV</v>
+      </c>
+      <c r="F23" s="106"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="106"/>
+      <c r="I23" s="107" t="str">
+        <v>基础手续费</v>
+      </c>
+      <c r="J23" s="120" t="n">
+        <f>$G$41</f>
+        <v>0.01</v>
+      </c>
+      <c r="K23" s="106"/>
+      <c r="L23" s="106"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="35" t="str">
-        <v>使用价格 / USDT</v>
-      </c>
-      <c r="D24" s="60" t="str">
-        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="35" t="str">
-        <v>行情时间 / UTC</v>
-      </c>
-      <c r="G24" s="65" t="n">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
-        <v>46283.229019363425</v>
-      </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="35" t="str">
-        <v>价格状态</v>
-      </c>
-      <c r="J24" s="60" t="str">
-        <f>IF($D$9&lt;&gt;"",IF($D$24="","手动价格无效","手动价格"),IF($D$24="","缺少价格","每日行情"))</f>
-        <v>缺少价格</v>
-      </c>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="C24" s="107" t="str">
+        <v>洗筹损耗</v>
+      </c>
+      <c r="D24" s="118" t="n">
+        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
+        <v>10073.7987731737</v>
+      </c>
+      <c r="E24" s="106" t="str">
+        <f>$D$7</f>
+        <v>SLV</v>
+      </c>
+      <c r="F24" s="106"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="106"/>
+      <c r="I24" s="107" t="str">
+        <v>买入含税费率</v>
+      </c>
+      <c r="J24" s="120" t="n">
+        <f>$G$41+$J$7</f>
+        <v>0.01</v>
+      </c>
+      <c r="K24" s="106"/>
+      <c r="L24" s="106"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="35" t="str">
-        <v>价格采用方式</v>
-      </c>
-      <c r="D25" s="60" t="str">
-        <f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</f>
-        <v>每日行情</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2" t="str">
-        <v>价格缺失时 USDT 结果留空</v>
-      </c>
-      <c r="J25" s="60"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="C25" s="107" t="str">
+        <v>资金预留</v>
+      </c>
+      <c r="D25" s="118" t="n">
+        <f>$G$12</f>
+        <v>5</v>
+      </c>
+      <c r="E25" s="106" t="str">
+        <f>$D$7</f>
+        <v>SLV</v>
+      </c>
+      <c r="F25" s="106"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="107" t="str">
+        <v>卖出含税费率</v>
+      </c>
+      <c r="J25" s="120" t="n">
+        <f>$G$41+$J$7</f>
+        <v>0.01</v>
+      </c>
+      <c r="K25" s="106"/>
+      <c r="L25" s="106"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="35" t="str">
-        <v>内盘基础手续费</v>
-      </c>
-      <c r="D26" s="59" t="n">
-        <f>$G$31</f>
-        <v>0.01</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="35" t="str">
-        <v>外盘 Hook 手续费</v>
-      </c>
-      <c r="G26" s="59" t="n">
-        <f>$G$32</f>
-        <v>0.01</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="35" t="str">
-        <v>洗筹双边总费率</v>
-      </c>
-      <c r="J26" s="59" t="n">
-        <f>SUM(G27,J27)</f>
-        <v>0.02</v>
-      </c>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="C26" s="107" t="str">
+        <v>恢复目标控筹资金</v>
+      </c>
+      <c r="D26" s="118" t="n">
+        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="106" t="str">
+        <f>$D$7</f>
+        <v>SLV</v>
+      </c>
+      <c r="F26" s="106"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="106"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="106"/>
+      <c r="K26" s="106"/>
+      <c r="L26" s="106"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="35" t="str">
-        <v>内盘买入含税费率</v>
-      </c>
-      <c r="D27" s="59" t="n">
-        <f>$G$31+$J$7</f>
-        <v>0.01</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="35" t="str">
-        <v>外盘买入含税费率</v>
-      </c>
-      <c r="G27" s="59" t="n">
-        <f>$G$32+$J$7</f>
-        <v>0.01</v>
-      </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="35" t="str">
-        <v>外盘卖出含税费率</v>
-      </c>
-      <c r="J27" s="59" t="n">
-        <f>$G$32+$J$7</f>
-        <v>0.01</v>
-      </c>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
+      <c r="C27" s="107" t="str">
+        <v>洗后控筹率（估算）</v>
+      </c>
+      <c r="D27" s="121" t="n">
+        <f>$D$8*$J$54</f>
+        <v>0.9</v>
+      </c>
+      <c r="E27" s="106"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="115" t="str">
+        <v>外盘 · Hook</v>
+      </c>
+      <c r="J27" s="116"/>
+      <c r="K27" s="116"/>
+      <c r="L27" s="116"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="35" t="str">
-        <v>沉没成本 / Quote</v>
-      </c>
-      <c r="D28" s="60" t="n">
-        <f>E88</f>
-        <v>38.399219359875104</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="35" t="str">
-        <v>一套内盘打满 / Quote</v>
-      </c>
-      <c r="G28" s="60" t="n">
-        <f>$J$31</f>
-        <v>174.54190618125045</v>
-      </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="58" t="str">
-        <v>费率为预算加总口径；双边合计用于 FDV 洗筹预算。沉没成本与一套打满仅作参考，不重复计入总额。</v>
-      </c>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" collapsed="1">
+      <c r="C28" s="107" t="str">
+        <v>补回目标控筹率</v>
+      </c>
+      <c r="D28" s="120" t="n">
+        <f>$D$8</f>
+        <v>0.9</v>
+      </c>
+      <c r="E28" s="106"/>
+      <c r="F28" s="106"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="106"/>
+      <c r="I28" s="107" t="str">
+        <v>基础手续费</v>
+      </c>
+      <c r="J28" s="120" t="n">
+        <f>$G$42</f>
+        <v>0.01</v>
+      </c>
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="8" t="str">
-        <v>三、模型信息与计算口径（默认折叠，点左侧 + 展开）</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-    </row>
-    <row r="30" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C29" s="107" t="str">
+        <v>洗筹双边总费率</v>
+      </c>
+      <c r="D29" s="120" t="n">
+        <f>$J$47*2</f>
+        <v>0.02</v>
+      </c>
+      <c r="E29" s="106"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="106"/>
+      <c r="I29" s="107" t="str">
+        <v>买入含税费率</v>
+      </c>
+      <c r="J29" s="120" t="n">
+        <f>$G$42+$J$7</f>
+        <v>0.01</v>
+      </c>
+      <c r="K29" s="106"/>
+      <c r="L29" s="106"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="48" t="str">
-        <v>Quote 信息</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="48" t="str">
-        <v>协议与曲线参数</v>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="48" t="str">
-        <v>预算中间计算</v>
-      </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C30" s="107" t="str">
+        <v>目标是否可达</v>
+      </c>
+      <c r="D30" s="107" t="str">
+        <f>IF($J$51&lt;&gt;"参数有效",$J$51,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$53),"Creator Tax无效",IF($D$31&gt;=$G$32,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</f>
+        <v>可达</v>
+      </c>
+      <c r="E30" s="106"/>
+      <c r="F30" s="106"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="106"/>
+      <c r="I30" s="107" t="str">
+        <v>卖出含税费率</v>
+      </c>
+      <c r="J30" s="120" t="n">
+        <f>$G$42+$J$7</f>
+        <v>0.01</v>
+      </c>
+      <c r="K30" s="106"/>
+      <c r="L30" s="106"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="35" t="str">
+      <c r="C31" s="107" t="str">
+        <v>预算使用控筹率</v>
+      </c>
+      <c r="D31" s="120" t="n">
+        <f>$D$8+1%</f>
+        <v>0.91</v>
+      </c>
+      <c r="E31" s="106"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="106"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="106"/>
+      <c r="L31" s="106"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="107" t="str">
+        <v>地址总数</v>
+      </c>
+      <c r="D32" s="118" t="n">
+        <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
+        <v>122</v>
+      </c>
+      <c r="E32" s="106"/>
+      <c r="F32" s="107" t="str">
+        <v>当前控筹上限</v>
+      </c>
+      <c r="G32" s="120" t="n">
+        <f>MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$7)*$G$48/$D$45)</f>
+        <v>0.916326530612245</v>
+      </c>
+      <c r="H32" s="106"/>
+      <c r="I32" s="106"/>
+      <c r="J32" s="106"/>
+      <c r="K32" s="106"/>
+      <c r="L32" s="106"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="107" t="str">
+        <v>Quote 价格 / USDT</v>
+      </c>
+      <c r="D33" s="119" t="str">
+        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+      </c>
+      <c r="E33" s="106"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="106"/>
+      <c r="H33" s="106"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="106"/>
+      <c r="K33" s="106"/>
+      <c r="L33" s="106"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="107" t="str">
+        <v>行情时间 / UTC</v>
+      </c>
+      <c r="D34" s="122" t="n">
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
+        <v>46283.229019363425</v>
+      </c>
+      <c r="E34" s="106"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="106"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="106"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="106"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="107" t="str">
+        <v>价格采用方式</v>
+      </c>
+      <c r="D35" s="106" t="str">
+        <f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</f>
+        <v>每日行情</v>
+      </c>
+      <c r="E35" s="106"/>
+      <c r="F35" s="107" t="str">
+        <f>IF($D$9&lt;&gt;"",IF($D$33="","手动价格无效","手动价格"),IF($D$33="","缺少价格","每日行情"))</f>
+        <v>缺少价格</v>
+      </c>
+      <c r="G35" s="107"/>
+      <c r="H35" s="107"/>
+      <c r="I35" s="106"/>
+      <c r="J35" s="106"/>
+      <c r="K35" s="106"/>
+      <c r="L35" s="106"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="111" t="str">
+        <v>Pons 按现有 Quote 洗筹损耗预算承担费用、持仓保持目标的口径，补回资金为 0；不代表免手续费。动态 Snipe Tax 未计入。</v>
+      </c>
+      <c r="D36" s="111"/>
+      <c r="E36" s="111"/>
+      <c r="F36" s="111"/>
+      <c r="G36" s="111"/>
+      <c r="H36" s="111"/>
+      <c r="I36" s="111"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="111"/>
+      <c r="L36" s="111"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="123" t="str">
+        <v>沉没成本（模型参考，不重复计入预算）</v>
+      </c>
+      <c r="D37" s="123"/>
+      <c r="E37" s="123"/>
+      <c r="F37" s="123"/>
+      <c r="G37" s="124" t="n">
+        <f>E98</f>
+        <v>38.399219359875104</v>
+      </c>
+      <c r="H37" s="123" t="str">
+        <f>$D$7</f>
+        <v>SLV</v>
+      </c>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+    </row>
+    <row r="38" ht="6" customHeight="1">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="106"/>
+      <c r="D38" s="106"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="106"/>
+      <c r="H38" s="106"/>
+      <c r="I38" s="106"/>
+      <c r="J38" s="106"/>
+      <c r="K38" s="106"/>
+      <c r="L38" s="106"/>
+    </row>
+    <row r="39" ht="24" customHeight="1" collapsed="1">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39" s="110" t="str">
+        <v>三、模型信息与计算口径（默认折叠，点左侧 + 展开）</v>
+      </c>
+      <c r="D39" s="110"/>
+      <c r="E39" s="110"/>
+      <c r="F39" s="110"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="110"/>
+      <c r="I39" s="110"/>
+      <c r="J39" s="110"/>
+      <c r="K39" s="110"/>
+      <c r="L39" s="110"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40" t="str">
+        <v>Quote 信息</v>
+      </c>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40" t="str">
+        <v>协议与曲线参数</v>
+      </c>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40" t="str">
+        <v>预算中间计算</v>
+      </c>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+    </row>
+    <row r="41" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41" t="str">
         <v>Quote 名称</v>
       </c>
-      <c r="D31" s="66" t="str">
+      <c r="D41" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</f>
         <v>iShares Silver Trust</v>
       </c>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35" t="str">
+      <c r="E41"/>
+      <c r="F41" t="str">
         <v>内盘基础费</v>
       </c>
-      <c r="G31" s="63" t="n">
+      <c r="G41" t="n">
         <f>1%</f>
         <v>0.01</v>
       </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="35" t="str">
+      <c r="H41"/>
+      <c r="I41" t="str">
         <v>一套内盘打满 / Quote</v>
       </c>
-      <c r="J31" s="60" t="n">
-        <f>IF(1-$G$31-$J$7&gt;0,$G$34/(1-$G$31-$J$7),"")</f>
+      <c r="J41" t="n">
+        <f>IF(1-$G$41-$J$7&gt;0,$G$44/(1-$G$41-$J$7),"")</f>
         <v>174.54190618125045</v>
       </c>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="35" t="str">
+      <c r="K41"/>
+      <c r="L41"/>
+    </row>
+    <row r="42" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42" t="str">
         <v>Quote 合约</v>
       </c>
-      <c r="D32" s="69" t="str">
+      <c r="D42" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</f>
         <v>​0x411efb0e7f985935daec3d4c3ebaea0d0ad7d89f</v>
       </c>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35" t="str">
+      <c r="E42"/>
+      <c r="F42" t="str">
         <v>外盘 Hook 费</v>
       </c>
-      <c r="G32" s="63" t="n">
+      <c r="G42" t="n">
         <f>1%</f>
         <v>0.01</v>
       </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="35" t="str">
+      <c r="H42"/>
+      <c r="I42" t="str">
         <v>目标+1% Pool TOKEN</v>
       </c>
-      <c r="J32" s="71" t="n">
-        <f>IF($J$22&lt;$G$23,$D$35*(1-$J$22)-$G$41,"")</f>
+      <c r="J42" t="n">
+        <f>IF($D$31&lt;$G$32,$D$45*(1-$D$31)-$G$51,"")</f>
         <v>8367346.938775495</v>
       </c>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" ht="20" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="66"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35" t="str">
+      <c r="K42"/>
+      <c r="L42"/>
+    </row>
+    <row r="43" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43" t="str">
         <v>毕业控筹率</v>
       </c>
-      <c r="G33" s="63" t="n">
-        <f>$G$34/($G$36+$G$34)</f>
+      <c r="G43" t="n">
+        <f>$G$44/($G$46+$G$44)</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="H33" s="2"/>
-      <c r="I33" s="35" t="str">
+      <c r="H43"/>
+      <c r="I43" t="str">
         <v>目标+1% Pool Quote</v>
       </c>
-      <c r="J33" s="60" t="n">
-        <f>IF($J$32="","",$G$40/$J$32)</f>
+      <c r="J43" t="n">
+        <f>IF($J$42="","",$G$50/$J$42)</f>
         <v>4214.548466327764</v>
       </c>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" ht="20" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="35" t="str">
+      <c r="K43"/>
+      <c r="L43"/>
+    </row>
+    <row r="44" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44" t="str">
         <v>Decimals</v>
       </c>
-      <c r="D34" s="67" t="n">
+      <c r="D44" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,4,FALSE)</f>
         <v>18</v>
       </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="35" t="str">
+      <c r="E44"/>
+      <c r="F44" t="str">
         <v>毕业真实 Quote</v>
       </c>
-      <c r="G34" s="60" t="n">
+      <c r="G44" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</f>
         <v>172.79648711943796</v>
       </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="35" t="str">
+      <c r="H44"/>
+      <c r="I44" t="str">
         <v>外盘净增加 / Quote</v>
       </c>
-      <c r="J34" s="60" t="n">
-        <f>IF($J$33="","",MAX(0,$J$33-$G$34))</f>
+      <c r="J44" t="n">
+        <f>IF($J$43="","",MAX(0,$J$43-$G$44))</f>
         <v>4041.751979208326</v>
       </c>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" ht="20" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="35" t="str">
+      <c r="K44"/>
+      <c r="L44"/>
+    </row>
+    <row r="45" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45" t="str">
         <v>总供应量</v>
       </c>
-      <c r="D35" s="64" t="n">
+      <c r="D45" t="n">
         <f>1000000000</f>
         <v>1000000000</v>
       </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="35" t="str">
+      <c r="E45"/>
+      <c r="F45" t="str">
         <v>内盘初始 TOKEN</v>
       </c>
-      <c r="G35" s="71" t="n">
-        <f>$D$35</f>
+      <c r="G45" t="n">
+        <f>$D$45</f>
         <v>1000000000</v>
       </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="35" t="str">
+      <c r="H45"/>
+      <c r="I45" t="str">
         <v>外盘含费投入 / Quote</v>
       </c>
-      <c r="J35" s="60" t="n">
-        <f>IF($J$32="","",$G$40/($G$38-MAX(0,($J$22-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="J45" t="n">
+        <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$31-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>5345.542940243272</v>
       </c>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="35" t="str">
+      <c r="K45"/>
+      <c r="L45"/>
+    </row>
+    <row r="46" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46" t="str">
         <v>协议参数证据</v>
       </c>
-      <c r="D36" s="72" t="n">
+      <c r="D46" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</f>
         <v>54430299</v>
       </c>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35" t="str">
+      <c r="E46"/>
+      <c r="F46" t="str">
         <v>phantom Quote</v>
       </c>
-      <c r="G36" s="60" t="n">
+      <c r="G46" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</f>
         <v>69.11859484777517</v>
       </c>
-      <c r="H36" s="2"/>
-      <c r="I36" s="35" t="str">
+      <c r="H46"/>
+      <c r="I46" t="str">
         <v>目标+1% FDV / Quote</v>
       </c>
-      <c r="J36" s="60" t="n">
-        <f>IF($J$33="","",$J$33/$J$32*$D$35)</f>
+      <c r="J46" t="n">
+        <f>IF($J$43="","",$J$43/$J$42*$D$45)</f>
         <v>503689.93865868496</v>
       </c>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" ht="20" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="35" t="str">
+      <c r="K46"/>
+      <c r="L46"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47" t="str">
         <v>外盘机制</v>
       </c>
-      <c r="D37" s="66" t="str">
+      <c r="D47" t="str">
         <v>Uniswap V4 / exact-input</v>
       </c>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35" t="str">
+      <c r="E47"/>
+      <c r="F47" t="str">
         <v>内盘 k</v>
       </c>
-      <c r="G37" s="68" t="n">
-        <f>$G$36*$D$35</f>
+      <c r="G47" t="n">
+        <f>$G$46*$D$45</f>
         <v>69118594847.77518</v>
       </c>
-      <c r="H37" s="2"/>
-      <c r="I37" s="35" t="str">
+      <c r="H47"/>
+      <c r="I47" t="str">
         <v>洗筹单边费率</v>
       </c>
-      <c r="J37" s="63" t="n">
-        <f>$G$32+$J$7</f>
+      <c r="J47" t="n">
+        <f>$G$42+$J$7</f>
         <v>0.01</v>
       </c>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-    </row>
-    <row r="38" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="35" t="str">
+      <c r="K47"/>
+      <c r="L47"/>
+    </row>
+    <row r="48" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A48"/>
+      <c r="B48"/>
+      <c r="C48" t="str">
         <v>费用方向</v>
       </c>
-      <c r="D38" s="66" t="str">
+      <c r="D48" t="str">
         <v>Hook + Creator Tax 从 Meme 输出扣除</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35" t="str">
+      <c r="E48"/>
+      <c r="F48" t="str">
         <v>外盘初始 TOKEN</v>
       </c>
-      <c r="G38" s="71" t="n">
-        <f>$D$35*$G$36*$G$34/($G$36+$G$34)^2</f>
+      <c r="G48" t="n">
+        <f>$D$45*$G$46*$G$44/($G$46+$G$44)^2</f>
         <v>204081632.65306124</v>
       </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="35" t="str">
+      <c r="H48"/>
+      <c r="I48" t="str">
         <v>预算缓冲</v>
       </c>
-      <c r="J38" s="59" t="n">
+      <c r="J48" t="n">
         <v>0.01</v>
       </c>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="35" t="str">
+      <c r="K48"/>
+      <c r="L48"/>
+    </row>
+    <row r="49" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A49"/>
+      <c r="B49"/>
+      <c r="C49" t="str">
         <v>洗筹口径</v>
       </c>
-      <c r="D39" s="66" t="str">
+      <c r="D49" t="str">
         <v>目标+1% FDV ×（Hook + Creator Tax）×2</v>
       </c>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35" t="str">
+      <c r="E49"/>
+      <c r="F49" t="str">
         <v>外盘初始 Quote</v>
       </c>
-      <c r="G39" s="60" t="n">
-        <f>$G$34</f>
+      <c r="G49" t="n">
+        <f>$G$44</f>
         <v>172.79648711943796</v>
       </c>
-      <c r="H39" s="2"/>
-      <c r="I39" s="35" t="str">
+      <c r="H49"/>
+      <c r="I49" t="str">
         <v>分红与回购口径</v>
       </c>
-      <c r="J39" s="73" t="str">
+      <c r="J49" t="str">
         <v>不抵扣分红 / 回购收益</v>
       </c>
-      <c r="K39" s="35"/>
-      <c r="L39" s="35"/>
-    </row>
-    <row r="40" ht="20" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35" t="str">
+      <c r="K49"/>
+      <c r="L49"/>
+    </row>
+    <row r="50" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A50"/>
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50" t="str">
         <v>外盘 k</v>
       </c>
-      <c r="G40" s="68" t="n">
-        <f>$G$38*$G$34</f>
+      <c r="G50" t="n">
+        <f>$G$48*$G$44</f>
         <v>35264589208.04857</v>
       </c>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="35"/>
-    </row>
-    <row r="41" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="35" t="str">
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
+    </row>
+    <row r="51" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A51"/>
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51" t="str">
         <v>Locker TOKEN</v>
       </c>
-      <c r="G41" s="71" t="n">
-        <f>$D$35*$G$36^2/($G$36+$G$34)^2</f>
+      <c r="G51" t="n">
+        <f>$D$45*$G$46^2/($G$46+$G$44)^2</f>
         <v>81632653.06122448</v>
       </c>
-      <c r="H41" s="2"/>
-      <c r="I41" s="35" t="str">
+      <c r="H51"/>
+      <c r="I51" t="str">
         <v>输入检查</v>
       </c>
-      <c r="J41" s="66" t="str">
+      <c r="J51" t="str">
         <f>IF(COUNT($D$8,$G$7:$G$12,$J$7:$J$8)&lt;&gt;9,"缺少或非数值参数",IF(OR($G$7&lt;1,$G$8&lt;0,$G$9&lt;0,$G$10&lt;0,$G$11&lt;0,$G$12&lt;0,$G$7&lt;&gt;INT($G$7),$G$8&lt;&gt;INT($G$8),$G$9&lt;&gt;INT($G$9),$G$10&lt;&gt;INT($G$10)),"地址/Gas/预留参数无效",IF(OR($J$8&lt;0,$J$8&gt;1,AND($J$9&lt;&gt;"是",$J$9&lt;&gt;"否"),AND($J$10&lt;&gt;"是",$J$10&lt;&gt;"否")),"平台设置无效","参数有效")))</f>
         <v>参数有效</v>
       </c>
-      <c r="K41" s="35"/>
-      <c r="L41" s="35"/>
-    </row>
-    <row r="42" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="35" t="str">
+      <c r="K51"/>
+      <c r="L51"/>
+    </row>
+    <row r="52" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A52"/>
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52" t="str">
         <v>Snipe 窗口</v>
       </c>
-      <c r="G42" s="73" t="str">
+      <c r="G52" t="str">
         <v>3 秒；默认豁免或避开</v>
       </c>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="60"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="35" t="str">
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+    </row>
+    <row r="53" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53" t="str">
         <v>Creator Tax 上限</v>
       </c>
-      <c r="G43" s="63" t="n">
+      <c r="G53" t="n">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="60"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" ht="6" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" ht="6" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-    </row>
-    <row r="46" ht="6" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-    </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="8" t="str">
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+    </row>
+    <row r="54" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54" s="108" t="str">
+        <v>洗后持仓保留比例</v>
+      </c>
+      <c r="J54" t="n">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="K54"/>
+      <c r="L54"/>
+    </row>
+    <row r="55" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A55"/>
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55" s="108" t="str">
+        <v>目标外盘 Pool TOKEN</v>
+      </c>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+    </row>
+    <row r="56" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56" s="108" t="str">
+        <v>洗后外盘 Pool TOKEN</v>
+      </c>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57"/>
+      <c r="B57"/>
+      <c r="C57" t="str">
         <v>内盘曲线</v>
       </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="77" t="str">
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58"/>
+      <c r="B58"/>
+      <c r="C58" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D48" s="77" t="str">
+      <c r="D58" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E48" s="77" t="str">
+      <c r="E58" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F48" s="77" t="str">
+      <c r="F58" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G48" s="77" t="str">
+      <c r="G58" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H48" s="77" t="str">
+      <c r="H58" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I48" s="77" t="str">
+      <c r="I58" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J48" s="77" t="str">
+      <c r="J58" t="str">
         <v>区间净投入
 / Quote</v>
       </c>
-      <c r="K48" s="77" t="str">
+      <c r="K58" t="str">
         <v>区间含费
 / Quote</v>
       </c>
-      <c r="L48" s="77" t="str">
+      <c r="L58" t="str">
         <v>理论累计所需
 / Quote</v>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="78" t="n">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59"/>
+      <c r="B59"/>
+      <c r="C59" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="81" t="n">
-        <f>$D$35*(1-C49)</f>
+      <c r="D59" s="125" t="n">
+        <f>$D$45*(1-C59)</f>
         <v>1000000000</v>
       </c>
-      <c r="E49" s="26" t="n">
-        <f>$G$37/D49</f>
+      <c r="E59" s="125" t="n">
+        <f>$G$47/D59</f>
         <v>69.11859484777517</v>
       </c>
-      <c r="F49" s="84" t="n">
-        <f>IF(OR(D49="",E49=""),"",E49/D49)</f>
+      <c r="F59" t="n">
+        <f>IF(OR(D59="",E59=""),"",E59/D59)</f>
         <v>6.911859484777517e-8</v>
       </c>
-      <c r="G49" s="84" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F49))),"",F49*$D$24)</f>
-      </c>
-      <c r="H49" s="26" t="n">
-        <f>IF(NOT(ISNUMBER(F49)),"",F49*$D$35)</f>
+      <c r="G59" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F59))),"",F59*$D$33)</f>
+      </c>
+      <c r="H59" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F59)),"",F59*$D$45)</f>
         <v>69.11859484777517</v>
       </c>
-      <c r="I49" s="26" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H49))),"",H49*$D$24)</f>
-      </c>
-      <c r="J49" s="26" t="n">
+      <c r="I59" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H59))),"",H59*$D$33)</f>
+      </c>
+      <c r="J59" s="125" t="n">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="K49" s="26" t="n">
-        <f>J49/(1-$G$31-$J$7)</f>
+      <c r="K59" s="125" t="n">
+        <f>J59/(1-$G$41-$J$7)</f>
         <v>0</v>
       </c>
-      <c r="L49" s="90" t="n">
-        <f>SUM($K$49:K49)</f>
+      <c r="L59" s="125" t="n">
+        <f>SUM($K$59:K59)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="79" t="n">
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60" t="n">
         <v>0.1</v>
       </c>
-      <c r="D50" s="82" t="n">
-        <f>$D$35*(1-C50)</f>
+      <c r="D60" s="125" t="n">
+        <f>$D$45*(1-C60)</f>
         <v>900000000</v>
       </c>
-      <c r="E50" s="27" t="n">
-        <f>$G$37/D50</f>
+      <c r="E60" s="125" t="n">
+        <f>$G$47/D60</f>
         <v>76.7984387197502</v>
       </c>
-      <c r="F50" s="85" t="n">
-        <f>IF(OR(D50="",E50=""),"",E50/D50)</f>
+      <c r="F60" t="n">
+        <f>IF(OR(D60="",E60=""),"",E60/D60)</f>
         <v>8.533159857750022e-8</v>
       </c>
-      <c r="G50" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F50))),"",F50*$D$24)</f>
-      </c>
-      <c r="H50" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F50)),"",F50*$D$35)</f>
+      <c r="G60" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F60))),"",F60*$D$33)</f>
+      </c>
+      <c r="H60" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F60)),"",F60*$D$45)</f>
         <v>85.33159857750022</v>
       </c>
-      <c r="I50" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H50))),"",H50*$D$24)</f>
-      </c>
-      <c r="J50" s="27" t="n">
-        <f>E50-E49</f>
+      <c r="I60" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H60))),"",H60*$D$33)</f>
+      </c>
+      <c r="J60" s="125" t="n">
+        <f>E60-E59</f>
         <v>7.679843871975024</v>
       </c>
-      <c r="K50" s="27" t="n">
-        <f>J50/(1-$G$31-$J$7)</f>
+      <c r="K60" s="125" t="n">
+        <f>J60/(1-$G$41-$J$7)</f>
         <v>7.757418052500024</v>
       </c>
-      <c r="L50" s="91" t="n">
-        <f>SUM($K$49:K50)</f>
+      <c r="L60" s="125" t="n">
+        <f>SUM($K$59:K60)</f>
         <v>7.757418052500024</v>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="79" t="n">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61" t="n">
         <v>0.2</v>
       </c>
-      <c r="D51" s="82" t="n">
-        <f>$D$35*(1-C51)</f>
+      <c r="D61" s="125" t="n">
+        <f>$D$45*(1-C61)</f>
         <v>800000000</v>
       </c>
-      <c r="E51" s="27" t="n">
-        <f>$G$37/D51</f>
+      <c r="E61" s="125" t="n">
+        <f>$G$47/D61</f>
         <v>86.39824355971898</v>
       </c>
-      <c r="F51" s="85" t="n">
-        <f>IF(OR(D51="",E51=""),"",E51/D51)</f>
+      <c r="F61" t="n">
+        <f>IF(OR(D61="",E61=""),"",E61/D61)</f>
         <v>1.0799780444964873e-7</v>
       </c>
-      <c r="G51" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F51))),"",F51*$D$24)</f>
-      </c>
-      <c r="H51" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F51)),"",F51*$D$35)</f>
+      <c r="G61" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F61))),"",F61*$D$33)</f>
+      </c>
+      <c r="H61" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F61)),"",F61*$D$45)</f>
         <v>107.99780444964873</v>
       </c>
-      <c r="I51" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H51))),"",H51*$D$24)</f>
-      </c>
-      <c r="J51" s="27" t="n">
-        <f>E51-E50</f>
+      <c r="I61" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H61))),"",H61*$D$33)</f>
+      </c>
+      <c r="J61" s="125" t="n">
+        <f>E61-E60</f>
         <v>9.599804839968783</v>
       </c>
-      <c r="K51" s="27" t="n">
-        <f>J51/(1-$G$31-$J$7)</f>
+      <c r="K61" s="125" t="n">
+        <f>J61/(1-$G$41-$J$7)</f>
         <v>9.696772565625034</v>
       </c>
-      <c r="L51" s="91" t="n">
-        <f>SUM($K$49:K51)</f>
+      <c r="L61" s="125" t="n">
+        <f>SUM($K$59:K61)</f>
         <v>17.454190618125057</v>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="79" t="n">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62"/>
+      <c r="B62"/>
+      <c r="C62" t="n">
         <v>0.3</v>
       </c>
-      <c r="D52" s="82" t="n">
-        <f>$D$35*(1-C52)</f>
+      <c r="D62" s="125" t="n">
+        <f>$D$45*(1-C62)</f>
         <v>700000000</v>
       </c>
-      <c r="E52" s="27" t="n">
-        <f>$G$37/D52</f>
+      <c r="E62" s="125" t="n">
+        <f>$G$47/D62</f>
         <v>98.74084978253596</v>
       </c>
-      <c r="F52" s="85" t="n">
-        <f>IF(OR(D52="",E52=""),"",E52/D52)</f>
+      <c r="F62" t="n">
+        <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
         <v>1.4105835683219424e-7</v>
       </c>
-      <c r="G52" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F52))),"",F52*$D$24)</f>
-      </c>
-      <c r="H52" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F52)),"",F52*$D$35)</f>
+      <c r="G62" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F62))),"",F62*$D$33)</f>
+      </c>
+      <c r="H62" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$45)</f>
         <v>141.05835683219425</v>
       </c>
-      <c r="I52" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H52))),"",H52*$D$24)</f>
-      </c>
-      <c r="J52" s="27" t="n">
-        <f>E52-E51</f>
+      <c r="I62" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H62))),"",H62*$D$33)</f>
+      </c>
+      <c r="J62" s="125" t="n">
+        <f>E62-E61</f>
         <v>12.342606222816983</v>
       </c>
-      <c r="K52" s="27" t="n">
-        <f>J52/(1-$G$31-$J$7)</f>
+      <c r="K62" s="125" t="n">
+        <f>J62/(1-$G$41-$J$7)</f>
         <v>12.467279012946447</v>
       </c>
-      <c r="L52" s="91" t="n">
-        <f>SUM($K$49:K52)</f>
+      <c r="L62" s="125" t="n">
+        <f>SUM($K$59:K62)</f>
         <v>29.921469631071503</v>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="79" t="n">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63"/>
+      <c r="B63"/>
+      <c r="C63" t="n">
         <v>0.4</v>
       </c>
-      <c r="D53" s="82" t="n">
-        <f>$D$35*(1-C53)</f>
+      <c r="D63" s="125" t="n">
+        <f>$D$45*(1-C63)</f>
         <v>600000000</v>
       </c>
-      <c r="E53" s="27" t="n">
-        <f>$G$37/D53</f>
+      <c r="E63" s="125" t="n">
+        <f>$G$47/D63</f>
         <v>115.1976580796253</v>
       </c>
-      <c r="F53" s="85" t="n">
-        <f>IF(OR(D53="",E53=""),"",E53/D53)</f>
+      <c r="F63" t="n">
+        <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
         <v>1.919960967993755e-7</v>
       </c>
-      <c r="G53" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F53))),"",F53*$D$24)</f>
-      </c>
-      <c r="H53" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F53)),"",F53*$D$35)</f>
+      <c r="G63" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F63))),"",F63*$D$33)</f>
+      </c>
+      <c r="H63" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$45)</f>
         <v>191.99609679937552</v>
       </c>
-      <c r="I53" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H53))),"",H53*$D$24)</f>
-      </c>
-      <c r="J53" s="27" t="n">
-        <f>E53-E52</f>
+      <c r="I63" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H63))),"",H63*$D$33)</f>
+      </c>
+      <c r="J63" s="125" t="n">
+        <f>E63-E62</f>
         <v>16.45680829708934</v>
       </c>
-      <c r="K53" s="27" t="n">
-        <f>J53/(1-$G$31-$J$7)</f>
+      <c r="K63" s="125" t="n">
+        <f>J63/(1-$G$41-$J$7)</f>
         <v>16.623038683928623</v>
       </c>
-      <c r="L53" s="91" t="n">
-        <f>SUM($K$49:K53)</f>
+      <c r="L63" s="125" t="n">
+        <f>SUM($K$59:K63)</f>
         <v>46.54450831500013</v>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="79" t="n">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64"/>
+      <c r="B64"/>
+      <c r="C64" t="n">
         <v>0.5</v>
       </c>
-      <c r="D54" s="82" t="n">
-        <f>$D$35*(1-C54)</f>
+      <c r="D64" s="125" t="n">
+        <f>$D$45*(1-C64)</f>
         <v>500000000</v>
       </c>
-      <c r="E54" s="27" t="n">
-        <f>$G$37/D54</f>
+      <c r="E64" s="125" t="n">
+        <f>$G$47/D64</f>
         <v>138.23718969555034</v>
       </c>
-      <c r="F54" s="85" t="n">
-        <f>IF(OR(D54="",E54=""),"",E54/D54)</f>
+      <c r="F64" t="n">
+        <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
         <v>2.7647437939110067e-7</v>
       </c>
-      <c r="G54" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F54))),"",F54*$D$24)</f>
-      </c>
-      <c r="H54" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F54)),"",F54*$D$35)</f>
+      <c r="G64" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F64))),"",F64*$D$33)</f>
+      </c>
+      <c r="H64" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$45)</f>
         <v>276.4743793911007</v>
       </c>
-      <c r="I54" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H54))),"",H54*$D$24)</f>
-      </c>
-      <c r="J54" s="27" t="n">
-        <f>E54-E53</f>
+      <c r="I64" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H64))),"",H64*$D$33)</f>
+      </c>
+      <c r="J64" s="125" t="n">
+        <f>E64-E63</f>
         <v>23.039531615925043</v>
       </c>
-      <c r="K54" s="27" t="n">
-        <f>J54/(1-$G$31-$J$7)</f>
+      <c r="K64" s="125" t="n">
+        <f>J64/(1-$G$41-$J$7)</f>
         <v>23.272254157500043</v>
       </c>
-      <c r="L54" s="91" t="n">
-        <f>SUM($K$49:K54)</f>
+      <c r="L64" s="125" t="n">
+        <f>SUM($K$59:K64)</f>
         <v>69.81676247250017</v>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="79" t="n">
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65"/>
+      <c r="B65"/>
+      <c r="C65" t="n">
         <v>0.6</v>
       </c>
-      <c r="D55" s="82" t="n">
-        <f>$D$35*(1-C55)</f>
+      <c r="D65" s="125" t="n">
+        <f>$D$45*(1-C65)</f>
         <v>400000000</v>
       </c>
-      <c r="E55" s="27" t="n">
-        <f>$G$37/D55</f>
+      <c r="E65" s="125" t="n">
+        <f>$G$47/D65</f>
         <v>172.79648711943796</v>
       </c>
-      <c r="F55" s="85" t="n">
-        <f>IF(OR(D55="",E55=""),"",E55/D55)</f>
+      <c r="F65" t="n">
+        <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
         <v>4.319912177985949e-7</v>
       </c>
-      <c r="G55" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F55))),"",F55*$D$24)</f>
-      </c>
-      <c r="H55" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F55)),"",F55*$D$35)</f>
+      <c r="G65" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F65))),"",F65*$D$33)</f>
+      </c>
+      <c r="H65" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$45)</f>
         <v>431.9912177985949</v>
       </c>
-      <c r="I55" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H55))),"",H55*$D$24)</f>
-      </c>
-      <c r="J55" s="27" t="n">
-        <f>E55-E54</f>
+      <c r="I65" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H65))),"",H65*$D$33)</f>
+      </c>
+      <c r="J65" s="125" t="n">
+        <f>E65-E64</f>
         <v>34.559297423887614</v>
       </c>
-      <c r="K55" s="27" t="n">
-        <f>J55/(1-$G$31-$J$7)</f>
+      <c r="K65" s="125" t="n">
+        <f>J65/(1-$G$41-$J$7)</f>
         <v>34.908381236250115</v>
       </c>
-      <c r="L55" s="91" t="n">
-        <f>SUM($K$49:K55)</f>
+      <c r="L65" s="125" t="n">
+        <f>SUM($K$59:K65)</f>
         <v>104.7251437087503</v>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="79" t="n">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66"/>
+      <c r="B66"/>
+      <c r="C66" t="n">
         <v>0.7</v>
       </c>
-      <c r="D56" s="82" t="n">
-        <f>$D$35*(1-C56)</f>
+      <c r="D66" s="125" t="n">
+        <f>$D$45*(1-C66)</f>
         <v>300000000.00000006</v>
       </c>
-      <c r="E56" s="27" t="n">
-        <f>$G$37/D56</f>
+      <c r="E66" s="125" t="n">
+        <f>$G$47/D66</f>
         <v>230.39531615925054</v>
       </c>
-      <c r="F56" s="85" t="n">
-        <f>IF(OR(D56="",E56=""),"",E56/D56)</f>
+      <c r="F66" t="n">
+        <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
         <v>7.679843871975016e-7</v>
       </c>
-      <c r="G56" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F56))),"",F56*$D$24)</f>
-      </c>
-      <c r="H56" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F56)),"",F56*$D$35)</f>
+      <c r="G66" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F66))),"",F66*$D$33)</f>
+      </c>
+      <c r="H66" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$45)</f>
         <v>767.9843871975016</v>
       </c>
-      <c r="I56" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H56))),"",H56*$D$24)</f>
-      </c>
-      <c r="J56" s="27" t="n">
-        <f>E56-E55</f>
+      <c r="I66" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H66))),"",H66*$D$33)</f>
+      </c>
+      <c r="J66" s="125" t="n">
+        <f>E66-E65</f>
         <v>57.598829039812586</v>
       </c>
-      <c r="K56" s="27" t="n">
-        <f>J56/(1-$G$31-$J$7)</f>
+      <c r="K66" s="125" t="n">
+        <f>J66/(1-$G$41-$J$7)</f>
         <v>58.18063539375009</v>
       </c>
-      <c r="L56" s="91" t="n">
-        <f>SUM($K$49:K56)</f>
+      <c r="L66" s="125" t="n">
+        <f>SUM($K$59:K66)</f>
         <v>162.9057791025004</v>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="93" t="n">
-        <f>$G$33</f>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67" t="n">
+        <f>$G$43</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="D57" s="94" t="n">
-        <f>$D$35*(1-C57)</f>
+      <c r="D67" s="125" t="n">
+        <f>$D$45*(1-C67)</f>
         <v>285714285.7142857</v>
       </c>
-      <c r="E57" s="95" t="n">
-        <f>$G$37/D57</f>
+      <c r="E67" s="125" t="n">
+        <f>$G$47/D67</f>
         <v>241.91508196721315</v>
       </c>
-      <c r="F57" s="96" t="n">
-        <f>IF(OR(D57="",E57=""),"",E57/D57)</f>
+      <c r="F67" t="n">
+        <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
         <v>8.467027868852461e-7</v>
       </c>
-      <c r="G57" s="96" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F57))),"",F57*$D$24)</f>
-      </c>
-      <c r="H57" s="95" t="n">
-        <f>IF(NOT(ISNUMBER(F57)),"",F57*$D$35)</f>
+      <c r="G67" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F67))),"",F67*$D$33)</f>
+      </c>
+      <c r="H67" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$45)</f>
         <v>846.7027868852462</v>
       </c>
-      <c r="I57" s="95" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H57))),"",H57*$D$24)</f>
-      </c>
-      <c r="J57" s="95" t="n">
-        <f>E57-E56</f>
+      <c r="I67" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H67))),"",H67*$D$33)</f>
+      </c>
+      <c r="J67" s="125" t="n">
+        <f>E67-E66</f>
         <v>11.519765807962614</v>
       </c>
-      <c r="K57" s="95" t="n">
-        <f>J57/(1-$G$31-$J$7)</f>
+      <c r="K67" s="125" t="n">
+        <f>J67/(1-$G$41-$J$7)</f>
         <v>11.636127078750116</v>
       </c>
-      <c r="L57" s="92" t="n">
-        <f>SUM($K$49:K57)</f>
+      <c r="L67" s="125" t="n">
+        <f>SUM($K$59:K67)</f>
         <v>174.5419061812505</v>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="8" t="str">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68"/>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="H68"/>
+      <c r="I68"/>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69"/>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
+      <c r="I69"/>
+      <c r="J69"/>
+      <c r="K69"/>
+      <c r="L69"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70"/>
+      <c r="B70"/>
+      <c r="C70" t="str">
         <v>外盘曲线</v>
       </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="8"/>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="77" t="str">
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="H70"/>
+      <c r="I70"/>
+      <c r="J70"/>
+      <c r="K70"/>
+      <c r="L70"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D61" s="77" t="str">
+      <c r="D71" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E61" s="77" t="str">
+      <c r="E71" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F61" s="77" t="str">
+      <c r="F71" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G61" s="77" t="str">
+      <c r="G71" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H61" s="77" t="str">
+      <c r="H71" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I61" s="77" t="str">
+      <c r="I71" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J61" s="77" t="str">
+      <c r="J71" t="str">
         <v>外盘净投入
 / Quote</v>
       </c>
-      <c r="K61" s="77" t="str">
+      <c r="K71" t="str">
         <v>外盘含费
 / Quote</v>
       </c>
-      <c r="L61" s="77" t="str">
+      <c r="L71" t="str">
         <v>理论累计所需
 / Quote</v>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="97" t="n">
-        <f>$G$33</f>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72"/>
+      <c r="B72"/>
+      <c r="C72" t="n">
+        <f>$G$43</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="D62" s="98" t="n">
-        <f>$G$38</f>
+      <c r="D72" s="125" t="n">
+        <f>$G$48</f>
         <v>204081632.65306124</v>
       </c>
-      <c r="E62" s="99" t="n">
-        <f>$G$34</f>
+      <c r="E72" s="125" t="n">
+        <f>$G$44</f>
         <v>172.79648711943796</v>
       </c>
-      <c r="F62" s="100" t="n">
-        <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
+      <c r="F72" t="n">
+        <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
         <v>8.467027868852459e-7</v>
       </c>
-      <c r="G62" s="100" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F62))),"",F62*$D$24)</f>
-      </c>
-      <c r="H62" s="99" t="n">
-        <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$35)</f>
+      <c r="G72" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F72))),"",F72*$D$33)</f>
+      </c>
+      <c r="H72" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$45)</f>
         <v>846.7027868852459</v>
       </c>
-      <c r="I62" s="99" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H62))),"",H62*$D$24)</f>
-      </c>
-      <c r="J62" s="99" t="n">
+      <c r="I72" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H72))),"",H72*$D$33)</f>
+      </c>
+      <c r="J72" s="125" t="n">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="K62" s="99" t="n">
+      <c r="K72" s="125" t="n">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="L62" s="90" t="n">
-        <f>$J$31</f>
+      <c r="L72" s="125" t="n">
+        <f>$J$41</f>
         <v>174.54190618125045</v>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="79" t="n">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73"/>
+      <c r="B73"/>
+      <c r="C73" t="n">
         <v>0.75</v>
       </c>
-      <c r="D63" s="82" t="n">
-        <f>IF(C63&lt;$G$23,$D$35*(1-C63)-$G$41,"")</f>
+      <c r="D73" s="125" t="n">
+        <f>IF(C73&lt;$G$32,$D$45*(1-C73)-$G$51,"")</f>
         <v>168367346.93877554</v>
       </c>
-      <c r="E63" s="27" t="n">
-        <f>IF(D63="","",$G$40/D63)</f>
+      <c r="E73" s="125" t="n">
+        <f>IF(D73="","",$G$50/D73)</f>
         <v>209.45028741750056</v>
       </c>
-      <c r="F63" s="85" t="n">
-        <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
+      <c r="F73" t="n">
+        <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
         <v>0.0000012440077676918213</v>
       </c>
-      <c r="G63" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F63))),"",F63*$D$24)</f>
-      </c>
-      <c r="H63" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$35)</f>
+      <c r="G73" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F73))),"",F73*$D$33)</f>
+      </c>
+      <c r="H73" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$45)</f>
         <v>1244.0077676918213</v>
       </c>
-      <c r="I63" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H63))),"",H63*$D$24)</f>
-      </c>
-      <c r="J63" s="27" t="n">
-        <f>IF(E63="","",MAX(0,E63-$G$34))</f>
+      <c r="I73" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H73))),"",H73*$D$33)</f>
+      </c>
+      <c r="J73" s="125" t="n">
+        <f>IF(E73="","",MAX(0,E73-$G$44))</f>
         <v>36.653800298062606</v>
       </c>
-      <c r="K63" s="27" t="n">
-        <f>IF(D63="","",$G$40/($G$38-MAX(0,(C63-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K73" s="125" t="n">
+        <f>IF(D73="","",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>37.103540179020456</v>
       </c>
-      <c r="L63" s="91" t="n">
-        <f>IF(K63="","",$J$31+K63)</f>
+      <c r="L73" s="125" t="n">
+        <f>IF(K73="","",$J$41+K73)</f>
         <v>211.6454463602709</v>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="79" t="n">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74"/>
+      <c r="B74"/>
+      <c r="C74" t="n">
         <v>0.8</v>
       </c>
-      <c r="D64" s="82" t="n">
-        <f>IF(C64&lt;$G$23,$D$35*(1-C64)-$G$41,"")</f>
+      <c r="D74" s="125" t="n">
+        <f>IF(C74&lt;$G$32,$D$45*(1-C74)-$G$51,"")</f>
         <v>118367346.9387755</v>
       </c>
-      <c r="E64" s="27" t="n">
-        <f>IF(D64="","",$G$40/D64)</f>
+      <c r="E74" s="125" t="n">
+        <f>IF(D74="","",$G$50/D74)</f>
         <v>297.9249777921345</v>
       </c>
-      <c r="F64" s="85" t="n">
-        <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
+      <c r="F74" t="n">
+        <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
         <v>0.0000025169523985887227</v>
       </c>
-      <c r="G64" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F64))),"",F64*$D$24)</f>
-      </c>
-      <c r="H64" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$35)</f>
+      <c r="G74" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F74))),"",F74*$D$33)</f>
+      </c>
+      <c r="H74" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$45)</f>
         <v>2516.9523985887226</v>
       </c>
-      <c r="I64" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H64))),"",H64*$D$24)</f>
-      </c>
-      <c r="J64" s="27" t="n">
-        <f>IF(E64="","",MAX(0,E64-$G$34))</f>
+      <c r="I74" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H74))),"",H74*$D$33)</f>
+      </c>
+      <c r="J74" s="125" t="n">
+        <f>IF(E74="","",MAX(0,E74-$G$44))</f>
         <v>125.12849067269653</v>
       </c>
-      <c r="K64" s="27" t="n">
-        <f>IF(D64="","",$G$40/($G$38-MAX(0,(C64-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K74" s="125" t="n">
+        <f>IF(D74="","",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>127.32372735116493</v>
       </c>
-      <c r="L64" s="91" t="n">
-        <f>IF(K64="","",$J$31+K64)</f>
+      <c r="L74" s="125" t="n">
+        <f>IF(K74="","",$J$41+K74)</f>
         <v>301.86563353241536</v>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="79" t="n">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75" t="n">
         <v>0.82</v>
       </c>
-      <c r="D65" s="82" t="n">
-        <f>IF(C65&lt;$G$23,$D$35*(1-C65)-$G$41,"")</f>
+      <c r="D75" s="125" t="n">
+        <f>IF(C75&lt;$G$32,$D$45*(1-C75)-$G$51,"")</f>
         <v>98367346.93877558</v>
       </c>
-      <c r="E65" s="27" t="n">
-        <f>IF(D65="","",$G$40/D65)</f>
+      <c r="E75" s="125" t="n">
+        <f>IF(D75="","",$G$50/D75)</f>
         <v>358.4989359324437</v>
       </c>
-      <c r="F65" s="85" t="n">
-        <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
+      <c r="F75" t="n">
+        <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
         <v>0.000003644491257404508</v>
       </c>
-      <c r="G65" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F65))),"",F65*$D$24)</f>
-      </c>
-      <c r="H65" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$35)</f>
+      <c r="G75" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F75))),"",F75*$D$33)</f>
+      </c>
+      <c r="H75" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$45)</f>
         <v>3644.4912574045084</v>
       </c>
-      <c r="I65" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H65))),"",H65*$D$24)</f>
-      </c>
-      <c r="J65" s="27" t="n">
-        <f>IF(E65="","",MAX(0,E65-$G$34))</f>
+      <c r="I75" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H75))),"",H75*$D$33)</f>
+      </c>
+      <c r="J75" s="125" t="n">
+        <f>IF(E75="","",MAX(0,E75-$G$44))</f>
         <v>185.70244881300576</v>
       </c>
-      <c r="K65" s="27" t="n">
-        <f>IF(D65="","",$G$40/($G$38-MAX(0,(C65-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K75" s="125" t="n">
+        <f>IF(D75="","",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>189.63682272853552</v>
       </c>
-      <c r="L65" s="91" t="n">
-        <f>IF(K65="","",$J$31+K65)</f>
+      <c r="L75" s="125" t="n">
+        <f>IF(K75="","",$J$41+K75)</f>
         <v>364.17872890978595</v>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="79" t="n">
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76"/>
+      <c r="B76"/>
+      <c r="C76" t="n">
         <v>0.84</v>
       </c>
-      <c r="D66" s="82" t="n">
-        <f>IF(C66&lt;$G$23,$D$35*(1-C66)-$G$41,"")</f>
+      <c r="D76" s="125" t="n">
+        <f>IF(C76&lt;$G$32,$D$45*(1-C76)-$G$51,"")</f>
         <v>78367346.93877555</v>
       </c>
-      <c r="E66" s="27" t="n">
-        <f>IF(D66="","",$G$40/D66)</f>
+      <c r="E76" s="125" t="n">
+        <f>IF(D76="","",$G$50/D76)</f>
         <v>449.99085187353614</v>
       </c>
-      <c r="F66" s="85" t="n">
-        <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
+      <c r="F76" t="n">
+        <f>IF(OR(D76="",E76=""),"",E76/D76)</f>
         <v>0.000005742070766094599</v>
       </c>
-      <c r="G66" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F66))),"",F66*$D$24)</f>
-      </c>
-      <c r="H66" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$35)</f>
+      <c r="G76" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F76))),"",F76*$D$33)</f>
+      </c>
+      <c r="H76" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F76)),"",F76*$D$45)</f>
         <v>5742.070766094599</v>
       </c>
-      <c r="I66" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H66))),"",H66*$D$24)</f>
-      </c>
-      <c r="J66" s="27" t="n">
-        <f>IF(E66="","",MAX(0,E66-$G$34))</f>
+      <c r="I76" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H76))),"",H76*$D$33)</f>
+      </c>
+      <c r="J76" s="125" t="n">
+        <f>IF(E76="","",MAX(0,E76-$G$44))</f>
         <v>277.19436475409816</v>
       </c>
-      <c r="K66" s="27" t="n">
-        <f>IF(D66="","",$G$40/($G$38-MAX(0,(C66-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K76" s="125" t="n">
+        <f>IF(D76="","",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>284.6059787849564</v>
       </c>
-      <c r="L66" s="91" t="n">
-        <f>IF(K66="","",$J$31+K66)</f>
+      <c r="L76" s="125" t="n">
+        <f>IF(K76="","",$J$41+K76)</f>
         <v>459.14788496620685</v>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="79" t="n">
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77" t="n">
         <v>0.86</v>
       </c>
-      <c r="D67" s="82" t="n">
-        <f>IF(C67&lt;$G$23,$D$35*(1-C67)-$G$41,"")</f>
+      <c r="D77" s="125" t="n">
+        <f>IF(C77&lt;$G$32,$D$45*(1-C77)-$G$51,"")</f>
         <v>58367346.938775524</v>
       </c>
-      <c r="E67" s="27" t="n">
-        <f>IF(D67="","",$G$40/D67)</f>
+      <c r="E77" s="125" t="n">
+        <f>IF(D77="","",$G$50/D77)</f>
         <v>604.1835213966361</v>
       </c>
-      <c r="F67" s="85" t="n">
-        <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
+      <c r="F77" t="n">
+        <f>IF(OR(D77="",E77=""),"",E77/D77)</f>
         <v>0.00001035139599595635</v>
       </c>
-      <c r="G67" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F67))),"",F67*$D$24)</f>
-      </c>
-      <c r="H67" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$35)</f>
+      <c r="G77" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F77))),"",F77*$D$33)</f>
+      </c>
+      <c r="H77" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F77)),"",F77*$D$45)</f>
         <v>10351.39599595635</v>
       </c>
-      <c r="I67" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H67))),"",H67*$D$24)</f>
-      </c>
-      <c r="J67" s="27" t="n">
-        <f>IF(E67="","",MAX(0,E67-$G$34))</f>
+      <c r="I77" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H77))),"",H77*$D$33)</f>
+      </c>
+      <c r="J77" s="125" t="n">
+        <f>IF(E77="","",MAX(0,E77-$G$44))</f>
         <v>431.38703427719815</v>
       </c>
-      <c r="K67" s="27" t="n">
-        <f>IF(D67="","",$G$40/($G$38-MAX(0,(C67-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K77" s="125" t="n">
+        <f>IF(D77="","",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>447.0169992872412</v>
       </c>
-      <c r="L67" s="91" t="n">
-        <f>IF(K67="","",$J$31+K67)</f>
+      <c r="L77" s="125" t="n">
+        <f>IF(K77="","",$J$41+K77)</f>
         <v>621.5589054684917</v>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="79" t="n">
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78"/>
+      <c r="B78"/>
+      <c r="C78" t="n">
         <v>0.88</v>
       </c>
-      <c r="D68" s="82" t="n">
-        <f>IF(C68&lt;$G$23,$D$35*(1-C68)-$G$41,"")</f>
+      <c r="D78" s="125" t="n">
+        <f>IF(C78&lt;$G$32,$D$45*(1-C78)-$G$51,"")</f>
         <v>38367346.938775524</v>
       </c>
-      <c r="E68" s="27" t="n">
-        <f>IF(D68="","",$G$40/D68)</f>
+      <c r="E78" s="125" t="n">
+        <f>IF(D78="","",$G$50/D78)</f>
         <v>919.1302506353081</v>
       </c>
-      <c r="F68" s="85" t="n">
-        <f>IF(OR(D68="",E68=""),"",E68/D68)</f>
+      <c r="F78" t="n">
+        <f>IF(OR(D78="",E78=""),"",E78/D78)</f>
         <v>0.000023956054404856426</v>
       </c>
-      <c r="G68" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F68))),"",F68*$D$24)</f>
-      </c>
-      <c r="H68" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F68)),"",F68*$D$35)</f>
+      <c r="G78" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F78))),"",F78*$D$33)</f>
+      </c>
+      <c r="H78" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F78)),"",F78*$D$45)</f>
         <v>23956.054404856426</v>
       </c>
-      <c r="I68" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H68))),"",H68*$D$24)</f>
-      </c>
-      <c r="J68" s="27" t="n">
-        <f>IF(E68="","",MAX(0,E68-$G$34))</f>
+      <c r="I78" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H78))),"",H78*$D$33)</f>
+      </c>
+      <c r="J78" s="125" t="n">
+        <f>IF(E78="","",MAX(0,E78-$G$44))</f>
         <v>746.3337635158701</v>
       </c>
-      <c r="K68" s="27" t="n">
-        <f>IF(D68="","",$G$40/($G$38-MAX(0,(C68-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K78" s="125" t="n">
+        <f>IF(D78="","",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>788.2626266347389</v>
       </c>
-      <c r="L68" s="91" t="n">
-        <f>IF(K68="","",$J$31+K68)</f>
+      <c r="L78" s="125" t="n">
+        <f>IF(K78="","",$J$41+K78)</f>
         <v>962.8045328159894</v>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="79" t="n">
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79"/>
+      <c r="B79"/>
+      <c r="C79" t="n">
         <v>0.89</v>
       </c>
-      <c r="D69" s="82" t="n">
-        <f>IF(C69&lt;$G$23,$D$35*(1-C69)-$G$41,"")</f>
+      <c r="D79" s="125" t="n">
+        <f>IF(C79&lt;$G$32,$D$45*(1-C79)-$G$51,"")</f>
         <v>28367346.93877551</v>
       </c>
-      <c r="E69" s="27" t="n">
-        <f>IF(D69="","",$G$40/D69)</f>
+      <c r="E79" s="125" t="n">
+        <f>IF(D79="","",$G$50/D79)</f>
         <v>1243.1401951038704</v>
       </c>
-      <c r="F69" s="85" t="n">
-        <f>IF(OR(D69="",E69=""),"",E69/D69)</f>
+      <c r="F79" t="n">
+        <f>IF(OR(D79="",E79=""),"",E79/D79)</f>
         <v>0.00004382292774107169</v>
       </c>
-      <c r="G69" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F69))),"",F69*$D$24)</f>
-      </c>
-      <c r="H69" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F69)),"",F69*$D$35)</f>
+      <c r="G79" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F79))),"",F79*$D$33)</f>
+      </c>
+      <c r="H79" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F79)),"",F79*$D$45)</f>
         <v>43822.92774107169</v>
       </c>
-      <c r="I69" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H69))),"",H69*$D$24)</f>
-      </c>
-      <c r="J69" s="27" t="n">
-        <f>IF(E69="","",MAX(0,E69-$G$34))</f>
+      <c r="I79" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H79))),"",H79*$D$33)</f>
+      </c>
+      <c r="J79" s="125" t="n">
+        <f>IF(E79="","",MAX(0,E79-$G$44))</f>
         <v>1070.3437079844325</v>
       </c>
-      <c r="K69" s="27" t="n">
-        <f>IF(D69="","",$G$40/($G$38-MAX(0,(C69-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K79" s="125" t="n">
+        <f>IF(D79="","",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>1153.31608844834</v>
       </c>
-      <c r="L69" s="91" t="n">
-        <f>IF(K69="","",$J$31+K69)</f>
+      <c r="L79" s="125" t="n">
+        <f>IF(K79="","",$J$41+K79)</f>
         <v>1327.8579946295904</v>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="79" t="n">
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80"/>
+      <c r="B80"/>
+      <c r="C80" t="n">
         <v>0.9</v>
       </c>
-      <c r="D70" s="82" t="n">
-        <f>IF(C70&lt;$G$23,$D$35*(1-C70)-$G$41,"")</f>
+      <c r="D80" s="125" t="n">
+        <f>IF(C80&lt;$G$32,$D$45*(1-C80)-$G$51,"")</f>
         <v>18367346.93877551</v>
       </c>
-      <c r="E70" s="27" t="n">
-        <f>IF(D70="","",$G$40/D70)</f>
+      <c r="E80" s="125" t="n">
+        <f>IF(D80="","",$G$50/D80)</f>
         <v>1919.9609679937555</v>
       </c>
-      <c r="F70" s="85" t="n">
-        <f>IF(OR(D70="",E70=""),"",E70/D70)</f>
+      <c r="F80" t="n">
+        <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
         <v>0.0001045312082574378</v>
       </c>
-      <c r="G70" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F70))),"",F70*$D$24)</f>
-      </c>
-      <c r="H70" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F70)),"",F70*$D$35)</f>
+      <c r="G80" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F80))),"",F80*$D$33)</f>
+      </c>
+      <c r="H80" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$45)</f>
         <v>104531.2082574378</v>
       </c>
-      <c r="I70" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H70))),"",H70*$D$24)</f>
-      </c>
-      <c r="J70" s="27" t="n">
-        <f>IF(E70="","",MAX(0,E70-$G$34))</f>
+      <c r="I80" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H80))),"",H80*$D$33)</f>
+      </c>
+      <c r="J80" s="125" t="n">
+        <f>IF(E80="","",MAX(0,E80-$G$44))</f>
         <v>1747.1644808743176</v>
       </c>
-      <c r="K70" s="27" t="n">
-        <f>IF(D70="","",$G$40/($G$38-MAX(0,(C70-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K80" s="125" t="n">
+        <f>IF(D80="","",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>1965.5600409836077</v>
       </c>
-      <c r="L70" s="91" t="n">
-        <f>IF(K70="","",$J$31+K70)</f>
+      <c r="L80" s="125" t="n">
+        <f>IF(K80="","",$J$41+K80)</f>
         <v>2140.1019471648583</v>
       </c>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="79" t="n">
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81" t="n">
         <v>0.905</v>
       </c>
-      <c r="D71" s="82" t="n">
-        <f>IF(C71&lt;$G$23,$D$35*(1-C71)-$G$41,"")</f>
+      <c r="D81" s="125" t="n">
+        <f>IF(C81&lt;$G$32,$D$45*(1-C81)-$G$51,"")</f>
         <v>13367346.938775495</v>
       </c>
-      <c r="E71" s="27" t="n">
-        <f>IF(D71="","",$G$40/D71)</f>
+      <c r="E81" s="125" t="n">
+        <f>IF(D81="","",$G$50/D81)</f>
         <v>2638.1143071669953</v>
       </c>
-      <c r="F71" s="85" t="n">
-        <f>IF(OR(D71="",E71=""),"",E71/D71)</f>
+      <c r="F81" t="n">
+        <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
         <v>0.00019735511610867622</v>
       </c>
-      <c r="G71" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F71))),"",F71*$D$24)</f>
-      </c>
-      <c r="H71" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F71)),"",F71*$D$35)</f>
+      <c r="G81" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F81))),"",F81*$D$33)</f>
+      </c>
+      <c r="H81" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$45)</f>
         <v>197355.11610867621</v>
       </c>
-      <c r="I71" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H71))),"",H71*$D$24)</f>
-      </c>
-      <c r="J71" s="27" t="n">
-        <f>IF(E71="","",MAX(0,E71-$G$34))</f>
+      <c r="I81" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H81))),"",H81*$D$33)</f>
+      </c>
+      <c r="J81" s="125" t="n">
+        <f>IF(E81="","",MAX(0,E81-$G$44))</f>
         <v>2465.3178200475572</v>
       </c>
-      <c r="K71" s="27" t="n">
-        <f>IF(D71="","",$G$40/($G$38-MAX(0,(C71-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K81" s="125" t="n">
+        <f>IF(D81="","",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>2909.51922906513</v>
       </c>
-      <c r="L71" s="91" t="n">
-        <f>IF(K71="","",$J$31+K71)</f>
+      <c r="L81" s="125" t="n">
+        <f>IF(K81="","",$J$41+K81)</f>
         <v>3084.06113524638</v>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="79" t="n">
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82" t="n">
         <v>0.91</v>
       </c>
-      <c r="D72" s="82" t="n">
-        <f>IF(C72&lt;$G$23,$D$35*(1-C72)-$G$41,"")</f>
+      <c r="D82" s="125" t="n">
+        <f>IF(C82&lt;$G$32,$D$45*(1-C82)-$G$51,"")</f>
         <v>8367346.938775495</v>
       </c>
-      <c r="E72" s="27" t="n">
-        <f>IF(D72="","",$G$40/D72)</f>
+      <c r="E82" s="125" t="n">
+        <f>IF(D82="","",$G$50/D82)</f>
         <v>4214.548466327764</v>
       </c>
-      <c r="F72" s="85" t="n">
-        <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
+      <c r="F82" t="n">
+        <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
         <v>0.0005036899386586849</v>
       </c>
-      <c r="G72" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F72))),"",F72*$D$24)</f>
-      </c>
-      <c r="H72" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$35)</f>
+      <c r="G82" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F82))),"",F82*$D$33)</f>
+      </c>
+      <c r="H82" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$45)</f>
         <v>503689.93865868496</v>
       </c>
-      <c r="I72" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H72))),"",H72*$D$24)</f>
-      </c>
-      <c r="J72" s="27" t="n">
-        <f>IF(E72="","",MAX(0,E72-$G$34))</f>
+      <c r="I82" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H82))),"",H82*$D$33)</f>
+      </c>
+      <c r="J82" s="125" t="n">
+        <f>IF(E82="","",MAX(0,E82-$G$44))</f>
         <v>4041.751979208326</v>
       </c>
-      <c r="K72" s="27" t="n">
-        <f>IF(D72="","",$G$40/($G$38-MAX(0,(C72-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K82" s="125" t="n">
+        <f>IF(D82="","",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>5345.542940243272</v>
       </c>
-      <c r="L72" s="91" t="n">
-        <f>IF(K72="","",$J$31+K72)</f>
+      <c r="L82" s="125" t="n">
+        <f>IF(K82="","",$J$41+K82)</f>
         <v>5520.084846424523</v>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="79" t="n">
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83" t="n">
         <v>0.915</v>
       </c>
-      <c r="D73" s="82" t="n">
-        <f>IF(C73&lt;$G$23,$D$35*(1-C73)-$G$41,"")</f>
+      <c r="D83" s="125" t="n">
+        <f>IF(C83&lt;$G$32,$D$45*(1-C83)-$G$51,"")</f>
         <v>3367346.9387754947</v>
       </c>
-      <c r="E73" s="27" t="n">
-        <f>IF(D73="","",$G$40/D73)</f>
+      <c r="E83" s="125" t="n">
+        <f>IF(D83="","",$G$50/D83)</f>
         <v>10472.514370875078</v>
       </c>
-      <c r="F73" s="85" t="n">
-        <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
+      <c r="F83" t="n">
+        <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
         <v>0.0031100194192295832</v>
       </c>
-      <c r="G73" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F73))),"",F73*$D$24)</f>
-      </c>
-      <c r="H73" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$35)</f>
+      <c r="G83" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F83))),"",F83*$D$33)</f>
+      </c>
+      <c r="H83" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$45)</f>
         <v>3110019.4192295833</v>
       </c>
-      <c r="I73" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H73))),"",H73*$D$24)</f>
-      </c>
-      <c r="J73" s="27" t="n">
-        <f>IF(E73="","",MAX(0,E73-$G$34))</f>
+      <c r="I83" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H83))),"",H83*$D$33)</f>
+      </c>
+      <c r="J83" s="125" t="n">
+        <f>IF(E83="","",MAX(0,E83-$G$44))</f>
         <v>10299.71788375564</v>
       </c>
-      <c r="K73" s="27" t="n">
-        <f>IF(D73="","",$G$40/($G$38-MAX(0,(C73-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
+      <c r="K83" s="125" t="n">
+        <f>IF(D83="","",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>26145.43770491818</v>
       </c>
-      <c r="L73" s="91" t="n">
-        <f>IF(K73="","",$J$31+K73)</f>
+      <c r="L83" s="125" t="n">
+        <f>IF(K83="","",$J$41+K83)</f>
         <v>26319.97961109943</v>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="79" t="n">
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84" t="n">
         <v>0.918</v>
       </c>
-      <c r="D74" s="82" t="str">
-        <f>IF(C74&lt;$G$23,$D$35*(1-C74)-$G$41,"")</f>
-      </c>
-      <c r="E74" s="27" t="str">
-        <f>IF(D74="","",$G$40/D74)</f>
-      </c>
-      <c r="F74" s="85" t="str">
-        <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
-      </c>
-      <c r="G74" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F74))),"",F74*$D$24)</f>
-      </c>
-      <c r="H74" s="27" t="str">
-        <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$35)</f>
-      </c>
-      <c r="I74" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H74))),"",H74*$D$24)</f>
-      </c>
-      <c r="J74" s="27" t="str">
-        <f>IF(E74="","",MAX(0,E74-$G$34))</f>
-      </c>
-      <c r="K74" s="27" t="str">
-        <f>IF(D74="","",$G$40/($G$38-MAX(0,(C74-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L74" s="91" t="str">
-        <f>IF(K74="","",$J$31+K74)</f>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="80" t="n">
+      <c r="D84" s="125" t="str">
+        <f>IF(C84&lt;$G$32,$D$45*(1-C84)-$G$51,"")</f>
+      </c>
+      <c r="E84" s="125" t="str">
+        <f>IF(D84="","",$G$50/D84)</f>
+      </c>
+      <c r="F84" t="str">
+        <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
+      </c>
+      <c r="G84" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F84))),"",F84*$D$33)</f>
+      </c>
+      <c r="H84" s="125" t="str">
+        <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$45)</f>
+      </c>
+      <c r="I84" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H84))),"",H84*$D$33)</f>
+      </c>
+      <c r="J84" s="125" t="str">
+        <f>IF(E84="","",MAX(0,E84-$G$44))</f>
+      </c>
+      <c r="K84" s="125" t="str">
+        <f>IF(D84="","",$G$50/($G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L84" s="125" t="str">
+        <f>IF(K84="","",$J$41+K84)</f>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85"/>
+      <c r="B85"/>
+      <c r="C85" t="n">
         <v>0.9183673469387755</v>
       </c>
-      <c r="D75" s="83" t="str">
-        <f>IF(C75&lt;$G$23,$D$35*(1-C75)-$G$41,"")</f>
-      </c>
-      <c r="E75" s="28" t="str">
-        <f>IF(D75="","",$G$40/D75)</f>
-      </c>
-      <c r="F75" s="86" t="str">
-        <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
-      </c>
-      <c r="G75" s="86" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F75))),"",F75*$D$24)</f>
-      </c>
-      <c r="H75" s="28" t="str">
-        <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$35)</f>
-      </c>
-      <c r="I75" s="28" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H75))),"",H75*$D$24)</f>
-      </c>
-      <c r="J75" s="28" t="str">
-        <f>IF(E75="","",MAX(0,E75-$G$34))</f>
-      </c>
-      <c r="K75" s="28" t="str">
-        <f>IF(D75="","",$G$40/($G$38-MAX(0,(C75-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L75" s="92" t="str">
-        <f>IF(K75="","",$J$31+K75)</f>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-    </row>
-    <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="102" t="str">
+      <c r="D85" s="125" t="str">
+        <f>IF(C85&lt;$G$32,$D$45*(1-C85)-$G$51,"")</f>
+      </c>
+      <c r="E85" s="125" t="str">
+        <f>IF(D85="","",$G$50/D85)</f>
+      </c>
+      <c r="F85" t="str">
+        <f>IF(OR(D85="",E85=""),"",E85/D85)</f>
+      </c>
+      <c r="G85" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F85))),"",F85*$D$33)</f>
+      </c>
+      <c r="H85" s="125" t="str">
+        <f>IF(NOT(ISNUMBER(F85)),"",F85*$D$45)</f>
+      </c>
+      <c r="I85" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H85))),"",H85*$D$33)</f>
+      </c>
+      <c r="J85" s="125" t="str">
+        <f>IF(E85="","",MAX(0,E85-$G$44))</f>
+      </c>
+      <c r="K85" s="125" t="str">
+        <f>IF(D85="","",$G$50/($G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L85" s="125" t="str">
+        <f>IF(K85="","",$J$41+K85)</f>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86"/>
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
+      <c r="I86"/>
+      <c r="J86"/>
+      <c r="K86"/>
+      <c r="L86"/>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="I87"/>
+      <c r="J87"/>
+      <c r="K87"/>
+      <c r="L87"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88"/>
+      <c r="B88"/>
+      <c r="C88" t="str">
         <v>外盘回落参考</v>
       </c>
-      <c r="D78" s="102"/>
-      <c r="E78" s="102"/>
-      <c r="F78" s="102"/>
-      <c r="G78" s="102"/>
-      <c r="H78" s="102"/>
-      <c r="I78" s="102"/>
-      <c r="J78" s="102"/>
-      <c r="K78" s="102"/>
-      <c r="L78" s="102"/>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="77" t="str">
+      <c r="D88"/>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="I88"/>
+      <c r="J88"/>
+      <c r="K88"/>
+      <c r="L88"/>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D79" s="77" t="str">
+      <c r="D89" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E79" s="77" t="str">
+      <c r="E89" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F79" s="77" t="str">
+      <c r="F89" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G79" s="77" t="str">
+      <c r="G89" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H79" s="77" t="str">
+      <c r="H89" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I79" s="77" t="str">
+      <c r="I89" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J79" s="77" t="str">
+      <c r="J89" t="str">
         <v>较毕业点回撤</v>
       </c>
-      <c r="K79" s="77" t="str"/>
-      <c r="L79" s="77" t="str"/>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="97" t="n">
+      <c r="K89" t="str"/>
+      <c r="L89" t="str"/>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90"/>
+      <c r="B90"/>
+      <c r="C90" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="D80" s="98" t="n">
-        <f>$D$35*(1-C80)-$G$41</f>
+      <c r="D90" s="125" t="n">
+        <f>$D$45*(1-C90)-$G$51</f>
         <v>204081632.6530612</v>
       </c>
-      <c r="E80" s="99" t="n">
-        <f>$G$40/D80</f>
+      <c r="E90" s="125" t="n">
+        <f>$G$50/D90</f>
         <v>172.79648711943798</v>
       </c>
-      <c r="F80" s="100" t="n">
-        <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
+      <c r="F90" t="n">
+        <f>IF(OR(D90="",E90=""),"",E90/D90)</f>
         <v>8.467027868852462e-7</v>
       </c>
-      <c r="G80" s="100" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F80))),"",F80*$D$24)</f>
-      </c>
-      <c r="H80" s="99" t="n">
-        <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$35)</f>
+      <c r="G90" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F90))),"",F90*$D$33)</f>
+      </c>
+      <c r="H90" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F90)),"",F90*$D$45)</f>
         <v>846.7027868852463</v>
       </c>
-      <c r="I80" s="99" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H80))),"",H80*$D$24)</f>
-      </c>
-      <c r="J80" s="97" t="n">
-        <f>IF($H$80&gt;0,1-H80/$H$80,0)</f>
+      <c r="I90" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H90))),"",H90*$D$33)</f>
+      </c>
+      <c r="J90" t="n">
+        <f>IF($H$90&gt;0,1-H90/$H$90,0)</f>
         <v>0</v>
       </c>
-      <c r="K80" s="99"/>
-      <c r="L80" s="99"/>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="79" t="n">
+      <c r="K90"/>
+      <c r="L90"/>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91" t="n">
         <v>0.7</v>
       </c>
-      <c r="D81" s="82" t="n">
-        <f>$D$35*(1-C81)-$G$41</f>
+      <c r="D91" s="125" t="n">
+        <f>$D$45*(1-C91)-$G$51</f>
         <v>218367346.9387756</v>
       </c>
-      <c r="E81" s="27" t="n">
-        <f>$G$40/D81</f>
+      <c r="E91" s="125" t="n">
+        <f>$G$50/D91</f>
         <v>161.49204403685786</v>
       </c>
-      <c r="F81" s="85" t="n">
-        <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
+      <c r="F91" t="n">
+        <f>IF(OR(D91="",E91=""),"",E91/D91)</f>
         <v>7.395430054024329e-7</v>
       </c>
-      <c r="G81" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F81))),"",F81*$D$24)</f>
-      </c>
-      <c r="H81" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$35)</f>
+      <c r="G91" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F91))),"",F91*$D$33)</f>
+      </c>
+      <c r="H91" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F91)),"",F91*$D$45)</f>
         <v>739.5430054024329</v>
       </c>
-      <c r="I81" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H81))),"",H81*$D$24)</f>
-      </c>
-      <c r="J81" s="79" t="n">
-        <f>IF($H$80&gt;0,1-H81/$H$80,0)</f>
+      <c r="I91" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H91))),"",H91*$D$33)</f>
+      </c>
+      <c r="J91" t="n">
+        <f>IF($H$90&gt;0,1-H91/$H$90,0)</f>
         <v>0.12656127172678933</v>
       </c>
-      <c r="K81" s="27"/>
-      <c r="L81" s="27"/>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="79" t="n">
+      <c r="K91"/>
+      <c r="L91"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92" t="n">
         <v>0.6</v>
       </c>
-      <c r="D82" s="82" t="n">
-        <f>$D$35*(1-C82)-$G$41</f>
+      <c r="D92" s="125" t="n">
+        <f>$D$45*(1-C92)-$G$51</f>
         <v>318367346.93877554</v>
       </c>
-      <c r="E82" s="27" t="n">
-        <f>$G$40/D82</f>
+      <c r="E92" s="125" t="n">
+        <f>$G$50/D92</f>
         <v>110.76697892271665</v>
       </c>
-      <c r="F82" s="85" t="n">
-        <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
+      <c r="F92" t="n">
+        <f>IF(OR(D92="",E92=""),"",E92/D92)</f>
         <v>3.479219209751997e-7</v>
       </c>
-      <c r="G82" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F82))),"",F82*$D$24)</f>
-      </c>
-      <c r="H82" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$35)</f>
+      <c r="G92" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F92))),"",F92*$D$33)</f>
+      </c>
+      <c r="H92" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F92)),"",F92*$D$45)</f>
         <v>347.9219209751997</v>
       </c>
-      <c r="I82" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H82))),"",H82*$D$24)</f>
-      </c>
-      <c r="J82" s="79" t="n">
-        <f>IF($H$80&gt;0,1-H82/$H$80,0)</f>
+      <c r="I92" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H92))),"",H92*$D$33)</f>
+      </c>
+      <c r="J92" t="n">
+        <f>IF($H$90&gt;0,1-H92/$H$90,0)</f>
         <v>0.5890861275476661</v>
       </c>
-      <c r="K82" s="27"/>
-      <c r="L82" s="27"/>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="79" t="n">
+      <c r="K92"/>
+      <c r="L92"/>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93"/>
+      <c r="B93"/>
+      <c r="C93" t="n">
         <v>0.5</v>
       </c>
-      <c r="D83" s="82" t="n">
-        <f>$D$35*(1-C83)-$G$41</f>
+      <c r="D93" s="125" t="n">
+        <f>$D$45*(1-C93)-$G$51</f>
         <v>418367346.93877554</v>
       </c>
-      <c r="E83" s="27" t="n">
-        <f>$G$40/D83</f>
+      <c r="E93" s="125" t="n">
+        <f>$G$50/D93</f>
         <v>84.29096932655511</v>
       </c>
-      <c r="F83" s="85" t="n">
-        <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
+      <c r="F93" t="n">
+        <f>IF(OR(D93="",E93=""),"",E93/D93)</f>
         <v>2.0147597546347317e-7</v>
       </c>
-      <c r="G83" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F83))),"",F83*$D$24)</f>
-      </c>
-      <c r="H83" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$35)</f>
+      <c r="G93" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F93))),"",F93*$D$33)</f>
+      </c>
+      <c r="H93" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F93)),"",F93*$D$45)</f>
         <v>201.47597546347316</v>
       </c>
-      <c r="I83" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H83))),"",H83*$D$24)</f>
-      </c>
-      <c r="J83" s="79" t="n">
-        <f>IF($H$80&gt;0,1-H83/$H$80,0)</f>
+      <c r="I93" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H93))),"",H93*$D$33)</f>
+      </c>
+      <c r="J93" t="n">
+        <f>IF($H$90&gt;0,1-H93/$H$90,0)</f>
         <v>0.7620464009518144</v>
       </c>
-      <c r="K83" s="27"/>
-      <c r="L83" s="27"/>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="79" t="n">
+      <c r="K93"/>
+      <c r="L93"/>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94" t="n">
         <v>0.4</v>
       </c>
-      <c r="D84" s="82" t="n">
-        <f>$D$35*(1-C84)-$G$41</f>
+      <c r="D94" s="125" t="n">
+        <f>$D$45*(1-C94)-$G$51</f>
         <v>518367346.93877554</v>
       </c>
-      <c r="E84" s="27" t="n">
-        <f>$G$40/D84</f>
+      <c r="E94" s="125" t="n">
+        <f>$G$50/D94</f>
         <v>68.03011303914882</v>
       </c>
-      <c r="F84" s="85" t="n">
-        <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
+      <c r="F94" t="n">
+        <f>IF(OR(D94="",E94=""),"",E94/D94)</f>
         <v>1.3123919444560203e-7</v>
       </c>
-      <c r="G84" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F84))),"",F84*$D$24)</f>
-      </c>
-      <c r="H84" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$35)</f>
+      <c r="G94" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F94))),"",F94*$D$33)</f>
+      </c>
+      <c r="H94" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F94)),"",F94*$D$45)</f>
         <v>131.23919444560204</v>
       </c>
-      <c r="I84" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H84))),"",H84*$D$24)</f>
-      </c>
-      <c r="J84" s="79" t="n">
-        <f>IF($H$80&gt;0,1-H84/$H$80,0)</f>
+      <c r="I94" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H94))),"",H94*$D$33)</f>
+      </c>
+      <c r="J94" t="n">
+        <f>IF($H$90&gt;0,1-H94/$H$90,0)</f>
         <v>0.84499968999938</v>
       </c>
-      <c r="K84" s="27"/>
-      <c r="L84" s="27"/>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="79" t="n">
+      <c r="K94"/>
+      <c r="L94"/>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95"/>
+      <c r="B95"/>
+      <c r="C95" t="n">
         <v>0.3</v>
       </c>
-      <c r="D85" s="82" t="n">
-        <f>$D$35*(1-C85)-$G$41</f>
+      <c r="D95" s="125" t="n">
+        <f>$D$45*(1-C95)-$G$51</f>
         <v>618367346.9387755</v>
       </c>
-      <c r="E85" s="27" t="n">
-        <f>$G$40/D85</f>
+      <c r="E95" s="125" t="n">
+        <f>$G$50/D95</f>
         <v>57.028543603774914</v>
       </c>
-      <c r="F85" s="85" t="n">
-        <f>IF(OR(D85="",E85=""),"",E85/D85)</f>
+      <c r="F95" t="n">
+        <f>IF(OR(D95="",E95=""),"",E95/D95)</f>
         <v>9.222437744504854e-8</v>
       </c>
-      <c r="G85" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F85))),"",F85*$D$24)</f>
-      </c>
-      <c r="H85" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F85)),"",F85*$D$35)</f>
+      <c r="G95" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F95))),"",F95*$D$33)</f>
+      </c>
+      <c r="H95" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F95)),"",F95*$D$45)</f>
         <v>92.22437744504853</v>
       </c>
-      <c r="I85" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H85))),"",H85*$D$24)</f>
-      </c>
-      <c r="J85" s="79" t="n">
-        <f>IF($H$80&gt;0,1-H85/$H$80,0)</f>
+      <c r="I95" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H95))),"",H95*$D$33)</f>
+      </c>
+      <c r="J95" t="n">
+        <f>IF($H$90&gt;0,1-H95/$H$90,0)</f>
         <v>0.8910782167325644</v>
       </c>
-      <c r="K85" s="27"/>
-      <c r="L85" s="27"/>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="79" t="n">
+      <c r="K95"/>
+      <c r="L95"/>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96"/>
+      <c r="B96"/>
+      <c r="C96" t="n">
         <v>0.2</v>
       </c>
-      <c r="D86" s="82" t="n">
-        <f>$D$35*(1-C86)-$G$41</f>
+      <c r="D96" s="125" t="n">
+        <f>$D$45*(1-C96)-$G$51</f>
         <v>718367346.9387755</v>
       </c>
-      <c r="E86" s="27" t="n">
-        <f>$G$40/D86</f>
+      <c r="E96" s="125" t="n">
+        <f>$G$50/D96</f>
         <v>49.089911113476695</v>
       </c>
-      <c r="F86" s="85" t="n">
-        <f>IF(OR(D86="",E86=""),"",E86/D86)</f>
+      <c r="F96" t="n">
+        <f>IF(OR(D96="",E96=""),"",E96/D96)</f>
         <v>6.833538762955562e-8</v>
       </c>
-      <c r="G86" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F86))),"",F86*$D$24)</f>
-      </c>
-      <c r="H86" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F86)),"",F86*$D$35)</f>
+      <c r="G96" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F96))),"",F96*$D$33)</f>
+      </c>
+      <c r="H96" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F96)),"",F96*$D$45)</f>
         <v>68.33538762955563</v>
       </c>
-      <c r="I86" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H86))),"",H86*$D$24)</f>
-      </c>
-      <c r="J86" s="79" t="n">
-        <f>IF($H$80&gt;0,1-H86/$H$80,0)</f>
+      <c r="I96" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H96))),"",H96*$D$33)</f>
+      </c>
+      <c r="J96" t="n">
+        <f>IF($H$90&gt;0,1-H96/$H$90,0)</f>
         <v>0.9192923553719008</v>
       </c>
-      <c r="K86" s="27"/>
-      <c r="L86" s="27"/>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="79" t="n">
+      <c r="K96"/>
+      <c r="L96"/>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97" t="n">
         <v>0.1</v>
       </c>
-      <c r="D87" s="82" t="n">
-        <f>$D$35*(1-C87)-$G$41</f>
+      <c r="D97" s="125" t="n">
+        <f>$D$45*(1-C97)-$G$51</f>
         <v>818367346.9387755</v>
       </c>
-      <c r="E87" s="27" t="n">
-        <f>$G$40/D87</f>
+      <c r="E97" s="125" t="n">
+        <f>$G$50/D97</f>
         <v>43.09139329661795</v>
       </c>
-      <c r="F87" s="85" t="n">
-        <f>IF(OR(D87="",E87=""),"",E87/D87)</f>
+      <c r="F97" t="n">
+        <f>IF(OR(D97="",E97=""),"",E97/D97)</f>
         <v>5.265531849212667e-8</v>
       </c>
-      <c r="G87" s="85" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F87))),"",F87*$D$24)</f>
-      </c>
-      <c r="H87" s="27" t="n">
-        <f>IF(NOT(ISNUMBER(F87)),"",F87*$D$35)</f>
+      <c r="G97" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F97))),"",F97*$D$33)</f>
+      </c>
+      <c r="H97" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F97)),"",F97*$D$45)</f>
         <v>52.65531849212667</v>
       </c>
-      <c r="I87" s="27" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H87))),"",H87*$D$24)</f>
-      </c>
-      <c r="J87" s="79" t="n">
-        <f>IF($H$80&gt;0,1-H87/$H$80,0)</f>
+      <c r="I97" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H97))),"",H97*$D$33)</f>
+      </c>
+      <c r="J97" t="n">
+        <f>IF($H$90&gt;0,1-H97/$H$90,0)</f>
         <v>0.9378113320190795</v>
       </c>
-      <c r="K87" s="27"/>
-      <c r="L87" s="27"/>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="80" t="n">
+      <c r="K97"/>
+      <c r="L97"/>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98" t="n">
         <v>0</v>
       </c>
-      <c r="D88" s="83" t="n">
-        <f>$D$35*(1-C88)-$G$41</f>
+      <c r="D98" s="125" t="n">
+        <f>$D$45*(1-C98)-$G$51</f>
         <v>918367346.9387755</v>
       </c>
-      <c r="E88" s="28" t="n">
-        <f>$G$40/D88</f>
+      <c r="E98" s="125" t="n">
+        <f>$G$50/D98</f>
         <v>38.399219359875104</v>
       </c>
-      <c r="F88" s="86" t="n">
-        <f>IF(OR(D88="",E88=""),"",E88/D88)</f>
+      <c r="F98" t="n">
+        <f>IF(OR(D98="",E98=""),"",E98/D98)</f>
         <v>4.181248330297511e-8</v>
       </c>
-      <c r="G88" s="86" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F88))),"",F88*$D$24)</f>
-      </c>
-      <c r="H88" s="28" t="n">
-        <f>IF(NOT(ISNUMBER(F88)),"",F88*$D$35)</f>
+      <c r="G98" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F98))),"",F98*$D$33)</f>
+      </c>
+      <c r="H98" s="125" t="n">
+        <f>IF(NOT(ISNUMBER(F98)),"",F98*$D$45)</f>
         <v>41.81248330297511</v>
       </c>
-      <c r="I88" s="28" t="str">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H88))),"",H88*$D$24)</f>
-      </c>
-      <c r="J88" s="80" t="n">
-        <f>IF($H$80&gt;0,1-H88/$H$80,0)</f>
+      <c r="I98" s="125" t="str">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H98))),"",H98*$D$33)</f>
+      </c>
+      <c r="J98" t="n">
+        <f>IF($H$90&gt;0,1-H98/$H$90,0)</f>
         <v>0.9506172839506173</v>
       </c>
-      <c r="K88" s="103" t="str">
+      <c r="K98" t="str">
         <v>沉没成本 / Quote</v>
       </c>
-      <c r="L88" s="28" t="n">
-        <f>E88</f>
+      <c r="L98" t="n">
+        <f>E98</f>
         <v>38.399219359875104</v>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="L89" s="2"/>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-      <c r="L92" s="2"/>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
-      <c r="L93" s="2"/>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
-      <c r="L94" s="2"/>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
-      <c r="L95" s="2"/>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
-      <c r="L96" s="2"/>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
-      <c r="L97" s="2"/>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
-      <c r="L98" s="2"/>
-    </row>
     <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
-      <c r="L99" s="2"/>
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+      <c r="I99"/>
+      <c r="J99"/>
+      <c r="K99"/>
+      <c r="L99"/>
     </row>
     <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
-      <c r="L100" s="2"/>
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
+      <c r="H100"/>
+      <c r="I100"/>
+      <c r="J100"/>
+      <c r="K100"/>
+      <c r="L100"/>
     </row>
     <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
-      <c r="L101" s="2"/>
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
+      <c r="L101"/>
     </row>
     <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
-      <c r="L102" s="2"/>
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102"/>
+      <c r="L102"/>
     </row>
     <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
-      <c r="L103" s="2"/>
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="I103"/>
+      <c r="J103"/>
+      <c r="K103"/>
+      <c r="L103"/>
     </row>
     <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
-      <c r="L104" s="2"/>
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104"/>
+      <c r="J104"/>
+      <c r="K104"/>
+      <c r="L104"/>
     </row>
     <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
-      <c r="L105" s="2"/>
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="I105"/>
+      <c r="J105"/>
+      <c r="K105"/>
+      <c r="L105"/>
     </row>
     <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
-      <c r="L106" s="2"/>
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="I106"/>
+      <c r="J106"/>
+      <c r="K106"/>
+      <c r="L106"/>
     </row>
     <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
-      <c r="L107" s="2"/>
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107"/>
+      <c r="J107"/>
+      <c r="K107"/>
+      <c r="L107"/>
     </row>
     <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
-      <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
-      <c r="L108" s="2"/>
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+      <c r="J108"/>
+      <c r="K108"/>
+      <c r="L108"/>
     </row>
     <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
-      <c r="J109" s="2"/>
-      <c r="K109" s="2"/>
-      <c r="L109" s="2"/>
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="I109"/>
+      <c r="J109"/>
+      <c r="K109"/>
+      <c r="L109"/>
     </row>
     <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="2"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2"/>
-      <c r="J110" s="2"/>
-      <c r="K110" s="2"/>
-      <c r="L110" s="2"/>
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110"/>
+      <c r="K110"/>
+      <c r="L110"/>
     </row>
     <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
-      <c r="J111" s="2"/>
-      <c r="K111" s="2"/>
-      <c r="L111" s="2"/>
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="K111"/>
+      <c r="L111"/>
     </row>
     <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2"/>
-      <c r="J112" s="2"/>
-      <c r="K112" s="2"/>
-      <c r="L112" s="2"/>
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+      <c r="H112"/>
+      <c r="I112"/>
+      <c r="J112"/>
+      <c r="K112"/>
+      <c r="L112"/>
     </row>
     <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
-      <c r="J113" s="2"/>
-      <c r="K113" s="2"/>
-      <c r="L113" s="2"/>
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="I113"/>
+      <c r="J113"/>
+      <c r="K113"/>
+      <c r="L113"/>
     </row>
     <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
-      <c r="K114" s="2"/>
-      <c r="L114" s="2"/>
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
+      <c r="H114"/>
+      <c r="I114"/>
+      <c r="J114"/>
+      <c r="K114"/>
+      <c r="L114"/>
     </row>
     <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="2"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2"/>
-      <c r="J115" s="2"/>
-      <c r="K115" s="2"/>
-      <c r="L115" s="2"/>
+      <c r="A115"/>
+      <c r="B115"/>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
+      <c r="H115"/>
+      <c r="I115"/>
+      <c r="J115"/>
+      <c r="K115"/>
+      <c r="L115"/>
     </row>
     <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
-      <c r="J116" s="2"/>
-      <c r="K116" s="2"/>
-      <c r="L116" s="2"/>
+      <c r="A116"/>
+      <c r="B116"/>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116"/>
+      <c r="H116"/>
+      <c r="I116"/>
+      <c r="J116"/>
+      <c r="K116"/>
+      <c r="L116"/>
     </row>
     <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="2"/>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
-      <c r="J117" s="2"/>
-      <c r="K117" s="2"/>
-      <c r="L117" s="2"/>
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
+      <c r="H117"/>
+      <c r="I117"/>
+      <c r="J117"/>
+      <c r="K117"/>
+      <c r="L117"/>
     </row>
     <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
-      <c r="J118" s="2"/>
-      <c r="K118" s="2"/>
-      <c r="L118" s="2"/>
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
+      <c r="G118"/>
+      <c r="H118"/>
+      <c r="I118"/>
+      <c r="J118"/>
+      <c r="K118"/>
+      <c r="L118"/>
     </row>
     <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="2"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-      <c r="H119" s="2"/>
-      <c r="I119" s="2"/>
-      <c r="J119" s="2"/>
-      <c r="K119" s="2"/>
-      <c r="L119" s="2"/>
+      <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
+      <c r="H119"/>
+      <c r="I119"/>
+      <c r="J119"/>
+      <c r="K119"/>
+      <c r="L119"/>
     </row>
     <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="2"/>
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-      <c r="H120" s="2"/>
-      <c r="I120" s="2"/>
-      <c r="J120" s="2"/>
-      <c r="K120" s="2"/>
-      <c r="L120" s="2"/>
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
+      <c r="H120"/>
+      <c r="I120"/>
+      <c r="J120"/>
+      <c r="K120"/>
+      <c r="L120"/>
     </row>
     <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="2"/>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="2"/>
-      <c r="J121" s="2"/>
-      <c r="K121" s="2"/>
-      <c r="L121" s="2"/>
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
+      <c r="D121"/>
+      <c r="E121"/>
+      <c r="F121"/>
+      <c r="G121"/>
+      <c r="H121"/>
+      <c r="I121"/>
+      <c r="J121"/>
+      <c r="K121"/>
+      <c r="L121"/>
     </row>
     <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="2"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-      <c r="H122" s="2"/>
-      <c r="I122" s="2"/>
-      <c r="J122" s="2"/>
-      <c r="K122" s="2"/>
-      <c r="L122" s="2"/>
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="H122"/>
+      <c r="I122"/>
+      <c r="J122"/>
+      <c r="K122"/>
+      <c r="L122"/>
     </row>
     <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="2"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-      <c r="H123" s="2"/>
-      <c r="I123" s="2"/>
-      <c r="J123" s="2"/>
-      <c r="K123" s="2"/>
-      <c r="L123" s="2"/>
+      <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
+      <c r="G123"/>
+      <c r="H123"/>
+      <c r="I123"/>
+      <c r="J123"/>
+      <c r="K123"/>
+      <c r="L123"/>
     </row>
     <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="2"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-      <c r="H124" s="2"/>
-      <c r="I124" s="2"/>
-      <c r="J124" s="2"/>
-      <c r="K124" s="2"/>
-      <c r="L124" s="2"/>
+      <c r="A124"/>
+      <c r="B124"/>
+      <c r="C124"/>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124"/>
+      <c r="G124"/>
+      <c r="H124"/>
+      <c r="I124"/>
+      <c r="J124"/>
+      <c r="K124"/>
+      <c r="L124"/>
     </row>
     <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-      <c r="H125" s="2"/>
-      <c r="I125" s="2"/>
-      <c r="J125" s="2"/>
-      <c r="K125" s="2"/>
-      <c r="L125" s="2"/>
+      <c r="A125"/>
+      <c r="B125"/>
+      <c r="C125"/>
+      <c r="D125"/>
+      <c r="E125"/>
+      <c r="F125"/>
+      <c r="G125"/>
+      <c r="H125"/>
+      <c r="I125"/>
+      <c r="J125"/>
+      <c r="K125"/>
+      <c r="L125"/>
     </row>
     <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="2"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-      <c r="H126" s="2"/>
-      <c r="I126" s="2"/>
-      <c r="J126" s="2"/>
-      <c r="K126" s="2"/>
-      <c r="L126" s="2"/>
+      <c r="A126"/>
+      <c r="B126"/>
+      <c r="C126"/>
+      <c r="D126"/>
+      <c r="E126"/>
+      <c r="F126"/>
+      <c r="G126"/>
+      <c r="H126"/>
+      <c r="I126"/>
+      <c r="J126"/>
+      <c r="K126"/>
+      <c r="L126"/>
     </row>
     <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="2"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-      <c r="H127" s="2"/>
-      <c r="I127" s="2"/>
-      <c r="J127" s="2"/>
-      <c r="K127" s="2"/>
-      <c r="L127" s="2"/>
+      <c r="A127"/>
+      <c r="B127"/>
+      <c r="C127"/>
+      <c r="D127"/>
+      <c r="E127"/>
+      <c r="F127"/>
+      <c r="G127"/>
+      <c r="H127"/>
+      <c r="I127"/>
+      <c r="J127"/>
+      <c r="K127"/>
+      <c r="L127"/>
     </row>
     <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="2"/>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-      <c r="H128" s="2"/>
-      <c r="I128" s="2"/>
-      <c r="J128" s="2"/>
-      <c r="K128" s="2"/>
-      <c r="L128" s="2"/>
+      <c r="A128"/>
+      <c r="B128"/>
+      <c r="C128"/>
+      <c r="D128"/>
+      <c r="E128"/>
+      <c r="F128"/>
+      <c r="G128"/>
+      <c r="H128"/>
+      <c r="I128"/>
+      <c r="J128"/>
+      <c r="K128"/>
+      <c r="L128"/>
     </row>
     <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="2"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-      <c r="H129" s="2"/>
-      <c r="I129" s="2"/>
-      <c r="J129" s="2"/>
-      <c r="K129" s="2"/>
-      <c r="L129" s="2"/>
+      <c r="A129"/>
+      <c r="B129"/>
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
+      <c r="H129"/>
+      <c r="I129"/>
+      <c r="J129"/>
+      <c r="K129"/>
+      <c r="L129"/>
     </row>
     <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="2"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
-      <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-      <c r="H130" s="2"/>
-      <c r="I130" s="2"/>
-      <c r="J130" s="2"/>
-      <c r="K130" s="2"/>
-      <c r="L130" s="2"/>
+      <c r="A130"/>
+      <c r="B130"/>
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="H130"/>
+      <c r="I130"/>
+      <c r="J130"/>
+      <c r="K130"/>
+      <c r="L130"/>
     </row>
     <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="2"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2"/>
-      <c r="J131" s="2"/>
-      <c r="K131" s="2"/>
-      <c r="L131" s="2"/>
+      <c r="A131"/>
+      <c r="B131"/>
+      <c r="C131"/>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
+      <c r="H131"/>
+      <c r="I131"/>
+      <c r="J131"/>
+      <c r="K131"/>
+      <c r="L131"/>
     </row>
     <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="2"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-      <c r="H132" s="2"/>
-      <c r="I132" s="2"/>
-      <c r="J132" s="2"/>
-      <c r="K132" s="2"/>
-      <c r="L132" s="2"/>
+      <c r="A132"/>
+      <c r="B132"/>
+      <c r="C132"/>
+      <c r="D132"/>
+      <c r="E132"/>
+      <c r="F132"/>
+      <c r="G132"/>
+      <c r="H132"/>
+      <c r="I132"/>
+      <c r="J132"/>
+      <c r="K132"/>
+      <c r="L132"/>
     </row>
     <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="2"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-      <c r="H133" s="2"/>
-      <c r="I133" s="2"/>
-      <c r="J133" s="2"/>
-      <c r="K133" s="2"/>
-      <c r="L133" s="2"/>
+      <c r="A133"/>
+      <c r="B133"/>
+      <c r="C133"/>
+      <c r="D133"/>
+      <c r="E133"/>
+      <c r="F133"/>
+      <c r="G133"/>
+      <c r="H133"/>
+      <c r="I133"/>
+      <c r="J133"/>
+      <c r="K133"/>
+      <c r="L133"/>
     </row>
     <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="2"/>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-      <c r="H134" s="2"/>
-      <c r="I134" s="2"/>
-      <c r="J134" s="2"/>
-      <c r="K134" s="2"/>
-      <c r="L134" s="2"/>
+      <c r="A134"/>
+      <c r="B134"/>
+      <c r="C134"/>
+      <c r="D134"/>
+      <c r="E134"/>
+      <c r="F134"/>
+      <c r="G134"/>
+      <c r="H134"/>
+      <c r="I134"/>
+      <c r="J134"/>
+      <c r="K134"/>
+      <c r="L134"/>
     </row>
     <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="2"/>
-      <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-      <c r="H135" s="2"/>
-      <c r="I135" s="2"/>
-      <c r="J135" s="2"/>
-      <c r="K135" s="2"/>
-      <c r="L135" s="2"/>
+      <c r="A135"/>
+      <c r="B135"/>
+      <c r="C135"/>
+      <c r="D135"/>
+      <c r="E135"/>
+      <c r="F135"/>
+      <c r="G135"/>
+      <c r="H135"/>
+      <c r="I135"/>
+      <c r="J135"/>
+      <c r="K135"/>
+      <c r="L135"/>
     </row>
     <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="2"/>
-      <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
-      <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-      <c r="H136" s="2"/>
-      <c r="I136" s="2"/>
-      <c r="J136" s="2"/>
-      <c r="K136" s="2"/>
-      <c r="L136" s="2"/>
+      <c r="A136"/>
+      <c r="B136"/>
+      <c r="C136"/>
+      <c r="D136"/>
+      <c r="E136"/>
+      <c r="F136"/>
+      <c r="G136"/>
+      <c r="H136"/>
+      <c r="I136"/>
+      <c r="J136"/>
+      <c r="K136"/>
+      <c r="L136"/>
     </row>
     <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="2"/>
-      <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2"/>
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-      <c r="H137" s="2"/>
-      <c r="I137" s="2"/>
-      <c r="J137" s="2"/>
-      <c r="K137" s="2"/>
-      <c r="L137" s="2"/>
+      <c r="A137"/>
+      <c r="B137"/>
+      <c r="C137"/>
+      <c r="D137"/>
+      <c r="E137"/>
+      <c r="F137"/>
+      <c r="G137"/>
+      <c r="H137"/>
+      <c r="I137"/>
+      <c r="J137"/>
+      <c r="K137"/>
+      <c r="L137"/>
     </row>
     <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="2"/>
-      <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-      <c r="H138" s="2"/>
-      <c r="I138" s="2"/>
-      <c r="J138" s="2"/>
-      <c r="K138" s="2"/>
-      <c r="L138" s="2"/>
+      <c r="A138"/>
+      <c r="B138"/>
+      <c r="C138"/>
+      <c r="D138"/>
+      <c r="E138"/>
+      <c r="F138"/>
+      <c r="G138"/>
+      <c r="H138"/>
+      <c r="I138"/>
+      <c r="J138"/>
+      <c r="K138"/>
+      <c r="L138"/>
     </row>
     <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="2"/>
-      <c r="B139" s="2"/>
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
-      <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-      <c r="H139" s="2"/>
-      <c r="I139" s="2"/>
-      <c r="J139" s="2"/>
-      <c r="K139" s="2"/>
-      <c r="L139" s="2"/>
+      <c r="A139"/>
+      <c r="B139"/>
+      <c r="C139"/>
+      <c r="D139"/>
+      <c r="E139"/>
+      <c r="F139"/>
+      <c r="G139"/>
+      <c r="H139"/>
+      <c r="I139"/>
+      <c r="J139"/>
+      <c r="K139"/>
+      <c r="L139"/>
     </row>
     <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="2"/>
-      <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-      <c r="H140" s="2"/>
-      <c r="I140" s="2"/>
-      <c r="J140" s="2"/>
-      <c r="K140" s="2"/>
-      <c r="L140" s="2"/>
+      <c r="A140"/>
+      <c r="B140"/>
+      <c r="C140"/>
+      <c r="D140"/>
+      <c r="E140"/>
+      <c r="F140"/>
+      <c r="G140"/>
+      <c r="H140"/>
+      <c r="I140"/>
+      <c r="J140"/>
+      <c r="K140"/>
+      <c r="L140"/>
+    </row>
+    <row r="141">
+      <c r="A141"/>
+      <c r="B141"/>
+      <c r="C141"/>
+      <c r="D141"/>
+      <c r="E141"/>
+      <c r="F141"/>
+      <c r="G141"/>
+      <c r="H141"/>
+      <c r="I141"/>
+      <c r="J141"/>
+      <c r="K141"/>
+      <c r="L141"/>
+    </row>
+    <row r="142">
+      <c r="A142"/>
+      <c r="B142"/>
+      <c r="C142"/>
+      <c r="D142"/>
+      <c r="E142"/>
+      <c r="F142"/>
+      <c r="G142"/>
+      <c r="H142"/>
+      <c r="I142"/>
+      <c r="J142"/>
+      <c r="K142"/>
+      <c r="L142"/>
+    </row>
+    <row r="143">
+      <c r="A143"/>
+      <c r="B143"/>
+      <c r="C143"/>
+      <c r="D143"/>
+      <c r="E143"/>
+      <c r="F143"/>
+      <c r="G143"/>
+      <c r="H143"/>
+      <c r="I143"/>
+      <c r="J143"/>
+      <c r="K143"/>
+      <c r="L143"/>
+    </row>
+    <row r="144">
+      <c r="A144"/>
+      <c r="B144"/>
+      <c r="C144"/>
+      <c r="D144"/>
+      <c r="E144"/>
+      <c r="F144"/>
+      <c r="G144"/>
+      <c r="H144"/>
+      <c r="I144"/>
+      <c r="J144"/>
+      <c r="K144"/>
+      <c r="L144"/>
+    </row>
+    <row r="145">
+      <c r="A145"/>
+      <c r="B145"/>
+      <c r="C145"/>
+      <c r="D145"/>
+      <c r="E145"/>
+      <c r="F145"/>
+      <c r="G145"/>
+      <c r="H145"/>
+      <c r="I145"/>
+      <c r="J145"/>
+      <c r="K145"/>
+      <c r="L145"/>
+    </row>
+    <row r="146">
+      <c r="A146"/>
+      <c r="B146"/>
+      <c r="C146"/>
+      <c r="D146"/>
+      <c r="E146"/>
+      <c r="F146"/>
+      <c r="G146"/>
+      <c r="H146"/>
+      <c r="I146"/>
+      <c r="J146"/>
+      <c r="K146"/>
+      <c r="L146"/>
+    </row>
+    <row r="147">
+      <c r="A147"/>
+      <c r="B147"/>
+      <c r="C147"/>
+      <c r="D147"/>
+      <c r="E147"/>
+      <c r="F147"/>
+      <c r="G147"/>
+      <c r="H147"/>
+      <c r="I147"/>
+      <c r="J147"/>
+      <c r="K147"/>
+      <c r="L147"/>
+    </row>
+    <row r="148">
+      <c r="A148"/>
+      <c r="B148"/>
+      <c r="C148"/>
+      <c r="D148"/>
+      <c r="E148"/>
+      <c r="F148"/>
+      <c r="G148"/>
+      <c r="H148"/>
+      <c r="I148"/>
+      <c r="J148"/>
+      <c r="K148"/>
+      <c r="L148"/>
+    </row>
+    <row r="149">
+      <c r="A149"/>
+      <c r="B149"/>
+      <c r="C149"/>
+      <c r="D149"/>
+      <c r="E149"/>
+      <c r="F149"/>
+      <c r="G149"/>
+      <c r="H149"/>
+      <c r="I149"/>
+      <c r="J149"/>
+      <c r="K149"/>
+      <c r="L149"/>
+    </row>
+    <row r="150">
+      <c r="A150"/>
+      <c r="B150"/>
+      <c r="C150"/>
+      <c r="D150"/>
+      <c r="E150"/>
+      <c r="F150"/>
+      <c r="G150"/>
+      <c r="H150"/>
+      <c r="I150"/>
+      <c r="J150"/>
+      <c r="K150"/>
+      <c r="L150"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -3936,20 +4284,20 @@
     <mergeCell ref="K10:L10"/>
     <mergeCell ref="K11:L12"/>
     <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="D32:E33"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E40"/>
-    <mergeCell ref="J39:L40"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="D42:E43"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E50"/>
+    <mergeCell ref="J51:L51"/>
+    <mergeCell ref="J49:L50"/>
+    <mergeCell ref="C36:L36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="F35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="D23:D23">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不可达"/>
@@ -3958,6 +4306,89 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="J24:J24">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="缺少"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30:D30">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="不可达"/>
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="无效"/>
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="缺少"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35:F35">
+    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="缺少"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:D18">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D26">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37:G37">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E59:E67">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H59:H67">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J59:J67">
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K59:K67">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L59:L67">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E72:E85">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H72:H85">
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J72:J85">
+    <cfRule type="expression" dxfId="18" priority="19">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K72:K85">
+    <cfRule type="expression" dxfId="19" priority="20">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L72:L85">
+    <cfRule type="expression" dxfId="20" priority="21">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E90:E98">
+    <cfRule type="expression" dxfId="21" priority="22">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H90:H98">
+    <cfRule type="expression" dxfId="22" priority="23">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="13">
     <dataValidation type="list" sqref="D7">

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R8302c7757af445bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R6ca9761c17d04849"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R595ba0064e4749df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R1fa0ef5cf6d64459"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -163,7 +163,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="126">
+  <x:cellXfs count="150">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -480,11 +480,27 @@
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
@@ -527,7 +543,69 @@
     <x:xf numFmtId="207" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="207" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="11" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1204,7 +1282,7 @@
       <c r="C18" s="107" t="str">
         <v>建议 Quote 资金</v>
       </c>
-      <c r="D18" s="117" t="n">
+      <c r="D18" s="121" t="n">
         <f>IF(ISNUMBER($D$26),(IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
         <v>15773.425525779472</v>
       </c>
@@ -1225,7 +1303,7 @@
       <c r="I18" s="107" t="str">
         <v>总折算 / USDT</v>
       </c>
-      <c r="J18" s="117" t="str">
+      <c r="J18" s="121" t="str">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
       </c>
       <c r="K18" s="62" t="str">
@@ -1239,7 +1317,7 @@
       <c r="C19" s="107" t="str">
         <v>Quote 折算 / USDT</v>
       </c>
-      <c r="D19" s="118" t="str">
+      <c r="D19" s="122" t="str">
         <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$33&gt;0,$D$18*$D$33,"")),"")</f>
       </c>
       <c r="E19" s="106" t="str">
@@ -1248,7 +1326,7 @@
       <c r="F19" s="107" t="str">
         <v>Gas 折算 / USDT</v>
       </c>
-      <c r="G19" s="118" t="n">
+      <c r="G19" s="122" t="n">
         <f>IF($G$18=0,0,IF($J$19="","",$G$18*$J$19))</f>
         <v>1513.8558244080918</v>
       </c>
@@ -1258,7 +1336,7 @@
       <c r="I19" s="107" t="str">
         <v>原生币价格 / USDT</v>
       </c>
-      <c r="J19" s="119" t="n">
+      <c r="J19" s="123" t="n">
         <f>IF($D$7="ETH",$D$33,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
         <v>2481.7308596853964</v>
       </c>
@@ -1304,7 +1382,7 @@
         <f>"预算 "&amp;TEXT($D$31,"0%")&amp;" 理论资金"</f>
         <v>预算 91% 理论资金</v>
       </c>
-      <c r="D22" s="118" t="n">
+      <c r="D22" s="122" t="n">
         <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
         <v>5520.084846424523</v>
       </c>
@@ -1315,12 +1393,12 @@
       <c r="F22" s="106"/>
       <c r="G22" s="106"/>
       <c r="H22" s="106"/>
-      <c r="I22" s="115" t="str">
+      <c r="I22" s="119" t="str">
         <v>内盘</v>
       </c>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="120"/>
+      <c r="L22" s="120"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2"/>
@@ -1328,7 +1406,7 @@
       <c r="C23" s="107" t="str">
         <v>额外内盘资金</v>
       </c>
-      <c r="D23" s="118" t="n">
+      <c r="D23" s="122" t="n">
         <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
         <v>174.54190618125045</v>
       </c>
@@ -1342,7 +1420,7 @@
       <c r="I23" s="107" t="str">
         <v>基础手续费</v>
       </c>
-      <c r="J23" s="120" t="n">
+      <c r="J23" s="124" t="n">
         <f>$G$41</f>
         <v>0.01</v>
       </c>
@@ -1355,7 +1433,7 @@
       <c r="C24" s="107" t="str">
         <v>洗筹损耗</v>
       </c>
-      <c r="D24" s="118" t="n">
+      <c r="D24" s="122" t="n">
         <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
         <v>10073.7987731737</v>
       </c>
@@ -1369,7 +1447,7 @@
       <c r="I24" s="107" t="str">
         <v>买入含税费率</v>
       </c>
-      <c r="J24" s="120" t="n">
+      <c r="J24" s="124" t="n">
         <f>$G$41+$J$7</f>
         <v>0.01</v>
       </c>
@@ -1382,7 +1460,7 @@
       <c r="C25" s="107" t="str">
         <v>资金预留</v>
       </c>
-      <c r="D25" s="118" t="n">
+      <c r="D25" s="122" t="n">
         <f>$G$12</f>
         <v>5</v>
       </c>
@@ -1396,7 +1474,7 @@
       <c r="I25" s="107" t="str">
         <v>卖出含税费率</v>
       </c>
-      <c r="J25" s="120" t="n">
+      <c r="J25" s="124" t="n">
         <f>$G$41+$J$7</f>
         <v>0.01</v>
       </c>
@@ -1409,7 +1487,7 @@
       <c r="C26" s="107" t="str">
         <v>恢复目标控筹资金</v>
       </c>
-      <c r="D26" s="118" t="n">
+      <c r="D26" s="122" t="n">
         <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",0)</f>
         <v>0</v>
       </c>
@@ -1431,7 +1509,7 @@
       <c r="C27" s="107" t="str">
         <v>洗后控筹率（估算）</v>
       </c>
-      <c r="D27" s="121" t="n">
+      <c r="D27" s="125" t="n">
         <f>$D$8*$J$54</f>
         <v>0.9</v>
       </c>
@@ -1439,12 +1517,12 @@
       <c r="F27" s="106"/>
       <c r="G27" s="106"/>
       <c r="H27" s="106"/>
-      <c r="I27" s="115" t="str">
+      <c r="I27" s="119" t="str">
         <v>外盘 · Hook</v>
       </c>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
-      <c r="L27" s="116"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2"/>
@@ -1452,7 +1530,7 @@
       <c r="C28" s="107" t="str">
         <v>补回目标控筹率</v>
       </c>
-      <c r="D28" s="120" t="n">
+      <c r="D28" s="124" t="n">
         <f>$D$8</f>
         <v>0.9</v>
       </c>
@@ -1463,7 +1541,7 @@
       <c r="I28" s="107" t="str">
         <v>基础手续费</v>
       </c>
-      <c r="J28" s="120" t="n">
+      <c r="J28" s="124" t="n">
         <f>$G$42</f>
         <v>0.01</v>
       </c>
@@ -1476,7 +1554,7 @@
       <c r="C29" s="107" t="str">
         <v>洗筹双边总费率</v>
       </c>
-      <c r="D29" s="120" t="n">
+      <c r="D29" s="124" t="n">
         <f>$J$47*2</f>
         <v>0.02</v>
       </c>
@@ -1487,7 +1565,7 @@
       <c r="I29" s="107" t="str">
         <v>买入含税费率</v>
       </c>
-      <c r="J29" s="120" t="n">
+      <c r="J29" s="124" t="n">
         <f>$G$42+$J$7</f>
         <v>0.01</v>
       </c>
@@ -1511,7 +1589,7 @@
       <c r="I30" s="107" t="str">
         <v>卖出含税费率</v>
       </c>
-      <c r="J30" s="120" t="n">
+      <c r="J30" s="124" t="n">
         <f>$G$42+$J$7</f>
         <v>0.01</v>
       </c>
@@ -1524,7 +1602,7 @@
       <c r="C31" s="107" t="str">
         <v>预算使用控筹率</v>
       </c>
-      <c r="D31" s="120" t="n">
+      <c r="D31" s="124" t="n">
         <f>$D$8+1%</f>
         <v>0.91</v>
       </c>
@@ -1543,7 +1621,7 @@
       <c r="C32" s="107" t="str">
         <v>地址总数</v>
       </c>
-      <c r="D32" s="118" t="n">
+      <c r="D32" s="122" t="n">
         <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
         <v>122</v>
       </c>
@@ -1551,7 +1629,7 @@
       <c r="F32" s="107" t="str">
         <v>当前控筹上限</v>
       </c>
-      <c r="G32" s="120" t="n">
+      <c r="G32" s="124" t="n">
         <f>MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$7)*$G$48/$D$45)</f>
         <v>0.916326530612245</v>
       </c>
@@ -1567,7 +1645,7 @@
       <c r="C33" s="107" t="str">
         <v>Quote 价格 / USDT</v>
       </c>
-      <c r="D33" s="119" t="str">
+      <c r="D33" s="123" t="str">
         <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
       </c>
       <c r="E33" s="106"/>
@@ -1585,7 +1663,7 @@
       <c r="C34" s="107" t="str">
         <v>行情时间 / UTC</v>
       </c>
-      <c r="D34" s="122" t="n">
+      <c r="D34" s="126" t="n">
         <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
         <v>46283.229019363425</v>
       </c>
@@ -1623,33 +1701,33 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="111" t="str">
+      <c r="C36" s="115" t="str">
         <v>Pons 按现有 Quote 洗筹损耗预算承担费用、持仓保持目标的口径，补回资金为 0；不代表免手续费。动态 Snipe Tax 未计入。</v>
       </c>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
+      <c r="D36" s="115"/>
+      <c r="E36" s="115"/>
+      <c r="F36" s="115"/>
+      <c r="G36" s="115"/>
+      <c r="H36" s="115"/>
+      <c r="I36" s="115"/>
+      <c r="J36" s="115"/>
+      <c r="K36" s="115"/>
+      <c r="L36" s="115"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="123" t="str">
+      <c r="C37" s="127" t="str">
         <v>沉没成本（模型参考，不重复计入预算）</v>
       </c>
-      <c r="D37" s="123"/>
-      <c r="E37" s="123"/>
-      <c r="F37" s="123"/>
-      <c r="G37" s="124" t="n">
+      <c r="D37" s="127"/>
+      <c r="E37" s="127"/>
+      <c r="F37" s="127"/>
+      <c r="G37" s="128" t="n">
         <f>E98</f>
         <v>38.399219359875104</v>
       </c>
-      <c r="H37" s="123" t="str">
+      <c r="H37" s="127" t="str">
         <f>$D$7</f>
         <v>SLV</v>
       </c>
@@ -1675,470 +1753,470 @@
     <row r="39" ht="24" customHeight="1" collapsed="1">
       <c r="A39"/>
       <c r="B39"/>
-      <c r="C39" s="110" t="str">
+      <c r="C39" s="8" t="str">
         <v>三、模型信息与计算口径（默认折叠，点左侧 + 展开）</v>
       </c>
-      <c r="D39" s="110"/>
-      <c r="E39" s="110"/>
-      <c r="F39" s="110"/>
-      <c r="G39" s="110"/>
-      <c r="H39" s="110"/>
-      <c r="I39" s="110"/>
-      <c r="J39" s="110"/>
-      <c r="K39" s="110"/>
-      <c r="L39" s="110"/>
-    </row>
-    <row r="40" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+    </row>
+    <row r="40" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A40"/>
       <c r="B40"/>
-      <c r="C40" t="str">
+      <c r="C40" s="107" t="str">
         <v>Quote 信息</v>
       </c>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40" t="str">
+      <c r="D40" s="107"/>
+      <c r="E40" s="107"/>
+      <c r="F40" s="107" t="str">
         <v>协议与曲线参数</v>
       </c>
-      <c r="G40"/>
-      <c r="H40"/>
-      <c r="I40" t="str">
+      <c r="G40" s="107"/>
+      <c r="H40" s="107"/>
+      <c r="I40" s="107" t="str">
         <v>预算中间计算</v>
       </c>
-      <c r="J40"/>
-      <c r="K40"/>
-      <c r="L40"/>
-    </row>
-    <row r="41" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="J40" s="107"/>
+      <c r="K40" s="107"/>
+      <c r="L40" s="107"/>
+    </row>
+    <row r="41" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A41"/>
       <c r="B41"/>
-      <c r="C41" t="str">
+      <c r="C41" s="107" t="str">
         <v>Quote 名称</v>
       </c>
-      <c r="D41" t="str">
+      <c r="D41" s="108" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</f>
         <v>iShares Silver Trust</v>
       </c>
-      <c r="E41"/>
-      <c r="F41" t="str">
+      <c r="E41" s="107"/>
+      <c r="F41" s="107" t="str">
         <v>内盘基础费</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41" s="112" t="n">
         <f>1%</f>
         <v>0.01</v>
       </c>
-      <c r="H41"/>
-      <c r="I41" t="str">
+      <c r="H41" s="107"/>
+      <c r="I41" s="107" t="str">
         <v>一套内盘打满 / Quote</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" s="108" t="n">
         <f>IF(1-$G$41-$J$7&gt;0,$G$44/(1-$G$41-$J$7),"")</f>
         <v>174.54190618125045</v>
       </c>
-      <c r="K41"/>
-      <c r="L41"/>
-    </row>
-    <row r="42" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K41" s="107"/>
+      <c r="L41" s="107"/>
+    </row>
+    <row r="42" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A42"/>
       <c r="B42"/>
-      <c r="C42" t="str">
+      <c r="C42" s="107" t="str">
         <v>Quote 合约</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D42" s="109" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</f>
         <v>​0x411efb0e7f985935daec3d4c3ebaea0d0ad7d89f</v>
       </c>
-      <c r="E42"/>
-      <c r="F42" t="str">
+      <c r="E42" s="107"/>
+      <c r="F42" s="107" t="str">
         <v>外盘 Hook 费</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42" s="112" t="n">
         <f>1%</f>
         <v>0.01</v>
       </c>
-      <c r="H42"/>
-      <c r="I42" t="str">
+      <c r="H42" s="107"/>
+      <c r="I42" s="107" t="str">
         <v>目标+1% Pool TOKEN</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" s="108" t="n">
         <f>IF($D$31&lt;$G$32,$D$45*(1-$D$31)-$G$51,"")</f>
         <v>8367346.938775495</v>
       </c>
-      <c r="K42"/>
-      <c r="L42"/>
-    </row>
-    <row r="43" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K42" s="107"/>
+      <c r="L42" s="107"/>
+    </row>
+    <row r="43" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A43"/>
       <c r="B43"/>
-      <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43" t="str">
+      <c r="C43" s="107"/>
+      <c r="D43" s="108"/>
+      <c r="E43" s="107"/>
+      <c r="F43" s="107" t="str">
         <v>毕业控筹率</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" s="112" t="n">
         <f>$G$44/($G$46+$G$44)</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="H43"/>
-      <c r="I43" t="str">
+      <c r="H43" s="107"/>
+      <c r="I43" s="107" t="str">
         <v>目标+1% Pool Quote</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="108" t="n">
         <f>IF($J$42="","",$G$50/$J$42)</f>
         <v>4214.548466327764</v>
       </c>
-      <c r="K43"/>
-      <c r="L43"/>
-    </row>
-    <row r="44" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K43" s="107"/>
+      <c r="L43" s="107"/>
+    </row>
+    <row r="44" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A44"/>
       <c r="B44"/>
-      <c r="C44" t="str">
+      <c r="C44" s="107" t="str">
         <v>Decimals</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="110" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,4,FALSE)</f>
         <v>18</v>
       </c>
-      <c r="E44"/>
-      <c r="F44" t="str">
+      <c r="E44" s="107"/>
+      <c r="F44" s="107" t="str">
         <v>毕业真实 Quote</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="108" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</f>
         <v>172.79648711943796</v>
       </c>
-      <c r="H44"/>
-      <c r="I44" t="str">
+      <c r="H44" s="107"/>
+      <c r="I44" s="107" t="str">
         <v>外盘净增加 / Quote</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="108" t="n">
         <f>IF($J$43="","",MAX(0,$J$43-$G$44))</f>
         <v>4041.751979208326</v>
       </c>
-      <c r="K44"/>
-      <c r="L44"/>
-    </row>
-    <row r="45" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K44" s="107"/>
+      <c r="L44" s="107"/>
+    </row>
+    <row r="45" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A45"/>
       <c r="B45"/>
-      <c r="C45" t="str">
+      <c r="C45" s="107" t="str">
         <v>总供应量</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="111" t="n">
         <f>1000000000</f>
         <v>1000000000</v>
       </c>
-      <c r="E45"/>
-      <c r="F45" t="str">
+      <c r="E45" s="107"/>
+      <c r="F45" s="107" t="str">
         <v>内盘初始 TOKEN</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" s="108" t="n">
         <f>$D$45</f>
         <v>1000000000</v>
       </c>
-      <c r="H45"/>
-      <c r="I45" t="str">
+      <c r="H45" s="107"/>
+      <c r="I45" s="107" t="str">
         <v>外盘含费投入 / Quote</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" s="108" t="n">
         <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$31-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>5345.542940243272</v>
       </c>
-      <c r="K45"/>
-      <c r="L45"/>
-    </row>
-    <row r="46" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K45" s="107"/>
+      <c r="L45" s="107"/>
+    </row>
+    <row r="46" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A46"/>
       <c r="B46"/>
-      <c r="C46" t="str">
+      <c r="C46" s="107" t="str">
         <v>协议参数证据</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="108" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</f>
         <v>54430299</v>
       </c>
-      <c r="E46"/>
-      <c r="F46" t="str">
+      <c r="E46" s="107"/>
+      <c r="F46" s="107" t="str">
         <v>phantom Quote</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46" s="108" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</f>
         <v>69.11859484777517</v>
       </c>
-      <c r="H46"/>
-      <c r="I46" t="str">
+      <c r="H46" s="107"/>
+      <c r="I46" s="107" t="str">
         <v>目标+1% FDV / Quote</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" s="108" t="n">
         <f>IF($J$43="","",$J$43/$J$42*$D$45)</f>
         <v>503689.93865868496</v>
       </c>
-      <c r="K46"/>
-      <c r="L46"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K46" s="107"/>
+      <c r="L46" s="107"/>
+    </row>
+    <row r="47" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A47"/>
       <c r="B47"/>
-      <c r="C47" t="str">
+      <c r="C47" s="107" t="str">
         <v>外盘机制</v>
       </c>
-      <c r="D47" t="str">
+      <c r="D47" s="108" t="str">
         <v>Uniswap V4 / exact-input</v>
       </c>
-      <c r="E47"/>
-      <c r="F47" t="str">
+      <c r="E47" s="107"/>
+      <c r="F47" s="107" t="str">
         <v>内盘 k</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" s="114" t="n">
         <f>$G$46*$D$45</f>
         <v>69118594847.77518</v>
       </c>
-      <c r="H47"/>
-      <c r="I47" t="str">
+      <c r="H47" s="107"/>
+      <c r="I47" s="107" t="str">
         <v>洗筹单边费率</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" s="112" t="n">
         <f>$G$42+$J$7</f>
         <v>0.01</v>
       </c>
-      <c r="K47"/>
-      <c r="L47"/>
+      <c r="K47" s="107"/>
+      <c r="L47" s="107"/>
     </row>
     <row r="48" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A48"/>
       <c r="B48"/>
-      <c r="C48" t="str">
+      <c r="C48" s="107" t="str">
         <v>费用方向</v>
       </c>
-      <c r="D48" t="str">
+      <c r="D48" s="108" t="str">
         <v>Hook + Creator Tax 从 Meme 输出扣除</v>
       </c>
-      <c r="E48"/>
-      <c r="F48" t="str">
+      <c r="E48" s="107"/>
+      <c r="F48" s="107" t="str">
         <v>外盘初始 TOKEN</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" s="108" t="n">
         <f>$D$45*$G$46*$G$44/($G$46+$G$44)^2</f>
         <v>204081632.65306124</v>
       </c>
-      <c r="H48"/>
-      <c r="I48" t="str">
+      <c r="H48" s="107"/>
+      <c r="I48" s="107" t="str">
         <v>预算缓冲</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" s="113" t="n">
         <v>0.01</v>
       </c>
-      <c r="K48"/>
-      <c r="L48"/>
-    </row>
-    <row r="49" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K48" s="107"/>
+      <c r="L48" s="107"/>
+    </row>
+    <row r="49" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A49"/>
       <c r="B49"/>
-      <c r="C49" t="str">
+      <c r="C49" s="107" t="str">
         <v>洗筹口径</v>
       </c>
-      <c r="D49" t="str">
+      <c r="D49" s="108" t="str">
         <v>目标+1% FDV ×（Hook + Creator Tax）×2</v>
       </c>
-      <c r="E49"/>
-      <c r="F49" t="str">
+      <c r="E49" s="107"/>
+      <c r="F49" s="107" t="str">
         <v>外盘初始 Quote</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" s="108" t="n">
         <f>$G$44</f>
         <v>172.79648711943796</v>
       </c>
-      <c r="H49"/>
-      <c r="I49" t="str">
+      <c r="H49" s="107"/>
+      <c r="I49" s="107" t="str">
         <v>分红与回购口径</v>
       </c>
-      <c r="J49" t="str">
+      <c r="J49" s="108" t="str">
         <v>不抵扣分红 / 回购收益</v>
       </c>
-      <c r="K49"/>
-      <c r="L49"/>
-    </row>
-    <row r="50" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K49" s="107"/>
+      <c r="L49" s="107"/>
+    </row>
+    <row r="50" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A50"/>
       <c r="B50"/>
-      <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50" t="str">
+      <c r="C50" s="107"/>
+      <c r="D50" s="108"/>
+      <c r="E50" s="107"/>
+      <c r="F50" s="107" t="str">
         <v>外盘 k</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" s="114" t="n">
         <f>$G$48*$G$44</f>
         <v>35264589208.04857</v>
       </c>
-      <c r="H50"/>
-      <c r="I50"/>
-      <c r="J50"/>
-      <c r="K50"/>
-      <c r="L50"/>
-    </row>
-    <row r="51" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="H50" s="107"/>
+      <c r="I50" s="107"/>
+      <c r="J50" s="108"/>
+      <c r="K50" s="107"/>
+      <c r="L50" s="107"/>
+    </row>
+    <row r="51" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A51"/>
       <c r="B51"/>
-      <c r="C51"/>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51" t="str">
+      <c r="C51" s="107"/>
+      <c r="D51" s="108"/>
+      <c r="E51" s="107"/>
+      <c r="F51" s="107" t="str">
         <v>Locker TOKEN</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" s="108" t="n">
         <f>$D$45*$G$46^2/($G$46+$G$44)^2</f>
         <v>81632653.06122448</v>
       </c>
-      <c r="H51"/>
-      <c r="I51" t="str">
+      <c r="H51" s="107"/>
+      <c r="I51" s="107" t="str">
         <v>输入检查</v>
       </c>
-      <c r="J51" t="str">
+      <c r="J51" s="108" t="str">
         <f>IF(COUNT($D$8,$G$7:$G$12,$J$7:$J$8)&lt;&gt;9,"缺少或非数值参数",IF(OR($G$7&lt;1,$G$8&lt;0,$G$9&lt;0,$G$10&lt;0,$G$11&lt;0,$G$12&lt;0,$G$7&lt;&gt;INT($G$7),$G$8&lt;&gt;INT($G$8),$G$9&lt;&gt;INT($G$9),$G$10&lt;&gt;INT($G$10)),"地址/Gas/预留参数无效",IF(OR($J$8&lt;0,$J$8&gt;1,AND($J$9&lt;&gt;"是",$J$9&lt;&gt;"否"),AND($J$10&lt;&gt;"是",$J$10&lt;&gt;"否")),"平台设置无效","参数有效")))</f>
         <v>参数有效</v>
       </c>
-      <c r="K51"/>
-      <c r="L51"/>
-    </row>
-    <row r="52" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K51" s="107"/>
+      <c r="L51" s="107"/>
+    </row>
+    <row r="52" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A52"/>
       <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52" t="str">
+      <c r="C52" s="107"/>
+      <c r="D52" s="108"/>
+      <c r="E52" s="107"/>
+      <c r="F52" s="107" t="str">
         <v>Snipe 窗口</v>
       </c>
-      <c r="G52" t="str">
+      <c r="G52" s="108" t="str">
         <v>3 秒；默认豁免或避开</v>
       </c>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52"/>
-    </row>
-    <row r="53" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="H52" s="107"/>
+      <c r="I52" s="107"/>
+      <c r="J52" s="108"/>
+      <c r="K52" s="107"/>
+      <c r="L52" s="107"/>
+    </row>
+    <row r="53" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A53"/>
       <c r="B53"/>
-      <c r="C53"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53" t="str">
+      <c r="C53" s="107"/>
+      <c r="D53" s="108"/>
+      <c r="E53" s="107"/>
+      <c r="F53" s="107" t="str">
         <v>Creator Tax 上限</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" s="112" t="n">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53"/>
-    </row>
-    <row r="54" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="H53" s="107"/>
+      <c r="I53" s="107"/>
+      <c r="J53" s="108"/>
+      <c r="K53" s="107"/>
+      <c r="L53" s="107"/>
+    </row>
+    <row r="54" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A54"/>
       <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54" s="108" t="str">
+      <c r="C54" s="107"/>
+      <c r="D54" s="108"/>
+      <c r="E54" s="107"/>
+      <c r="F54" s="107"/>
+      <c r="G54" s="108"/>
+      <c r="H54" s="107"/>
+      <c r="I54" s="107" t="str">
         <v>洗后持仓保留比例</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" s="112" t="n">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="K54"/>
-      <c r="L54"/>
-    </row>
-    <row r="55" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K54" s="107"/>
+      <c r="L54" s="107"/>
+    </row>
+    <row r="55" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A55"/>
       <c r="B55"/>
-      <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55" s="108" t="str">
+      <c r="C55" s="107"/>
+      <c r="D55" s="108"/>
+      <c r="E55" s="107"/>
+      <c r="F55" s="107"/>
+      <c r="G55" s="108"/>
+      <c r="H55" s="107"/>
+      <c r="I55" s="107" t="str">
         <v>目标外盘 Pool TOKEN</v>
       </c>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55"/>
-    </row>
-    <row r="56" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="J55" s="108"/>
+      <c r="K55" s="107"/>
+      <c r="L55" s="107"/>
+    </row>
+    <row r="56" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A56"/>
       <c r="B56"/>
-      <c r="C56"/>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
-      <c r="I56" s="108" t="str">
+      <c r="C56" s="107"/>
+      <c r="D56" s="108"/>
+      <c r="E56" s="107"/>
+      <c r="F56" s="107"/>
+      <c r="G56" s="108"/>
+      <c r="H56" s="107"/>
+      <c r="I56" s="107" t="str">
         <v>洗后外盘 Pool TOKEN</v>
       </c>
-      <c r="J56"/>
-      <c r="K56"/>
-      <c r="L56"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
+      <c r="J56" s="108"/>
+      <c r="K56" s="107"/>
+      <c r="L56" s="107"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
       <c r="A57"/>
       <c r="B57"/>
-      <c r="C57" t="str">
+      <c r="C57" s="8" t="str">
         <v>内盘曲线</v>
       </c>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57"/>
-      <c r="I57"/>
-      <c r="J57"/>
-      <c r="K57"/>
-      <c r="L57"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+    </row>
+    <row r="58" ht="32" customHeight="1">
       <c r="A58"/>
       <c r="B58"/>
-      <c r="C58" t="str">
+      <c r="C58" s="77" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D58" t="str">
+      <c r="D58" s="77" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E58" t="str">
+      <c r="E58" s="77" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F58" t="str">
+      <c r="F58" s="77" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G58" t="str">
+      <c r="G58" s="77" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H58" t="str">
+      <c r="H58" s="77" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I58" t="str">
+      <c r="I58" s="77" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J58" t="str">
+      <c r="J58" s="77" t="str">
         <v>区间净投入
 / Quote</v>
       </c>
-      <c r="K58" t="str">
+      <c r="K58" s="77" t="str">
         <v>区间含费
 / Quote</v>
       </c>
-      <c r="L58" t="str">
+      <c r="L58" s="77" t="str">
         <v>理论累计所需
 / Quote</v>
       </c>
@@ -2146,122 +2224,122 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59"/>
       <c r="B59"/>
-      <c r="C59" t="n">
+      <c r="C59" s="132" t="n">
         <v>0</v>
       </c>
-      <c r="D59" s="125" t="n">
+      <c r="D59" s="144" t="n">
         <f>$D$45*(1-C59)</f>
         <v>1000000000</v>
       </c>
-      <c r="E59" s="125" t="n">
+      <c r="E59" s="144" t="n">
         <f>$G$47/D59</f>
         <v>69.11859484777517</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="135" t="n">
         <f>IF(OR(D59="",E59=""),"",E59/D59)</f>
         <v>6.911859484777517e-8</v>
       </c>
-      <c r="G59" t="str">
+      <c r="G59" s="135" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F59))),"",F59*$D$33)</f>
       </c>
-      <c r="H59" s="125" t="n">
+      <c r="H59" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F59)),"",F59*$D$45)</f>
         <v>69.11859484777517</v>
       </c>
-      <c r="I59" s="125" t="str">
+      <c r="I59" s="144" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H59))),"",H59*$D$33)</f>
       </c>
-      <c r="J59" s="125" t="n">
+      <c r="J59" s="144" t="n">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="K59" s="125" t="n">
+      <c r="K59" s="144" t="n">
         <f>J59/(1-$G$41-$J$7)</f>
         <v>0</v>
       </c>
-      <c r="L59" s="125" t="n">
+      <c r="L59" s="147" t="n">
         <f>SUM($K$59:K59)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1">
+    <row r="60" ht="20" customHeight="1">
       <c r="A60"/>
       <c r="B60"/>
-      <c r="C60" t="n">
+      <c r="C60" s="133" t="n">
         <v>0.1</v>
       </c>
-      <c r="D60" s="125" t="n">
+      <c r="D60" s="145" t="n">
         <f>$D$45*(1-C60)</f>
         <v>900000000</v>
       </c>
-      <c r="E60" s="125" t="n">
+      <c r="E60" s="145" t="n">
         <f>$G$47/D60</f>
         <v>76.7984387197502</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="136" t="n">
         <f>IF(OR(D60="",E60=""),"",E60/D60)</f>
         <v>8.533159857750022e-8</v>
       </c>
-      <c r="G60" t="str">
+      <c r="G60" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F60))),"",F60*$D$33)</f>
       </c>
-      <c r="H60" s="125" t="n">
+      <c r="H60" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F60)),"",F60*$D$45)</f>
         <v>85.33159857750022</v>
       </c>
-      <c r="I60" s="125" t="str">
+      <c r="I60" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H60))),"",H60*$D$33)</f>
       </c>
-      <c r="J60" s="125" t="n">
+      <c r="J60" s="145" t="n">
         <f>E60-E59</f>
         <v>7.679843871975024</v>
       </c>
-      <c r="K60" s="125" t="n">
+      <c r="K60" s="145" t="n">
         <f>J60/(1-$G$41-$J$7)</f>
         <v>7.757418052500024</v>
       </c>
-      <c r="L60" s="125" t="n">
+      <c r="L60" s="148" t="n">
         <f>SUM($K$59:K60)</f>
         <v>7.757418052500024</v>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
+    <row r="61" ht="20" customHeight="1">
       <c r="A61"/>
       <c r="B61"/>
-      <c r="C61" t="n">
+      <c r="C61" s="133" t="n">
         <v>0.2</v>
       </c>
-      <c r="D61" s="125" t="n">
+      <c r="D61" s="145" t="n">
         <f>$D$45*(1-C61)</f>
         <v>800000000</v>
       </c>
-      <c r="E61" s="125" t="n">
+      <c r="E61" s="145" t="n">
         <f>$G$47/D61</f>
         <v>86.39824355971898</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="136" t="n">
         <f>IF(OR(D61="",E61=""),"",E61/D61)</f>
         <v>1.0799780444964873e-7</v>
       </c>
-      <c r="G61" t="str">
+      <c r="G61" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F61))),"",F61*$D$33)</f>
       </c>
-      <c r="H61" s="125" t="n">
+      <c r="H61" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F61)),"",F61*$D$45)</f>
         <v>107.99780444964873</v>
       </c>
-      <c r="I61" s="125" t="str">
+      <c r="I61" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H61))),"",H61*$D$33)</f>
       </c>
-      <c r="J61" s="125" t="n">
+      <c r="J61" s="145" t="n">
         <f>E61-E60</f>
         <v>9.599804839968783</v>
       </c>
-      <c r="K61" s="125" t="n">
+      <c r="K61" s="145" t="n">
         <f>J61/(1-$G$41-$J$7)</f>
         <v>9.696772565625034</v>
       </c>
-      <c r="L61" s="125" t="n">
+      <c r="L61" s="148" t="n">
         <f>SUM($K$59:K61)</f>
         <v>17.454190618125057</v>
       </c>
@@ -2269,40 +2347,40 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62"/>
       <c r="B62"/>
-      <c r="C62" t="n">
+      <c r="C62" s="133" t="n">
         <v>0.3</v>
       </c>
-      <c r="D62" s="125" t="n">
+      <c r="D62" s="145" t="n">
         <f>$D$45*(1-C62)</f>
         <v>700000000</v>
       </c>
-      <c r="E62" s="125" t="n">
+      <c r="E62" s="145" t="n">
         <f>$G$47/D62</f>
         <v>98.74084978253596</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="136" t="n">
         <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
         <v>1.4105835683219424e-7</v>
       </c>
-      <c r="G62" t="str">
+      <c r="G62" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F62))),"",F62*$D$33)</f>
       </c>
-      <c r="H62" s="125" t="n">
+      <c r="H62" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$45)</f>
         <v>141.05835683219425</v>
       </c>
-      <c r="I62" s="125" t="str">
+      <c r="I62" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H62))),"",H62*$D$33)</f>
       </c>
-      <c r="J62" s="125" t="n">
+      <c r="J62" s="145" t="n">
         <f>E62-E61</f>
         <v>12.342606222816983</v>
       </c>
-      <c r="K62" s="125" t="n">
+      <c r="K62" s="145" t="n">
         <f>J62/(1-$G$41-$J$7)</f>
         <v>12.467279012946447</v>
       </c>
-      <c r="L62" s="125" t="n">
+      <c r="L62" s="148" t="n">
         <f>SUM($K$59:K62)</f>
         <v>29.921469631071503</v>
       </c>
@@ -2310,40 +2388,40 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63"/>
       <c r="B63"/>
-      <c r="C63" t="n">
+      <c r="C63" s="133" t="n">
         <v>0.4</v>
       </c>
-      <c r="D63" s="125" t="n">
+      <c r="D63" s="145" t="n">
         <f>$D$45*(1-C63)</f>
         <v>600000000</v>
       </c>
-      <c r="E63" s="125" t="n">
+      <c r="E63" s="145" t="n">
         <f>$G$47/D63</f>
         <v>115.1976580796253</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="136" t="n">
         <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
         <v>1.919960967993755e-7</v>
       </c>
-      <c r="G63" t="str">
+      <c r="G63" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F63))),"",F63*$D$33)</f>
       </c>
-      <c r="H63" s="125" t="n">
+      <c r="H63" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$45)</f>
         <v>191.99609679937552</v>
       </c>
-      <c r="I63" s="125" t="str">
+      <c r="I63" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H63))),"",H63*$D$33)</f>
       </c>
-      <c r="J63" s="125" t="n">
+      <c r="J63" s="145" t="n">
         <f>E63-E62</f>
         <v>16.45680829708934</v>
       </c>
-      <c r="K63" s="125" t="n">
+      <c r="K63" s="145" t="n">
         <f>J63/(1-$G$41-$J$7)</f>
         <v>16.623038683928623</v>
       </c>
-      <c r="L63" s="125" t="n">
+      <c r="L63" s="148" t="n">
         <f>SUM($K$59:K63)</f>
         <v>46.54450831500013</v>
       </c>
@@ -2351,40 +2429,40 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64"/>
       <c r="B64"/>
-      <c r="C64" t="n">
+      <c r="C64" s="133" t="n">
         <v>0.5</v>
       </c>
-      <c r="D64" s="125" t="n">
+      <c r="D64" s="145" t="n">
         <f>$D$45*(1-C64)</f>
         <v>500000000</v>
       </c>
-      <c r="E64" s="125" t="n">
+      <c r="E64" s="145" t="n">
         <f>$G$47/D64</f>
         <v>138.23718969555034</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="136" t="n">
         <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
         <v>2.7647437939110067e-7</v>
       </c>
-      <c r="G64" t="str">
+      <c r="G64" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F64))),"",F64*$D$33)</f>
       </c>
-      <c r="H64" s="125" t="n">
+      <c r="H64" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$45)</f>
         <v>276.4743793911007</v>
       </c>
-      <c r="I64" s="125" t="str">
+      <c r="I64" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H64))),"",H64*$D$33)</f>
       </c>
-      <c r="J64" s="125" t="n">
+      <c r="J64" s="145" t="n">
         <f>E64-E63</f>
         <v>23.039531615925043</v>
       </c>
-      <c r="K64" s="125" t="n">
+      <c r="K64" s="145" t="n">
         <f>J64/(1-$G$41-$J$7)</f>
         <v>23.272254157500043</v>
       </c>
-      <c r="L64" s="125" t="n">
+      <c r="L64" s="148" t="n">
         <f>SUM($K$59:K64)</f>
         <v>69.81676247250017</v>
       </c>
@@ -2392,40 +2470,40 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65"/>
       <c r="B65"/>
-      <c r="C65" t="n">
+      <c r="C65" s="133" t="n">
         <v>0.6</v>
       </c>
-      <c r="D65" s="125" t="n">
+      <c r="D65" s="145" t="n">
         <f>$D$45*(1-C65)</f>
         <v>400000000</v>
       </c>
-      <c r="E65" s="125" t="n">
+      <c r="E65" s="145" t="n">
         <f>$G$47/D65</f>
         <v>172.79648711943796</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="136" t="n">
         <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
         <v>4.319912177985949e-7</v>
       </c>
-      <c r="G65" t="str">
+      <c r="G65" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F65))),"",F65*$D$33)</f>
       </c>
-      <c r="H65" s="125" t="n">
+      <c r="H65" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$45)</f>
         <v>431.9912177985949</v>
       </c>
-      <c r="I65" s="125" t="str">
+      <c r="I65" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H65))),"",H65*$D$33)</f>
       </c>
-      <c r="J65" s="125" t="n">
+      <c r="J65" s="145" t="n">
         <f>E65-E64</f>
         <v>34.559297423887614</v>
       </c>
-      <c r="K65" s="125" t="n">
+      <c r="K65" s="145" t="n">
         <f>J65/(1-$G$41-$J$7)</f>
         <v>34.908381236250115</v>
       </c>
-      <c r="L65" s="125" t="n">
+      <c r="L65" s="148" t="n">
         <f>SUM($K$59:K65)</f>
         <v>104.7251437087503</v>
       </c>
@@ -2433,40 +2511,40 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66"/>
       <c r="B66"/>
-      <c r="C66" t="n">
+      <c r="C66" s="133" t="n">
         <v>0.7</v>
       </c>
-      <c r="D66" s="125" t="n">
+      <c r="D66" s="145" t="n">
         <f>$D$45*(1-C66)</f>
         <v>300000000.00000006</v>
       </c>
-      <c r="E66" s="125" t="n">
+      <c r="E66" s="145" t="n">
         <f>$G$47/D66</f>
         <v>230.39531615925054</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="136" t="n">
         <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
         <v>7.679843871975016e-7</v>
       </c>
-      <c r="G66" t="str">
+      <c r="G66" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F66))),"",F66*$D$33)</f>
       </c>
-      <c r="H66" s="125" t="n">
+      <c r="H66" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$45)</f>
         <v>767.9843871975016</v>
       </c>
-      <c r="I66" s="125" t="str">
+      <c r="I66" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H66))),"",H66*$D$33)</f>
       </c>
-      <c r="J66" s="125" t="n">
+      <c r="J66" s="145" t="n">
         <f>E66-E65</f>
         <v>57.598829039812586</v>
       </c>
-      <c r="K66" s="125" t="n">
+      <c r="K66" s="145" t="n">
         <f>J66/(1-$G$41-$J$7)</f>
         <v>58.18063539375009</v>
       </c>
-      <c r="L66" s="125" t="n">
+      <c r="L66" s="148" t="n">
         <f>SUM($K$59:K66)</f>
         <v>162.9057791025004</v>
       </c>
@@ -2474,41 +2552,41 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67"/>
       <c r="B67"/>
-      <c r="C67" t="n">
+      <c r="C67" s="134" t="n">
         <f>$G$43</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="D67" s="125" t="n">
+      <c r="D67" s="146" t="n">
         <f>$D$45*(1-C67)</f>
         <v>285714285.7142857</v>
       </c>
-      <c r="E67" s="125" t="n">
+      <c r="E67" s="146" t="n">
         <f>$G$47/D67</f>
         <v>241.91508196721315</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="137" t="n">
         <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
         <v>8.467027868852461e-7</v>
       </c>
-      <c r="G67" t="str">
+      <c r="G67" s="137" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F67))),"",F67*$D$33)</f>
       </c>
-      <c r="H67" s="125" t="n">
+      <c r="H67" s="146" t="n">
         <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$45)</f>
         <v>846.7027868852462</v>
       </c>
-      <c r="I67" s="125" t="str">
+      <c r="I67" s="146" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H67))),"",H67*$D$33)</f>
       </c>
-      <c r="J67" s="125" t="n">
+      <c r="J67" s="146" t="n">
         <f>E67-E66</f>
         <v>11.519765807962614</v>
       </c>
-      <c r="K67" s="125" t="n">
+      <c r="K67" s="146" t="n">
         <f>J67/(1-$G$41-$J$7)</f>
         <v>11.636127078750116</v>
       </c>
-      <c r="L67" s="125" t="n">
+      <c r="L67" s="149" t="n">
         <f>SUM($K$59:K67)</f>
         <v>174.5419061812505</v>
       </c>
@@ -2516,80 +2594,80 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68"/>
       <c r="B68"/>
-      <c r="C68"/>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
-      <c r="G68"/>
-      <c r="H68"/>
-      <c r="I68"/>
-      <c r="J68"/>
-      <c r="K68"/>
-      <c r="L68"/>
+      <c r="C68" s="106"/>
+      <c r="D68" s="106"/>
+      <c r="E68" s="106"/>
+      <c r="F68" s="106"/>
+      <c r="G68" s="106"/>
+      <c r="H68" s="106"/>
+      <c r="I68" s="106"/>
+      <c r="J68" s="106"/>
+      <c r="K68" s="106"/>
+      <c r="L68" s="106"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69"/>
       <c r="B69"/>
-      <c r="C69"/>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69"/>
-      <c r="H69"/>
-      <c r="I69"/>
-      <c r="J69"/>
-      <c r="K69"/>
-      <c r="L69"/>
-    </row>
-    <row r="70" ht="20" customHeight="1">
+      <c r="C69" s="106"/>
+      <c r="D69" s="106"/>
+      <c r="E69" s="106"/>
+      <c r="F69" s="106"/>
+      <c r="G69" s="106"/>
+      <c r="H69" s="106"/>
+      <c r="I69" s="106"/>
+      <c r="J69" s="106"/>
+      <c r="K69" s="106"/>
+      <c r="L69" s="106"/>
+    </row>
+    <row r="70" ht="24" customHeight="1">
       <c r="A70"/>
       <c r="B70"/>
-      <c r="C70" t="str">
+      <c r="C70" s="8" t="str">
         <v>外盘曲线</v>
       </c>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
-      <c r="G70"/>
-      <c r="H70"/>
-      <c r="I70"/>
-      <c r="J70"/>
-      <c r="K70"/>
-      <c r="L70"/>
-    </row>
-    <row r="71" ht="20" customHeight="1">
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+    </row>
+    <row r="71" ht="32" customHeight="1">
       <c r="A71"/>
       <c r="B71"/>
-      <c r="C71" t="str">
+      <c r="C71" s="77" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D71" t="str">
+      <c r="D71" s="77" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E71" t="str">
+      <c r="E71" s="77" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F71" t="str">
+      <c r="F71" s="77" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G71" t="str">
+      <c r="G71" s="77" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H71" t="str">
+      <c r="H71" s="77" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I71" t="str">
+      <c r="I71" s="77" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J71" t="str">
+      <c r="J71" s="77" t="str">
         <v>外盘净投入
 / Quote</v>
       </c>
-      <c r="K71" t="str">
+      <c r="K71" s="77" t="str">
         <v>外盘含费
 / Quote</v>
       </c>
-      <c r="L71" t="str">
+      <c r="L71" s="77" t="str">
         <v>理论累计所需
 / Quote</v>
       </c>
@@ -2597,41 +2675,41 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72"/>
       <c r="B72"/>
-      <c r="C72" t="n">
+      <c r="C72" s="132" t="n">
         <f>$G$43</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="D72" s="125" t="n">
+      <c r="D72" s="144" t="n">
         <f>$G$48</f>
         <v>204081632.65306124</v>
       </c>
-      <c r="E72" s="125" t="n">
+      <c r="E72" s="144" t="n">
         <f>$G$44</f>
         <v>172.79648711943796</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="135" t="n">
         <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
         <v>8.467027868852459e-7</v>
       </c>
-      <c r="G72" t="str">
+      <c r="G72" s="135" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F72))),"",F72*$D$33)</f>
       </c>
-      <c r="H72" s="125" t="n">
+      <c r="H72" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$45)</f>
         <v>846.7027868852459</v>
       </c>
-      <c r="I72" s="125" t="str">
+      <c r="I72" s="144" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H72))),"",H72*$D$33)</f>
       </c>
-      <c r="J72" s="125" t="n">
+      <c r="J72" s="144" t="n">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="K72" s="125" t="n">
+      <c r="K72" s="144" t="n">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="L72" s="125" t="n">
+      <c r="L72" s="147" t="n">
         <f>$J$41</f>
         <v>174.54190618125045</v>
       </c>
@@ -2639,40 +2717,40 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73"/>
       <c r="B73"/>
-      <c r="C73" t="n">
+      <c r="C73" s="133" t="n">
         <v>0.75</v>
       </c>
-      <c r="D73" s="125" t="n">
+      <c r="D73" s="145" t="n">
         <f>IF(C73&lt;$G$32,$D$45*(1-C73)-$G$51,"")</f>
         <v>168367346.93877554</v>
       </c>
-      <c r="E73" s="125" t="n">
+      <c r="E73" s="145" t="n">
         <f>IF(D73="","",$G$50/D73)</f>
         <v>209.45028741750056</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="136" t="n">
         <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
         <v>0.0000012440077676918213</v>
       </c>
-      <c r="G73" t="str">
+      <c r="G73" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F73))),"",F73*$D$33)</f>
       </c>
-      <c r="H73" s="125" t="n">
+      <c r="H73" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$45)</f>
         <v>1244.0077676918213</v>
       </c>
-      <c r="I73" s="125" t="str">
+      <c r="I73" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H73))),"",H73*$D$33)</f>
       </c>
-      <c r="J73" s="125" t="n">
+      <c r="J73" s="145" t="n">
         <f>IF(E73="","",MAX(0,E73-$G$44))</f>
         <v>36.653800298062606</v>
       </c>
-      <c r="K73" s="125" t="n">
+      <c r="K73" s="145" t="n">
         <f>IF(D73="","",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>37.103540179020456</v>
       </c>
-      <c r="L73" s="125" t="n">
+      <c r="L73" s="148" t="n">
         <f>IF(K73="","",$J$41+K73)</f>
         <v>211.6454463602709</v>
       </c>
@@ -2680,40 +2758,40 @@
     <row r="74" ht="20" customHeight="1">
       <c r="A74"/>
       <c r="B74"/>
-      <c r="C74" t="n">
+      <c r="C74" s="133" t="n">
         <v>0.8</v>
       </c>
-      <c r="D74" s="125" t="n">
+      <c r="D74" s="145" t="n">
         <f>IF(C74&lt;$G$32,$D$45*(1-C74)-$G$51,"")</f>
         <v>118367346.9387755</v>
       </c>
-      <c r="E74" s="125" t="n">
+      <c r="E74" s="145" t="n">
         <f>IF(D74="","",$G$50/D74)</f>
         <v>297.9249777921345</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="136" t="n">
         <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
         <v>0.0000025169523985887227</v>
       </c>
-      <c r="G74" t="str">
+      <c r="G74" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F74))),"",F74*$D$33)</f>
       </c>
-      <c r="H74" s="125" t="n">
+      <c r="H74" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$45)</f>
         <v>2516.9523985887226</v>
       </c>
-      <c r="I74" s="125" t="str">
+      <c r="I74" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H74))),"",H74*$D$33)</f>
       </c>
-      <c r="J74" s="125" t="n">
+      <c r="J74" s="145" t="n">
         <f>IF(E74="","",MAX(0,E74-$G$44))</f>
         <v>125.12849067269653</v>
       </c>
-      <c r="K74" s="125" t="n">
+      <c r="K74" s="145" t="n">
         <f>IF(D74="","",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>127.32372735116493</v>
       </c>
-      <c r="L74" s="125" t="n">
+      <c r="L74" s="148" t="n">
         <f>IF(K74="","",$J$41+K74)</f>
         <v>301.86563353241536</v>
       </c>
@@ -2721,40 +2799,40 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75"/>
       <c r="B75"/>
-      <c r="C75" t="n">
+      <c r="C75" s="133" t="n">
         <v>0.82</v>
       </c>
-      <c r="D75" s="125" t="n">
+      <c r="D75" s="145" t="n">
         <f>IF(C75&lt;$G$32,$D$45*(1-C75)-$G$51,"")</f>
         <v>98367346.93877558</v>
       </c>
-      <c r="E75" s="125" t="n">
+      <c r="E75" s="145" t="n">
         <f>IF(D75="","",$G$50/D75)</f>
         <v>358.4989359324437</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="136" t="n">
         <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
         <v>0.000003644491257404508</v>
       </c>
-      <c r="G75" t="str">
+      <c r="G75" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F75))),"",F75*$D$33)</f>
       </c>
-      <c r="H75" s="125" t="n">
+      <c r="H75" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$45)</f>
         <v>3644.4912574045084</v>
       </c>
-      <c r="I75" s="125" t="str">
+      <c r="I75" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H75))),"",H75*$D$33)</f>
       </c>
-      <c r="J75" s="125" t="n">
+      <c r="J75" s="145" t="n">
         <f>IF(E75="","",MAX(0,E75-$G$44))</f>
         <v>185.70244881300576</v>
       </c>
-      <c r="K75" s="125" t="n">
+      <c r="K75" s="145" t="n">
         <f>IF(D75="","",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>189.63682272853552</v>
       </c>
-      <c r="L75" s="125" t="n">
+      <c r="L75" s="148" t="n">
         <f>IF(K75="","",$J$41+K75)</f>
         <v>364.17872890978595</v>
       </c>
@@ -2762,40 +2840,40 @@
     <row r="76" ht="20" customHeight="1">
       <c r="A76"/>
       <c r="B76"/>
-      <c r="C76" t="n">
+      <c r="C76" s="133" t="n">
         <v>0.84</v>
       </c>
-      <c r="D76" s="125" t="n">
+      <c r="D76" s="145" t="n">
         <f>IF(C76&lt;$G$32,$D$45*(1-C76)-$G$51,"")</f>
         <v>78367346.93877555</v>
       </c>
-      <c r="E76" s="125" t="n">
+      <c r="E76" s="145" t="n">
         <f>IF(D76="","",$G$50/D76)</f>
         <v>449.99085187353614</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" s="136" t="n">
         <f>IF(OR(D76="",E76=""),"",E76/D76)</f>
         <v>0.000005742070766094599</v>
       </c>
-      <c r="G76" t="str">
+      <c r="G76" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F76))),"",F76*$D$33)</f>
       </c>
-      <c r="H76" s="125" t="n">
+      <c r="H76" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F76)),"",F76*$D$45)</f>
         <v>5742.070766094599</v>
       </c>
-      <c r="I76" s="125" t="str">
+      <c r="I76" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H76))),"",H76*$D$33)</f>
       </c>
-      <c r="J76" s="125" t="n">
+      <c r="J76" s="145" t="n">
         <f>IF(E76="","",MAX(0,E76-$G$44))</f>
         <v>277.19436475409816</v>
       </c>
-      <c r="K76" s="125" t="n">
+      <c r="K76" s="145" t="n">
         <f>IF(D76="","",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>284.6059787849564</v>
       </c>
-      <c r="L76" s="125" t="n">
+      <c r="L76" s="148" t="n">
         <f>IF(K76="","",$J$41+K76)</f>
         <v>459.14788496620685</v>
       </c>
@@ -2803,122 +2881,122 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77"/>
       <c r="B77"/>
-      <c r="C77" t="n">
+      <c r="C77" s="133" t="n">
         <v>0.86</v>
       </c>
-      <c r="D77" s="125" t="n">
+      <c r="D77" s="145" t="n">
         <f>IF(C77&lt;$G$32,$D$45*(1-C77)-$G$51,"")</f>
         <v>58367346.938775524</v>
       </c>
-      <c r="E77" s="125" t="n">
+      <c r="E77" s="145" t="n">
         <f>IF(D77="","",$G$50/D77)</f>
         <v>604.1835213966361</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="136" t="n">
         <f>IF(OR(D77="",E77=""),"",E77/D77)</f>
         <v>0.00001035139599595635</v>
       </c>
-      <c r="G77" t="str">
+      <c r="G77" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F77))),"",F77*$D$33)</f>
       </c>
-      <c r="H77" s="125" t="n">
+      <c r="H77" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F77)),"",F77*$D$45)</f>
         <v>10351.39599595635</v>
       </c>
-      <c r="I77" s="125" t="str">
+      <c r="I77" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H77))),"",H77*$D$33)</f>
       </c>
-      <c r="J77" s="125" t="n">
+      <c r="J77" s="145" t="n">
         <f>IF(E77="","",MAX(0,E77-$G$44))</f>
         <v>431.38703427719815</v>
       </c>
-      <c r="K77" s="125" t="n">
+      <c r="K77" s="145" t="n">
         <f>IF(D77="","",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>447.0169992872412</v>
       </c>
-      <c r="L77" s="125" t="n">
+      <c r="L77" s="148" t="n">
         <f>IF(K77="","",$J$41+K77)</f>
         <v>621.5589054684917</v>
       </c>
     </row>
-    <row r="78" ht="24" customHeight="1">
+    <row r="78" ht="20" customHeight="1">
       <c r="A78"/>
       <c r="B78"/>
-      <c r="C78" t="n">
+      <c r="C78" s="133" t="n">
         <v>0.88</v>
       </c>
-      <c r="D78" s="125" t="n">
+      <c r="D78" s="145" t="n">
         <f>IF(C78&lt;$G$32,$D$45*(1-C78)-$G$51,"")</f>
         <v>38367346.938775524</v>
       </c>
-      <c r="E78" s="125" t="n">
+      <c r="E78" s="145" t="n">
         <f>IF(D78="","",$G$50/D78)</f>
         <v>919.1302506353081</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" s="136" t="n">
         <f>IF(OR(D78="",E78=""),"",E78/D78)</f>
         <v>0.000023956054404856426</v>
       </c>
-      <c r="G78" t="str">
+      <c r="G78" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F78))),"",F78*$D$33)</f>
       </c>
-      <c r="H78" s="125" t="n">
+      <c r="H78" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F78)),"",F78*$D$45)</f>
         <v>23956.054404856426</v>
       </c>
-      <c r="I78" s="125" t="str">
+      <c r="I78" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H78))),"",H78*$D$33)</f>
       </c>
-      <c r="J78" s="125" t="n">
+      <c r="J78" s="145" t="n">
         <f>IF(E78="","",MAX(0,E78-$G$44))</f>
         <v>746.3337635158701</v>
       </c>
-      <c r="K78" s="125" t="n">
+      <c r="K78" s="145" t="n">
         <f>IF(D78="","",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>788.2626266347389</v>
       </c>
-      <c r="L78" s="125" t="n">
+      <c r="L78" s="148" t="n">
         <f>IF(K78="","",$J$41+K78)</f>
         <v>962.8045328159894</v>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1">
+    <row r="79" ht="20" customHeight="1">
       <c r="A79"/>
       <c r="B79"/>
-      <c r="C79" t="n">
+      <c r="C79" s="133" t="n">
         <v>0.89</v>
       </c>
-      <c r="D79" s="125" t="n">
+      <c r="D79" s="145" t="n">
         <f>IF(C79&lt;$G$32,$D$45*(1-C79)-$G$51,"")</f>
         <v>28367346.93877551</v>
       </c>
-      <c r="E79" s="125" t="n">
+      <c r="E79" s="145" t="n">
         <f>IF(D79="","",$G$50/D79)</f>
         <v>1243.1401951038704</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" s="136" t="n">
         <f>IF(OR(D79="",E79=""),"",E79/D79)</f>
         <v>0.00004382292774107169</v>
       </c>
-      <c r="G79" t="str">
+      <c r="G79" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F79))),"",F79*$D$33)</f>
       </c>
-      <c r="H79" s="125" t="n">
+      <c r="H79" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F79)),"",F79*$D$45)</f>
         <v>43822.92774107169</v>
       </c>
-      <c r="I79" s="125" t="str">
+      <c r="I79" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H79))),"",H79*$D$33)</f>
       </c>
-      <c r="J79" s="125" t="n">
+      <c r="J79" s="145" t="n">
         <f>IF(E79="","",MAX(0,E79-$G$44))</f>
         <v>1070.3437079844325</v>
       </c>
-      <c r="K79" s="125" t="n">
+      <c r="K79" s="145" t="n">
         <f>IF(D79="","",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>1153.31608844834</v>
       </c>
-      <c r="L79" s="125" t="n">
+      <c r="L79" s="148" t="n">
         <f>IF(K79="","",$J$41+K79)</f>
         <v>1327.8579946295904</v>
       </c>
@@ -2926,40 +3004,40 @@
     <row r="80" ht="20" customHeight="1">
       <c r="A80"/>
       <c r="B80"/>
-      <c r="C80" t="n">
+      <c r="C80" s="133" t="n">
         <v>0.9</v>
       </c>
-      <c r="D80" s="125" t="n">
+      <c r="D80" s="145" t="n">
         <f>IF(C80&lt;$G$32,$D$45*(1-C80)-$G$51,"")</f>
         <v>18367346.93877551</v>
       </c>
-      <c r="E80" s="125" t="n">
+      <c r="E80" s="145" t="n">
         <f>IF(D80="","",$G$50/D80)</f>
         <v>1919.9609679937555</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" s="136" t="n">
         <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
         <v>0.0001045312082574378</v>
       </c>
-      <c r="G80" t="str">
+      <c r="G80" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F80))),"",F80*$D$33)</f>
       </c>
-      <c r="H80" s="125" t="n">
+      <c r="H80" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$45)</f>
         <v>104531.2082574378</v>
       </c>
-      <c r="I80" s="125" t="str">
+      <c r="I80" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H80))),"",H80*$D$33)</f>
       </c>
-      <c r="J80" s="125" t="n">
+      <c r="J80" s="145" t="n">
         <f>IF(E80="","",MAX(0,E80-$G$44))</f>
         <v>1747.1644808743176</v>
       </c>
-      <c r="K80" s="125" t="n">
+      <c r="K80" s="145" t="n">
         <f>IF(D80="","",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>1965.5600409836077</v>
       </c>
-      <c r="L80" s="125" t="n">
+      <c r="L80" s="148" t="n">
         <f>IF(K80="","",$J$41+K80)</f>
         <v>2140.1019471648583</v>
       </c>
@@ -2967,40 +3045,40 @@
     <row r="81" ht="20" customHeight="1">
       <c r="A81"/>
       <c r="B81"/>
-      <c r="C81" t="n">
+      <c r="C81" s="133" t="n">
         <v>0.905</v>
       </c>
-      <c r="D81" s="125" t="n">
+      <c r="D81" s="145" t="n">
         <f>IF(C81&lt;$G$32,$D$45*(1-C81)-$G$51,"")</f>
         <v>13367346.938775495</v>
       </c>
-      <c r="E81" s="125" t="n">
+      <c r="E81" s="145" t="n">
         <f>IF(D81="","",$G$50/D81)</f>
         <v>2638.1143071669953</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81" s="136" t="n">
         <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
         <v>0.00019735511610867622</v>
       </c>
-      <c r="G81" t="str">
+      <c r="G81" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F81))),"",F81*$D$33)</f>
       </c>
-      <c r="H81" s="125" t="n">
+      <c r="H81" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$45)</f>
         <v>197355.11610867621</v>
       </c>
-      <c r="I81" s="125" t="str">
+      <c r="I81" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H81))),"",H81*$D$33)</f>
       </c>
-      <c r="J81" s="125" t="n">
+      <c r="J81" s="145" t="n">
         <f>IF(E81="","",MAX(0,E81-$G$44))</f>
         <v>2465.3178200475572</v>
       </c>
-      <c r="K81" s="125" t="n">
+      <c r="K81" s="145" t="n">
         <f>IF(D81="","",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>2909.51922906513</v>
       </c>
-      <c r="L81" s="125" t="n">
+      <c r="L81" s="148" t="n">
         <f>IF(K81="","",$J$41+K81)</f>
         <v>3084.06113524638</v>
       </c>
@@ -3008,40 +3086,40 @@
     <row r="82" ht="20" customHeight="1">
       <c r="A82"/>
       <c r="B82"/>
-      <c r="C82" t="n">
+      <c r="C82" s="133" t="n">
         <v>0.91</v>
       </c>
-      <c r="D82" s="125" t="n">
+      <c r="D82" s="145" t="n">
         <f>IF(C82&lt;$G$32,$D$45*(1-C82)-$G$51,"")</f>
         <v>8367346.938775495</v>
       </c>
-      <c r="E82" s="125" t="n">
+      <c r="E82" s="145" t="n">
         <f>IF(D82="","",$G$50/D82)</f>
         <v>4214.548466327764</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82" s="136" t="n">
         <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
         <v>0.0005036899386586849</v>
       </c>
-      <c r="G82" t="str">
+      <c r="G82" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F82))),"",F82*$D$33)</f>
       </c>
-      <c r="H82" s="125" t="n">
+      <c r="H82" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$45)</f>
         <v>503689.93865868496</v>
       </c>
-      <c r="I82" s="125" t="str">
+      <c r="I82" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H82))),"",H82*$D$33)</f>
       </c>
-      <c r="J82" s="125" t="n">
+      <c r="J82" s="145" t="n">
         <f>IF(E82="","",MAX(0,E82-$G$44))</f>
         <v>4041.751979208326</v>
       </c>
-      <c r="K82" s="125" t="n">
+      <c r="K82" s="145" t="n">
         <f>IF(D82="","",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>5345.542940243272</v>
       </c>
-      <c r="L82" s="125" t="n">
+      <c r="L82" s="148" t="n">
         <f>IF(K82="","",$J$41+K82)</f>
         <v>5520.084846424523</v>
       </c>
@@ -3049,40 +3127,40 @@
     <row r="83" ht="20" customHeight="1">
       <c r="A83"/>
       <c r="B83"/>
-      <c r="C83" t="n">
+      <c r="C83" s="133" t="n">
         <v>0.915</v>
       </c>
-      <c r="D83" s="125" t="n">
+      <c r="D83" s="145" t="n">
         <f>IF(C83&lt;$G$32,$D$45*(1-C83)-$G$51,"")</f>
         <v>3367346.9387754947</v>
       </c>
-      <c r="E83" s="125" t="n">
+      <c r="E83" s="145" t="n">
         <f>IF(D83="","",$G$50/D83)</f>
         <v>10472.514370875078</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83" s="136" t="n">
         <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
         <v>0.0031100194192295832</v>
       </c>
-      <c r="G83" t="str">
+      <c r="G83" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F83))),"",F83*$D$33)</f>
       </c>
-      <c r="H83" s="125" t="n">
+      <c r="H83" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$45)</f>
         <v>3110019.4192295833</v>
       </c>
-      <c r="I83" s="125" t="str">
+      <c r="I83" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H83))),"",H83*$D$33)</f>
       </c>
-      <c r="J83" s="125" t="n">
+      <c r="J83" s="145" t="n">
         <f>IF(E83="","",MAX(0,E83-$G$44))</f>
         <v>10299.71788375564</v>
       </c>
-      <c r="K83" s="125" t="n">
+      <c r="K83" s="145" t="n">
         <f>IF(D83="","",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>26145.43770491818</v>
       </c>
-      <c r="L83" s="125" t="n">
+      <c r="L83" s="148" t="n">
         <f>IF(K83="","",$J$41+K83)</f>
         <v>26319.97961109943</v>
       </c>
@@ -3090,461 +3168,461 @@
     <row r="84" ht="20" customHeight="1">
       <c r="A84"/>
       <c r="B84"/>
-      <c r="C84" t="n">
+      <c r="C84" s="133" t="n">
         <v>0.918</v>
       </c>
-      <c r="D84" s="125" t="str">
+      <c r="D84" s="145" t="str">
         <f>IF(C84&lt;$G$32,$D$45*(1-C84)-$G$51,"")</f>
       </c>
-      <c r="E84" s="125" t="str">
+      <c r="E84" s="145" t="str">
         <f>IF(D84="","",$G$50/D84)</f>
       </c>
-      <c r="F84" t="str">
+      <c r="F84" s="136" t="str">
         <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
       </c>
-      <c r="G84" t="str">
+      <c r="G84" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F84))),"",F84*$D$33)</f>
       </c>
-      <c r="H84" s="125" t="str">
+      <c r="H84" s="145" t="str">
         <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$45)</f>
       </c>
-      <c r="I84" s="125" t="str">
+      <c r="I84" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H84))),"",H84*$D$33)</f>
       </c>
-      <c r="J84" s="125" t="str">
+      <c r="J84" s="145" t="str">
         <f>IF(E84="","",MAX(0,E84-$G$44))</f>
       </c>
-      <c r="K84" s="125" t="str">
+      <c r="K84" s="145" t="str">
         <f>IF(D84="","",$G$50/($G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L84" s="125" t="str">
+      <c r="L84" s="148" t="str">
         <f>IF(K84="","",$J$41+K84)</f>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85"/>
       <c r="B85"/>
-      <c r="C85" t="n">
+      <c r="C85" s="134" t="n">
         <v>0.9183673469387755</v>
       </c>
-      <c r="D85" s="125" t="str">
+      <c r="D85" s="146" t="str">
         <f>IF(C85&lt;$G$32,$D$45*(1-C85)-$G$51,"")</f>
       </c>
-      <c r="E85" s="125" t="str">
+      <c r="E85" s="146" t="str">
         <f>IF(D85="","",$G$50/D85)</f>
       </c>
-      <c r="F85" t="str">
+      <c r="F85" s="137" t="str">
         <f>IF(OR(D85="",E85=""),"",E85/D85)</f>
       </c>
-      <c r="G85" t="str">
+      <c r="G85" s="137" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F85))),"",F85*$D$33)</f>
       </c>
-      <c r="H85" s="125" t="str">
+      <c r="H85" s="146" t="str">
         <f>IF(NOT(ISNUMBER(F85)),"",F85*$D$45)</f>
       </c>
-      <c r="I85" s="125" t="str">
+      <c r="I85" s="146" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H85))),"",H85*$D$33)</f>
       </c>
-      <c r="J85" s="125" t="str">
+      <c r="J85" s="146" t="str">
         <f>IF(E85="","",MAX(0,E85-$G$44))</f>
       </c>
-      <c r="K85" s="125" t="str">
+      <c r="K85" s="146" t="str">
         <f>IF(D85="","",$G$50/($G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L85" s="125" t="str">
+      <c r="L85" s="149" t="str">
         <f>IF(K85="","",$J$41+K85)</f>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86"/>
       <c r="B86"/>
-      <c r="C86"/>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
-      <c r="I86"/>
-      <c r="J86"/>
-      <c r="K86"/>
-      <c r="L86"/>
+      <c r="C86" s="106"/>
+      <c r="D86" s="106"/>
+      <c r="E86" s="106"/>
+      <c r="F86" s="106"/>
+      <c r="G86" s="106"/>
+      <c r="H86" s="106"/>
+      <c r="I86" s="106"/>
+      <c r="J86" s="106"/>
+      <c r="K86" s="106"/>
+      <c r="L86" s="106"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87"/>
       <c r="B87"/>
-      <c r="C87"/>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
-      <c r="I87"/>
-      <c r="J87"/>
-      <c r="K87"/>
-      <c r="L87"/>
-    </row>
-    <row r="88" ht="20" customHeight="1">
+      <c r="C87" s="106"/>
+      <c r="D87" s="106"/>
+      <c r="E87" s="106"/>
+      <c r="F87" s="106"/>
+      <c r="G87" s="106"/>
+      <c r="H87" s="106"/>
+      <c r="I87" s="106"/>
+      <c r="J87" s="106"/>
+      <c r="K87" s="106"/>
+      <c r="L87" s="106"/>
+    </row>
+    <row r="88" ht="24" customHeight="1">
       <c r="A88"/>
       <c r="B88"/>
-      <c r="C88" t="str">
+      <c r="C88" s="102" t="str">
         <v>外盘回落参考</v>
       </c>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
-      <c r="G88"/>
-      <c r="H88"/>
-      <c r="I88"/>
-      <c r="J88"/>
-      <c r="K88"/>
-      <c r="L88"/>
-    </row>
-    <row r="89" ht="20" customHeight="1">
+      <c r="D88" s="102"/>
+      <c r="E88" s="102"/>
+      <c r="F88" s="102"/>
+      <c r="G88" s="102"/>
+      <c r="H88" s="102"/>
+      <c r="I88" s="102"/>
+      <c r="J88" s="102"/>
+      <c r="K88" s="102"/>
+      <c r="L88" s="102"/>
+    </row>
+    <row r="89" ht="32" customHeight="1">
       <c r="A89"/>
       <c r="B89"/>
-      <c r="C89" t="str">
+      <c r="C89" s="77" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D89" t="str">
+      <c r="D89" s="77" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E89" t="str">
+      <c r="E89" s="77" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F89" t="str">
+      <c r="F89" s="77" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G89" t="str">
+      <c r="G89" s="77" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H89" t="str">
+      <c r="H89" s="77" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I89" t="str">
+      <c r="I89" s="77" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J89" t="str">
+      <c r="J89" s="77" t="str">
         <v>较毕业点回撤</v>
       </c>
-      <c r="K89" t="str"/>
-      <c r="L89" t="str"/>
+      <c r="K89" s="77" t="str"/>
+      <c r="L89" s="77" t="str"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90"/>
       <c r="B90"/>
-      <c r="C90" t="n">
+      <c r="C90" s="132" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="D90" s="125" t="n">
+      <c r="D90" s="144" t="n">
         <f>$D$45*(1-C90)-$G$51</f>
         <v>204081632.6530612</v>
       </c>
-      <c r="E90" s="125" t="n">
+      <c r="E90" s="144" t="n">
         <f>$G$50/D90</f>
         <v>172.79648711943798</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90" s="135" t="n">
         <f>IF(OR(D90="",E90=""),"",E90/D90)</f>
         <v>8.467027868852462e-7</v>
       </c>
-      <c r="G90" t="str">
+      <c r="G90" s="135" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F90))),"",F90*$D$33)</f>
       </c>
-      <c r="H90" s="125" t="n">
+      <c r="H90" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F90)),"",F90*$D$45)</f>
         <v>846.7027868852463</v>
       </c>
-      <c r="I90" s="125" t="str">
+      <c r="I90" s="144" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H90))),"",H90*$D$33)</f>
       </c>
-      <c r="J90" t="n">
+      <c r="J90" s="132" t="n">
         <f>IF($H$90&gt;0,1-H90/$H$90,0)</f>
         <v>0</v>
       </c>
-      <c r="K90"/>
-      <c r="L90"/>
+      <c r="K90" s="129"/>
+      <c r="L90" s="129"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91"/>
       <c r="B91"/>
-      <c r="C91" t="n">
+      <c r="C91" s="133" t="n">
         <v>0.7</v>
       </c>
-      <c r="D91" s="125" t="n">
+      <c r="D91" s="145" t="n">
         <f>$D$45*(1-C91)-$G$51</f>
         <v>218367346.9387756</v>
       </c>
-      <c r="E91" s="125" t="n">
+      <c r="E91" s="145" t="n">
         <f>$G$50/D91</f>
         <v>161.49204403685786</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91" s="136" t="n">
         <f>IF(OR(D91="",E91=""),"",E91/D91)</f>
         <v>7.395430054024329e-7</v>
       </c>
-      <c r="G91" t="str">
+      <c r="G91" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F91))),"",F91*$D$33)</f>
       </c>
-      <c r="H91" s="125" t="n">
+      <c r="H91" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F91)),"",F91*$D$45)</f>
         <v>739.5430054024329</v>
       </c>
-      <c r="I91" s="125" t="str">
+      <c r="I91" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H91))),"",H91*$D$33)</f>
       </c>
-      <c r="J91" t="n">
+      <c r="J91" s="133" t="n">
         <f>IF($H$90&gt;0,1-H91/$H$90,0)</f>
         <v>0.12656127172678933</v>
       </c>
-      <c r="K91"/>
-      <c r="L91"/>
+      <c r="K91" s="130"/>
+      <c r="L91" s="130"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92"/>
       <c r="B92"/>
-      <c r="C92" t="n">
+      <c r="C92" s="133" t="n">
         <v>0.6</v>
       </c>
-      <c r="D92" s="125" t="n">
+      <c r="D92" s="145" t="n">
         <f>$D$45*(1-C92)-$G$51</f>
         <v>318367346.93877554</v>
       </c>
-      <c r="E92" s="125" t="n">
+      <c r="E92" s="145" t="n">
         <f>$G$50/D92</f>
         <v>110.76697892271665</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92" s="136" t="n">
         <f>IF(OR(D92="",E92=""),"",E92/D92)</f>
         <v>3.479219209751997e-7</v>
       </c>
-      <c r="G92" t="str">
+      <c r="G92" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F92))),"",F92*$D$33)</f>
       </c>
-      <c r="H92" s="125" t="n">
+      <c r="H92" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F92)),"",F92*$D$45)</f>
         <v>347.9219209751997</v>
       </c>
-      <c r="I92" s="125" t="str">
+      <c r="I92" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H92))),"",H92*$D$33)</f>
       </c>
-      <c r="J92" t="n">
+      <c r="J92" s="133" t="n">
         <f>IF($H$90&gt;0,1-H92/$H$90,0)</f>
         <v>0.5890861275476661</v>
       </c>
-      <c r="K92"/>
-      <c r="L92"/>
+      <c r="K92" s="130"/>
+      <c r="L92" s="130"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93"/>
       <c r="B93"/>
-      <c r="C93" t="n">
+      <c r="C93" s="133" t="n">
         <v>0.5</v>
       </c>
-      <c r="D93" s="125" t="n">
+      <c r="D93" s="145" t="n">
         <f>$D$45*(1-C93)-$G$51</f>
         <v>418367346.93877554</v>
       </c>
-      <c r="E93" s="125" t="n">
+      <c r="E93" s="145" t="n">
         <f>$G$50/D93</f>
         <v>84.29096932655511</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" s="136" t="n">
         <f>IF(OR(D93="",E93=""),"",E93/D93)</f>
         <v>2.0147597546347317e-7</v>
       </c>
-      <c r="G93" t="str">
+      <c r="G93" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F93))),"",F93*$D$33)</f>
       </c>
-      <c r="H93" s="125" t="n">
+      <c r="H93" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F93)),"",F93*$D$45)</f>
         <v>201.47597546347316</v>
       </c>
-      <c r="I93" s="125" t="str">
+      <c r="I93" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H93))),"",H93*$D$33)</f>
       </c>
-      <c r="J93" t="n">
+      <c r="J93" s="133" t="n">
         <f>IF($H$90&gt;0,1-H93/$H$90,0)</f>
         <v>0.7620464009518144</v>
       </c>
-      <c r="K93"/>
-      <c r="L93"/>
+      <c r="K93" s="130"/>
+      <c r="L93" s="130"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94"/>
       <c r="B94"/>
-      <c r="C94" t="n">
+      <c r="C94" s="133" t="n">
         <v>0.4</v>
       </c>
-      <c r="D94" s="125" t="n">
+      <c r="D94" s="145" t="n">
         <f>$D$45*(1-C94)-$G$51</f>
         <v>518367346.93877554</v>
       </c>
-      <c r="E94" s="125" t="n">
+      <c r="E94" s="145" t="n">
         <f>$G$50/D94</f>
         <v>68.03011303914882</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94" s="136" t="n">
         <f>IF(OR(D94="",E94=""),"",E94/D94)</f>
         <v>1.3123919444560203e-7</v>
       </c>
-      <c r="G94" t="str">
+      <c r="G94" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F94))),"",F94*$D$33)</f>
       </c>
-      <c r="H94" s="125" t="n">
+      <c r="H94" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F94)),"",F94*$D$45)</f>
         <v>131.23919444560204</v>
       </c>
-      <c r="I94" s="125" t="str">
+      <c r="I94" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H94))),"",H94*$D$33)</f>
       </c>
-      <c r="J94" t="n">
+      <c r="J94" s="133" t="n">
         <f>IF($H$90&gt;0,1-H94/$H$90,0)</f>
         <v>0.84499968999938</v>
       </c>
-      <c r="K94"/>
-      <c r="L94"/>
+      <c r="K94" s="130"/>
+      <c r="L94" s="130"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95"/>
       <c r="B95"/>
-      <c r="C95" t="n">
+      <c r="C95" s="133" t="n">
         <v>0.3</v>
       </c>
-      <c r="D95" s="125" t="n">
+      <c r="D95" s="145" t="n">
         <f>$D$45*(1-C95)-$G$51</f>
         <v>618367346.9387755</v>
       </c>
-      <c r="E95" s="125" t="n">
+      <c r="E95" s="145" t="n">
         <f>$G$50/D95</f>
         <v>57.028543603774914</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95" s="136" t="n">
         <f>IF(OR(D95="",E95=""),"",E95/D95)</f>
         <v>9.222437744504854e-8</v>
       </c>
-      <c r="G95" t="str">
+      <c r="G95" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F95))),"",F95*$D$33)</f>
       </c>
-      <c r="H95" s="125" t="n">
+      <c r="H95" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F95)),"",F95*$D$45)</f>
         <v>92.22437744504853</v>
       </c>
-      <c r="I95" s="125" t="str">
+      <c r="I95" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H95))),"",H95*$D$33)</f>
       </c>
-      <c r="J95" t="n">
+      <c r="J95" s="133" t="n">
         <f>IF($H$90&gt;0,1-H95/$H$90,0)</f>
         <v>0.8910782167325644</v>
       </c>
-      <c r="K95"/>
-      <c r="L95"/>
+      <c r="K95" s="130"/>
+      <c r="L95" s="130"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96"/>
       <c r="B96"/>
-      <c r="C96" t="n">
+      <c r="C96" s="133" t="n">
         <v>0.2</v>
       </c>
-      <c r="D96" s="125" t="n">
+      <c r="D96" s="145" t="n">
         <f>$D$45*(1-C96)-$G$51</f>
         <v>718367346.9387755</v>
       </c>
-      <c r="E96" s="125" t="n">
+      <c r="E96" s="145" t="n">
         <f>$G$50/D96</f>
         <v>49.089911113476695</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96" s="136" t="n">
         <f>IF(OR(D96="",E96=""),"",E96/D96)</f>
         <v>6.833538762955562e-8</v>
       </c>
-      <c r="G96" t="str">
+      <c r="G96" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F96))),"",F96*$D$33)</f>
       </c>
-      <c r="H96" s="125" t="n">
+      <c r="H96" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F96)),"",F96*$D$45)</f>
         <v>68.33538762955563</v>
       </c>
-      <c r="I96" s="125" t="str">
+      <c r="I96" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H96))),"",H96*$D$33)</f>
       </c>
-      <c r="J96" t="n">
+      <c r="J96" s="133" t="n">
         <f>IF($H$90&gt;0,1-H96/$H$90,0)</f>
         <v>0.9192923553719008</v>
       </c>
-      <c r="K96"/>
-      <c r="L96"/>
+      <c r="K96" s="130"/>
+      <c r="L96" s="130"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97"/>
       <c r="B97"/>
-      <c r="C97" t="n">
+      <c r="C97" s="133" t="n">
         <v>0.1</v>
       </c>
-      <c r="D97" s="125" t="n">
+      <c r="D97" s="145" t="n">
         <f>$D$45*(1-C97)-$G$51</f>
         <v>818367346.9387755</v>
       </c>
-      <c r="E97" s="125" t="n">
+      <c r="E97" s="145" t="n">
         <f>$G$50/D97</f>
         <v>43.09139329661795</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" s="136" t="n">
         <f>IF(OR(D97="",E97=""),"",E97/D97)</f>
         <v>5.265531849212667e-8</v>
       </c>
-      <c r="G97" t="str">
+      <c r="G97" s="136" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F97))),"",F97*$D$33)</f>
       </c>
-      <c r="H97" s="125" t="n">
+      <c r="H97" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F97)),"",F97*$D$45)</f>
         <v>52.65531849212667</v>
       </c>
-      <c r="I97" s="125" t="str">
+      <c r="I97" s="145" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H97))),"",H97*$D$33)</f>
       </c>
-      <c r="J97" t="n">
+      <c r="J97" s="133" t="n">
         <f>IF($H$90&gt;0,1-H97/$H$90,0)</f>
         <v>0.9378113320190795</v>
       </c>
-      <c r="K97"/>
-      <c r="L97"/>
+      <c r="K97" s="130"/>
+      <c r="L97" s="130"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98"/>
       <c r="B98"/>
-      <c r="C98" t="n">
+      <c r="C98" s="134" t="n">
         <v>0</v>
       </c>
-      <c r="D98" s="125" t="n">
+      <c r="D98" s="146" t="n">
         <f>$D$45*(1-C98)-$G$51</f>
         <v>918367346.9387755</v>
       </c>
-      <c r="E98" s="125" t="n">
+      <c r="E98" s="146" t="n">
         <f>$G$50/D98</f>
         <v>38.399219359875104</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98" s="137" t="n">
         <f>IF(OR(D98="",E98=""),"",E98/D98)</f>
         <v>4.181248330297511e-8</v>
       </c>
-      <c r="G98" t="str">
+      <c r="G98" s="137" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F98))),"",F98*$D$33)</f>
       </c>
-      <c r="H98" s="125" t="n">
+      <c r="H98" s="146" t="n">
         <f>IF(NOT(ISNUMBER(F98)),"",F98*$D$45)</f>
         <v>41.81248330297511</v>
       </c>
-      <c r="I98" s="125" t="str">
+      <c r="I98" s="146" t="str">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H98))),"",H98*$D$33)</f>
       </c>
-      <c r="J98" t="n">
+      <c r="J98" s="134" t="n">
         <f>IF($H$90&gt;0,1-H98/$H$90,0)</f>
         <v>0.9506172839506173</v>
       </c>
-      <c r="K98" t="str">
+      <c r="K98" s="131" t="str">
         <v>沉没成本 / Quote</v>
       </c>
-      <c r="L98" t="n">
+      <c r="L98" s="131" t="n">
         <f>E98</f>
         <v>38.399219359875104</v>
       </c>
@@ -3552,730 +3630,730 @@
     <row r="99" ht="20" customHeight="1">
       <c r="A99"/>
       <c r="B99"/>
-      <c r="C99"/>
-      <c r="D99"/>
-      <c r="E99"/>
-      <c r="F99"/>
-      <c r="G99"/>
-      <c r="H99"/>
-      <c r="I99"/>
-      <c r="J99"/>
-      <c r="K99"/>
-      <c r="L99"/>
+      <c r="C99" s="106"/>
+      <c r="D99" s="106"/>
+      <c r="E99" s="106"/>
+      <c r="F99" s="106"/>
+      <c r="G99" s="106"/>
+      <c r="H99" s="106"/>
+      <c r="I99" s="106"/>
+      <c r="J99" s="106"/>
+      <c r="K99" s="106"/>
+      <c r="L99" s="106"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100"/>
       <c r="B100"/>
-      <c r="C100"/>
-      <c r="D100"/>
-      <c r="E100"/>
-      <c r="F100"/>
-      <c r="G100"/>
-      <c r="H100"/>
-      <c r="I100"/>
-      <c r="J100"/>
-      <c r="K100"/>
-      <c r="L100"/>
+      <c r="C100" s="106"/>
+      <c r="D100" s="106"/>
+      <c r="E100" s="106"/>
+      <c r="F100" s="106"/>
+      <c r="G100" s="106"/>
+      <c r="H100" s="106"/>
+      <c r="I100" s="106"/>
+      <c r="J100" s="106"/>
+      <c r="K100" s="106"/>
+      <c r="L100" s="106"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101"/>
       <c r="B101"/>
-      <c r="C101"/>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
-      <c r="I101"/>
-      <c r="J101"/>
-      <c r="K101"/>
-      <c r="L101"/>
+      <c r="C101" s="106"/>
+      <c r="D101" s="106"/>
+      <c r="E101" s="106"/>
+      <c r="F101" s="106"/>
+      <c r="G101" s="106"/>
+      <c r="H101" s="106"/>
+      <c r="I101" s="106"/>
+      <c r="J101" s="106"/>
+      <c r="K101" s="106"/>
+      <c r="L101" s="106"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102"/>
       <c r="B102"/>
-      <c r="C102"/>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
-      <c r="I102"/>
-      <c r="J102"/>
-      <c r="K102"/>
-      <c r="L102"/>
+      <c r="C102" s="106"/>
+      <c r="D102" s="106"/>
+      <c r="E102" s="106"/>
+      <c r="F102" s="106"/>
+      <c r="G102" s="106"/>
+      <c r="H102" s="106"/>
+      <c r="I102" s="106"/>
+      <c r="J102" s="106"/>
+      <c r="K102" s="106"/>
+      <c r="L102" s="106"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103"/>
       <c r="B103"/>
-      <c r="C103"/>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103"/>
-      <c r="H103"/>
-      <c r="I103"/>
-      <c r="J103"/>
-      <c r="K103"/>
-      <c r="L103"/>
+      <c r="C103" s="106"/>
+      <c r="D103" s="106"/>
+      <c r="E103" s="106"/>
+      <c r="F103" s="106"/>
+      <c r="G103" s="106"/>
+      <c r="H103" s="106"/>
+      <c r="I103" s="106"/>
+      <c r="J103" s="106"/>
+      <c r="K103" s="106"/>
+      <c r="L103" s="106"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104"/>
       <c r="B104"/>
-      <c r="C104"/>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104"/>
-      <c r="H104"/>
-      <c r="I104"/>
-      <c r="J104"/>
-      <c r="K104"/>
-      <c r="L104"/>
+      <c r="C104" s="106"/>
+      <c r="D104" s="106"/>
+      <c r="E104" s="106"/>
+      <c r="F104" s="106"/>
+      <c r="G104" s="106"/>
+      <c r="H104" s="106"/>
+      <c r="I104" s="106"/>
+      <c r="J104" s="106"/>
+      <c r="K104" s="106"/>
+      <c r="L104" s="106"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105"/>
       <c r="B105"/>
-      <c r="C105"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105"/>
-      <c r="H105"/>
-      <c r="I105"/>
-      <c r="J105"/>
-      <c r="K105"/>
-      <c r="L105"/>
+      <c r="C105" s="106"/>
+      <c r="D105" s="106"/>
+      <c r="E105" s="106"/>
+      <c r="F105" s="106"/>
+      <c r="G105" s="106"/>
+      <c r="H105" s="106"/>
+      <c r="I105" s="106"/>
+      <c r="J105" s="106"/>
+      <c r="K105" s="106"/>
+      <c r="L105" s="106"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106"/>
       <c r="B106"/>
-      <c r="C106"/>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
-      <c r="I106"/>
-      <c r="J106"/>
-      <c r="K106"/>
-      <c r="L106"/>
+      <c r="C106" s="106"/>
+      <c r="D106" s="106"/>
+      <c r="E106" s="106"/>
+      <c r="F106" s="106"/>
+      <c r="G106" s="106"/>
+      <c r="H106" s="106"/>
+      <c r="I106" s="106"/>
+      <c r="J106" s="106"/>
+      <c r="K106" s="106"/>
+      <c r="L106" s="106"/>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107"/>
       <c r="B107"/>
-      <c r="C107"/>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107"/>
-      <c r="I107"/>
-      <c r="J107"/>
-      <c r="K107"/>
-      <c r="L107"/>
+      <c r="C107" s="106"/>
+      <c r="D107" s="106"/>
+      <c r="E107" s="106"/>
+      <c r="F107" s="106"/>
+      <c r="G107" s="106"/>
+      <c r="H107" s="106"/>
+      <c r="I107" s="106"/>
+      <c r="J107" s="106"/>
+      <c r="K107" s="106"/>
+      <c r="L107" s="106"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108"/>
       <c r="B108"/>
-      <c r="C108"/>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
-      <c r="G108"/>
-      <c r="H108"/>
-      <c r="I108"/>
-      <c r="J108"/>
-      <c r="K108"/>
-      <c r="L108"/>
+      <c r="C108" s="106"/>
+      <c r="D108" s="106"/>
+      <c r="E108" s="106"/>
+      <c r="F108" s="106"/>
+      <c r="G108" s="106"/>
+      <c r="H108" s="106"/>
+      <c r="I108" s="106"/>
+      <c r="J108" s="106"/>
+      <c r="K108" s="106"/>
+      <c r="L108" s="106"/>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109"/>
       <c r="B109"/>
-      <c r="C109"/>
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
-      <c r="G109"/>
-      <c r="H109"/>
-      <c r="I109"/>
-      <c r="J109"/>
-      <c r="K109"/>
-      <c r="L109"/>
+      <c r="C109" s="106"/>
+      <c r="D109" s="106"/>
+      <c r="E109" s="106"/>
+      <c r="F109" s="106"/>
+      <c r="G109" s="106"/>
+      <c r="H109" s="106"/>
+      <c r="I109" s="106"/>
+      <c r="J109" s="106"/>
+      <c r="K109" s="106"/>
+      <c r="L109" s="106"/>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110"/>
       <c r="B110"/>
-      <c r="C110"/>
-      <c r="D110"/>
-      <c r="E110"/>
-      <c r="F110"/>
-      <c r="G110"/>
-      <c r="H110"/>
-      <c r="I110"/>
-      <c r="J110"/>
-      <c r="K110"/>
-      <c r="L110"/>
+      <c r="C110" s="106"/>
+      <c r="D110" s="106"/>
+      <c r="E110" s="106"/>
+      <c r="F110" s="106"/>
+      <c r="G110" s="106"/>
+      <c r="H110" s="106"/>
+      <c r="I110" s="106"/>
+      <c r="J110" s="106"/>
+      <c r="K110" s="106"/>
+      <c r="L110" s="106"/>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111"/>
       <c r="B111"/>
-      <c r="C111"/>
-      <c r="D111"/>
-      <c r="E111"/>
-      <c r="F111"/>
-      <c r="G111"/>
-      <c r="H111"/>
-      <c r="I111"/>
-      <c r="J111"/>
-      <c r="K111"/>
-      <c r="L111"/>
+      <c r="C111" s="106"/>
+      <c r="D111" s="106"/>
+      <c r="E111" s="106"/>
+      <c r="F111" s="106"/>
+      <c r="G111" s="106"/>
+      <c r="H111" s="106"/>
+      <c r="I111" s="106"/>
+      <c r="J111" s="106"/>
+      <c r="K111" s="106"/>
+      <c r="L111" s="106"/>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112"/>
       <c r="B112"/>
-      <c r="C112"/>
-      <c r="D112"/>
-      <c r="E112"/>
-      <c r="F112"/>
-      <c r="G112"/>
-      <c r="H112"/>
-      <c r="I112"/>
-      <c r="J112"/>
-      <c r="K112"/>
-      <c r="L112"/>
+      <c r="C112" s="106"/>
+      <c r="D112" s="106"/>
+      <c r="E112" s="106"/>
+      <c r="F112" s="106"/>
+      <c r="G112" s="106"/>
+      <c r="H112" s="106"/>
+      <c r="I112" s="106"/>
+      <c r="J112" s="106"/>
+      <c r="K112" s="106"/>
+      <c r="L112" s="106"/>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113"/>
       <c r="B113"/>
-      <c r="C113"/>
-      <c r="D113"/>
-      <c r="E113"/>
-      <c r="F113"/>
-      <c r="G113"/>
-      <c r="H113"/>
-      <c r="I113"/>
-      <c r="J113"/>
-      <c r="K113"/>
-      <c r="L113"/>
+      <c r="C113" s="106"/>
+      <c r="D113" s="106"/>
+      <c r="E113" s="106"/>
+      <c r="F113" s="106"/>
+      <c r="G113" s="106"/>
+      <c r="H113" s="106"/>
+      <c r="I113" s="106"/>
+      <c r="J113" s="106"/>
+      <c r="K113" s="106"/>
+      <c r="L113" s="106"/>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114"/>
       <c r="B114"/>
-      <c r="C114"/>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
-      <c r="G114"/>
-      <c r="H114"/>
-      <c r="I114"/>
-      <c r="J114"/>
-      <c r="K114"/>
-      <c r="L114"/>
+      <c r="C114" s="106"/>
+      <c r="D114" s="106"/>
+      <c r="E114" s="106"/>
+      <c r="F114" s="106"/>
+      <c r="G114" s="106"/>
+      <c r="H114" s="106"/>
+      <c r="I114" s="106"/>
+      <c r="J114" s="106"/>
+      <c r="K114" s="106"/>
+      <c r="L114" s="106"/>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115"/>
       <c r="B115"/>
-      <c r="C115"/>
-      <c r="D115"/>
-      <c r="E115"/>
-      <c r="F115"/>
-      <c r="G115"/>
-      <c r="H115"/>
-      <c r="I115"/>
-      <c r="J115"/>
-      <c r="K115"/>
-      <c r="L115"/>
+      <c r="C115" s="106"/>
+      <c r="D115" s="106"/>
+      <c r="E115" s="106"/>
+      <c r="F115" s="106"/>
+      <c r="G115" s="106"/>
+      <c r="H115" s="106"/>
+      <c r="I115" s="106"/>
+      <c r="J115" s="106"/>
+      <c r="K115" s="106"/>
+      <c r="L115" s="106"/>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116"/>
       <c r="B116"/>
-      <c r="C116"/>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116"/>
-      <c r="G116"/>
-      <c r="H116"/>
-      <c r="I116"/>
-      <c r="J116"/>
-      <c r="K116"/>
-      <c r="L116"/>
+      <c r="C116" s="106"/>
+      <c r="D116" s="106"/>
+      <c r="E116" s="106"/>
+      <c r="F116" s="106"/>
+      <c r="G116" s="106"/>
+      <c r="H116" s="106"/>
+      <c r="I116" s="106"/>
+      <c r="J116" s="106"/>
+      <c r="K116" s="106"/>
+      <c r="L116" s="106"/>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117"/>
       <c r="B117"/>
-      <c r="C117"/>
-      <c r="D117"/>
-      <c r="E117"/>
-      <c r="F117"/>
-      <c r="G117"/>
-      <c r="H117"/>
-      <c r="I117"/>
-      <c r="J117"/>
-      <c r="K117"/>
-      <c r="L117"/>
+      <c r="C117" s="106"/>
+      <c r="D117" s="106"/>
+      <c r="E117" s="106"/>
+      <c r="F117" s="106"/>
+      <c r="G117" s="106"/>
+      <c r="H117" s="106"/>
+      <c r="I117" s="106"/>
+      <c r="J117" s="106"/>
+      <c r="K117" s="106"/>
+      <c r="L117" s="106"/>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118"/>
       <c r="B118"/>
-      <c r="C118"/>
-      <c r="D118"/>
-      <c r="E118"/>
-      <c r="F118"/>
-      <c r="G118"/>
-      <c r="H118"/>
-      <c r="I118"/>
-      <c r="J118"/>
-      <c r="K118"/>
-      <c r="L118"/>
+      <c r="C118" s="106"/>
+      <c r="D118" s="106"/>
+      <c r="E118" s="106"/>
+      <c r="F118" s="106"/>
+      <c r="G118" s="106"/>
+      <c r="H118" s="106"/>
+      <c r="I118" s="106"/>
+      <c r="J118" s="106"/>
+      <c r="K118" s="106"/>
+      <c r="L118" s="106"/>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119"/>
       <c r="B119"/>
-      <c r="C119"/>
-      <c r="D119"/>
-      <c r="E119"/>
-      <c r="F119"/>
-      <c r="G119"/>
-      <c r="H119"/>
-      <c r="I119"/>
-      <c r="J119"/>
-      <c r="K119"/>
-      <c r="L119"/>
+      <c r="C119" s="106"/>
+      <c r="D119" s="106"/>
+      <c r="E119" s="106"/>
+      <c r="F119" s="106"/>
+      <c r="G119" s="106"/>
+      <c r="H119" s="106"/>
+      <c r="I119" s="106"/>
+      <c r="J119" s="106"/>
+      <c r="K119" s="106"/>
+      <c r="L119" s="106"/>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120"/>
       <c r="B120"/>
-      <c r="C120"/>
-      <c r="D120"/>
-      <c r="E120"/>
-      <c r="F120"/>
-      <c r="G120"/>
-      <c r="H120"/>
-      <c r="I120"/>
-      <c r="J120"/>
-      <c r="K120"/>
-      <c r="L120"/>
+      <c r="C120" s="106"/>
+      <c r="D120" s="106"/>
+      <c r="E120" s="106"/>
+      <c r="F120" s="106"/>
+      <c r="G120" s="106"/>
+      <c r="H120" s="106"/>
+      <c r="I120" s="106"/>
+      <c r="J120" s="106"/>
+      <c r="K120" s="106"/>
+      <c r="L120" s="106"/>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121"/>
       <c r="B121"/>
-      <c r="C121"/>
-      <c r="D121"/>
-      <c r="E121"/>
-      <c r="F121"/>
-      <c r="G121"/>
-      <c r="H121"/>
-      <c r="I121"/>
-      <c r="J121"/>
-      <c r="K121"/>
-      <c r="L121"/>
+      <c r="C121" s="106"/>
+      <c r="D121" s="106"/>
+      <c r="E121" s="106"/>
+      <c r="F121" s="106"/>
+      <c r="G121" s="106"/>
+      <c r="H121" s="106"/>
+      <c r="I121" s="106"/>
+      <c r="J121" s="106"/>
+      <c r="K121" s="106"/>
+      <c r="L121" s="106"/>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122"/>
       <c r="B122"/>
-      <c r="C122"/>
-      <c r="D122"/>
-      <c r="E122"/>
-      <c r="F122"/>
-      <c r="G122"/>
-      <c r="H122"/>
-      <c r="I122"/>
-      <c r="J122"/>
-      <c r="K122"/>
-      <c r="L122"/>
+      <c r="C122" s="106"/>
+      <c r="D122" s="106"/>
+      <c r="E122" s="106"/>
+      <c r="F122" s="106"/>
+      <c r="G122" s="106"/>
+      <c r="H122" s="106"/>
+      <c r="I122" s="106"/>
+      <c r="J122" s="106"/>
+      <c r="K122" s="106"/>
+      <c r="L122" s="106"/>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123"/>
       <c r="B123"/>
-      <c r="C123"/>
-      <c r="D123"/>
-      <c r="E123"/>
-      <c r="F123"/>
-      <c r="G123"/>
-      <c r="H123"/>
-      <c r="I123"/>
-      <c r="J123"/>
-      <c r="K123"/>
-      <c r="L123"/>
+      <c r="C123" s="106"/>
+      <c r="D123" s="106"/>
+      <c r="E123" s="106"/>
+      <c r="F123" s="106"/>
+      <c r="G123" s="106"/>
+      <c r="H123" s="106"/>
+      <c r="I123" s="106"/>
+      <c r="J123" s="106"/>
+      <c r="K123" s="106"/>
+      <c r="L123" s="106"/>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124"/>
       <c r="B124"/>
-      <c r="C124"/>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
-      <c r="G124"/>
-      <c r="H124"/>
-      <c r="I124"/>
-      <c r="J124"/>
-      <c r="K124"/>
-      <c r="L124"/>
+      <c r="C124" s="106"/>
+      <c r="D124" s="106"/>
+      <c r="E124" s="106"/>
+      <c r="F124" s="106"/>
+      <c r="G124" s="106"/>
+      <c r="H124" s="106"/>
+      <c r="I124" s="106"/>
+      <c r="J124" s="106"/>
+      <c r="K124" s="106"/>
+      <c r="L124" s="106"/>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125"/>
       <c r="B125"/>
-      <c r="C125"/>
-      <c r="D125"/>
-      <c r="E125"/>
-      <c r="F125"/>
-      <c r="G125"/>
-      <c r="H125"/>
-      <c r="I125"/>
-      <c r="J125"/>
-      <c r="K125"/>
-      <c r="L125"/>
+      <c r="C125" s="106"/>
+      <c r="D125" s="106"/>
+      <c r="E125" s="106"/>
+      <c r="F125" s="106"/>
+      <c r="G125" s="106"/>
+      <c r="H125" s="106"/>
+      <c r="I125" s="106"/>
+      <c r="J125" s="106"/>
+      <c r="K125" s="106"/>
+      <c r="L125" s="106"/>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126"/>
       <c r="B126"/>
-      <c r="C126"/>
-      <c r="D126"/>
-      <c r="E126"/>
-      <c r="F126"/>
-      <c r="G126"/>
-      <c r="H126"/>
-      <c r="I126"/>
-      <c r="J126"/>
-      <c r="K126"/>
-      <c r="L126"/>
+      <c r="C126" s="106"/>
+      <c r="D126" s="106"/>
+      <c r="E126" s="106"/>
+      <c r="F126" s="106"/>
+      <c r="G126" s="106"/>
+      <c r="H126" s="106"/>
+      <c r="I126" s="106"/>
+      <c r="J126" s="106"/>
+      <c r="K126" s="106"/>
+      <c r="L126" s="106"/>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127"/>
       <c r="B127"/>
-      <c r="C127"/>
-      <c r="D127"/>
-      <c r="E127"/>
-      <c r="F127"/>
-      <c r="G127"/>
-      <c r="H127"/>
-      <c r="I127"/>
-      <c r="J127"/>
-      <c r="K127"/>
-      <c r="L127"/>
+      <c r="C127" s="106"/>
+      <c r="D127" s="106"/>
+      <c r="E127" s="106"/>
+      <c r="F127" s="106"/>
+      <c r="G127" s="106"/>
+      <c r="H127" s="106"/>
+      <c r="I127" s="106"/>
+      <c r="J127" s="106"/>
+      <c r="K127" s="106"/>
+      <c r="L127" s="106"/>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128"/>
       <c r="B128"/>
-      <c r="C128"/>
-      <c r="D128"/>
-      <c r="E128"/>
-      <c r="F128"/>
-      <c r="G128"/>
-      <c r="H128"/>
-      <c r="I128"/>
-      <c r="J128"/>
-      <c r="K128"/>
-      <c r="L128"/>
+      <c r="C128" s="106"/>
+      <c r="D128" s="106"/>
+      <c r="E128" s="106"/>
+      <c r="F128" s="106"/>
+      <c r="G128" s="106"/>
+      <c r="H128" s="106"/>
+      <c r="I128" s="106"/>
+      <c r="J128" s="106"/>
+      <c r="K128" s="106"/>
+      <c r="L128" s="106"/>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129"/>
       <c r="B129"/>
-      <c r="C129"/>
-      <c r="D129"/>
-      <c r="E129"/>
-      <c r="F129"/>
-      <c r="G129"/>
-      <c r="H129"/>
-      <c r="I129"/>
-      <c r="J129"/>
-      <c r="K129"/>
-      <c r="L129"/>
+      <c r="C129" s="106"/>
+      <c r="D129" s="106"/>
+      <c r="E129" s="106"/>
+      <c r="F129" s="106"/>
+      <c r="G129" s="106"/>
+      <c r="H129" s="106"/>
+      <c r="I129" s="106"/>
+      <c r="J129" s="106"/>
+      <c r="K129" s="106"/>
+      <c r="L129" s="106"/>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130"/>
       <c r="B130"/>
-      <c r="C130"/>
-      <c r="D130"/>
-      <c r="E130"/>
-      <c r="F130"/>
-      <c r="G130"/>
-      <c r="H130"/>
-      <c r="I130"/>
-      <c r="J130"/>
-      <c r="K130"/>
-      <c r="L130"/>
+      <c r="C130" s="106"/>
+      <c r="D130" s="106"/>
+      <c r="E130" s="106"/>
+      <c r="F130" s="106"/>
+      <c r="G130" s="106"/>
+      <c r="H130" s="106"/>
+      <c r="I130" s="106"/>
+      <c r="J130" s="106"/>
+      <c r="K130" s="106"/>
+      <c r="L130" s="106"/>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131"/>
       <c r="B131"/>
-      <c r="C131"/>
-      <c r="D131"/>
-      <c r="E131"/>
-      <c r="F131"/>
-      <c r="G131"/>
-      <c r="H131"/>
-      <c r="I131"/>
-      <c r="J131"/>
-      <c r="K131"/>
-      <c r="L131"/>
+      <c r="C131" s="106"/>
+      <c r="D131" s="106"/>
+      <c r="E131" s="106"/>
+      <c r="F131" s="106"/>
+      <c r="G131" s="106"/>
+      <c r="H131" s="106"/>
+      <c r="I131" s="106"/>
+      <c r="J131" s="106"/>
+      <c r="K131" s="106"/>
+      <c r="L131" s="106"/>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132"/>
       <c r="B132"/>
-      <c r="C132"/>
-      <c r="D132"/>
-      <c r="E132"/>
-      <c r="F132"/>
-      <c r="G132"/>
-      <c r="H132"/>
-      <c r="I132"/>
-      <c r="J132"/>
-      <c r="K132"/>
-      <c r="L132"/>
+      <c r="C132" s="106"/>
+      <c r="D132" s="106"/>
+      <c r="E132" s="106"/>
+      <c r="F132" s="106"/>
+      <c r="G132" s="106"/>
+      <c r="H132" s="106"/>
+      <c r="I132" s="106"/>
+      <c r="J132" s="106"/>
+      <c r="K132" s="106"/>
+      <c r="L132" s="106"/>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133"/>
       <c r="B133"/>
-      <c r="C133"/>
-      <c r="D133"/>
-      <c r="E133"/>
-      <c r="F133"/>
-      <c r="G133"/>
-      <c r="H133"/>
-      <c r="I133"/>
-      <c r="J133"/>
-      <c r="K133"/>
-      <c r="L133"/>
+      <c r="C133" s="106"/>
+      <c r="D133" s="106"/>
+      <c r="E133" s="106"/>
+      <c r="F133" s="106"/>
+      <c r="G133" s="106"/>
+      <c r="H133" s="106"/>
+      <c r="I133" s="106"/>
+      <c r="J133" s="106"/>
+      <c r="K133" s="106"/>
+      <c r="L133" s="106"/>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134"/>
       <c r="B134"/>
-      <c r="C134"/>
-      <c r="D134"/>
-      <c r="E134"/>
-      <c r="F134"/>
-      <c r="G134"/>
-      <c r="H134"/>
-      <c r="I134"/>
-      <c r="J134"/>
-      <c r="K134"/>
-      <c r="L134"/>
+      <c r="C134" s="106"/>
+      <c r="D134" s="106"/>
+      <c r="E134" s="106"/>
+      <c r="F134" s="106"/>
+      <c r="G134" s="106"/>
+      <c r="H134" s="106"/>
+      <c r="I134" s="106"/>
+      <c r="J134" s="106"/>
+      <c r="K134" s="106"/>
+      <c r="L134" s="106"/>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135"/>
       <c r="B135"/>
-      <c r="C135"/>
-      <c r="D135"/>
-      <c r="E135"/>
-      <c r="F135"/>
-      <c r="G135"/>
-      <c r="H135"/>
-      <c r="I135"/>
-      <c r="J135"/>
-      <c r="K135"/>
-      <c r="L135"/>
+      <c r="C135" s="106"/>
+      <c r="D135" s="106"/>
+      <c r="E135" s="106"/>
+      <c r="F135" s="106"/>
+      <c r="G135" s="106"/>
+      <c r="H135" s="106"/>
+      <c r="I135" s="106"/>
+      <c r="J135" s="106"/>
+      <c r="K135" s="106"/>
+      <c r="L135" s="106"/>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136"/>
       <c r="B136"/>
-      <c r="C136"/>
-      <c r="D136"/>
-      <c r="E136"/>
-      <c r="F136"/>
-      <c r="G136"/>
-      <c r="H136"/>
-      <c r="I136"/>
-      <c r="J136"/>
-      <c r="K136"/>
-      <c r="L136"/>
+      <c r="C136" s="106"/>
+      <c r="D136" s="106"/>
+      <c r="E136" s="106"/>
+      <c r="F136" s="106"/>
+      <c r="G136" s="106"/>
+      <c r="H136" s="106"/>
+      <c r="I136" s="106"/>
+      <c r="J136" s="106"/>
+      <c r="K136" s="106"/>
+      <c r="L136" s="106"/>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137"/>
       <c r="B137"/>
-      <c r="C137"/>
-      <c r="D137"/>
-      <c r="E137"/>
-      <c r="F137"/>
-      <c r="G137"/>
-      <c r="H137"/>
-      <c r="I137"/>
-      <c r="J137"/>
-      <c r="K137"/>
-      <c r="L137"/>
+      <c r="C137" s="106"/>
+      <c r="D137" s="106"/>
+      <c r="E137" s="106"/>
+      <c r="F137" s="106"/>
+      <c r="G137" s="106"/>
+      <c r="H137" s="106"/>
+      <c r="I137" s="106"/>
+      <c r="J137" s="106"/>
+      <c r="K137" s="106"/>
+      <c r="L137" s="106"/>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138"/>
       <c r="B138"/>
-      <c r="C138"/>
-      <c r="D138"/>
-      <c r="E138"/>
-      <c r="F138"/>
-      <c r="G138"/>
-      <c r="H138"/>
-      <c r="I138"/>
-      <c r="J138"/>
-      <c r="K138"/>
-      <c r="L138"/>
+      <c r="C138" s="106"/>
+      <c r="D138" s="106"/>
+      <c r="E138" s="106"/>
+      <c r="F138" s="106"/>
+      <c r="G138" s="106"/>
+      <c r="H138" s="106"/>
+      <c r="I138" s="106"/>
+      <c r="J138" s="106"/>
+      <c r="K138" s="106"/>
+      <c r="L138" s="106"/>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139"/>
       <c r="B139"/>
-      <c r="C139"/>
-      <c r="D139"/>
-      <c r="E139"/>
-      <c r="F139"/>
-      <c r="G139"/>
-      <c r="H139"/>
-      <c r="I139"/>
-      <c r="J139"/>
-      <c r="K139"/>
-      <c r="L139"/>
+      <c r="C139" s="106"/>
+      <c r="D139" s="106"/>
+      <c r="E139" s="106"/>
+      <c r="F139" s="106"/>
+      <c r="G139" s="106"/>
+      <c r="H139" s="106"/>
+      <c r="I139" s="106"/>
+      <c r="J139" s="106"/>
+      <c r="K139" s="106"/>
+      <c r="L139" s="106"/>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140"/>
       <c r="B140"/>
-      <c r="C140"/>
-      <c r="D140"/>
-      <c r="E140"/>
-      <c r="F140"/>
-      <c r="G140"/>
-      <c r="H140"/>
-      <c r="I140"/>
-      <c r="J140"/>
-      <c r="K140"/>
-      <c r="L140"/>
-    </row>
-    <row r="141">
+      <c r="C140" s="106"/>
+      <c r="D140" s="106"/>
+      <c r="E140" s="106"/>
+      <c r="F140" s="106"/>
+      <c r="G140" s="106"/>
+      <c r="H140" s="106"/>
+      <c r="I140" s="106"/>
+      <c r="J140" s="106"/>
+      <c r="K140" s="106"/>
+      <c r="L140" s="106"/>
+    </row>
+    <row r="141" ht="20" customHeight="1">
       <c r="A141"/>
       <c r="B141"/>
-      <c r="C141"/>
-      <c r="D141"/>
-      <c r="E141"/>
-      <c r="F141"/>
-      <c r="G141"/>
-      <c r="H141"/>
-      <c r="I141"/>
-      <c r="J141"/>
-      <c r="K141"/>
-      <c r="L141"/>
-    </row>
-    <row r="142">
+      <c r="C141" s="106"/>
+      <c r="D141" s="106"/>
+      <c r="E141" s="106"/>
+      <c r="F141" s="106"/>
+      <c r="G141" s="106"/>
+      <c r="H141" s="106"/>
+      <c r="I141" s="106"/>
+      <c r="J141" s="106"/>
+      <c r="K141" s="106"/>
+      <c r="L141" s="106"/>
+    </row>
+    <row r="142" ht="20" customHeight="1">
       <c r="A142"/>
       <c r="B142"/>
-      <c r="C142"/>
-      <c r="D142"/>
-      <c r="E142"/>
-      <c r="F142"/>
-      <c r="G142"/>
-      <c r="H142"/>
-      <c r="I142"/>
-      <c r="J142"/>
-      <c r="K142"/>
-      <c r="L142"/>
-    </row>
-    <row r="143">
+      <c r="C142" s="106"/>
+      <c r="D142" s="106"/>
+      <c r="E142" s="106"/>
+      <c r="F142" s="106"/>
+      <c r="G142" s="106"/>
+      <c r="H142" s="106"/>
+      <c r="I142" s="106"/>
+      <c r="J142" s="106"/>
+      <c r="K142" s="106"/>
+      <c r="L142" s="106"/>
+    </row>
+    <row r="143" ht="20" customHeight="1">
       <c r="A143"/>
       <c r="B143"/>
-      <c r="C143"/>
-      <c r="D143"/>
-      <c r="E143"/>
-      <c r="F143"/>
-      <c r="G143"/>
-      <c r="H143"/>
-      <c r="I143"/>
-      <c r="J143"/>
-      <c r="K143"/>
-      <c r="L143"/>
-    </row>
-    <row r="144">
+      <c r="C143" s="106"/>
+      <c r="D143" s="106"/>
+      <c r="E143" s="106"/>
+      <c r="F143" s="106"/>
+      <c r="G143" s="106"/>
+      <c r="H143" s="106"/>
+      <c r="I143" s="106"/>
+      <c r="J143" s="106"/>
+      <c r="K143" s="106"/>
+      <c r="L143" s="106"/>
+    </row>
+    <row r="144" ht="20" customHeight="1">
       <c r="A144"/>
       <c r="B144"/>
-      <c r="C144"/>
-      <c r="D144"/>
-      <c r="E144"/>
-      <c r="F144"/>
-      <c r="G144"/>
-      <c r="H144"/>
-      <c r="I144"/>
-      <c r="J144"/>
-      <c r="K144"/>
-      <c r="L144"/>
-    </row>
-    <row r="145">
+      <c r="C144" s="106"/>
+      <c r="D144" s="106"/>
+      <c r="E144" s="106"/>
+      <c r="F144" s="106"/>
+      <c r="G144" s="106"/>
+      <c r="H144" s="106"/>
+      <c r="I144" s="106"/>
+      <c r="J144" s="106"/>
+      <c r="K144" s="106"/>
+      <c r="L144" s="106"/>
+    </row>
+    <row r="145" ht="20" customHeight="1">
       <c r="A145"/>
       <c r="B145"/>
-      <c r="C145"/>
-      <c r="D145"/>
-      <c r="E145"/>
-      <c r="F145"/>
-      <c r="G145"/>
-      <c r="H145"/>
-      <c r="I145"/>
-      <c r="J145"/>
-      <c r="K145"/>
-      <c r="L145"/>
-    </row>
-    <row r="146">
+      <c r="C145" s="106"/>
+      <c r="D145" s="106"/>
+      <c r="E145" s="106"/>
+      <c r="F145" s="106"/>
+      <c r="G145" s="106"/>
+      <c r="H145" s="106"/>
+      <c r="I145" s="106"/>
+      <c r="J145" s="106"/>
+      <c r="K145" s="106"/>
+      <c r="L145" s="106"/>
+    </row>
+    <row r="146" ht="20" customHeight="1">
       <c r="A146"/>
       <c r="B146"/>
-      <c r="C146"/>
-      <c r="D146"/>
-      <c r="E146"/>
-      <c r="F146"/>
-      <c r="G146"/>
-      <c r="H146"/>
-      <c r="I146"/>
-      <c r="J146"/>
-      <c r="K146"/>
-      <c r="L146"/>
-    </row>
-    <row r="147">
+      <c r="C146" s="106"/>
+      <c r="D146" s="106"/>
+      <c r="E146" s="106"/>
+      <c r="F146" s="106"/>
+      <c r="G146" s="106"/>
+      <c r="H146" s="106"/>
+      <c r="I146" s="106"/>
+      <c r="J146" s="106"/>
+      <c r="K146" s="106"/>
+      <c r="L146" s="106"/>
+    </row>
+    <row r="147" ht="20" customHeight="1">
       <c r="A147"/>
       <c r="B147"/>
-      <c r="C147"/>
-      <c r="D147"/>
-      <c r="E147"/>
-      <c r="F147"/>
-      <c r="G147"/>
-      <c r="H147"/>
-      <c r="I147"/>
-      <c r="J147"/>
-      <c r="K147"/>
-      <c r="L147"/>
-    </row>
-    <row r="148">
+      <c r="C147" s="106"/>
+      <c r="D147" s="106"/>
+      <c r="E147" s="106"/>
+      <c r="F147" s="106"/>
+      <c r="G147" s="106"/>
+      <c r="H147" s="106"/>
+      <c r="I147" s="106"/>
+      <c r="J147" s="106"/>
+      <c r="K147" s="106"/>
+      <c r="L147" s="106"/>
+    </row>
+    <row r="148" ht="20" customHeight="1">
       <c r="A148"/>
       <c r="B148"/>
-      <c r="C148"/>
-      <c r="D148"/>
-      <c r="E148"/>
-      <c r="F148"/>
-      <c r="G148"/>
-      <c r="H148"/>
-      <c r="I148"/>
-      <c r="J148"/>
-      <c r="K148"/>
-      <c r="L148"/>
-    </row>
-    <row r="149">
+      <c r="C148" s="106"/>
+      <c r="D148" s="106"/>
+      <c r="E148" s="106"/>
+      <c r="F148" s="106"/>
+      <c r="G148" s="106"/>
+      <c r="H148" s="106"/>
+      <c r="I148" s="106"/>
+      <c r="J148" s="106"/>
+      <c r="K148" s="106"/>
+      <c r="L148" s="106"/>
+    </row>
+    <row r="149" ht="20" customHeight="1">
       <c r="A149"/>
       <c r="B149"/>
-      <c r="C149"/>
-      <c r="D149"/>
-      <c r="E149"/>
-      <c r="F149"/>
-      <c r="G149"/>
-      <c r="H149"/>
-      <c r="I149"/>
-      <c r="J149"/>
-      <c r="K149"/>
-      <c r="L149"/>
-    </row>
-    <row r="150">
+      <c r="C149" s="106"/>
+      <c r="D149" s="106"/>
+      <c r="E149" s="106"/>
+      <c r="F149" s="106"/>
+      <c r="G149" s="106"/>
+      <c r="H149" s="106"/>
+      <c r="I149" s="106"/>
+      <c r="J149" s="106"/>
+      <c r="K149" s="106"/>
+      <c r="L149" s="106"/>
+    </row>
+    <row r="150" ht="20" customHeight="1">
       <c r="A150"/>
       <c r="B150"/>
-      <c r="C150"/>
-      <c r="D150"/>
-      <c r="E150"/>
-      <c r="F150"/>
-      <c r="G150"/>
-      <c r="H150"/>
-      <c r="I150"/>
-      <c r="J150"/>
-      <c r="K150"/>
-      <c r="L150"/>
+      <c r="C150" s="106"/>
+      <c r="D150" s="106"/>
+      <c r="E150" s="106"/>
+      <c r="F150" s="106"/>
+      <c r="G150" s="106"/>
+      <c r="H150" s="106"/>
+      <c r="I150" s="106"/>
+      <c r="J150" s="106"/>
+      <c r="K150" s="106"/>
+      <c r="L150" s="106"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R595ba0064e4749df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R1fa0ef5cf6d64459"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R74814a66d1064eec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rb96d4fcf946144c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -163,7 +163,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="150">
+  <x:cellXfs count="151">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -605,12 +605,15 @@
     </x:xf>
     <x:xf numFmtId="207" fontId="11" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="23">
+  <x:dxfs count="27">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -743,6 +746,50 @@
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
@@ -1283,7 +1330,7 @@
         <v>建议 Quote 资金</v>
       </c>
       <c r="D18" s="121" t="n">
-        <f>IF(ISNUMBER($D$26),(IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
+        <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
         <v>15773.425525779472</v>
       </c>
       <c r="E18" s="62" t="str">
@@ -1294,7 +1341,7 @@
         <v>原生币 Gas 储备</v>
       </c>
       <c r="G18" s="74" t="n">
-        <f>$D$32*MAX(0,$G$11)</f>
+        <f>$D$53*MAX(0,$G$11)</f>
         <v>0.61</v>
       </c>
       <c r="H18" s="62" t="str">
@@ -1318,7 +1365,7 @@
         <v>Quote 折算 / USDT</v>
       </c>
       <c r="D19" s="122" t="str">
-        <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$33&gt;0,$D$18*$D$33,"")),"")</f>
+        <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$55&gt;0,$D$18*$D$55,"")),"")</f>
       </c>
       <c r="E19" s="106" t="str">
         <v>USDT</v>
@@ -1337,7 +1384,7 @@
         <v>原生币价格 / USDT</v>
       </c>
       <c r="J19" s="123" t="n">
-        <f>IF($D$7="ETH",$D$33,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+        <f>IF($D$7="ETH",$D$55,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
         <v>2481.7308596853964</v>
       </c>
       <c r="K19" s="106"/>
@@ -1379,11 +1426,11 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="106" t="str">
-        <f>"预算 "&amp;TEXT($D$31,"0%")&amp;" 理论资金"</f>
+        <f>"预算 "&amp;TEXT($D$52,"0%")&amp;" 理论资金"</f>
         <v>预算 91% 理论资金</v>
       </c>
       <c r="D22" s="122" t="n">
-        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
         <v>5520.084846424523</v>
       </c>
       <c r="E22" s="106" t="str">
@@ -1407,7 +1454,7 @@
         <v>额外内盘资金</v>
       </c>
       <c r="D23" s="122" t="n">
-        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
         <v>174.54190618125045</v>
       </c>
       <c r="E23" s="106" t="str">
@@ -1434,7 +1481,7 @@
         <v>洗筹损耗</v>
       </c>
       <c r="D24" s="122" t="n">
-        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
         <v>10073.7987731737</v>
       </c>
       <c r="E24" s="106" t="str">
@@ -1488,7 +1535,7 @@
         <v>恢复目标控筹资金</v>
       </c>
       <c r="D26" s="122" t="n">
-        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",0)</f>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",0)</f>
         <v>0</v>
       </c>
       <c r="E26" s="106" t="str">
@@ -1575,17 +1622,12 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="107" t="str">
-        <v>目标是否可达</v>
-      </c>
-      <c r="D30" s="107" t="str">
-        <f>IF($J$51&lt;&gt;"参数有效",$J$51,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$53),"Creator Tax无效",IF($D$31&gt;=$G$32,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</f>
-        <v>可达</v>
-      </c>
-      <c r="E30" s="106"/>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="106"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
       <c r="I30" s="107" t="str">
         <v>卖出含税费率</v>
       </c>
@@ -1596,103 +1638,71 @@
       <c r="K30" s="106"/>
       <c r="L30" s="106"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
+    <row r="31" customHeight="1" hidden="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="107" t="str">
-        <v>预算使用控筹率</v>
-      </c>
-      <c r="D31" s="124" t="n">
-        <f>$D$8+1%</f>
-        <v>0.91</v>
-      </c>
-      <c r="E31" s="106"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="106"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
       <c r="I31" s="106"/>
       <c r="J31" s="106"/>
       <c r="K31" s="106"/>
       <c r="L31" s="106"/>
     </row>
-    <row r="32" ht="20" customHeight="1">
+    <row r="32" customHeight="1" hidden="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="107" t="str">
-        <v>地址总数</v>
-      </c>
-      <c r="D32" s="122" t="n">
-        <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
-        <v>122</v>
-      </c>
-      <c r="E32" s="106"/>
-      <c r="F32" s="107" t="str">
-        <v>当前控筹上限</v>
-      </c>
-      <c r="G32" s="124" t="n">
-        <f>MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$7)*$G$48/$D$45)</f>
-        <v>0.916326530612245</v>
-      </c>
-      <c r="H32" s="106"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
       <c r="I32" s="106"/>
       <c r="J32" s="106"/>
       <c r="K32" s="106"/>
       <c r="L32" s="106"/>
     </row>
-    <row r="33" ht="20" customHeight="1">
+    <row r="33" customHeight="1" hidden="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="107" t="str">
-        <v>Quote 价格 / USDT</v>
-      </c>
-      <c r="D33" s="123" t="str">
-        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
-      </c>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
       <c r="I33" s="106"/>
       <c r="J33" s="106"/>
       <c r="K33" s="106"/>
       <c r="L33" s="106"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" customHeight="1" hidden="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="107" t="str">
-        <v>行情时间 / UTC</v>
-      </c>
-      <c r="D34" s="126" t="n">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
-        <v>46283.229019363425</v>
-      </c>
-      <c r="E34" s="106"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="106"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
       <c r="I34" s="106"/>
       <c r="J34" s="106"/>
       <c r="K34" s="106"/>
       <c r="L34" s="106"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35" customHeight="1" hidden="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="107" t="str">
-        <v>价格采用方式</v>
-      </c>
-      <c r="D35" s="106" t="str">
-        <f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</f>
-        <v>每日行情</v>
-      </c>
-      <c r="E35" s="106"/>
-      <c r="F35" s="107" t="str">
-        <f>IF($D$9&lt;&gt;"",IF($D$33="","手动价格无效","手动价格"),IF($D$33="","缺少价格","每日行情"))</f>
-        <v>缺少价格</v>
-      </c>
-      <c r="G35" s="107"/>
-      <c r="H35" s="107"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
       <c r="I35" s="106"/>
       <c r="J35" s="106"/>
       <c r="K35" s="106"/>
@@ -1838,7 +1848,7 @@
         <v>目标+1% Pool TOKEN</v>
       </c>
       <c r="J42" s="108" t="n">
-        <f>IF($D$31&lt;$G$32,$D$45*(1-$D$31)-$G$51,"")</f>
+        <f>IF($D$52&lt;$D$54,$D$45*(1-$D$52)-$G$51,"")</f>
         <v>8367346.938775495</v>
       </c>
       <c r="K42" s="107"/>
@@ -1920,7 +1930,7 @@
         <v>外盘含费投入 / Quote</v>
       </c>
       <c r="J45" s="108" t="n">
-        <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$31-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$52-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
         <v>5345.542940243272</v>
       </c>
       <c r="K45" s="107"/>
@@ -2059,8 +2069,13 @@
     <row r="51" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A51"/>
       <c r="B51"/>
-      <c r="C51" s="107"/>
-      <c r="D51" s="108"/>
+      <c r="C51" s="107" t="str">
+        <v>目标是否可达</v>
+      </c>
+      <c r="D51" s="108" t="str">
+        <f>IF($J$51&lt;&gt;"参数有效",$J$51,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$53),"Creator Tax无效",IF($D$52&gt;=$D$54,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</f>
+        <v>可达</v>
+      </c>
       <c r="E51" s="107"/>
       <c r="F51" s="107" t="str">
         <v>Locker TOKEN</v>
@@ -2083,8 +2098,13 @@
     <row r="52" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A52"/>
       <c r="B52"/>
-      <c r="C52" s="107"/>
-      <c r="D52" s="108"/>
+      <c r="C52" s="107" t="str">
+        <v>预算使用控筹率</v>
+      </c>
+      <c r="D52" s="113" t="n">
+        <f>$D$8+1%</f>
+        <v>0.91</v>
+      </c>
       <c r="E52" s="107"/>
       <c r="F52" s="107" t="str">
         <v>Snipe 窗口</v>
@@ -2101,8 +2121,13 @@
     <row r="53" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A53"/>
       <c r="B53"/>
-      <c r="C53" s="107"/>
-      <c r="D53" s="108"/>
+      <c r="C53" s="107" t="str">
+        <v>地址总数</v>
+      </c>
+      <c r="D53" s="111" t="n">
+        <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
+        <v>122</v>
+      </c>
       <c r="E53" s="107"/>
       <c r="F53" s="107" t="str">
         <v>Creator Tax 上限</v>
@@ -2120,11 +2145,21 @@
     <row r="54" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A54"/>
       <c r="B54"/>
-      <c r="C54" s="107"/>
-      <c r="D54" s="108"/>
+      <c r="C54" s="107" t="str">
+        <v>当前控筹上限</v>
+      </c>
+      <c r="D54" s="113" t="n">
+        <f>MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$7)*$G$48/$D$45)</f>
+        <v>0.916326530612245</v>
+      </c>
       <c r="E54" s="107"/>
-      <c r="F54" s="107"/>
-      <c r="G54" s="108"/>
+      <c r="F54" s="107" t="str">
+        <v>价格采用方式</v>
+      </c>
+      <c r="G54" s="108" t="str">
+        <f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</f>
+        <v>每日行情</v>
+      </c>
       <c r="H54" s="107"/>
       <c r="I54" s="107" t="str">
         <v>洗后持仓保留比例</v>
@@ -2139,11 +2174,20 @@
     <row r="55" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A55"/>
       <c r="B55"/>
-      <c r="C55" s="107"/>
-      <c r="D55" s="108"/>
+      <c r="C55" s="107" t="str">
+        <v>Quote 价格 / USDT</v>
+      </c>
+      <c r="D55" s="108" t="str">
+        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+      </c>
       <c r="E55" s="107"/>
-      <c r="F55" s="107"/>
-      <c r="G55" s="108"/>
+      <c r="F55" s="107" t="str">
+        <v>价格状态</v>
+      </c>
+      <c r="G55" s="108" t="str">
+        <f>IF($D$9&lt;&gt;"",IF($D$55="","手动价格无效","手动价格"),IF($D$55="","缺少价格","每日行情"))</f>
+        <v>缺少价格</v>
+      </c>
       <c r="H55" s="107"/>
       <c r="I55" s="107" t="str">
         <v>目标外盘 Pool TOKEN</v>
@@ -2155,8 +2199,13 @@
     <row r="56" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A56"/>
       <c r="B56"/>
-      <c r="C56" s="107"/>
-      <c r="D56" s="108"/>
+      <c r="C56" s="107" t="str">
+        <v>行情时间 / UTC</v>
+      </c>
+      <c r="D56" s="150" t="n">
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
+        <v>46283.229019363425</v>
+      </c>
       <c r="E56" s="107"/>
       <c r="F56" s="107"/>
       <c r="G56" s="108"/>
@@ -2240,14 +2289,14 @@
         <v>6.911859484777517e-8</v>
       </c>
       <c r="G59" s="135" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F59))),"",F59*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F59))),"",F59*$D$55)</f>
       </c>
       <c r="H59" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F59)),"",F59*$D$45)</f>
         <v>69.11859484777517</v>
       </c>
       <c r="I59" s="144" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H59))),"",H59*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H59))),"",H59*$D$55)</f>
       </c>
       <c r="J59" s="144" t="n">
         <f>0</f>
@@ -2281,14 +2330,14 @@
         <v>8.533159857750022e-8</v>
       </c>
       <c r="G60" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F60))),"",F60*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F60))),"",F60*$D$55)</f>
       </c>
       <c r="H60" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F60)),"",F60*$D$45)</f>
         <v>85.33159857750022</v>
       </c>
       <c r="I60" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H60))),"",H60*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H60))),"",H60*$D$55)</f>
       </c>
       <c r="J60" s="145" t="n">
         <f>E60-E59</f>
@@ -2322,14 +2371,14 @@
         <v>1.0799780444964873e-7</v>
       </c>
       <c r="G61" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F61))),"",F61*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F61))),"",F61*$D$55)</f>
       </c>
       <c r="H61" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F61)),"",F61*$D$45)</f>
         <v>107.99780444964873</v>
       </c>
       <c r="I61" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H61))),"",H61*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H61))),"",H61*$D$55)</f>
       </c>
       <c r="J61" s="145" t="n">
         <f>E61-E60</f>
@@ -2363,14 +2412,14 @@
         <v>1.4105835683219424e-7</v>
       </c>
       <c r="G62" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F62))),"",F62*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F62))),"",F62*$D$55)</f>
       </c>
       <c r="H62" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$45)</f>
         <v>141.05835683219425</v>
       </c>
       <c r="I62" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H62))),"",H62*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H62))),"",H62*$D$55)</f>
       </c>
       <c r="J62" s="145" t="n">
         <f>E62-E61</f>
@@ -2404,14 +2453,14 @@
         <v>1.919960967993755e-7</v>
       </c>
       <c r="G63" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F63))),"",F63*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F63))),"",F63*$D$55)</f>
       </c>
       <c r="H63" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$45)</f>
         <v>191.99609679937552</v>
       </c>
       <c r="I63" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H63))),"",H63*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H63))),"",H63*$D$55)</f>
       </c>
       <c r="J63" s="145" t="n">
         <f>E63-E62</f>
@@ -2445,14 +2494,14 @@
         <v>2.7647437939110067e-7</v>
       </c>
       <c r="G64" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F64))),"",F64*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F64))),"",F64*$D$55)</f>
       </c>
       <c r="H64" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$45)</f>
         <v>276.4743793911007</v>
       </c>
       <c r="I64" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H64))),"",H64*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H64))),"",H64*$D$55)</f>
       </c>
       <c r="J64" s="145" t="n">
         <f>E64-E63</f>
@@ -2486,14 +2535,14 @@
         <v>4.319912177985949e-7</v>
       </c>
       <c r="G65" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F65))),"",F65*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F65))),"",F65*$D$55)</f>
       </c>
       <c r="H65" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$45)</f>
         <v>431.9912177985949</v>
       </c>
       <c r="I65" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H65))),"",H65*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H65))),"",H65*$D$55)</f>
       </c>
       <c r="J65" s="145" t="n">
         <f>E65-E64</f>
@@ -2527,14 +2576,14 @@
         <v>7.679843871975016e-7</v>
       </c>
       <c r="G66" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F66))),"",F66*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F66))),"",F66*$D$55)</f>
       </c>
       <c r="H66" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$45)</f>
         <v>767.9843871975016</v>
       </c>
       <c r="I66" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H66))),"",H66*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H66))),"",H66*$D$55)</f>
       </c>
       <c r="J66" s="145" t="n">
         <f>E66-E65</f>
@@ -2569,14 +2618,14 @@
         <v>8.467027868852461e-7</v>
       </c>
       <c r="G67" s="137" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F67))),"",F67*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F67))),"",F67*$D$55)</f>
       </c>
       <c r="H67" s="146" t="n">
         <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$45)</f>
         <v>846.7027868852462</v>
       </c>
       <c r="I67" s="146" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H67))),"",H67*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H67))),"",H67*$D$55)</f>
       </c>
       <c r="J67" s="146" t="n">
         <f>E67-E66</f>
@@ -2692,14 +2741,14 @@
         <v>8.467027868852459e-7</v>
       </c>
       <c r="G72" s="135" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F72))),"",F72*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F72))),"",F72*$D$55)</f>
       </c>
       <c r="H72" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$45)</f>
         <v>846.7027868852459</v>
       </c>
       <c r="I72" s="144" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H72))),"",H72*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H72))),"",H72*$D$55)</f>
       </c>
       <c r="J72" s="144" t="n">
         <f>0</f>
@@ -2721,7 +2770,7 @@
         <v>0.75</v>
       </c>
       <c r="D73" s="145" t="n">
-        <f>IF(C73&lt;$G$32,$D$45*(1-C73)-$G$51,"")</f>
+        <f>IF(C73&lt;$D$54,$D$45*(1-C73)-$G$51,"")</f>
         <v>168367346.93877554</v>
       </c>
       <c r="E73" s="145" t="n">
@@ -2733,14 +2782,14 @@
         <v>0.0000012440077676918213</v>
       </c>
       <c r="G73" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F73))),"",F73*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F73))),"",F73*$D$55)</f>
       </c>
       <c r="H73" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$45)</f>
         <v>1244.0077676918213</v>
       </c>
       <c r="I73" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H73))),"",H73*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H73))),"",H73*$D$55)</f>
       </c>
       <c r="J73" s="145" t="n">
         <f>IF(E73="","",MAX(0,E73-$G$44))</f>
@@ -2762,7 +2811,7 @@
         <v>0.8</v>
       </c>
       <c r="D74" s="145" t="n">
-        <f>IF(C74&lt;$G$32,$D$45*(1-C74)-$G$51,"")</f>
+        <f>IF(C74&lt;$D$54,$D$45*(1-C74)-$G$51,"")</f>
         <v>118367346.9387755</v>
       </c>
       <c r="E74" s="145" t="n">
@@ -2774,14 +2823,14 @@
         <v>0.0000025169523985887227</v>
       </c>
       <c r="G74" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F74))),"",F74*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F74))),"",F74*$D$55)</f>
       </c>
       <c r="H74" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$45)</f>
         <v>2516.9523985887226</v>
       </c>
       <c r="I74" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H74))),"",H74*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H74))),"",H74*$D$55)</f>
       </c>
       <c r="J74" s="145" t="n">
         <f>IF(E74="","",MAX(0,E74-$G$44))</f>
@@ -2803,7 +2852,7 @@
         <v>0.82</v>
       </c>
       <c r="D75" s="145" t="n">
-        <f>IF(C75&lt;$G$32,$D$45*(1-C75)-$G$51,"")</f>
+        <f>IF(C75&lt;$D$54,$D$45*(1-C75)-$G$51,"")</f>
         <v>98367346.93877558</v>
       </c>
       <c r="E75" s="145" t="n">
@@ -2815,14 +2864,14 @@
         <v>0.000003644491257404508</v>
       </c>
       <c r="G75" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F75))),"",F75*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F75))),"",F75*$D$55)</f>
       </c>
       <c r="H75" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$45)</f>
         <v>3644.4912574045084</v>
       </c>
       <c r="I75" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H75))),"",H75*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H75))),"",H75*$D$55)</f>
       </c>
       <c r="J75" s="145" t="n">
         <f>IF(E75="","",MAX(0,E75-$G$44))</f>
@@ -2844,7 +2893,7 @@
         <v>0.84</v>
       </c>
       <c r="D76" s="145" t="n">
-        <f>IF(C76&lt;$G$32,$D$45*(1-C76)-$G$51,"")</f>
+        <f>IF(C76&lt;$D$54,$D$45*(1-C76)-$G$51,"")</f>
         <v>78367346.93877555</v>
       </c>
       <c r="E76" s="145" t="n">
@@ -2856,14 +2905,14 @@
         <v>0.000005742070766094599</v>
       </c>
       <c r="G76" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F76))),"",F76*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F76))),"",F76*$D$55)</f>
       </c>
       <c r="H76" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F76)),"",F76*$D$45)</f>
         <v>5742.070766094599</v>
       </c>
       <c r="I76" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H76))),"",H76*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H76))),"",H76*$D$55)</f>
       </c>
       <c r="J76" s="145" t="n">
         <f>IF(E76="","",MAX(0,E76-$G$44))</f>
@@ -2885,7 +2934,7 @@
         <v>0.86</v>
       </c>
       <c r="D77" s="145" t="n">
-        <f>IF(C77&lt;$G$32,$D$45*(1-C77)-$G$51,"")</f>
+        <f>IF(C77&lt;$D$54,$D$45*(1-C77)-$G$51,"")</f>
         <v>58367346.938775524</v>
       </c>
       <c r="E77" s="145" t="n">
@@ -2897,14 +2946,14 @@
         <v>0.00001035139599595635</v>
       </c>
       <c r="G77" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F77))),"",F77*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F77))),"",F77*$D$55)</f>
       </c>
       <c r="H77" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F77)),"",F77*$D$45)</f>
         <v>10351.39599595635</v>
       </c>
       <c r="I77" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H77))),"",H77*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H77))),"",H77*$D$55)</f>
       </c>
       <c r="J77" s="145" t="n">
         <f>IF(E77="","",MAX(0,E77-$G$44))</f>
@@ -2926,7 +2975,7 @@
         <v>0.88</v>
       </c>
       <c r="D78" s="145" t="n">
-        <f>IF(C78&lt;$G$32,$D$45*(1-C78)-$G$51,"")</f>
+        <f>IF(C78&lt;$D$54,$D$45*(1-C78)-$G$51,"")</f>
         <v>38367346.938775524</v>
       </c>
       <c r="E78" s="145" t="n">
@@ -2938,14 +2987,14 @@
         <v>0.000023956054404856426</v>
       </c>
       <c r="G78" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F78))),"",F78*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F78))),"",F78*$D$55)</f>
       </c>
       <c r="H78" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F78)),"",F78*$D$45)</f>
         <v>23956.054404856426</v>
       </c>
       <c r="I78" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H78))),"",H78*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H78))),"",H78*$D$55)</f>
       </c>
       <c r="J78" s="145" t="n">
         <f>IF(E78="","",MAX(0,E78-$G$44))</f>
@@ -2967,7 +3016,7 @@
         <v>0.89</v>
       </c>
       <c r="D79" s="145" t="n">
-        <f>IF(C79&lt;$G$32,$D$45*(1-C79)-$G$51,"")</f>
+        <f>IF(C79&lt;$D$54,$D$45*(1-C79)-$G$51,"")</f>
         <v>28367346.93877551</v>
       </c>
       <c r="E79" s="145" t="n">
@@ -2979,14 +3028,14 @@
         <v>0.00004382292774107169</v>
       </c>
       <c r="G79" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F79))),"",F79*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F79))),"",F79*$D$55)</f>
       </c>
       <c r="H79" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F79)),"",F79*$D$45)</f>
         <v>43822.92774107169</v>
       </c>
       <c r="I79" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H79))),"",H79*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H79))),"",H79*$D$55)</f>
       </c>
       <c r="J79" s="145" t="n">
         <f>IF(E79="","",MAX(0,E79-$G$44))</f>
@@ -3008,7 +3057,7 @@
         <v>0.9</v>
       </c>
       <c r="D80" s="145" t="n">
-        <f>IF(C80&lt;$G$32,$D$45*(1-C80)-$G$51,"")</f>
+        <f>IF(C80&lt;$D$54,$D$45*(1-C80)-$G$51,"")</f>
         <v>18367346.93877551</v>
       </c>
       <c r="E80" s="145" t="n">
@@ -3020,14 +3069,14 @@
         <v>0.0001045312082574378</v>
       </c>
       <c r="G80" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F80))),"",F80*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F80))),"",F80*$D$55)</f>
       </c>
       <c r="H80" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$45)</f>
         <v>104531.2082574378</v>
       </c>
       <c r="I80" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H80))),"",H80*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H80))),"",H80*$D$55)</f>
       </c>
       <c r="J80" s="145" t="n">
         <f>IF(E80="","",MAX(0,E80-$G$44))</f>
@@ -3049,7 +3098,7 @@
         <v>0.905</v>
       </c>
       <c r="D81" s="145" t="n">
-        <f>IF(C81&lt;$G$32,$D$45*(1-C81)-$G$51,"")</f>
+        <f>IF(C81&lt;$D$54,$D$45*(1-C81)-$G$51,"")</f>
         <v>13367346.938775495</v>
       </c>
       <c r="E81" s="145" t="n">
@@ -3061,14 +3110,14 @@
         <v>0.00019735511610867622</v>
       </c>
       <c r="G81" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F81))),"",F81*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F81))),"",F81*$D$55)</f>
       </c>
       <c r="H81" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$45)</f>
         <v>197355.11610867621</v>
       </c>
       <c r="I81" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H81))),"",H81*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H81))),"",H81*$D$55)</f>
       </c>
       <c r="J81" s="145" t="n">
         <f>IF(E81="","",MAX(0,E81-$G$44))</f>
@@ -3090,7 +3139,7 @@
         <v>0.91</v>
       </c>
       <c r="D82" s="145" t="n">
-        <f>IF(C82&lt;$G$32,$D$45*(1-C82)-$G$51,"")</f>
+        <f>IF(C82&lt;$D$54,$D$45*(1-C82)-$G$51,"")</f>
         <v>8367346.938775495</v>
       </c>
       <c r="E82" s="145" t="n">
@@ -3102,14 +3151,14 @@
         <v>0.0005036899386586849</v>
       </c>
       <c r="G82" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F82))),"",F82*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F82))),"",F82*$D$55)</f>
       </c>
       <c r="H82" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$45)</f>
         <v>503689.93865868496</v>
       </c>
       <c r="I82" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H82))),"",H82*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H82))),"",H82*$D$55)</f>
       </c>
       <c r="J82" s="145" t="n">
         <f>IF(E82="","",MAX(0,E82-$G$44))</f>
@@ -3131,7 +3180,7 @@
         <v>0.915</v>
       </c>
       <c r="D83" s="145" t="n">
-        <f>IF(C83&lt;$G$32,$D$45*(1-C83)-$G$51,"")</f>
+        <f>IF(C83&lt;$D$54,$D$45*(1-C83)-$G$51,"")</f>
         <v>3367346.9387754947</v>
       </c>
       <c r="E83" s="145" t="n">
@@ -3143,14 +3192,14 @@
         <v>0.0031100194192295832</v>
       </c>
       <c r="G83" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F83))),"",F83*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F83))),"",F83*$D$55)</f>
       </c>
       <c r="H83" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$45)</f>
         <v>3110019.4192295833</v>
       </c>
       <c r="I83" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H83))),"",H83*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H83))),"",H83*$D$55)</f>
       </c>
       <c r="J83" s="145" t="n">
         <f>IF(E83="","",MAX(0,E83-$G$44))</f>
@@ -3172,7 +3221,7 @@
         <v>0.918</v>
       </c>
       <c r="D84" s="145" t="str">
-        <f>IF(C84&lt;$G$32,$D$45*(1-C84)-$G$51,"")</f>
+        <f>IF(C84&lt;$D$54,$D$45*(1-C84)-$G$51,"")</f>
       </c>
       <c r="E84" s="145" t="str">
         <f>IF(D84="","",$G$50/D84)</f>
@@ -3181,13 +3230,13 @@
         <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
       </c>
       <c r="G84" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F84))),"",F84*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F84))),"",F84*$D$55)</f>
       </c>
       <c r="H84" s="145" t="str">
         <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$45)</f>
       </c>
       <c r="I84" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H84))),"",H84*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H84))),"",H84*$D$55)</f>
       </c>
       <c r="J84" s="145" t="str">
         <f>IF(E84="","",MAX(0,E84-$G$44))</f>
@@ -3206,7 +3255,7 @@
         <v>0.9183673469387755</v>
       </c>
       <c r="D85" s="146" t="str">
-        <f>IF(C85&lt;$G$32,$D$45*(1-C85)-$G$51,"")</f>
+        <f>IF(C85&lt;$D$54,$D$45*(1-C85)-$G$51,"")</f>
       </c>
       <c r="E85" s="146" t="str">
         <f>IF(D85="","",$G$50/D85)</f>
@@ -3215,13 +3264,13 @@
         <f>IF(OR(D85="",E85=""),"",E85/D85)</f>
       </c>
       <c r="G85" s="137" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F85))),"",F85*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F85))),"",F85*$D$55)</f>
       </c>
       <c r="H85" s="146" t="str">
         <f>IF(NOT(ISNUMBER(F85)),"",F85*$D$45)</f>
       </c>
       <c r="I85" s="146" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H85))),"",H85*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H85))),"",H85*$D$55)</f>
       </c>
       <c r="J85" s="146" t="str">
         <f>IF(E85="","",MAX(0,E85-$G$44))</f>
@@ -3326,14 +3375,14 @@
         <v>8.467027868852462e-7</v>
       </c>
       <c r="G90" s="135" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F90))),"",F90*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F90))),"",F90*$D$55)</f>
       </c>
       <c r="H90" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F90)),"",F90*$D$45)</f>
         <v>846.7027868852463</v>
       </c>
       <c r="I90" s="144" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H90))),"",H90*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H90))),"",H90*$D$55)</f>
       </c>
       <c r="J90" s="132" t="n">
         <f>IF($H$90&gt;0,1-H90/$H$90,0)</f>
@@ -3361,14 +3410,14 @@
         <v>7.395430054024329e-7</v>
       </c>
       <c r="G91" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F91))),"",F91*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F91))),"",F91*$D$55)</f>
       </c>
       <c r="H91" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F91)),"",F91*$D$45)</f>
         <v>739.5430054024329</v>
       </c>
       <c r="I91" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H91))),"",H91*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H91))),"",H91*$D$55)</f>
       </c>
       <c r="J91" s="133" t="n">
         <f>IF($H$90&gt;0,1-H91/$H$90,0)</f>
@@ -3396,14 +3445,14 @@
         <v>3.479219209751997e-7</v>
       </c>
       <c r="G92" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F92))),"",F92*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F92))),"",F92*$D$55)</f>
       </c>
       <c r="H92" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F92)),"",F92*$D$45)</f>
         <v>347.9219209751997</v>
       </c>
       <c r="I92" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H92))),"",H92*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H92))),"",H92*$D$55)</f>
       </c>
       <c r="J92" s="133" t="n">
         <f>IF($H$90&gt;0,1-H92/$H$90,0)</f>
@@ -3431,14 +3480,14 @@
         <v>2.0147597546347317e-7</v>
       </c>
       <c r="G93" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F93))),"",F93*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F93))),"",F93*$D$55)</f>
       </c>
       <c r="H93" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F93)),"",F93*$D$45)</f>
         <v>201.47597546347316</v>
       </c>
       <c r="I93" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H93))),"",H93*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H93))),"",H93*$D$55)</f>
       </c>
       <c r="J93" s="133" t="n">
         <f>IF($H$90&gt;0,1-H93/$H$90,0)</f>
@@ -3466,14 +3515,14 @@
         <v>1.3123919444560203e-7</v>
       </c>
       <c r="G94" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F94))),"",F94*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F94))),"",F94*$D$55)</f>
       </c>
       <c r="H94" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F94)),"",F94*$D$45)</f>
         <v>131.23919444560204</v>
       </c>
       <c r="I94" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H94))),"",H94*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H94))),"",H94*$D$55)</f>
       </c>
       <c r="J94" s="133" t="n">
         <f>IF($H$90&gt;0,1-H94/$H$90,0)</f>
@@ -3501,14 +3550,14 @@
         <v>9.222437744504854e-8</v>
       </c>
       <c r="G95" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F95))),"",F95*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F95))),"",F95*$D$55)</f>
       </c>
       <c r="H95" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F95)),"",F95*$D$45)</f>
         <v>92.22437744504853</v>
       </c>
       <c r="I95" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H95))),"",H95*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H95))),"",H95*$D$55)</f>
       </c>
       <c r="J95" s="133" t="n">
         <f>IF($H$90&gt;0,1-H95/$H$90,0)</f>
@@ -3536,14 +3585,14 @@
         <v>6.833538762955562e-8</v>
       </c>
       <c r="G96" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F96))),"",F96*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F96))),"",F96*$D$55)</f>
       </c>
       <c r="H96" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F96)),"",F96*$D$45)</f>
         <v>68.33538762955563</v>
       </c>
       <c r="I96" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H96))),"",H96*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H96))),"",H96*$D$55)</f>
       </c>
       <c r="J96" s="133" t="n">
         <f>IF($H$90&gt;0,1-H96/$H$90,0)</f>
@@ -3571,14 +3620,14 @@
         <v>5.265531849212667e-8</v>
       </c>
       <c r="G97" s="136" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F97))),"",F97*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F97))),"",F97*$D$55)</f>
       </c>
       <c r="H97" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F97)),"",F97*$D$45)</f>
         <v>52.65531849212667</v>
       </c>
       <c r="I97" s="145" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H97))),"",H97*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H97))),"",H97*$D$55)</f>
       </c>
       <c r="J97" s="133" t="n">
         <f>IF($H$90&gt;0,1-H97/$H$90,0)</f>
@@ -3606,14 +3655,14 @@
         <v>4.181248330297511e-8</v>
       </c>
       <c r="G98" s="137" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F98))),"",F98*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F98))),"",F98*$D$55)</f>
       </c>
       <c r="H98" s="146" t="n">
         <f>IF(NOT(ISNUMBER(F98)),"",F98*$D$45)</f>
         <v>41.81248330297511</v>
       </c>
       <c r="I98" s="146" t="str">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H98))),"",H98*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H98))),"",H98*$D$55)</f>
       </c>
       <c r="J98" s="134" t="n">
         <f>IF($H$90&gt;0,1-H98/$H$90,0)</f>
@@ -4374,8 +4423,7 @@
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="I22:L22"/>
     <mergeCell ref="I27:L27"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D56:E56"/>
   </mergeCells>
   <conditionalFormatting sqref="D23:D23">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不可达"/>
@@ -4384,14 +4432,6 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="J24:J24">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="缺少"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D30:D30">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="不可达"/>
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="无效"/>
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="缺少"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F35:F35">
-    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="缺少"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:D18">
     <cfRule type="expression" dxfId="8" priority="9">
@@ -4467,6 +4507,14 @@
     <cfRule type="expression" dxfId="22" priority="23">
       <formula>$D$7="ETH"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D51:D51">
+    <cfRule type="containsText" dxfId="23" priority="24" operator="containsText" text="不可达"/>
+    <cfRule type="containsText" dxfId="24" priority="25" operator="containsText" text="无效"/>
+    <cfRule type="containsText" dxfId="25" priority="26" operator="containsText" text="缺少"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G55:G55">
+    <cfRule type="containsText" dxfId="26" priority="27" operator="containsText" text="缺少"/>
   </conditionalFormatting>
   <dataValidations count="13">
     <dataValidation type="list" sqref="D7">

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R74814a66d1064eec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rb96d4fcf946144c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R918d13da31044a3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rcab139deb5424cbf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -163,7 +163,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="151">
+  <x:cellXfs count="153">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -608,6 +608,12 @@
     </x:xf>
     <x:xf numFmtId="203" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1110,7 +1116,7 @@
         <v>Quote</v>
       </c>
       <c r="D7" s="51" t="str">
-        <v>SLV</v>
+        <v>ETH</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="35" t="str">
@@ -1145,7 +1151,7 @@
         <v>内盘地址 / 套</v>
       </c>
       <c r="G8" s="51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="35" t="str">
@@ -1173,7 +1179,7 @@
         <v>外盘地址数</v>
       </c>
       <c r="G9" s="51" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="35" t="str">
@@ -1195,7 +1201,7 @@
         <v>Holder 地址数</v>
       </c>
       <c r="G10" s="51" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="35" t="str">
@@ -1240,7 +1246,8 @@
       <c r="F12" s="35" t="str">
         <v>资金预留 / Quote</v>
       </c>
-      <c r="G12" s="54" t="n">
+      <c r="G12" s="152" t="n">
+        <f>IF(AND(ISNUMBER($D$55),$D$55&gt;0),ROUNDUP($G$56/$D$55,0),"")</f>
         <v>5</v>
       </c>
       <c r="H12" s="2"/>
@@ -1253,7 +1260,7 @@
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="55" t="str">
-        <v>手动价格只用于 USDT 换算，不改变 Quote 控筹预算。清空覆盖格后恢复自动取价。</v>
+        <v>预留资金 = 10,000 USDT ÷ Quote 价格，向上取整。手动价格会同时调整预留与折算价值；清空后恢复每日价。</v>
       </c>
       <c r="D13" s="55"/>
       <c r="E13" s="55"/>
@@ -1331,18 +1338,18 @@
       </c>
       <c r="D18" s="121" t="n">
         <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
-        <v>15773.425525779472</v>
+        <v>388.2681341634973</v>
       </c>
       <c r="E18" s="62" t="str">
         <f>$D$7</f>
-        <v>SLV</v>
+        <v>ETH</v>
       </c>
       <c r="F18" s="107" t="str">
         <v>原生币 Gas 储备</v>
       </c>
       <c r="G18" s="74" t="n">
         <f>$D$53*MAX(0,$G$11)</f>
-        <v>0.61</v>
+        <v>1.1</v>
       </c>
       <c r="H18" s="62" t="str">
         <v>ETH</v>
@@ -1350,8 +1357,9 @@
       <c r="I18" s="107" t="str">
         <v>总折算 / USDT</v>
       </c>
-      <c r="J18" s="121" t="str">
+      <c r="J18" s="121" t="n">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
+        <v>966306.9143316748</v>
       </c>
       <c r="K18" s="62" t="str">
         <v>USDT</v>
@@ -1364,8 +1372,9 @@
       <c r="C19" s="107" t="str">
         <v>Quote 折算 / USDT</v>
       </c>
-      <c r="D19" s="122" t="str">
+      <c r="D19" s="122" t="n">
         <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$55&gt;0,$D$18*$D$55,"")),"")</f>
+        <v>963577.0103860209</v>
       </c>
       <c r="E19" s="106" t="str">
         <v>USDT</v>
@@ -1375,7 +1384,7 @@
       </c>
       <c r="G19" s="122" t="n">
         <f>IF($G$18=0,0,IF($J$19="","",$G$18*$J$19))</f>
-        <v>1513.8558244080918</v>
+        <v>2729.9039456539363</v>
       </c>
       <c r="H19" s="106" t="str">
         <v>USDT</v>
@@ -1431,11 +1440,11 @@
       </c>
       <c r="D22" s="122" t="n">
         <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
-        <v>5520.084846424523</v>
+        <v>134.1714565004891</v>
       </c>
       <c r="E22" s="106" t="str">
         <f>$D$7</f>
-        <v>SLV</v>
+        <v>ETH</v>
       </c>
       <c r="F22" s="106"/>
       <c r="G22" s="106"/>
@@ -1455,11 +1464,11 @@
       </c>
       <c r="D23" s="122" t="n">
         <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
-        <v>174.54190618125045</v>
+        <v>4.242424242424242</v>
       </c>
       <c r="E23" s="106" t="str">
         <f>$D$7</f>
-        <v>SLV</v>
+        <v>ETH</v>
       </c>
       <c r="F23" s="106"/>
       <c r="G23" s="106"/>
@@ -1482,11 +1491,11 @@
       </c>
       <c r="D24" s="122" t="n">
         <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
-        <v>10073.7987731737</v>
+        <v>244.85425342058392</v>
       </c>
       <c r="E24" s="106" t="str">
         <f>$D$7</f>
-        <v>SLV</v>
+        <v>ETH</v>
       </c>
       <c r="F24" s="106"/>
       <c r="G24" s="106"/>
@@ -1513,7 +1522,7 @@
       </c>
       <c r="E25" s="106" t="str">
         <f>$D$7</f>
-        <v>SLV</v>
+        <v>ETH</v>
       </c>
       <c r="F25" s="106"/>
       <c r="G25" s="106"/>
@@ -1540,7 +1549,7 @@
       </c>
       <c r="E26" s="106" t="str">
         <f>$D$7</f>
-        <v>SLV</v>
+        <v>ETH</v>
       </c>
       <c r="F26" s="106"/>
       <c r="G26" s="106"/>
@@ -1735,11 +1744,11 @@
       <c r="F37" s="127"/>
       <c r="G37" s="128" t="n">
         <f>E98</f>
-        <v>38.399219359875104</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="H37" s="127" t="str">
         <f>$D$7</f>
-        <v>SLV</v>
+        <v>ETH</v>
       </c>
       <c r="I37" s="106"/>
       <c r="J37" s="106"/>
@@ -1804,7 +1813,7 @@
       </c>
       <c r="D41" s="108" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</f>
-        <v>iShares Silver Trust</v>
+        <v>Ether</v>
       </c>
       <c r="E41" s="107"/>
       <c r="F41" s="107" t="str">
@@ -1820,7 +1829,7 @@
       </c>
       <c r="J41" s="108" t="n">
         <f>IF(1-$G$41-$J$7&gt;0,$G$44/(1-$G$41-$J$7),"")</f>
-        <v>174.54190618125045</v>
+        <v>4.242424242424242</v>
       </c>
       <c r="K41" s="107"/>
       <c r="L41" s="107"/>
@@ -1833,7 +1842,7 @@
       </c>
       <c r="D42" s="109" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</f>
-        <v>​0x411efb0e7f985935daec3d4c3ebaea0d0ad7d89f</v>
+        <v>​Native ETH</v>
       </c>
       <c r="E42" s="107"/>
       <c r="F42" s="107" t="str">
@@ -1873,7 +1882,7 @@
       </c>
       <c r="J43" s="108" t="n">
         <f>IF($J$42="","",$G$50/$J$42)</f>
-        <v>4214.548466327764</v>
+        <v>102.4390243902441</v>
       </c>
       <c r="K43" s="107"/>
       <c r="L43" s="107"/>
@@ -1894,7 +1903,7 @@
       </c>
       <c r="G44" s="108" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</f>
-        <v>172.79648711943796</v>
+        <v>4.2</v>
       </c>
       <c r="H44" s="107"/>
       <c r="I44" s="107" t="str">
@@ -1902,7 +1911,7 @@
       </c>
       <c r="J44" s="108" t="n">
         <f>IF($J$43="","",MAX(0,$J$43-$G$44))</f>
-        <v>4041.751979208326</v>
+        <v>98.2390243902441</v>
       </c>
       <c r="K44" s="107"/>
       <c r="L44" s="107"/>
@@ -1931,7 +1940,7 @@
       </c>
       <c r="J45" s="108" t="n">
         <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$52-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>5345.542940243272</v>
+        <v>129.92903225806486</v>
       </c>
       <c r="K45" s="107"/>
       <c r="L45" s="107"/>
@@ -1942,9 +1951,9 @@
       <c r="C46" s="107" t="str">
         <v>协议参数证据</v>
       </c>
-      <c r="D46" s="108" t="n">
+      <c r="D46" s="108" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</f>
-        <v>54430299</v>
+        <v>TIME 实币验证</v>
       </c>
       <c r="E46" s="107"/>
       <c r="F46" s="107" t="str">
@@ -1952,7 +1961,7 @@
       </c>
       <c r="G46" s="108" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</f>
-        <v>69.11859484777517</v>
+        <v>1.68</v>
       </c>
       <c r="H46" s="107"/>
       <c r="I46" s="107" t="str">
@@ -1960,7 +1969,7 @@
       </c>
       <c r="J46" s="108" t="n">
         <f>IF($J$43="","",$J$43/$J$42*$D$45)</f>
-        <v>503689.93865868496</v>
+        <v>12242.712671029196</v>
       </c>
       <c r="K46" s="107"/>
       <c r="L46" s="107"/>
@@ -1980,7 +1989,7 @@
       </c>
       <c r="G47" s="114" t="n">
         <f>$G$46*$D$45</f>
-        <v>69118594847.77518</v>
+        <v>1680000000</v>
       </c>
       <c r="H47" s="107"/>
       <c r="I47" s="107" t="str">
@@ -2035,7 +2044,7 @@
       </c>
       <c r="G49" s="108" t="n">
         <f>$G$44</f>
-        <v>172.79648711943796</v>
+        <v>4.2</v>
       </c>
       <c r="H49" s="107"/>
       <c r="I49" s="107" t="str">
@@ -2058,7 +2067,7 @@
       </c>
       <c r="G50" s="114" t="n">
         <f>$G$48*$G$44</f>
-        <v>35264589208.04857</v>
+        <v>857142857.1428572</v>
       </c>
       <c r="H50" s="107"/>
       <c r="I50" s="107"/>
@@ -2126,7 +2135,7 @@
       </c>
       <c r="D53" s="111" t="n">
         <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
-        <v>122</v>
+        <v>220</v>
       </c>
       <c r="E53" s="107"/>
       <c r="F53" s="107" t="str">
@@ -2177,8 +2186,9 @@
       <c r="C55" s="107" t="str">
         <v>Quote 价格 / USDT</v>
       </c>
-      <c r="D55" s="108" t="str">
+      <c r="D55" s="108" t="n">
         <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+        <v>2481.7308596853964</v>
       </c>
       <c r="E55" s="107"/>
       <c r="F55" s="107" t="str">
@@ -2186,7 +2196,7 @@
       </c>
       <c r="G55" s="108" t="str">
         <f>IF($D$9&lt;&gt;"",IF($D$55="","手动价格无效","手动价格"),IF($D$55="","缺少价格","每日行情"))</f>
-        <v>缺少价格</v>
+        <v>每日行情</v>
       </c>
       <c r="H55" s="107"/>
       <c r="I55" s="107" t="str">
@@ -2204,11 +2214,15 @@
       </c>
       <c r="D56" s="150" t="n">
         <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
-        <v>46283.229019363425</v>
+        <v>46283.229076828706</v>
       </c>
       <c r="E56" s="107"/>
-      <c r="F56" s="107"/>
-      <c r="G56" s="108"/>
+      <c r="F56" s="107" t="str">
+        <v>预留预算 / USDT</v>
+      </c>
+      <c r="G56" s="111" t="n">
+        <v>10000</v>
+      </c>
       <c r="H56" s="107"/>
       <c r="I56" s="107" t="str">
         <v>洗后外盘 Pool TOKEN</v>
@@ -2282,21 +2296,23 @@
       </c>
       <c r="E59" s="144" t="n">
         <f>$G$47/D59</f>
-        <v>69.11859484777517</v>
+        <v>1.68</v>
       </c>
       <c r="F59" s="135" t="n">
         <f>IF(OR(D59="",E59=""),"",E59/D59)</f>
-        <v>6.911859484777517e-8</v>
-      </c>
-      <c r="G59" s="135" t="str">
+        <v>1.68e-9</v>
+      </c>
+      <c r="G59" s="135" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F59))),"",F59*$D$55)</f>
+        <v>0.000004169307844271466</v>
       </c>
       <c r="H59" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F59)),"",F59*$D$45)</f>
-        <v>69.11859484777517</v>
-      </c>
-      <c r="I59" s="144" t="str">
+        <v>1.68</v>
+      </c>
+      <c r="I59" s="144" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H59))),"",H59*$D$55)</f>
+        <v>4169.307844271466</v>
       </c>
       <c r="J59" s="144" t="n">
         <f>0</f>
@@ -2323,33 +2339,35 @@
       </c>
       <c r="E60" s="145" t="n">
         <f>$G$47/D60</f>
-        <v>76.7984387197502</v>
+        <v>1.8666666666666667</v>
       </c>
       <c r="F60" s="136" t="n">
         <f>IF(OR(D60="",E60=""),"",E60/D60)</f>
-        <v>8.533159857750022e-8</v>
-      </c>
-      <c r="G60" s="136" t="str">
+        <v>2.074074074074074e-9</v>
+      </c>
+      <c r="G60" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F60))),"",F60*$D$55)</f>
+        <v>0.000005147293634903044</v>
       </c>
       <c r="H60" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F60)),"",F60*$D$45)</f>
-        <v>85.33159857750022</v>
-      </c>
-      <c r="I60" s="145" t="str">
+        <v>2.074074074074074</v>
+      </c>
+      <c r="I60" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H60))),"",H60*$D$55)</f>
+        <v>5147.293634903044</v>
       </c>
       <c r="J60" s="145" t="n">
         <f>E60-E59</f>
-        <v>7.679843871975024</v>
+        <v>0.18666666666666676</v>
       </c>
       <c r="K60" s="145" t="n">
         <f>J60/(1-$G$41-$J$7)</f>
-        <v>7.757418052500024</v>
+        <v>0.18855218855218864</v>
       </c>
       <c r="L60" s="148" t="n">
         <f>SUM($K$59:K60)</f>
-        <v>7.757418052500024</v>
+        <v>0.18855218855218864</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2364,33 +2382,35 @@
       </c>
       <c r="E61" s="145" t="n">
         <f>$G$47/D61</f>
-        <v>86.39824355971898</v>
+        <v>2.1</v>
       </c>
       <c r="F61" s="136" t="n">
         <f>IF(OR(D61="",E61=""),"",E61/D61)</f>
-        <v>1.0799780444964873e-7</v>
-      </c>
-      <c r="G61" s="136" t="str">
+        <v>2.625e-9</v>
+      </c>
+      <c r="G61" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F61))),"",F61*$D$55)</f>
+        <v>0.0000065145435066741655</v>
       </c>
       <c r="H61" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F61)),"",F61*$D$45)</f>
-        <v>107.99780444964873</v>
-      </c>
-      <c r="I61" s="145" t="str">
+        <v>2.625</v>
+      </c>
+      <c r="I61" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H61))),"",H61*$D$55)</f>
+        <v>6514.543506674166</v>
       </c>
       <c r="J61" s="145" t="n">
         <f>E61-E60</f>
-        <v>9.599804839968783</v>
+        <v>0.2333333333333334</v>
       </c>
       <c r="K61" s="145" t="n">
         <f>J61/(1-$G$41-$J$7)</f>
-        <v>9.696772565625034</v>
+        <v>0.23569023569023576</v>
       </c>
       <c r="L61" s="148" t="n">
         <f>SUM($K$59:K61)</f>
-        <v>17.454190618125057</v>
+        <v>0.4242424242424244</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2405,33 +2425,35 @@
       </c>
       <c r="E62" s="145" t="n">
         <f>$G$47/D62</f>
-        <v>98.74084978253596</v>
+        <v>2.4</v>
       </c>
       <c r="F62" s="136" t="n">
         <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
-        <v>1.4105835683219424e-7</v>
-      </c>
-      <c r="G62" s="136" t="str">
+        <v>3.4285714285714283e-9</v>
+      </c>
+      <c r="G62" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F62))),"",F62*$D$55)</f>
+        <v>0.000008508791518921358</v>
       </c>
       <c r="H62" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$45)</f>
-        <v>141.05835683219425</v>
-      </c>
-      <c r="I62" s="145" t="str">
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="I62" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H62))),"",H62*$D$55)</f>
+        <v>8508.791518921358</v>
       </c>
       <c r="J62" s="145" t="n">
         <f>E62-E61</f>
-        <v>12.342606222816983</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="K62" s="145" t="n">
         <f>J62/(1-$G$41-$J$7)</f>
-        <v>12.467279012946447</v>
+        <v>0.30303030303030287</v>
       </c>
       <c r="L62" s="148" t="n">
         <f>SUM($K$59:K62)</f>
-        <v>29.921469631071503</v>
+        <v>0.7272727272727273</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2446,33 +2468,35 @@
       </c>
       <c r="E63" s="145" t="n">
         <f>$G$47/D63</f>
-        <v>115.1976580796253</v>
+        <v>2.8</v>
       </c>
       <c r="F63" s="136" t="n">
         <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
-        <v>1.919960967993755e-7</v>
-      </c>
-      <c r="G63" s="136" t="str">
+        <v>4.666666666666666e-9</v>
+      </c>
+      <c r="G63" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F63))),"",F63*$D$55)</f>
+        <v>0.00001158141067853185</v>
       </c>
       <c r="H63" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$45)</f>
-        <v>191.99609679937552</v>
-      </c>
-      <c r="I63" s="145" t="str">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="I63" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H63))),"",H63*$D$55)</f>
+        <v>11581.410678531849</v>
       </c>
       <c r="J63" s="145" t="n">
         <f>E63-E62</f>
-        <v>16.45680829708934</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="K63" s="145" t="n">
         <f>J63/(1-$G$41-$J$7)</f>
-        <v>16.623038683928623</v>
+        <v>0.404040404040404</v>
       </c>
       <c r="L63" s="148" t="n">
         <f>SUM($K$59:K63)</f>
-        <v>46.54450831500013</v>
+        <v>1.1313131313131313</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2487,33 +2511,35 @@
       </c>
       <c r="E64" s="145" t="n">
         <f>$G$47/D64</f>
-        <v>138.23718969555034</v>
+        <v>3.36</v>
       </c>
       <c r="F64" s="136" t="n">
         <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
-        <v>2.7647437939110067e-7</v>
-      </c>
-      <c r="G64" s="136" t="str">
+        <v>6.72e-9</v>
+      </c>
+      <c r="G64" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F64))),"",F64*$D$55)</f>
+        <v>0.000016677231377085863</v>
       </c>
       <c r="H64" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$45)</f>
-        <v>276.4743793911007</v>
-      </c>
-      <c r="I64" s="145" t="str">
+        <v>6.72</v>
+      </c>
+      <c r="I64" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H64))),"",H64*$D$55)</f>
+        <v>16677.231377085864</v>
       </c>
       <c r="J64" s="145" t="n">
         <f>E64-E63</f>
-        <v>23.039531615925043</v>
+        <v>0.56</v>
       </c>
       <c r="K64" s="145" t="n">
         <f>J64/(1-$G$41-$J$7)</f>
-        <v>23.272254157500043</v>
+        <v>0.5656565656565657</v>
       </c>
       <c r="L64" s="148" t="n">
         <f>SUM($K$59:K64)</f>
-        <v>69.81676247250017</v>
+        <v>1.696969696969697</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2528,33 +2554,35 @@
       </c>
       <c r="E65" s="145" t="n">
         <f>$G$47/D65</f>
-        <v>172.79648711943796</v>
+        <v>4.2</v>
       </c>
       <c r="F65" s="136" t="n">
         <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
-        <v>4.319912177985949e-7</v>
-      </c>
-      <c r="G65" s="136" t="str">
+        <v>1.05e-8</v>
+      </c>
+      <c r="G65" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F65))),"",F65*$D$55)</f>
+        <v>0.000026058174026696662</v>
       </c>
       <c r="H65" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$45)</f>
-        <v>431.9912177985949</v>
-      </c>
-      <c r="I65" s="145" t="str">
+        <v>10.5</v>
+      </c>
+      <c r="I65" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H65))),"",H65*$D$55)</f>
+        <v>26058.174026696663</v>
       </c>
       <c r="J65" s="145" t="n">
         <f>E65-E64</f>
-        <v>34.559297423887614</v>
+        <v>0.8400000000000003</v>
       </c>
       <c r="K65" s="145" t="n">
         <f>J65/(1-$G$41-$J$7)</f>
-        <v>34.908381236250115</v>
+        <v>0.8484848484848488</v>
       </c>
       <c r="L65" s="148" t="n">
         <f>SUM($K$59:K65)</f>
-        <v>104.7251437087503</v>
+        <v>2.545454545454546</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2569,33 +2597,35 @@
       </c>
       <c r="E66" s="145" t="n">
         <f>$G$47/D66</f>
-        <v>230.39531615925054</v>
+        <v>5.599999999999999</v>
       </c>
       <c r="F66" s="136" t="n">
         <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
-        <v>7.679843871975016e-7</v>
-      </c>
-      <c r="G66" s="136" t="str">
+        <v>1.866666666666666e-8</v>
+      </c>
+      <c r="G66" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F66))),"",F66*$D$55)</f>
+        <v>0.000046325642714127376</v>
       </c>
       <c r="H66" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$45)</f>
-        <v>767.9843871975016</v>
-      </c>
-      <c r="I66" s="145" t="str">
+        <v>18.666666666666657</v>
+      </c>
+      <c r="I66" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H66))),"",H66*$D$55)</f>
+        <v>46325.642714127374</v>
       </c>
       <c r="J66" s="145" t="n">
         <f>E66-E65</f>
-        <v>57.598829039812586</v>
+        <v>1.3999999999999986</v>
       </c>
       <c r="K66" s="145" t="n">
         <f>J66/(1-$G$41-$J$7)</f>
-        <v>58.18063539375009</v>
+        <v>1.4141414141414128</v>
       </c>
       <c r="L66" s="148" t="n">
         <f>SUM($K$59:K66)</f>
-        <v>162.9057791025004</v>
+        <v>3.9595959595959584</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2611,33 +2641,35 @@
       </c>
       <c r="E67" s="146" t="n">
         <f>$G$47/D67</f>
-        <v>241.91508196721315</v>
+        <v>5.880000000000001</v>
       </c>
       <c r="F67" s="137" t="n">
         <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
-        <v>8.467027868852461e-7</v>
-      </c>
-      <c r="G67" s="137" t="str">
+        <v>2.0580000000000006e-8</v>
+      </c>
+      <c r="G67" s="137" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F67))),"",F67*$D$55)</f>
+        <v>0.00005107402109232547</v>
       </c>
       <c r="H67" s="146" t="n">
         <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$45)</f>
-        <v>846.7027868852462</v>
-      </c>
-      <c r="I67" s="146" t="str">
+        <v>20.580000000000005</v>
+      </c>
+      <c r="I67" s="146" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H67))),"",H67*$D$55)</f>
+        <v>51074.02109232547</v>
       </c>
       <c r="J67" s="146" t="n">
         <f>E67-E66</f>
-        <v>11.519765807962614</v>
+        <v>0.280000000000002</v>
       </c>
       <c r="K67" s="146" t="n">
         <f>J67/(1-$G$41-$J$7)</f>
-        <v>11.636127078750116</v>
+        <v>0.28282828282828487</v>
       </c>
       <c r="L67" s="149" t="n">
         <f>SUM($K$59:K67)</f>
-        <v>174.5419061812505</v>
+        <v>4.242424242424243</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2734,21 +2766,23 @@
       </c>
       <c r="E72" s="144" t="n">
         <f>$G$44</f>
-        <v>172.79648711943796</v>
+        <v>4.2</v>
       </c>
       <c r="F72" s="135" t="n">
         <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
-        <v>8.467027868852459e-7</v>
-      </c>
-      <c r="G72" s="135" t="str">
+        <v>2.058e-8</v>
+      </c>
+      <c r="G72" s="135" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F72))),"",F72*$D$55)</f>
+        <v>0.000051074021092325456</v>
       </c>
       <c r="H72" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$45)</f>
-        <v>846.7027868852459</v>
-      </c>
-      <c r="I72" s="144" t="str">
+        <v>20.58</v>
+      </c>
+      <c r="I72" s="144" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H72))),"",H72*$D$55)</f>
+        <v>51074.021092325456</v>
       </c>
       <c r="J72" s="144" t="n">
         <f>0</f>
@@ -2760,7 +2794,7 @@
       </c>
       <c r="L72" s="147" t="n">
         <f>$J$41</f>
-        <v>174.54190618125045</v>
+        <v>4.242424242424242</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2775,33 +2809,35 @@
       </c>
       <c r="E73" s="145" t="n">
         <f>IF(D73="","",$G$50/D73)</f>
-        <v>209.45028741750056</v>
+        <v>5.09090909090909</v>
       </c>
       <c r="F73" s="136" t="n">
         <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
-        <v>0.0000012440077676918213</v>
-      </c>
-      <c r="G73" s="136" t="str">
+        <v>3.023691460055095e-8</v>
+      </c>
+      <c r="G73" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F73))),"",F73*$D$55)</f>
+        <v>0.00007503988406585923</v>
       </c>
       <c r="H73" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$45)</f>
-        <v>1244.0077676918213</v>
-      </c>
-      <c r="I73" s="145" t="str">
+        <v>30.236914600550953</v>
+      </c>
+      <c r="I73" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H73))),"",H73*$D$55)</f>
+        <v>75039.88406585922</v>
       </c>
       <c r="J73" s="145" t="n">
         <f>IF(E73="","",MAX(0,E73-$G$44))</f>
-        <v>36.653800298062606</v>
+        <v>0.8909090909090898</v>
       </c>
       <c r="K73" s="145" t="n">
         <f>IF(D73="","",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>37.103540179020456</v>
+        <v>0.9018404907975457</v>
       </c>
       <c r="L73" s="148" t="n">
         <f>IF(K73="","",$J$41+K73)</f>
-        <v>211.6454463602709</v>
+        <v>5.144264733221788</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2816,33 +2852,35 @@
       </c>
       <c r="E74" s="145" t="n">
         <f>IF(D74="","",$G$50/D74)</f>
-        <v>297.9249777921345</v>
+        <v>7.241379310344829</v>
       </c>
       <c r="F74" s="136" t="n">
         <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
-        <v>0.0000025169523985887227</v>
-      </c>
-      <c r="G74" s="136" t="str">
+        <v>6.117717003567184e-8</v>
+      </c>
+      <c r="G74" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F74))),"",F74*$D$55)</f>
+        <v>0.00015182527078574755</v>
       </c>
       <c r="H74" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$45)</f>
-        <v>2516.9523985887226</v>
-      </c>
-      <c r="I74" s="145" t="str">
+        <v>61.17717003567184</v>
+      </c>
+      <c r="I74" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H74))),"",H74*$D$55)</f>
+        <v>151825.27078574756</v>
       </c>
       <c r="J74" s="145" t="n">
         <f>IF(E74="","",MAX(0,E74-$G$44))</f>
-        <v>125.12849067269653</v>
+        <v>3.041379310344829</v>
       </c>
       <c r="K74" s="145" t="n">
         <f>IF(D74="","",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>127.32372735116493</v>
+        <v>3.094736842105265</v>
       </c>
       <c r="L74" s="148" t="n">
         <f>IF(K74="","",$J$41+K74)</f>
-        <v>301.86563353241536</v>
+        <v>7.337161084529507</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2857,33 +2895,35 @@
       </c>
       <c r="E75" s="145" t="n">
         <f>IF(D75="","",$G$50/D75)</f>
-        <v>358.4989359324437</v>
+        <v>8.713692946058085</v>
       </c>
       <c r="F75" s="136" t="n">
         <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
-        <v>0.000003644491257404508</v>
-      </c>
-      <c r="G75" s="136" t="str">
+        <v>8.858318555121283e-8</v>
+      </c>
+      <c r="G75" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F75))),"",F75*$D$55)</f>
+        <v>0.00021983962523168242</v>
       </c>
       <c r="H75" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$45)</f>
-        <v>3644.4912574045084</v>
-      </c>
-      <c r="I75" s="145" t="str">
+        <v>88.58318555121284</v>
+      </c>
+      <c r="I75" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H75))),"",H75*$D$55)</f>
+        <v>219839.6252316824</v>
       </c>
       <c r="J75" s="145" t="n">
         <f>IF(E75="","",MAX(0,E75-$G$44))</f>
-        <v>185.70244881300576</v>
+        <v>4.513692946058085</v>
       </c>
       <c r="K75" s="145" t="n">
         <f>IF(D75="","",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>189.63682272853552</v>
+        <v>4.609322033898299</v>
       </c>
       <c r="L75" s="148" t="n">
         <f>IF(K75="","",$J$41+K75)</f>
-        <v>364.17872890978595</v>
+        <v>8.85174627632254</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2898,33 +2938,35 @@
       </c>
       <c r="E76" s="145" t="n">
         <f>IF(D76="","",$G$50/D76)</f>
-        <v>449.99085187353614</v>
+        <v>10.937499999999995</v>
       </c>
       <c r="F76" s="136" t="n">
         <f>IF(OR(D76="",E76=""),"",E76/D76)</f>
-        <v>0.000005742070766094599</v>
-      </c>
-      <c r="G76" s="136" t="str">
+        <v>1.3956705729166652e-7</v>
+      </c>
+      <c r="G76" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F76))),"",F76*$D$55)</f>
+        <v>0.00034636787307620854</v>
       </c>
       <c r="H76" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F76)),"",F76*$D$45)</f>
-        <v>5742.070766094599</v>
-      </c>
-      <c r="I76" s="145" t="str">
+        <v>139.56705729166652</v>
+      </c>
+      <c r="I76" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H76))),"",H76*$D$55)</f>
+        <v>346367.8730762085</v>
       </c>
       <c r="J76" s="145" t="n">
         <f>IF(E76="","",MAX(0,E76-$G$44))</f>
-        <v>277.19436475409816</v>
+        <v>6.7374999999999945</v>
       </c>
       <c r="K76" s="145" t="n">
         <f>IF(D76="","",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>284.6059787849564</v>
+        <v>6.917647058823522</v>
       </c>
       <c r="L76" s="148" t="n">
         <f>IF(K76="","",$J$41+K76)</f>
-        <v>459.14788496620685</v>
+        <v>11.160071301247765</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2939,33 +2981,35 @@
       </c>
       <c r="E77" s="145" t="n">
         <f>IF(D77="","",$G$50/D77)</f>
-        <v>604.1835213966361</v>
+        <v>14.685314685314683</v>
       </c>
       <c r="F77" s="136" t="n">
         <f>IF(OR(D77="",E77=""),"",E77/D77)</f>
-        <v>0.00001035139599595635</v>
-      </c>
-      <c r="G77" s="136" t="str">
+        <v>2.5160154530783893e-7</v>
+      </c>
+      <c r="G77" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F77))),"",F77*$D$55)</f>
+        <v>0.0006244073193349972</v>
       </c>
       <c r="H77" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F77)),"",F77*$D$45)</f>
-        <v>10351.39599595635</v>
-      </c>
-      <c r="I77" s="145" t="str">
+        <v>251.60154530783893</v>
+      </c>
+      <c r="I77" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H77))),"",H77*$D$55)</f>
+        <v>624407.3193349973</v>
       </c>
       <c r="J77" s="145" t="n">
         <f>IF(E77="","",MAX(0,E77-$G$44))</f>
-        <v>431.38703427719815</v>
+        <v>10.485314685314684</v>
       </c>
       <c r="K77" s="145" t="n">
         <f>IF(D77="","",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>447.0169992872412</v>
+        <v>10.865217391304334</v>
       </c>
       <c r="L77" s="148" t="n">
         <f>IF(K77="","",$J$41+K77)</f>
-        <v>621.5589054684917</v>
+        <v>15.107641633728576</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2980,33 +3024,35 @@
       </c>
       <c r="E78" s="145" t="n">
         <f>IF(D78="","",$G$50/D78)</f>
-        <v>919.1302506353081</v>
+        <v>22.340425531914885</v>
       </c>
       <c r="F78" s="136" t="n">
         <f>IF(OR(D78="",E78=""),"",E78/D78)</f>
-        <v>0.000023956054404856426</v>
-      </c>
-      <c r="G78" s="136" t="str">
+        <v>5.822770484382069e-7</v>
+      </c>
+      <c r="G78" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F78))),"",F78*$D$55)</f>
+        <v>0.0014450549199956262</v>
       </c>
       <c r="H78" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F78)),"",F78*$D$45)</f>
-        <v>23956.054404856426</v>
-      </c>
-      <c r="I78" s="145" t="str">
+        <v>582.2770484382069</v>
+      </c>
+      <c r="I78" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H78))),"",H78*$D$55)</f>
+        <v>1445054.9199956262</v>
       </c>
       <c r="J78" s="145" t="n">
         <f>IF(E78="","",MAX(0,E78-$G$44))</f>
-        <v>746.3337635158701</v>
+        <v>18.140425531914886</v>
       </c>
       <c r="K78" s="145" t="n">
         <f>IF(D78="","",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>788.2626266347389</v>
+        <v>19.15955056179774</v>
       </c>
       <c r="L78" s="148" t="n">
         <f>IF(K78="","",$J$41+K78)</f>
-        <v>962.8045328159894</v>
+        <v>23.401974804221982</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3021,33 +3067,35 @@
       </c>
       <c r="E79" s="145" t="n">
         <f>IF(D79="","",$G$50/D79)</f>
-        <v>1243.1401951038704</v>
+        <v>30.2158273381295</v>
       </c>
       <c r="F79" s="136" t="n">
         <f>IF(OR(D79="",E79=""),"",E79/D79)</f>
-        <v>0.00004382292774107169</v>
-      </c>
-      <c r="G79" s="136" t="str">
+        <v>0.0000010651622586822629</v>
+      </c>
+      <c r="G79" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F79))),"",F79*$D$55)</f>
+        <v>0.0026434460479439707</v>
       </c>
       <c r="H79" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F79)),"",F79*$D$45)</f>
-        <v>43822.92774107169</v>
-      </c>
-      <c r="I79" s="145" t="str">
+        <v>1065.162258682263</v>
+      </c>
+      <c r="I79" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H79))),"",H79*$D$55)</f>
+        <v>2643446.047943971</v>
       </c>
       <c r="J79" s="145" t="n">
         <f>IF(E79="","",MAX(0,E79-$G$44))</f>
-        <v>1070.3437079844325</v>
+        <v>26.0158273381295</v>
       </c>
       <c r="K79" s="145" t="n">
         <f>IF(D79="","",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>1153.31608844834</v>
+        <v>28.03255813953484</v>
       </c>
       <c r="L79" s="148" t="n">
         <f>IF(K79="","",$J$41+K79)</f>
-        <v>1327.8579946295904</v>
+        <v>32.27498238195908</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3062,33 +3110,35 @@
       </c>
       <c r="E80" s="145" t="n">
         <f>IF(D80="","",$G$50/D80)</f>
-        <v>1919.9609679937555</v>
+        <v>46.66666666666667</v>
       </c>
       <c r="F80" s="136" t="n">
         <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
-        <v>0.0001045312082574378</v>
-      </c>
-      <c r="G80" s="136" t="str">
+        <v>0.000002540740740740741</v>
+      </c>
+      <c r="G80" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F80))),"",F80*$D$55)</f>
+        <v>0.0063054347027562295</v>
       </c>
       <c r="H80" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$45)</f>
-        <v>104531.2082574378</v>
-      </c>
-      <c r="I80" s="145" t="str">
+        <v>2540.740740740741</v>
+      </c>
+      <c r="I80" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H80))),"",H80*$D$55)</f>
+        <v>6305434.70275623</v>
       </c>
       <c r="J80" s="145" t="n">
         <f>IF(E80="","",MAX(0,E80-$G$44))</f>
-        <v>1747.1644808743176</v>
+        <v>42.46666666666667</v>
       </c>
       <c r="K80" s="145" t="n">
         <f>IF(D80="","",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>1965.5600409836077</v>
+        <v>47.775000000000006</v>
       </c>
       <c r="L80" s="148" t="n">
         <f>IF(K80="","",$J$41+K80)</f>
-        <v>2140.1019471648583</v>
+        <v>52.01742424242425</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3103,33 +3153,35 @@
       </c>
       <c r="E81" s="145" t="n">
         <f>IF(D81="","",$G$50/D81)</f>
-        <v>2638.1143071669953</v>
+        <v>64.12213740458023</v>
       </c>
       <c r="F81" s="136" t="n">
         <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
-        <v>0.00019735511610867622</v>
-      </c>
-      <c r="G81" s="136" t="str">
+        <v>0.000004796923256220511</v>
+      </c>
+      <c r="G81" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F81))),"",F81*$D$55)</f>
+        <v>0.011904672476504998</v>
       </c>
       <c r="H81" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$45)</f>
-        <v>197355.11610867621</v>
-      </c>
-      <c r="I81" s="145" t="str">
+        <v>4796.923256220511</v>
+      </c>
+      <c r="I81" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H81))),"",H81*$D$55)</f>
+        <v>11904672.476504998</v>
       </c>
       <c r="J81" s="145" t="n">
         <f>IF(E81="","",MAX(0,E81-$G$44))</f>
-        <v>2465.3178200475572</v>
+        <v>59.922137404580226</v>
       </c>
       <c r="K81" s="145" t="n">
         <f>IF(D81="","",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>2909.51922906513</v>
+        <v>70.71891891891889</v>
       </c>
       <c r="L81" s="148" t="n">
         <f>IF(K81="","",$J$41+K81)</f>
-        <v>3084.06113524638</v>
+        <v>74.96134316134314</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3144,33 +3196,35 @@
       </c>
       <c r="E82" s="145" t="n">
         <f>IF(D82="","",$G$50/D82)</f>
-        <v>4214.548466327764</v>
+        <v>102.4390243902441</v>
       </c>
       <c r="F82" s="136" t="n">
         <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
-        <v>0.0005036899386586849</v>
-      </c>
-      <c r="G82" s="136" t="str">
+        <v>0.000012242712671029196</v>
+      </c>
+      <c r="G82" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F82))),"",F82*$D$55)</f>
+        <v>0.03038311784195458</v>
       </c>
       <c r="H82" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$45)</f>
-        <v>503689.93865868496</v>
-      </c>
-      <c r="I82" s="145" t="str">
+        <v>12242.712671029196</v>
+      </c>
+      <c r="I82" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H82))),"",H82*$D$55)</f>
+        <v>30383117.84195458</v>
       </c>
       <c r="J82" s="145" t="n">
         <f>IF(E82="","",MAX(0,E82-$G$44))</f>
-        <v>4041.751979208326</v>
+        <v>98.2390243902441</v>
       </c>
       <c r="K82" s="145" t="n">
         <f>IF(D82="","",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>5345.542940243272</v>
+        <v>129.92903225806486</v>
       </c>
       <c r="L82" s="148" t="n">
         <f>IF(K82="","",$J$41+K82)</f>
-        <v>5520.084846424523</v>
+        <v>134.1714565004891</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3185,33 +3239,35 @@
       </c>
       <c r="E83" s="145" t="n">
         <f>IF(D83="","",$G$50/D83)</f>
-        <v>10472.514370875078</v>
+        <v>254.54545454545573</v>
       </c>
       <c r="F83" s="136" t="n">
         <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
-        <v>0.0031100194192295832</v>
-      </c>
-      <c r="G83" s="136" t="str">
+        <v>0.00007559228650137811</v>
+      </c>
+      <c r="G83" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F83))),"",F83*$D$55)</f>
+        <v>0.18759971016464988</v>
       </c>
       <c r="H83" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$45)</f>
-        <v>3110019.4192295833</v>
-      </c>
-      <c r="I83" s="145" t="str">
+        <v>75592.28650137811</v>
+      </c>
+      <c r="I83" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H83))),"",H83*$D$55)</f>
+        <v>187599710.16464987</v>
       </c>
       <c r="J83" s="145" t="n">
         <f>IF(E83="","",MAX(0,E83-$G$44))</f>
-        <v>10299.71788375564</v>
+        <v>250.34545454545574</v>
       </c>
       <c r="K83" s="145" t="n">
         <f>IF(D83="","",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>26145.43770491818</v>
+        <v>635.4923076923111</v>
       </c>
       <c r="L83" s="148" t="n">
         <f>IF(K83="","",$J$41+K83)</f>
-        <v>26319.97961109943</v>
+        <v>639.7347319347354</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3368,21 +3424,23 @@
       </c>
       <c r="E90" s="144" t="n">
         <f>$G$50/D90</f>
-        <v>172.79648711943798</v>
+        <v>4.2</v>
       </c>
       <c r="F90" s="135" t="n">
         <f>IF(OR(D90="",E90=""),"",E90/D90)</f>
-        <v>8.467027868852462e-7</v>
-      </c>
-      <c r="G90" s="135" t="str">
+        <v>2.0580000000000003e-8</v>
+      </c>
+      <c r="G90" s="135" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F90))),"",F90*$D$55)</f>
+        <v>0.00005107402109232546</v>
       </c>
       <c r="H90" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F90)),"",F90*$D$45)</f>
-        <v>846.7027868852463</v>
-      </c>
-      <c r="I90" s="144" t="str">
+        <v>20.580000000000002</v>
+      </c>
+      <c r="I90" s="144" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H90))),"",H90*$D$55)</f>
+        <v>51074.02109232546</v>
       </c>
       <c r="J90" s="132" t="n">
         <f>IF($H$90&gt;0,1-H90/$H$90,0)</f>
@@ -3403,25 +3461,27 @@
       </c>
       <c r="E91" s="145" t="n">
         <f>$G$50/D91</f>
-        <v>161.49204403685786</v>
+        <v>3.9252336448598117</v>
       </c>
       <c r="F91" s="136" t="n">
         <f>IF(OR(D91="",E91=""),"",E91/D91)</f>
-        <v>7.395430054024329e-7</v>
-      </c>
-      <c r="G91" s="136" t="str">
+        <v>1.797536902786268e-8</v>
+      </c>
+      <c r="G91" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F91))),"",F91*$D$55)</f>
+        <v>0.0000446100280306799</v>
       </c>
       <c r="H91" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F91)),"",F91*$D$45)</f>
-        <v>739.5430054024329</v>
-      </c>
-      <c r="I91" s="145" t="str">
+        <v>17.97536902786268</v>
+      </c>
+      <c r="I91" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H91))),"",H91*$D$55)</f>
+        <v>44610.028030679896</v>
       </c>
       <c r="J91" s="133" t="n">
         <f>IF($H$90&gt;0,1-H91/$H$90,0)</f>
-        <v>0.12656127172678933</v>
+        <v>0.12656127172678922</v>
       </c>
       <c r="K91" s="130"/>
       <c r="L91" s="130"/>
@@ -3438,21 +3498,23 @@
       </c>
       <c r="E92" s="145" t="n">
         <f>$G$50/D92</f>
-        <v>110.76697892271665</v>
+        <v>2.692307692307692</v>
       </c>
       <c r="F92" s="136" t="n">
         <f>IF(OR(D92="",E92=""),"",E92/D92)</f>
-        <v>3.479219209751997e-7</v>
-      </c>
-      <c r="G92" s="136" t="str">
+        <v>8.456607495069032e-9</v>
+      </c>
+      <c r="G92" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F92))),"",F92*$D$55)</f>
+        <v>0.000020987023788759636</v>
       </c>
       <c r="H92" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F92)),"",F92*$D$45)</f>
-        <v>347.9219209751997</v>
-      </c>
-      <c r="I92" s="145" t="str">
+        <v>8.456607495069033</v>
+      </c>
+      <c r="I92" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H92))),"",H92*$D$55)</f>
+        <v>20987.023788759638</v>
       </c>
       <c r="J92" s="133" t="n">
         <f>IF($H$90&gt;0,1-H92/$H$90,0)</f>
@@ -3473,21 +3535,23 @@
       </c>
       <c r="E93" s="145" t="n">
         <f>$G$50/D93</f>
-        <v>84.29096932655511</v>
+        <v>2.048780487804878</v>
       </c>
       <c r="F93" s="136" t="n">
         <f>IF(OR(D93="",E93=""),"",E93/D93)</f>
-        <v>2.0147597546347317e-7</v>
-      </c>
-      <c r="G93" s="136" t="str">
+        <v>4.89708506841166e-9</v>
+      </c>
+      <c r="G93" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F93))),"",F93*$D$55)</f>
+        <v>0.000012153247136781787</v>
       </c>
       <c r="H93" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F93)),"",F93*$D$45)</f>
-        <v>201.47597546347316</v>
-      </c>
-      <c r="I93" s="145" t="str">
+        <v>4.89708506841166</v>
+      </c>
+      <c r="I93" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H93))),"",H93*$D$55)</f>
+        <v>12153.247136781787</v>
       </c>
       <c r="J93" s="133" t="n">
         <f>IF($H$90&gt;0,1-H93/$H$90,0)</f>
@@ -3508,21 +3572,23 @@
       </c>
       <c r="E94" s="145" t="n">
         <f>$G$50/D94</f>
-        <v>68.03011303914882</v>
+        <v>1.6535433070866141</v>
       </c>
       <c r="F94" s="136" t="n">
         <f>IF(OR(D94="",E94=""),"",E94/D94)</f>
-        <v>1.3123919444560203e-7</v>
-      </c>
-      <c r="G94" s="136" t="str">
+        <v>3.189906379812759e-9</v>
+      </c>
+      <c r="G94" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F94))),"",F94*$D$55)</f>
+        <v>0.000007916489102288648</v>
       </c>
       <c r="H94" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F94)),"",F94*$D$45)</f>
-        <v>131.23919444560204</v>
-      </c>
-      <c r="I94" s="145" t="str">
+        <v>3.189906379812759</v>
+      </c>
+      <c r="I94" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H94))),"",H94*$D$55)</f>
+        <v>7916.4891022886495</v>
       </c>
       <c r="J94" s="133" t="n">
         <f>IF($H$90&gt;0,1-H94/$H$90,0)</f>
@@ -3543,21 +3609,23 @@
       </c>
       <c r="E95" s="145" t="n">
         <f>$G$50/D95</f>
-        <v>57.028543603774914</v>
+        <v>1.3861386138613863</v>
       </c>
       <c r="F95" s="136" t="n">
         <f>IF(OR(D95="",E95=""),"",E95/D95)</f>
-        <v>9.222437744504854e-8</v>
-      </c>
-      <c r="G95" s="136" t="str">
+        <v>2.2416102996438257e-9</v>
+      </c>
+      <c r="G95" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F95))),"",F95*$D$55)</f>
+        <v>0.000005563073456014711</v>
       </c>
       <c r="H95" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F95)),"",F95*$D$45)</f>
-        <v>92.22437744504853</v>
-      </c>
-      <c r="I95" s="145" t="str">
+        <v>2.241610299643826</v>
+      </c>
+      <c r="I95" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H95))),"",H95*$D$55)</f>
+        <v>5563.073456014711</v>
       </c>
       <c r="J95" s="133" t="n">
         <f>IF($H$90&gt;0,1-H95/$H$90,0)</f>
@@ -3578,21 +3646,23 @@
       </c>
       <c r="E96" s="145" t="n">
         <f>$G$50/D96</f>
-        <v>49.089911113476695</v>
+        <v>1.1931818181818181</v>
       </c>
       <c r="F96" s="136" t="n">
         <f>IF(OR(D96="",E96=""),"",E96/D96)</f>
-        <v>6.833538762955562e-8</v>
-      </c>
-      <c r="G96" s="136" t="str">
+        <v>1.6609633264462809e-9</v>
+      </c>
+      <c r="G96" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F96))),"",F96*$D$55)</f>
+        <v>0.000004122063944047444</v>
       </c>
       <c r="H96" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F96)),"",F96*$D$45)</f>
-        <v>68.33538762955563</v>
-      </c>
-      <c r="I96" s="145" t="str">
+        <v>1.6609633264462809</v>
+      </c>
+      <c r="I96" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H96))),"",H96*$D$55)</f>
+        <v>4122.063944047444</v>
       </c>
       <c r="J96" s="133" t="n">
         <f>IF($H$90&gt;0,1-H96/$H$90,0)</f>
@@ -3613,21 +3683,23 @@
       </c>
       <c r="E97" s="145" t="n">
         <f>$G$50/D97</f>
-        <v>43.09139329661795</v>
+        <v>1.0473815461346634</v>
       </c>
       <c r="F97" s="136" t="n">
         <f>IF(OR(D97="",E97=""),"",E97/D97)</f>
-        <v>5.265531849212667e-8</v>
-      </c>
-      <c r="G97" s="136" t="str">
+        <v>1.2798427870473443e-9</v>
+      </c>
+      <c r="G97" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F97))),"",F97*$D$55)</f>
+        <v>0.0000031762253401611592</v>
       </c>
       <c r="H97" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F97)),"",F97*$D$45)</f>
-        <v>52.65531849212667</v>
-      </c>
-      <c r="I97" s="145" t="str">
+        <v>1.2798427870473443</v>
+      </c>
+      <c r="I97" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H97))),"",H97*$D$55)</f>
+        <v>3176.2253401611597</v>
       </c>
       <c r="J97" s="133" t="n">
         <f>IF($H$90&gt;0,1-H97/$H$90,0)</f>
@@ -3648,21 +3720,23 @@
       </c>
       <c r="E98" s="146" t="n">
         <f>$G$50/D98</f>
-        <v>38.399219359875104</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F98" s="137" t="n">
         <f>IF(OR(D98="",E98=""),"",E98/D98)</f>
-        <v>4.181248330297511e-8</v>
-      </c>
-      <c r="G98" s="137" t="str">
+        <v>1.0162962962962963e-9</v>
+      </c>
+      <c r="G98" s="137" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F98))),"",F98*$D$55)</f>
+        <v>0.0000025221738811024916</v>
       </c>
       <c r="H98" s="146" t="n">
         <f>IF(NOT(ISNUMBER(F98)),"",F98*$D$45)</f>
-        <v>41.81248330297511</v>
-      </c>
-      <c r="I98" s="146" t="str">
+        <v>1.0162962962962963</v>
+      </c>
+      <c r="I98" s="146" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H98))),"",H98*$D$55)</f>
+        <v>2522.1738811024916</v>
       </c>
       <c r="J98" s="134" t="n">
         <f>IF($H$90&gt;0,1-H98/$H$90,0)</f>
@@ -3673,7 +3747,7 @@
       </c>
       <c r="L98" s="131" t="n">
         <f>E98</f>
-        <v>38.399219359875104</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R918d13da31044a3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rcab139deb5424cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R1503447c5fe24ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R121b487aa5444b30"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -163,7 +163,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="153">
+  <x:cellXfs count="155">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -614,6 +614,12 @@
     </x:xf>
     <x:xf numFmtId="207" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -626,7 +632,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -637,7 +643,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -648,7 +654,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -659,7 +665,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -670,7 +676,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -681,7 +687,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -692,7 +698,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -703,7 +709,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -759,7 +765,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -770,7 +776,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -781,7 +787,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -792,7 +798,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -1338,7 +1344,7 @@
       </c>
       <c r="D18" s="121" t="n">
         <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
-        <v>388.2681341634973</v>
+        <v>406.73789645197434</v>
       </c>
       <c r="E18" s="62" t="str">
         <f>$D$7</f>
@@ -1359,7 +1365,7 @@
       </c>
       <c r="J18" s="121" t="n">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
-        <v>966306.9143316748</v>
+        <v>1012143.8933740419</v>
       </c>
       <c r="K18" s="62" t="str">
         <v>USDT</v>
@@ -1374,7 +1380,7 @@
       </c>
       <c r="D19" s="122" t="n">
         <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$55&gt;0,$D$18*$D$55,"")),"")</f>
-        <v>963577.0103860209</v>
+        <v>1009413.989428388</v>
       </c>
       <c r="E19" s="106" t="str">
         <v>USDT</v>
@@ -1541,11 +1547,11 @@
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="107" t="str">
-        <v>恢复目标控筹资金</v>
+        <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="122" t="n">
-        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",0)</f>
-        <v>0</v>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,$G$50/$J$55-$G$50/$J$56),""))</f>
+        <v>18.469762288477078</v>
       </c>
       <c r="E26" s="106" t="str">
         <f>$D$7</f>
@@ -1567,7 +1573,7 @@
       </c>
       <c r="D27" s="125" t="n">
         <f>$D$8*$J$54</f>
-        <v>0.9</v>
+        <v>0.891</v>
       </c>
       <c r="E27" s="106"/>
       <c r="F27" s="106"/>
@@ -1647,7 +1653,7 @@
       <c r="K30" s="106"/>
       <c r="L30" s="106"/>
     </row>
-    <row r="31" customHeight="1" hidden="1">
+    <row r="31" hidden="1" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31"/>
@@ -1661,7 +1667,7 @@
       <c r="K31" s="106"/>
       <c r="L31" s="106"/>
     </row>
-    <row r="32" customHeight="1" hidden="1">
+    <row r="32" hidden="1" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32"/>
@@ -1675,7 +1681,7 @@
       <c r="K32" s="106"/>
       <c r="L32" s="106"/>
     </row>
-    <row r="33" customHeight="1" hidden="1">
+    <row r="33" hidden="1" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33"/>
@@ -1689,7 +1695,7 @@
       <c r="K33" s="106"/>
       <c r="L33" s="106"/>
     </row>
-    <row r="34" customHeight="1" hidden="1">
+    <row r="34" hidden="1" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34"/>
@@ -1703,7 +1709,7 @@
       <c r="K34" s="106"/>
       <c r="L34" s="106"/>
     </row>
-    <row r="35" customHeight="1" hidden="1">
+    <row r="35" hidden="1" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35"/>
@@ -1717,11 +1723,11 @@
       <c r="K35" s="106"/>
       <c r="L35" s="106"/>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="115" t="str">
-        <v>Pons 按现有 Quote 洗筹损耗预算承担费用、持仓保持目标的口径，补回资金为 0；不代表免手续费。动态 Snipe Tax 未计入。</v>
+        <v>Pons 外盘买入时 Hook fee 与 Creator Tax 从输出 Meme 扣除，卖出时从输出 Quote 扣除。洗筹后 Meme 持仓会按买入侧费率减少；补回按洗后 TOKEN 缺口与现有 V4 曲线差额估算，不重复计入洗筹损耗。</v>
       </c>
       <c r="D36" s="115"/>
       <c r="E36" s="115"/>
@@ -1785,7 +1791,7 @@
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="40" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40" s="107" t="str">
@@ -1805,7 +1811,7 @@
       <c r="K40" s="107"/>
       <c r="L40" s="107"/>
     </row>
-    <row r="41" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="41" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A41"/>
       <c r="B41"/>
       <c r="C41" s="107" t="str">
@@ -1834,7 +1840,7 @@
       <c r="K41" s="107"/>
       <c r="L41" s="107"/>
     </row>
-    <row r="42" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="42" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42" s="107" t="str">
@@ -1863,7 +1869,7 @@
       <c r="K42" s="107"/>
       <c r="L42" s="107"/>
     </row>
-    <row r="43" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="43" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43" s="107"/>
@@ -1887,7 +1893,7 @@
       <c r="K43" s="107"/>
       <c r="L43" s="107"/>
     </row>
-    <row r="44" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="44" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44" s="107" t="str">
@@ -1916,7 +1922,7 @@
       <c r="K44" s="107"/>
       <c r="L44" s="107"/>
     </row>
-    <row r="45" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="45" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A45"/>
       <c r="B45"/>
       <c r="C45" s="107" t="str">
@@ -1945,7 +1951,7 @@
       <c r="K45" s="107"/>
       <c r="L45" s="107"/>
     </row>
-    <row r="46" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="46" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46" s="107" t="str">
@@ -1974,7 +1980,7 @@
       <c r="K46" s="107"/>
       <c r="L46" s="107"/>
     </row>
-    <row r="47" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="47" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47" s="107" t="str">
@@ -2002,7 +2008,7 @@
       <c r="K47" s="107"/>
       <c r="L47" s="107"/>
     </row>
-    <row r="48" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="48" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48" s="107" t="str">
@@ -2029,7 +2035,7 @@
       <c r="K48" s="107"/>
       <c r="L48" s="107"/>
     </row>
-    <row r="49" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="49" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49" s="107" t="str">
@@ -2056,7 +2062,7 @@
       <c r="K49" s="107"/>
       <c r="L49" s="107"/>
     </row>
-    <row r="50" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="50" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A50"/>
       <c r="B50"/>
       <c r="C50" s="107"/>
@@ -2075,7 +2081,7 @@
       <c r="K50" s="107"/>
       <c r="L50" s="107"/>
     </row>
-    <row r="51" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="51" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A51"/>
       <c r="B51"/>
       <c r="C51" s="107" t="str">
@@ -2104,7 +2110,7 @@
       <c r="K51" s="107"/>
       <c r="L51" s="107"/>
     </row>
-    <row r="52" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="52" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52" s="107" t="str">
@@ -2127,7 +2133,7 @@
       <c r="K52" s="107"/>
       <c r="L52" s="107"/>
     </row>
-    <row r="53" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="53" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A53"/>
       <c r="B53"/>
       <c r="C53" s="107" t="str">
@@ -2151,7 +2157,7 @@
       <c r="K53" s="107"/>
       <c r="L53" s="107"/>
     </row>
-    <row r="54" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="54" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A54"/>
       <c r="B54"/>
       <c r="C54" s="107" t="str">
@@ -2174,13 +2180,13 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="112" t="n">
-        <f>1</f>
-        <v>1</v>
+        <f>MAX(0,1-$G$42-$J$7)</f>
+        <v>0.99</v>
       </c>
       <c r="K54" s="107"/>
       <c r="L54" s="107"/>
     </row>
-    <row r="55" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="55" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55" s="107" t="str">
@@ -2202,11 +2208,14 @@
       <c r="I55" s="107" t="str">
         <v>目标外盘 Pool TOKEN</v>
       </c>
-      <c r="J55" s="108"/>
+      <c r="J55" s="108" t="n">
+        <f>$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$7)</f>
+        <v>16491445.062873632</v>
+      </c>
       <c r="K55" s="107"/>
       <c r="L55" s="107"/>
     </row>
-    <row r="56" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="56" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56" s="107" t="str">
@@ -2227,7 +2236,10 @@
       <c r="I56" s="107" t="str">
         <v>洗后外盘 Pool TOKEN</v>
       </c>
-      <c r="J56" s="108"/>
+      <c r="J56" s="108" t="n">
+        <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$7)</f>
+        <v>25582354.153782755</v>
+      </c>
       <c r="K56" s="107"/>
       <c r="L56" s="107"/>
     </row>
@@ -4810,7 +4822,7 @@
         <x:v>场景价格覆盖请用控筹模型</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="60" customHeight="1">
+    <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="2"/>
       <x:c r="B6" s="2"/>
       <x:c r="C6" s="35" t="str">
@@ -4822,25 +4834,27 @@
       </x:c>
       <x:c r="F6" s="35"/>
       <x:c r="G6" s="35"/>
-      <x:c r="H6" s="35" t="str">
-        <x:v>外盘成交口径</x:v>
-      </x:c>
-      <x:c r="I6" s="35"/>
-      <x:c r="J6" s="35" t="str">
-        <x:v>exact-input；Hook fee 与 Creator Tax 从 Meme 输出端扣除</x:v>
-      </x:c>
-      <x:c r="K6" s="35"/>
-      <x:c r="L6" s="35"/>
-      <x:c r="M6" s="35"/>
-      <x:c r="N6" s="35"/>
-      <x:c r="O6" s="35"/>
-      <x:c r="P6" s="35"/>
-      <x:c r="Q6" s="35"/>
-      <x:c r="R6" s="35"/>
-      <x:c r="S6" s="2"/>
-      <x:c r="T6" s="2"/>
-      <x:c r="U6" s="2"/>
-      <x:c r="V6" s="2"/>
+      <x:c r="H6" s="153" t="str">
+        <x:v>外盘扣费依据</x:v>
+      </x:c>
+      <x:c r="I6" s="153"/>
+      <x:c r="J6" s="153" t="str">
+        <x:v>V4 Hook 按交易方向从输出币收取；买入输出为 Meme，卖出输出为 Quote。</x:v>
+      </x:c>
+      <x:c r="K6" s="153"/>
+      <x:c r="L6" s="153"/>
+      <x:c r="M6" s="153"/>
+      <x:c r="N6" s="153"/>
+      <x:c r="O6" s="153"/>
+      <x:c r="P6" s="153"/>
+      <x:c r="Q6" s="153"/>
+      <x:c r="R6" s="153" t="str">
+        <x:v>https://docs.ponsfamily.com/v2</x:v>
+      </x:c>
+      <x:c r="S6" s="153"/>
+      <x:c r="T6" s="153"/>
+      <x:c r="U6" s="153"/>
+      <x:c r="V6" s="153"/>
     </x:row>
     <x:row r="7" ht="60" customHeight="1">
       <x:c r="A7" s="2"/>

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R1503447c5fe24ac7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R121b487aa5444b30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rf7e4b787ee604d02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R4dbb6c88067644a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="D18" s="121" t="n">
         <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
-        <v>406.73789645197434</v>
+        <v>388.2681341634973</v>
       </c>
       <c r="E18" s="62" t="str">
         <f>$D$7</f>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J18" s="121" t="n">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
-        <v>1012143.8933740419</v>
+        <v>966306.9143316748</v>
       </c>
       <c r="K18" s="62" t="str">
         <v>USDT</v>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="D19" s="122" t="n">
         <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$55&gt;0,$D$18*$D$55,"")),"")</f>
-        <v>1009413.989428388</v>
+        <v>963577.0103860209</v>
       </c>
       <c r="E19" s="106" t="str">
         <v>USDT</v>
@@ -1550,8 +1550,8 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="122" t="n">
-        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,$G$50/$J$55-$G$50/$J$56),""))</f>
-        <v>18.469762288477078</v>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",0)</f>
+        <v>0</v>
       </c>
       <c r="E26" s="106" t="str">
         <f>$D$7</f>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D27" s="125" t="n">
         <f>$D$8*$J$54</f>
-        <v>0.891</v>
+        <v>0.9</v>
       </c>
       <c r="E27" s="106"/>
       <c r="F27" s="106"/>
@@ -1727,7 +1727,7 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="115" t="str">
-        <v>Pons 外盘买入时 Hook fee 与 Creator Tax 从输出 Meme 扣除，卖出时从输出 Quote 扣除。洗筹后 Meme 持仓会按买入侧费率减少；补回按洗后 TOKEN 缺口与现有 V4 曲线差额估算，不重复计入洗筹损耗。</v>
+        <v>Pons V2 外盘手续费始终按 Quote leg 计收；Hook 某些方向暂存的 Meme 费用会在池内转换回 Quote，属于内部归集路径。按本模型口径不降低 TOKEN 控筹率，因此恢复目标控筹预留为 0。</v>
       </c>
       <c r="D36" s="115"/>
       <c r="E36" s="115"/>
@@ -2180,8 +2180,8 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="112" t="n">
-        <f>MAX(0,1-$G$42-$J$7)</f>
-        <v>0.99</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="K54" s="107"/>
       <c r="L54" s="107"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="J56" s="108" t="n">
         <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$7)</f>
-        <v>25582354.153782755</v>
+        <v>16491445.062873632</v>
       </c>
       <c r="K56" s="107"/>
       <c r="L56" s="107"/>
@@ -4839,7 +4839,7 @@
       </x:c>
       <x:c r="I6" s="153"/>
       <x:c r="J6" s="153" t="str">
-        <x:v>V4 Hook 按交易方向从输出币收取；买入输出为 Meme，卖出输出为 Quote。</x:v>
+        <x:v>费用始终按 Quote leg 计收；Hook 暂存的 Meme 费用会转换回 Quote。</x:v>
       </x:c>
       <x:c r="K6" s="153"/>
       <x:c r="L6" s="153"/>

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rf7e4b787ee604d02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R4dbb6c88067644a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R4da12d0f94ab4c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R82fe03f62c564d75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="D18" s="121" t="n">
         <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
-        <v>388.2681341634973</v>
+        <v>357.57043967335574</v>
       </c>
       <c r="E18" s="62" t="str">
         <f>$D$7</f>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J18" s="121" t="n">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
-        <v>966306.9143316748</v>
+        <v>890123.4985942962</v>
       </c>
       <c r="K18" s="62" t="str">
         <v>USDT</v>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="D19" s="122" t="n">
         <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$55&gt;0,$D$18*$D$55,"")),"")</f>
-        <v>963577.0103860209</v>
+        <v>887393.5946486422</v>
       </c>
       <c r="E19" s="106" t="str">
         <v>USDT</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D22" s="122" t="n">
         <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
-        <v>134.1714565004891</v>
+        <v>103.47376201034757</v>
       </c>
       <c r="E22" s="106" t="str">
         <f>$D$7</f>
@@ -1945,8 +1945,8 @@
         <v>外盘含费投入 / Quote</v>
       </c>
       <c r="J45" s="108" t="n">
-        <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$52-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>129.92903225806486</v>
+        <f>IF($J$42="","",($J$43-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>99.23133776792334</v>
       </c>
       <c r="K45" s="107"/>
       <c r="L45" s="107"/>
@@ -2164,8 +2164,8 @@
         <v>当前控筹上限</v>
       </c>
       <c r="D54" s="113" t="n">
-        <f>MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$7)*$G$48/$D$45)</f>
-        <v>0.916326530612245</v>
+        <f>1-$G$51/$D$45</f>
+        <v>0.9183673469387755</v>
       </c>
       <c r="E54" s="107"/>
       <c r="F54" s="107" t="str">
@@ -2209,8 +2209,8 @@
         <v>目标外盘 Pool TOKEN</v>
       </c>
       <c r="J55" s="108" t="n">
-        <f>$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$7)</f>
-        <v>16491445.062873632</v>
+        <f>$G$48-MAX(0,($D$8-$G$43)*$D$45)</f>
+        <v>18367346.93877551</v>
       </c>
       <c r="K55" s="107"/>
       <c r="L55" s="107"/>
@@ -2237,8 +2237,8 @@
         <v>洗后外盘 Pool TOKEN</v>
       </c>
       <c r="J56" s="108" t="n">
-        <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$7)</f>
-        <v>16491445.062873632</v>
+        <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)</f>
+        <v>18367346.93877551</v>
       </c>
       <c r="K56" s="107"/>
       <c r="L56" s="107"/>
@@ -2844,12 +2844,12 @@
         <v>0.8909090909090898</v>
       </c>
       <c r="K73" s="145" t="n">
-        <f>IF(D73="","",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>0.9018404907975457</v>
+        <f>IF(D73="","",MAX(0,$G$50/D73-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>0.8999081726354442</v>
       </c>
       <c r="L73" s="148" t="n">
         <f>IF(K73="","",$J$41+K73)</f>
-        <v>5.144264733221788</v>
+        <v>5.142332415059687</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2887,12 +2887,12 @@
         <v>3.041379310344829</v>
       </c>
       <c r="K74" s="145" t="n">
-        <f>IF(D74="","",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>3.094736842105265</v>
+        <f>IF(D74="","",MAX(0,$G$50/D74-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>3.072100313479625</v>
       </c>
       <c r="L74" s="148" t="n">
         <f>IF(K74="","",$J$41+K74)</f>
-        <v>7.337161084529507</v>
+        <v>7.314524555903867</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2930,12 +2930,12 @@
         <v>4.513692946058085</v>
       </c>
       <c r="K75" s="145" t="n">
-        <f>IF(D75="","",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>4.609322033898299</v>
+        <f>IF(D75="","",MAX(0,$G$50/D75-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>4.559285804099076</v>
       </c>
       <c r="L75" s="148" t="n">
         <f>IF(K75="","",$J$41+K75)</f>
-        <v>8.85174627632254</v>
+        <v>8.801710046523318</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2973,12 +2973,12 @@
         <v>6.7374999999999945</v>
       </c>
       <c r="K76" s="145" t="n">
-        <f>IF(D76="","",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>6.917647058823522</v>
+        <f>IF(D76="","",MAX(0,$G$50/D76-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>6.80555555555555</v>
       </c>
       <c r="L76" s="148" t="n">
         <f>IF(K76="","",$J$41+K76)</f>
-        <v>11.160071301247765</v>
+        <v>11.047979797979792</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -3016,12 +3016,12 @@
         <v>10.485314685314684</v>
       </c>
       <c r="K77" s="145" t="n">
-        <f>IF(D77="","",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>10.865217391304334</v>
+        <f>IF(D77="","",MAX(0,$G$50/D77-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>10.591226954863318</v>
       </c>
       <c r="L77" s="148" t="n">
         <f>IF(K77="","",$J$41+K77)</f>
-        <v>15.107641633728576</v>
+        <v>14.83365119728756</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3059,12 +3059,12 @@
         <v>18.140425531914886</v>
       </c>
       <c r="K78" s="145" t="n">
-        <f>IF(D78="","",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>19.15955056179774</v>
+        <f>IF(D78="","",MAX(0,$G$50/D78-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>18.32366215344938</v>
       </c>
       <c r="L78" s="148" t="n">
         <f>IF(K78="","",$J$41+K78)</f>
-        <v>23.401974804221982</v>
+        <v>22.566086395873622</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3102,12 +3102,12 @@
         <v>26.0158273381295</v>
       </c>
       <c r="K79" s="145" t="n">
-        <f>IF(D79="","",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>28.03255813953484</v>
+        <f>IF(D79="","",MAX(0,$G$50/D79-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>26.278613472858083</v>
       </c>
       <c r="L79" s="148" t="n">
         <f>IF(K79="","",$J$41+K79)</f>
-        <v>32.27498238195908</v>
+        <v>30.521037715282326</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3145,12 +3145,12 @@
         <v>42.46666666666667</v>
       </c>
       <c r="K80" s="145" t="n">
-        <f>IF(D80="","",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>47.775000000000006</v>
+        <f>IF(D80="","",MAX(0,$G$50/D80-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>42.8956228956229</v>
       </c>
       <c r="L80" s="148" t="n">
         <f>IF(K80="","",$J$41+K80)</f>
-        <v>52.01742424242425</v>
+        <v>47.13804713804714</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3188,12 +3188,12 @@
         <v>59.922137404580226</v>
       </c>
       <c r="K81" s="145" t="n">
-        <f>IF(D81="","",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>70.71891891891889</v>
+        <f>IF(D81="","",MAX(0,$G$50/D81-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>60.527411519778006</v>
       </c>
       <c r="L81" s="148" t="n">
         <f>IF(K81="","",$J$41+K81)</f>
-        <v>74.96134316134314</v>
+        <v>64.76983576220225</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3231,12 +3231,12 @@
         <v>98.2390243902441</v>
       </c>
       <c r="K82" s="145" t="n">
-        <f>IF(D82="","",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>129.92903225806486</v>
+        <f>IF(D82="","",MAX(0,$G$50/D82-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>99.23133776792334</v>
       </c>
       <c r="L82" s="148" t="n">
         <f>IF(K82="","",$J$41+K82)</f>
-        <v>134.1714565004891</v>
+        <v>103.47376201034757</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3274,12 +3274,12 @@
         <v>250.34545454545574</v>
       </c>
       <c r="K83" s="145" t="n">
-        <f>IF(D83="","",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-        <v>635.4923076923111</v>
+        <f>IF(D83="","",MAX(0,$G$50/D83-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>252.87419651056135</v>
       </c>
       <c r="L83" s="148" t="n">
         <f>IF(K83="","",$J$41+K83)</f>
-        <v>639.7347319347354</v>
+        <v>257.11662075298557</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3288,32 +3288,41 @@
       <c r="C84" s="133" t="n">
         <v>0.918</v>
       </c>
-      <c r="D84" s="145" t="str">
+      <c r="D84" s="145" t="n">
         <f>IF(C84&lt;$D$54,$D$45*(1-C84)-$G$51,"")</f>
-      </c>
-      <c r="E84" s="145" t="str">
+        <v>367346.9387754798</v>
+      </c>
+      <c r="E84" s="145" t="n">
         <f>IF(D84="","",$G$50/D84)</f>
-      </c>
-      <c r="F84" s="136" t="str">
+        <v>2333.3333333335268</v>
+      </c>
+      <c r="F84" s="136" t="n">
         <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
-      </c>
-      <c r="G84" s="136" t="str">
+        <v>0.0063518518518529046</v>
+      </c>
+      <c r="G84" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F84))),"",F84*$D$55)</f>
-      </c>
-      <c r="H84" s="145" t="str">
+        <v>15.763586756893186</v>
+      </c>
+      <c r="H84" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$45)</f>
-      </c>
-      <c r="I84" s="145" t="str">
+        <v>6351851.851852905</v>
+      </c>
+      <c r="I84" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H84))),"",H84*$D$55)</f>
-      </c>
-      <c r="J84" s="145" t="str">
+        <v>15763586756.893187</v>
+      </c>
+      <c r="J84" s="145" t="n">
         <f>IF(E84="","",MAX(0,E84-$G$44))</f>
-      </c>
-      <c r="K84" s="145" t="str">
-        <f>IF(D84="","",$G$50/($G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
-      </c>
-      <c r="L84" s="148" t="str">
+        <v>2329.133333333527</v>
+      </c>
+      <c r="K84" s="145" t="n">
+        <f>IF(D84="","",MAX(0,$G$50/D84-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
+        <v>2352.659932660128</v>
+      </c>
+      <c r="L84" s="148" t="n">
         <f>IF(K84="","",$J$41+K84)</f>
+        <v>2356.902356902552</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3344,7 +3353,7 @@
         <f>IF(E85="","",MAX(0,E85-$G$44))</f>
       </c>
       <c r="K85" s="146" t="str">
-        <f>IF(D85="","",$G$50/($G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D85="","",MAX(0,$G$50/D85-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L85" s="149" t="str">
         <f>IF(K85="","",$J$41+K85)</f>

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R4da12d0f94ab4c51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R82fe03f62c564d75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R6c70b30a17644365"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R3ed7d1eb6cff4109"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -163,7 +163,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="155">
+  <x:cellXfs count="158">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -620,6 +620,11 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1122,7 +1127,7 @@
         <v>Quote</v>
       </c>
       <c r="D7" s="51" t="str">
-        <v>ETH</v>
+        <v>USDG</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="35" t="str">
@@ -1254,7 +1259,7 @@
       </c>
       <c r="G12" s="152" t="n">
         <f>IF(AND(ISNUMBER($D$55),$D$55&gt;0),ROUNDUP($G$56/$D$55,0),"")</f>
-        <v>5</v>
+        <v>9997</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1344,11 +1349,11 @@
       </c>
       <c r="D18" s="121" t="n">
         <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
-        <v>357.57043967335574</v>
+        <v>52441.863942819284</v>
       </c>
       <c r="E18" s="62" t="str">
         <f>$D$7</f>
-        <v>ETH</v>
+        <v>USDG</v>
       </c>
       <c r="F18" s="107" t="str">
         <v>原生币 Gas 储备</v>
@@ -1365,7 +1370,7 @@
       </c>
       <c r="J18" s="121" t="n">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
-        <v>890123.4985942962</v>
+        <v>55192.5430935758</v>
       </c>
       <c r="K18" s="62" t="str">
         <v>USDT</v>
@@ -1380,7 +1385,7 @@
       </c>
       <c r="D19" s="122" t="n">
         <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$55&gt;0,$D$18*$D$55,"")),"")</f>
-        <v>887393.5946486422</v>
+        <v>52462.63914792186</v>
       </c>
       <c r="E19" s="106" t="str">
         <v>USDT</v>
@@ -1399,7 +1404,7 @@
         <v>原生币价格 / USDT</v>
       </c>
       <c r="J19" s="123" t="n">
-        <f>IF($D$7="ETH",$D$55,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+        <f>IF($D$7="ETH",$D$55,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$63,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$63,15,FALSE),""))</f>
         <v>2481.7308596853964</v>
       </c>
       <c r="K19" s="106"/>
@@ -1446,11 +1451,11 @@
       </c>
       <c r="D22" s="122" t="n">
         <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
-        <v>103.47376201034757</v>
+        <v>12456.885932495734</v>
       </c>
       <c r="E22" s="106" t="str">
         <f>$D$7</f>
-        <v>ETH</v>
+        <v>USDG</v>
       </c>
       <c r="F22" s="106"/>
       <c r="G22" s="106"/>
@@ -1470,11 +1475,11 @@
       </c>
       <c r="D23" s="122" t="n">
         <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
-        <v>4.242424242424242</v>
+        <v>510.7323232323232</v>
       </c>
       <c r="E23" s="106" t="str">
         <f>$D$7</f>
-        <v>ETH</v>
+        <v>USDG</v>
       </c>
       <c r="F23" s="106"/>
       <c r="G23" s="106"/>
@@ -1497,11 +1502,11 @@
       </c>
       <c r="D24" s="122" t="n">
         <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
-        <v>244.85425342058392</v>
+        <v>29477.24568709123</v>
       </c>
       <c r="E24" s="106" t="str">
         <f>$D$7</f>
-        <v>ETH</v>
+        <v>USDG</v>
       </c>
       <c r="F24" s="106"/>
       <c r="G24" s="106"/>
@@ -1524,11 +1529,11 @@
       </c>
       <c r="D25" s="122" t="n">
         <f>$G$12</f>
-        <v>5</v>
+        <v>9997</v>
       </c>
       <c r="E25" s="106" t="str">
         <f>$D$7</f>
-        <v>ETH</v>
+        <v>USDG</v>
       </c>
       <c r="F25" s="106"/>
       <c r="G25" s="106"/>
@@ -1555,7 +1560,7 @@
       </c>
       <c r="E26" s="106" t="str">
         <f>$D$7</f>
-        <v>ETH</v>
+        <v>USDG</v>
       </c>
       <c r="F26" s="106"/>
       <c r="G26" s="106"/>
@@ -1750,11 +1755,11 @@
       <c r="F37" s="127"/>
       <c r="G37" s="128" t="n">
         <f>E98</f>
-        <v>0.9333333333333333</v>
+        <v>112.3611111111111</v>
       </c>
       <c r="H37" s="127" t="str">
         <f>$D$7</f>
-        <v>ETH</v>
+        <v>USDG</v>
       </c>
       <c r="I37" s="106"/>
       <c r="J37" s="106"/>
@@ -1818,8 +1823,8 @@
         <v>Quote 名称</v>
       </c>
       <c r="D41" s="108" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</f>
-        <v>Ether</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,2,FALSE)</f>
+        <v>Global Dollar</v>
       </c>
       <c r="E41" s="107"/>
       <c r="F41" s="107" t="str">
@@ -1835,7 +1840,7 @@
       </c>
       <c r="J41" s="108" t="n">
         <f>IF(1-$G$41-$J$7&gt;0,$G$44/(1-$G$41-$J$7),"")</f>
-        <v>4.242424242424242</v>
+        <v>510.7323232323232</v>
       </c>
       <c r="K41" s="107"/>
       <c r="L41" s="107"/>
@@ -1847,8 +1852,8 @@
         <v>Quote 合约</v>
       </c>
       <c r="D42" s="109" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</f>
-        <v>​Native ETH</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,3,FALSE)</f>
+        <v>​0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="E42" s="107"/>
       <c r="F42" s="107" t="str">
@@ -1864,7 +1869,7 @@
       </c>
       <c r="J42" s="108" t="n">
         <f>IF($D$52&lt;$D$54,$D$45*(1-$D$52)-$G$51,"")</f>
-        <v>8367346.938775495</v>
+        <v>8367346.93877548</v>
       </c>
       <c r="K42" s="107"/>
       <c r="L42" s="107"/>
@@ -1888,7 +1893,7 @@
       </c>
       <c r="J43" s="108" t="n">
         <f>IF($J$42="","",$G$50/$J$42)</f>
-        <v>102.4390243902441</v>
+        <v>12332.317073170776</v>
       </c>
       <c r="K43" s="107"/>
       <c r="L43" s="107"/>
@@ -1900,16 +1905,16 @@
         <v>Decimals</v>
       </c>
       <c r="D44" s="110" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,4,FALSE)</f>
-        <v>18</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,4,FALSE)</f>
+        <v>6</v>
       </c>
       <c r="E44" s="107"/>
       <c r="F44" s="107" t="str">
         <v>毕业真实 Quote</v>
       </c>
       <c r="G44" s="108" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</f>
-        <v>4.2</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,6,FALSE)</f>
+        <v>505.625</v>
       </c>
       <c r="H44" s="107"/>
       <c r="I44" s="107" t="str">
@@ -1917,7 +1922,7 @@
       </c>
       <c r="J44" s="108" t="n">
         <f>IF($J$43="","",MAX(0,$J$43-$G$44))</f>
-        <v>98.2390243902441</v>
+        <v>11826.692073170776</v>
       </c>
       <c r="K44" s="107"/>
       <c r="L44" s="107"/>
@@ -1946,7 +1951,7 @@
       </c>
       <c r="J45" s="108" t="n">
         <f>IF($J$42="","",($J$43-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>99.23133776792334</v>
+        <v>11946.15360926341</v>
       </c>
       <c r="K45" s="107"/>
       <c r="L45" s="107"/>
@@ -1957,17 +1962,17 @@
       <c r="C46" s="107" t="str">
         <v>协议参数证据</v>
       </c>
-      <c r="D46" s="108" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</f>
-        <v>TIME 实币验证</v>
+      <c r="D46" s="108" t="n">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$63,12,FALSE)</f>
+        <v>68708148</v>
       </c>
       <c r="E46" s="107"/>
       <c r="F46" s="107" t="str">
         <v>phantom Quote</v>
       </c>
       <c r="G46" s="108" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</f>
-        <v>1.68</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,5,FALSE)</f>
+        <v>202.25</v>
       </c>
       <c r="H46" s="107"/>
       <c r="I46" s="107" t="str">
@@ -1975,7 +1980,7 @@
       </c>
       <c r="J46" s="108" t="n">
         <f>IF($J$43="","",$J$43/$J$42*$D$45)</f>
-        <v>12242.712671029196</v>
+        <v>1473862.2843545615</v>
       </c>
       <c r="K46" s="107"/>
       <c r="L46" s="107"/>
@@ -1995,7 +2000,7 @@
       </c>
       <c r="G47" s="114" t="n">
         <f>$G$46*$D$45</f>
-        <v>1680000000</v>
+        <v>202250000000</v>
       </c>
       <c r="H47" s="107"/>
       <c r="I47" s="107" t="str">
@@ -2023,7 +2028,7 @@
       </c>
       <c r="G48" s="108" t="n">
         <f>$D$45*$G$46*$G$44/($G$46+$G$44)^2</f>
-        <v>204081632.65306124</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="H48" s="107"/>
       <c r="I48" s="107" t="str">
@@ -2050,7 +2055,7 @@
       </c>
       <c r="G49" s="108" t="n">
         <f>$G$44</f>
-        <v>4.2</v>
+        <v>505.625</v>
       </c>
       <c r="H49" s="107"/>
       <c r="I49" s="107" t="str">
@@ -2073,7 +2078,7 @@
       </c>
       <c r="G50" s="114" t="n">
         <f>$G$48*$G$44</f>
-        <v>857142857.1428572</v>
+        <v>103188775510.20407</v>
       </c>
       <c r="H50" s="107"/>
       <c r="I50" s="107"/>
@@ -2097,7 +2102,7 @@
       </c>
       <c r="G51" s="108" t="n">
         <f>$D$45*$G$46^2/($G$46+$G$44)^2</f>
-        <v>81632653.06122448</v>
+        <v>81632653.06122449</v>
       </c>
       <c r="H51" s="107"/>
       <c r="I51" s="107" t="str">
@@ -2193,8 +2198,8 @@
         <v>Quote 价格 / USDT</v>
       </c>
       <c r="D55" s="108" t="n">
-        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
-        <v>2481.7308596853964</v>
+        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$63,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$63,15,FALSE),""))</f>
+        <v>1.0003961568781237</v>
       </c>
       <c r="E55" s="107"/>
       <c r="F55" s="107" t="str">
@@ -2210,7 +2215,7 @@
       </c>
       <c r="J55" s="108" t="n">
         <f>$G$48-MAX(0,($D$8-$G$43)*$D$45)</f>
-        <v>18367346.93877551</v>
+        <v>18367346.93877548</v>
       </c>
       <c r="K55" s="107"/>
       <c r="L55" s="107"/>
@@ -2222,8 +2227,8 @@
         <v>行情时间 / UTC</v>
       </c>
       <c r="D56" s="150" t="n">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
-        <v>46283.229076828706</v>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$63,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$63,16,FALSE))</f>
+        <v>46285.27349457176</v>
       </c>
       <c r="E56" s="107"/>
       <c r="F56" s="107" t="str">
@@ -2238,7 +2243,7 @@
       </c>
       <c r="J56" s="108" t="n">
         <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)</f>
-        <v>18367346.93877551</v>
+        <v>18367346.93877548</v>
       </c>
       <c r="K56" s="107"/>
       <c r="L56" s="107"/>
@@ -2308,23 +2313,23 @@
       </c>
       <c r="E59" s="144" t="n">
         <f>$G$47/D59</f>
-        <v>1.68</v>
+        <v>202.25</v>
       </c>
       <c r="F59" s="135" t="n">
         <f>IF(OR(D59="",E59=""),"",E59/D59)</f>
-        <v>1.68e-9</v>
+        <v>2.0225e-7</v>
       </c>
       <c r="G59" s="135" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F59))),"",F59*$D$55)</f>
-        <v>0.000004169307844271466</v>
+        <v>2.0233012272860051e-7</v>
       </c>
       <c r="H59" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F59)),"",F59*$D$45)</f>
-        <v>1.68</v>
+        <v>202.25</v>
       </c>
       <c r="I59" s="144" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H59))),"",H59*$D$55)</f>
-        <v>4169.307844271466</v>
+        <v>202.33012272860051</v>
       </c>
       <c r="J59" s="144" t="n">
         <f>0</f>
@@ -2351,35 +2356,35 @@
       </c>
       <c r="E60" s="145" t="n">
         <f>$G$47/D60</f>
-        <v>1.8666666666666667</v>
+        <v>224.72222222222223</v>
       </c>
       <c r="F60" s="136" t="n">
         <f>IF(OR(D60="",E60=""),"",E60/D60)</f>
-        <v>2.074074074074074e-9</v>
+        <v>2.496913580246914e-7</v>
       </c>
       <c r="G60" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F60))),"",F60*$D$55)</f>
-        <v>0.000005147293634903044</v>
+        <v>2.497902749735809e-7</v>
       </c>
       <c r="H60" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F60)),"",F60*$D$45)</f>
-        <v>2.074074074074074</v>
+        <v>249.6913580246914</v>
       </c>
       <c r="I60" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H60))),"",H60*$D$55)</f>
-        <v>5147.293634903044</v>
+        <v>249.79027497358092</v>
       </c>
       <c r="J60" s="145" t="n">
         <f>E60-E59</f>
-        <v>0.18666666666666676</v>
+        <v>22.47222222222223</v>
       </c>
       <c r="K60" s="145" t="n">
         <f>J60/(1-$G$41-$J$7)</f>
-        <v>0.18855218855218864</v>
+        <v>22.69921436588104</v>
       </c>
       <c r="L60" s="148" t="n">
         <f>SUM($K$59:K60)</f>
-        <v>0.18855218855218864</v>
+        <v>22.69921436588104</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2394,35 +2399,35 @@
       </c>
       <c r="E61" s="145" t="n">
         <f>$G$47/D61</f>
-        <v>2.1</v>
+        <v>252.8125</v>
       </c>
       <c r="F61" s="136" t="n">
         <f>IF(OR(D61="",E61=""),"",E61/D61)</f>
-        <v>2.625e-9</v>
+        <v>3.16015625e-7</v>
       </c>
       <c r="G61" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F61))),"",F61*$D$55)</f>
-        <v>0.0000065145435066741655</v>
+        <v>3.161408167634383e-7</v>
       </c>
       <c r="H61" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F61)),"",F61*$D$45)</f>
-        <v>2.625</v>
+        <v>316.015625</v>
       </c>
       <c r="I61" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H61))),"",H61*$D$55)</f>
-        <v>6514.543506674166</v>
+        <v>316.1408167634383</v>
       </c>
       <c r="J61" s="145" t="n">
         <f>E61-E60</f>
-        <v>0.2333333333333334</v>
+        <v>28.09027777777777</v>
       </c>
       <c r="K61" s="145" t="n">
         <f>J61/(1-$G$41-$J$7)</f>
-        <v>0.23569023569023576</v>
+        <v>28.374017957351285</v>
       </c>
       <c r="L61" s="148" t="n">
         <f>SUM($K$59:K61)</f>
-        <v>0.4242424242424244</v>
+        <v>51.073232323232325</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2437,35 +2442,35 @@
       </c>
       <c r="E62" s="145" t="n">
         <f>$G$47/D62</f>
-        <v>2.4</v>
+        <v>288.92857142857144</v>
       </c>
       <c r="F62" s="136" t="n">
         <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
-        <v>3.4285714285714283e-9</v>
+        <v>4.1275510204081637e-7</v>
       </c>
       <c r="G62" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F62))),"",F62*$D$55)</f>
-        <v>0.000008508791518921358</v>
+        <v>4.1291861781347046e-7</v>
       </c>
       <c r="H62" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$45)</f>
-        <v>3.4285714285714284</v>
+        <v>412.7551020408164</v>
       </c>
       <c r="I62" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H62))),"",H62*$D$55)</f>
-        <v>8508.791518921358</v>
+        <v>412.91861781347046</v>
       </c>
       <c r="J62" s="145" t="n">
         <f>E62-E61</f>
-        <v>0.2999999999999998</v>
+        <v>36.116071428571445</v>
       </c>
       <c r="K62" s="145" t="n">
         <f>J62/(1-$G$41-$J$7)</f>
-        <v>0.30303030303030287</v>
+        <v>36.480880230880246</v>
       </c>
       <c r="L62" s="148" t="n">
         <f>SUM($K$59:K62)</f>
-        <v>0.7272727272727273</v>
+        <v>87.55411255411258</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2480,35 +2485,35 @@
       </c>
       <c r="E63" s="145" t="n">
         <f>$G$47/D63</f>
-        <v>2.8</v>
+        <v>337.0833333333333</v>
       </c>
       <c r="F63" s="136" t="n">
         <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
-        <v>4.666666666666666e-9</v>
+        <v>5.618055555555556e-7</v>
       </c>
       <c r="G63" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F63))),"",F63*$D$55)</f>
-        <v>0.00001158141067853185</v>
+        <v>5.62028118690557e-7</v>
       </c>
       <c r="H63" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$45)</f>
-        <v>4.666666666666666</v>
+        <v>561.8055555555555</v>
       </c>
       <c r="I63" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H63))),"",H63*$D$55)</f>
-        <v>11581.410678531849</v>
+        <v>562.028118690557</v>
       </c>
       <c r="J63" s="145" t="n">
         <f>E63-E62</f>
-        <v>0.3999999999999999</v>
+        <v>48.15476190476187</v>
       </c>
       <c r="K63" s="145" t="n">
         <f>J63/(1-$G$41-$J$7)</f>
-        <v>0.404040404040404</v>
+        <v>48.64117364117361</v>
       </c>
       <c r="L63" s="148" t="n">
         <f>SUM($K$59:K63)</f>
-        <v>1.1313131313131313</v>
+        <v>136.1952861952862</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2523,35 +2528,35 @@
       </c>
       <c r="E64" s="145" t="n">
         <f>$G$47/D64</f>
-        <v>3.36</v>
+        <v>404.5</v>
       </c>
       <c r="F64" s="136" t="n">
         <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
-        <v>6.72e-9</v>
+        <v>8.09e-7</v>
       </c>
       <c r="G64" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F64))),"",F64*$D$55)</f>
-        <v>0.000016677231377085863</v>
+        <v>8.093204909144021e-7</v>
       </c>
       <c r="H64" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$45)</f>
-        <v>6.72</v>
+        <v>809</v>
       </c>
       <c r="I64" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H64))),"",H64*$D$55)</f>
-        <v>16677.231377085864</v>
+        <v>809.3204909144021</v>
       </c>
       <c r="J64" s="145" t="n">
         <f>E64-E63</f>
-        <v>0.56</v>
+        <v>67.41666666666669</v>
       </c>
       <c r="K64" s="145" t="n">
         <f>J64/(1-$G$41-$J$7)</f>
-        <v>0.5656565656565657</v>
+        <v>68.09764309764311</v>
       </c>
       <c r="L64" s="148" t="n">
         <f>SUM($K$59:K64)</f>
-        <v>1.696969696969697</v>
+        <v>204.29292929292933</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2566,35 +2571,35 @@
       </c>
       <c r="E65" s="145" t="n">
         <f>$G$47/D65</f>
-        <v>4.2</v>
+        <v>505.625</v>
       </c>
       <c r="F65" s="136" t="n">
         <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
-        <v>1.05e-8</v>
+        <v>0.0000012640625</v>
       </c>
       <c r="G65" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F65))),"",F65*$D$55)</f>
-        <v>0.000026058174026696662</v>
+        <v>0.0000012645632670537531</v>
       </c>
       <c r="H65" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$45)</f>
-        <v>10.5</v>
+        <v>1264.0625</v>
       </c>
       <c r="I65" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H65))),"",H65*$D$55)</f>
-        <v>26058.174026696663</v>
+        <v>1264.5632670537532</v>
       </c>
       <c r="J65" s="145" t="n">
         <f>E65-E64</f>
-        <v>0.8400000000000003</v>
+        <v>101.125</v>
       </c>
       <c r="K65" s="145" t="n">
         <f>J65/(1-$G$41-$J$7)</f>
-        <v>0.8484848484848488</v>
+        <v>102.14646464646465</v>
       </c>
       <c r="L65" s="148" t="n">
         <f>SUM($K$59:K65)</f>
-        <v>2.545454545454546</v>
+        <v>306.439393939394</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2609,35 +2614,35 @@
       </c>
       <c r="E66" s="145" t="n">
         <f>$G$47/D66</f>
-        <v>5.599999999999999</v>
+        <v>674.1666666666665</v>
       </c>
       <c r="F66" s="136" t="n">
         <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
-        <v>1.866666666666666e-8</v>
+        <v>0.0000022472222222222214</v>
       </c>
       <c r="G66" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F66))),"",F66*$D$55)</f>
-        <v>0.000046325642714127376</v>
+        <v>0.000002248112474762227</v>
       </c>
       <c r="H66" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$45)</f>
-        <v>18.666666666666657</v>
+        <v>2247.2222222222213</v>
       </c>
       <c r="I66" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H66))),"",H66*$D$55)</f>
-        <v>46325.642714127374</v>
+        <v>2248.112474762227</v>
       </c>
       <c r="J66" s="145" t="n">
         <f>E66-E65</f>
-        <v>1.3999999999999986</v>
+        <v>168.54166666666652</v>
       </c>
       <c r="K66" s="145" t="n">
         <f>J66/(1-$G$41-$J$7)</f>
-        <v>1.4141414141414128</v>
+        <v>170.2441077441076</v>
       </c>
       <c r="L66" s="148" t="n">
         <f>SUM($K$59:K66)</f>
-        <v>3.9595959595959584</v>
+        <v>476.6835016835016</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2653,35 +2658,35 @@
       </c>
       <c r="E67" s="146" t="n">
         <f>$G$47/D67</f>
-        <v>5.880000000000001</v>
+        <v>707.8750000000001</v>
       </c>
       <c r="F67" s="137" t="n">
         <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
-        <v>2.0580000000000006e-8</v>
+        <v>0.0000024775625000000006</v>
       </c>
       <c r="G67" s="137" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F67))),"",F67*$D$55)</f>
-        <v>0.00005107402109232547</v>
+        <v>0.0000024785440034253568</v>
       </c>
       <c r="H67" s="146" t="n">
         <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$45)</f>
-        <v>20.580000000000005</v>
+        <v>2477.5625000000005</v>
       </c>
       <c r="I67" s="146" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H67))),"",H67*$D$55)</f>
-        <v>51074.02109232547</v>
+        <v>2478.5440034253565</v>
       </c>
       <c r="J67" s="146" t="n">
         <f>E67-E66</f>
-        <v>0.280000000000002</v>
+        <v>33.7083333333336</v>
       </c>
       <c r="K67" s="146" t="n">
         <f>J67/(1-$G$41-$J$7)</f>
-        <v>0.28282828282828487</v>
+        <v>34.04882154882182</v>
       </c>
       <c r="L67" s="149" t="n">
         <f>SUM($K$59:K67)</f>
-        <v>4.242424242424243</v>
+        <v>510.73232323232344</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2774,27 +2779,27 @@
       </c>
       <c r="D72" s="144" t="n">
         <f>$G$48</f>
-        <v>204081632.65306124</v>
+        <v>204081632.6530612</v>
       </c>
       <c r="E72" s="144" t="n">
         <f>$G$44</f>
-        <v>4.2</v>
+        <v>505.625</v>
       </c>
       <c r="F72" s="135" t="n">
         <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
-        <v>2.058e-8</v>
+        <v>0.0000024775625</v>
       </c>
       <c r="G72" s="135" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F72))),"",F72*$D$55)</f>
-        <v>0.000051074021092325456</v>
+        <v>0.0000024785440034253564</v>
       </c>
       <c r="H72" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$45)</f>
-        <v>20.58</v>
+        <v>2477.5625</v>
       </c>
       <c r="I72" s="144" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H72))),"",H72*$D$55)</f>
-        <v>51074.021092325456</v>
+        <v>2478.544003425356</v>
       </c>
       <c r="J72" s="144" t="n">
         <f>0</f>
@@ -2806,7 +2811,7 @@
       </c>
       <c r="L72" s="147" t="n">
         <f>$J$41</f>
-        <v>4.242424242424242</v>
+        <v>510.7323232323232</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2817,39 +2822,39 @@
       </c>
       <c r="D73" s="145" t="n">
         <f>IF(C73&lt;$D$54,$D$45*(1-C73)-$G$51,"")</f>
-        <v>168367346.93877554</v>
+        <v>168367346.9387755</v>
       </c>
       <c r="E73" s="145" t="n">
         <f>IF(D73="","",$G$50/D73)</f>
-        <v>5.09090909090909</v>
+        <v>612.8787878787878</v>
       </c>
       <c r="F73" s="136" t="n">
         <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
-        <v>3.023691460055095e-8</v>
+        <v>0.000003640128558310376</v>
       </c>
       <c r="G73" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F73))),"",F73*$D$55)</f>
-        <v>0.00007503988406585923</v>
+        <v>0.000003641570620276005</v>
       </c>
       <c r="H73" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$45)</f>
-        <v>30.236914600550953</v>
+        <v>3640.128558310376</v>
       </c>
       <c r="I73" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H73))),"",H73*$D$55)</f>
-        <v>75039.88406585922</v>
+        <v>3641.570620276005</v>
       </c>
       <c r="J73" s="145" t="n">
         <f>IF(E73="","",MAX(0,E73-$G$44))</f>
-        <v>0.8909090909090898</v>
+        <v>107.25378787878776</v>
       </c>
       <c r="K73" s="145" t="n">
         <f>IF(D73="","",MAX(0,$G$50/D73-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>0.8999081726354442</v>
+        <v>108.33715947352299</v>
       </c>
       <c r="L73" s="148" t="n">
         <f>IF(K73="","",$J$41+K73)</f>
-        <v>5.142332415059687</v>
+        <v>619.0694827058462</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2860,39 +2865,39 @@
       </c>
       <c r="D74" s="145" t="n">
         <f>IF(C74&lt;$D$54,$D$45*(1-C74)-$G$51,"")</f>
-        <v>118367346.9387755</v>
+        <v>118367346.93877548</v>
       </c>
       <c r="E74" s="145" t="n">
         <f>IF(D74="","",$G$50/D74)</f>
-        <v>7.241379310344829</v>
+        <v>871.7672413793105</v>
       </c>
       <c r="F74" s="136" t="n">
         <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
-        <v>6.117717003567184e-8</v>
+        <v>0.00000736493014268728</v>
       </c>
       <c r="G74" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F74))),"",F74*$D$55)</f>
-        <v>0.00015182527078574755</v>
+        <v>0.000007367847810420206</v>
       </c>
       <c r="H74" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$45)</f>
-        <v>61.17717003567184</v>
+        <v>7364.93014268728</v>
       </c>
       <c r="I74" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H74))),"",H74*$D$55)</f>
-        <v>151825.27078574756</v>
+        <v>7367.847810420206</v>
       </c>
       <c r="J74" s="145" t="n">
         <f>IF(E74="","",MAX(0,E74-$G$44))</f>
-        <v>3.041379310344829</v>
+        <v>366.14224137931046</v>
       </c>
       <c r="K74" s="145" t="n">
         <f>IF(D74="","",MAX(0,$G$50/D74-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>3.072100313479625</v>
+        <v>369.84064785788934</v>
       </c>
       <c r="L74" s="148" t="n">
         <f>IF(K74="","",$J$41+K74)</f>
-        <v>7.314524555903867</v>
+        <v>880.5729710902126</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2903,39 +2908,39 @@
       </c>
       <c r="D75" s="145" t="n">
         <f>IF(C75&lt;$D$54,$D$45*(1-C75)-$G$51,"")</f>
-        <v>98367346.93877558</v>
+        <v>98367346.93877557</v>
       </c>
       <c r="E75" s="145" t="n">
         <f>IF(D75="","",$G$50/D75)</f>
-        <v>8.713692946058085</v>
+        <v>1049.014522821576</v>
       </c>
       <c r="F75" s="136" t="n">
         <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
-        <v>8.858318555121283e-8</v>
+        <v>0.000010664255522459999</v>
       </c>
       <c r="G75" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F75))),"",F75*$D$55)</f>
-        <v>0.00021983962523168242</v>
+        <v>0.000010668480240635289</v>
       </c>
       <c r="H75" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$45)</f>
-        <v>88.58318555121284</v>
+        <v>10664.255522459998</v>
       </c>
       <c r="I75" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H75))),"",H75*$D$55)</f>
-        <v>219839.6252316824</v>
+        <v>10668.480240635288</v>
       </c>
       <c r="J75" s="145" t="n">
         <f>IF(E75="","",MAX(0,E75-$G$44))</f>
-        <v>4.513692946058085</v>
+        <v>543.3895228215761</v>
       </c>
       <c r="K75" s="145" t="n">
         <f>IF(D75="","",MAX(0,$G$50/D75-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>4.559285804099076</v>
+        <v>548.8783058803799</v>
       </c>
       <c r="L75" s="148" t="n">
         <f>IF(K75="","",$J$41+K75)</f>
-        <v>8.801710046523318</v>
+        <v>1059.610629112703</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2946,39 +2951,39 @@
       </c>
       <c r="D76" s="145" t="n">
         <f>IF(C76&lt;$D$54,$D$45*(1-C76)-$G$51,"")</f>
-        <v>78367346.93877555</v>
+        <v>78367346.93877554</v>
       </c>
       <c r="E76" s="145" t="n">
         <f>IF(D76="","",$G$50/D76)</f>
-        <v>10.937499999999995</v>
+        <v>1316.7317708333328</v>
       </c>
       <c r="F76" s="136" t="n">
         <f>IF(OR(D76="",E76=""),"",E76/D76)</f>
-        <v>1.3956705729166652e-7</v>
+        <v>0.000016802046034071167</v>
       </c>
       <c r="G76" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F76))),"",F76*$D$55)</f>
-        <v>0.00034636787307620854</v>
+        <v>0.000016808702280174114</v>
       </c>
       <c r="H76" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F76)),"",F76*$D$45)</f>
-        <v>139.56705729166652</v>
+        <v>16802.046034071165</v>
       </c>
       <c r="I76" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H76))),"",H76*$D$55)</f>
-        <v>346367.8730762085</v>
+        <v>16808.70228017411</v>
       </c>
       <c r="J76" s="145" t="n">
         <f>IF(E76="","",MAX(0,E76-$G$44))</f>
-        <v>6.7374999999999945</v>
+        <v>811.1067708333328</v>
       </c>
       <c r="K76" s="145" t="n">
         <f>IF(D76="","",MAX(0,$G$50/D76-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>6.80555555555555</v>
+        <v>819.299768518518</v>
       </c>
       <c r="L76" s="148" t="n">
         <f>IF(K76="","",$J$41+K76)</f>
-        <v>11.047979797979792</v>
+        <v>1330.0320917508411</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2989,39 +2994,39 @@
       </c>
       <c r="D77" s="145" t="n">
         <f>IF(C77&lt;$D$54,$D$45*(1-C77)-$G$51,"")</f>
-        <v>58367346.938775524</v>
+        <v>58367346.93877551</v>
       </c>
       <c r="E77" s="145" t="n">
         <f>IF(D77="","",$G$50/D77)</f>
-        <v>14.685314685314683</v>
+        <v>1767.9195804195804</v>
       </c>
       <c r="F77" s="136" t="n">
         <f>IF(OR(D77="",E77=""),"",E77/D77)</f>
-        <v>2.5160154530783893e-7</v>
+        <v>0.000030289531272922882</v>
       </c>
       <c r="G77" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F77))),"",F77*$D$55)</f>
-        <v>0.0006244073193349972</v>
+        <v>0.000030301530679071792</v>
       </c>
       <c r="H77" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F77)),"",F77*$D$45)</f>
-        <v>251.60154530783893</v>
+        <v>30289.531272922883</v>
       </c>
       <c r="I77" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H77))),"",H77*$D$55)</f>
-        <v>624407.3193349973</v>
+        <v>30301.53067907179</v>
       </c>
       <c r="J77" s="145" t="n">
         <f>IF(E77="","",MAX(0,E77-$G$44))</f>
-        <v>10.485314685314684</v>
+        <v>1262.2945804195804</v>
       </c>
       <c r="K77" s="145" t="n">
         <f>IF(D77="","",MAX(0,$G$50/D77-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>10.591226954863318</v>
+        <v>1275.0450307268488</v>
       </c>
       <c r="L77" s="148" t="n">
         <f>IF(K77="","",$J$41+K77)</f>
-        <v>14.83365119728756</v>
+        <v>1785.7773539591722</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3032,39 +3037,39 @@
       </c>
       <c r="D78" s="145" t="n">
         <f>IF(C78&lt;$D$54,$D$45*(1-C78)-$G$51,"")</f>
-        <v>38367346.938775524</v>
+        <v>38367346.93877551</v>
       </c>
       <c r="E78" s="145" t="n">
         <f>IF(D78="","",$G$50/D78)</f>
-        <v>22.340425531914885</v>
+        <v>2689.4946808510635</v>
       </c>
       <c r="F78" s="136" t="n">
         <f>IF(OR(D78="",E78=""),"",E78/D78)</f>
-        <v>5.822770484382069e-7</v>
+        <v>0.00007009853157537346</v>
       </c>
       <c r="G78" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F78))),"",F78*$D$55)</f>
-        <v>0.0014450549199956262</v>
+        <v>0.00007012630159080341</v>
       </c>
       <c r="H78" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F78)),"",F78*$D$45)</f>
-        <v>582.2770484382069</v>
+        <v>70098.53157537346</v>
       </c>
       <c r="I78" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H78))),"",H78*$D$55)</f>
-        <v>1445054.9199956262</v>
+        <v>70126.30159080341</v>
       </c>
       <c r="J78" s="145" t="n">
         <f>IF(E78="","",MAX(0,E78-$G$44))</f>
-        <v>18.140425531914886</v>
+        <v>2183.8696808510635</v>
       </c>
       <c r="K78" s="145" t="n">
         <f>IF(D78="","",MAX(0,$G$50/D78-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>18.32366215344938</v>
+        <v>2205.92897055663</v>
       </c>
       <c r="L78" s="148" t="n">
         <f>IF(K78="","",$J$41+K78)</f>
-        <v>22.566086395873622</v>
+        <v>2716.661293788953</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3075,39 +3080,39 @@
       </c>
       <c r="D79" s="145" t="n">
         <f>IF(C79&lt;$D$54,$D$45*(1-C79)-$G$51,"")</f>
-        <v>28367346.93877551</v>
+        <v>28367346.938775495</v>
       </c>
       <c r="E79" s="145" t="n">
         <f>IF(D79="","",$G$50/D79)</f>
-        <v>30.2158273381295</v>
+        <v>3637.5899280575554</v>
       </c>
       <c r="F79" s="136" t="n">
         <f>IF(OR(D79="",E79=""),"",E79/D79)</f>
-        <v>0.0000010651622586822629</v>
+        <v>0.00012823158739195707</v>
       </c>
       <c r="G79" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F79))),"",F79*$D$55)</f>
-        <v>0.0026434460479439707</v>
+        <v>0.0001282823872172951</v>
       </c>
       <c r="H79" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F79)),"",F79*$D$45)</f>
-        <v>1065.162258682263</v>
+        <v>128231.58739195707</v>
       </c>
       <c r="I79" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H79))),"",H79*$D$55)</f>
-        <v>2643446.047943971</v>
+        <v>128282.38721729511</v>
       </c>
       <c r="J79" s="145" t="n">
         <f>IF(E79="","",MAX(0,E79-$G$44))</f>
-        <v>26.0158273381295</v>
+        <v>3131.9649280575554</v>
       </c>
       <c r="K79" s="145" t="n">
         <f>IF(D79="","",MAX(0,$G$50/D79-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>26.278613472858083</v>
+        <v>3163.600937431874</v>
       </c>
       <c r="L79" s="148" t="n">
         <f>IF(K79="","",$J$41+K79)</f>
-        <v>30.521037715282326</v>
+        <v>3674.3332606641975</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3118,39 +3123,39 @@
       </c>
       <c r="D80" s="145" t="n">
         <f>IF(C80&lt;$D$54,$D$45*(1-C80)-$G$51,"")</f>
-        <v>18367346.93877551</v>
+        <v>18367346.938775495</v>
       </c>
       <c r="E80" s="145" t="n">
         <f>IF(D80="","",$G$50/D80)</f>
-        <v>46.66666666666667</v>
+        <v>5618.055555555559</v>
       </c>
       <c r="F80" s="136" t="n">
         <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
-        <v>0.000002540740740740741</v>
+        <v>0.00030587191358024735</v>
       </c>
       <c r="G80" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F80))),"",F80*$D$55)</f>
-        <v>0.0063054347027562295</v>
+        <v>0.00030599308684263704</v>
       </c>
       <c r="H80" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$45)</f>
-        <v>2540.740740740741</v>
+        <v>305871.9135802474</v>
       </c>
       <c r="I80" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H80))),"",H80*$D$55)</f>
-        <v>6305434.70275623</v>
+        <v>305993.08684263704</v>
       </c>
       <c r="J80" s="145" t="n">
         <f>IF(E80="","",MAX(0,E80-$G$44))</f>
-        <v>42.46666666666667</v>
+        <v>5112.430555555559</v>
       </c>
       <c r="K80" s="145" t="n">
         <f>IF(D80="","",MAX(0,$G$50/D80-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>42.8956228956229</v>
+        <v>5164.071268237939</v>
       </c>
       <c r="L80" s="148" t="n">
         <f>IF(K80="","",$J$41+K80)</f>
-        <v>47.13804713804714</v>
+        <v>5674.803591470262</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3161,39 +3166,39 @@
       </c>
       <c r="D81" s="145" t="n">
         <f>IF(C81&lt;$D$54,$D$45*(1-C81)-$G$51,"")</f>
-        <v>13367346.938775495</v>
+        <v>13367346.93877548</v>
       </c>
       <c r="E81" s="145" t="n">
         <f>IF(D81="","",$G$50/D81)</f>
-        <v>64.12213740458023</v>
+        <v>7719.465648854979</v>
       </c>
       <c r="F81" s="136" t="n">
         <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
-        <v>0.000004796923256220511</v>
+        <v>0.000577486743196786</v>
       </c>
       <c r="G81" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F81))),"",F81*$D$55)</f>
-        <v>0.011904672476504998</v>
+        <v>0.0005777155185421286</v>
       </c>
       <c r="H81" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$45)</f>
-        <v>4796.923256220511</v>
+        <v>577486.743196786</v>
       </c>
       <c r="I81" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H81))),"",H81*$D$55)</f>
-        <v>11904672.476504998</v>
+        <v>577715.5185421287</v>
       </c>
       <c r="J81" s="145" t="n">
         <f>IF(E81="","",MAX(0,E81-$G$44))</f>
-        <v>59.922137404580226</v>
+        <v>7213.840648854979</v>
       </c>
       <c r="K81" s="145" t="n">
         <f>IF(D81="","",MAX(0,$G$50/D81-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>60.527411519778006</v>
+        <v>7286.70772611614</v>
       </c>
       <c r="L81" s="148" t="n">
         <f>IF(K81="","",$J$41+K81)</f>
-        <v>64.76983576220225</v>
+        <v>7797.440049348464</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3204,39 +3209,39 @@
       </c>
       <c r="D82" s="145" t="n">
         <f>IF(C82&lt;$D$54,$D$45*(1-C82)-$G$51,"")</f>
-        <v>8367346.938775495</v>
+        <v>8367346.93877548</v>
       </c>
       <c r="E82" s="145" t="n">
         <f>IF(D82="","",$G$50/D82)</f>
-        <v>102.4390243902441</v>
+        <v>12332.317073170776</v>
       </c>
       <c r="F82" s="136" t="n">
         <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
-        <v>0.000012242712671029196</v>
+        <v>0.0014738622843545614</v>
       </c>
       <c r="G82" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F82))),"",F82*$D$55)</f>
-        <v>0.03038311784195458</v>
+        <v>0.0014744461650359156</v>
       </c>
       <c r="H82" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$45)</f>
-        <v>12242.712671029196</v>
+        <v>1473862.2843545615</v>
       </c>
       <c r="I82" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H82))),"",H82*$D$55)</f>
-        <v>30383117.84195458</v>
+        <v>1474446.1650359156</v>
       </c>
       <c r="J82" s="145" t="n">
         <f>IF(E82="","",MAX(0,E82-$G$44))</f>
-        <v>98.2390243902441</v>
+        <v>11826.692073170776</v>
       </c>
       <c r="K82" s="145" t="n">
         <f>IF(D82="","",MAX(0,$G$50/D82-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>99.23133776792334</v>
+        <v>11946.15360926341</v>
       </c>
       <c r="L82" s="148" t="n">
         <f>IF(K82="","",$J$41+K82)</f>
-        <v>103.47376201034757</v>
+        <v>12456.885932495734</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3247,39 +3252,39 @@
       </c>
       <c r="D83" s="145" t="n">
         <f>IF(C83&lt;$D$54,$D$45*(1-C83)-$G$51,"")</f>
-        <v>3367346.9387754947</v>
+        <v>3367346.93877548</v>
       </c>
       <c r="E83" s="145" t="n">
         <f>IF(D83="","",$G$50/D83)</f>
-        <v>254.54545454545573</v>
+        <v>30643.93939393967</v>
       </c>
       <c r="F83" s="136" t="n">
         <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
-        <v>0.00007559228650137811</v>
+        <v>0.009100321395776104</v>
       </c>
       <c r="G83" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F83))),"",F83*$D$55)</f>
-        <v>0.18759971016464988</v>
+        <v>0.009103926550690178</v>
       </c>
       <c r="H83" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$45)</f>
-        <v>75592.28650137811</v>
+        <v>9100321.395776104</v>
       </c>
       <c r="I83" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H83))),"",H83*$D$55)</f>
-        <v>187599710.16464987</v>
+        <v>9103926.550690176</v>
       </c>
       <c r="J83" s="145" t="n">
         <f>IF(E83="","",MAX(0,E83-$G$44))</f>
-        <v>250.34545454545574</v>
+        <v>30138.31439393967</v>
       </c>
       <c r="K83" s="145" t="n">
         <f>IF(D83="","",MAX(0,$G$50/D83-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>252.87419651056135</v>
+        <v>30442.74181206027</v>
       </c>
       <c r="L83" s="148" t="n">
         <f>IF(K83="","",$J$41+K83)</f>
-        <v>257.11662075298557</v>
+        <v>30953.474135292592</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3290,39 +3295,39 @@
       </c>
       <c r="D84" s="145" t="n">
         <f>IF(C84&lt;$D$54,$D$45*(1-C84)-$G$51,"")</f>
-        <v>367346.9387754798</v>
+        <v>367346.9387754649</v>
       </c>
       <c r="E84" s="145" t="n">
         <f>IF(D84="","",$G$50/D84)</f>
-        <v>2333.3333333335268</v>
+        <v>280902.7777778124</v>
       </c>
       <c r="F84" s="136" t="n">
         <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
-        <v>0.0063518518518529046</v>
+        <v>0.7646797839508058</v>
       </c>
       <c r="G84" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F84))),"",F84*$D$55)</f>
-        <v>15.763586756893186</v>
+        <v>0.76498271710678</v>
       </c>
       <c r="H84" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$45)</f>
-        <v>6351851.851852905</v>
+        <v>764679783.9508058</v>
       </c>
       <c r="I84" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H84))),"",H84*$D$55)</f>
-        <v>15763586756.893187</v>
+        <v>764982717.10678</v>
       </c>
       <c r="J84" s="145" t="n">
         <f>IF(E84="","",MAX(0,E84-$G$44))</f>
-        <v>2329.133333333527</v>
+        <v>280397.1527778124</v>
       </c>
       <c r="K84" s="145" t="n">
         <f>IF(D84="","",MAX(0,$G$50/D84-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>2352.659932660128</v>
+        <v>283229.44725031557</v>
       </c>
       <c r="L84" s="148" t="n">
         <f>IF(K84="","",$J$41+K84)</f>
-        <v>2356.902356902552</v>
+        <v>283740.1795735479</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3441,27 +3446,27 @@
       </c>
       <c r="D90" s="144" t="n">
         <f>$D$45*(1-C90)-$G$51</f>
-        <v>204081632.6530612</v>
+        <v>204081632.65306118</v>
       </c>
       <c r="E90" s="144" t="n">
         <f>$G$50/D90</f>
-        <v>4.2</v>
+        <v>505.62500000000006</v>
       </c>
       <c r="F90" s="135" t="n">
         <f>IF(OR(D90="",E90=""),"",E90/D90)</f>
-        <v>2.0580000000000003e-8</v>
+        <v>0.000002477562500000001</v>
       </c>
       <c r="G90" s="135" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F90))),"",F90*$D$55)</f>
-        <v>0.00005107402109232546</v>
+        <v>0.000002478544003425357</v>
       </c>
       <c r="H90" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F90)),"",F90*$D$45)</f>
-        <v>20.580000000000002</v>
+        <v>2477.562500000001</v>
       </c>
       <c r="I90" s="144" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H90))),"",H90*$D$55)</f>
-        <v>51074.02109232546</v>
+        <v>2478.544003425357</v>
       </c>
       <c r="J90" s="132" t="n">
         <f>IF($H$90&gt;0,1-H90/$H$90,0)</f>
@@ -3478,27 +3483,27 @@
       </c>
       <c r="D91" s="145" t="n">
         <f>$D$45*(1-C91)-$G$51</f>
-        <v>218367346.9387756</v>
+        <v>218367346.93877557</v>
       </c>
       <c r="E91" s="145" t="n">
         <f>$G$50/D91</f>
-        <v>3.9252336448598117</v>
+        <v>472.54672897196247</v>
       </c>
       <c r="F91" s="136" t="n">
         <f>IF(OR(D91="",E91=""),"",E91/D91)</f>
-        <v>1.797536902786268e-8</v>
+        <v>0.0000021639990392173977</v>
       </c>
       <c r="G91" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F91))),"",F91*$D$55)</f>
-        <v>0.0000446100280306799</v>
+        <v>0.000002164856322321037</v>
       </c>
       <c r="H91" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F91)),"",F91*$D$45)</f>
-        <v>17.97536902786268</v>
+        <v>2163.9990392173977</v>
       </c>
       <c r="I91" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H91))),"",H91*$D$55)</f>
-        <v>44610.028030679896</v>
+        <v>2164.8563223210367</v>
       </c>
       <c r="J91" s="133" t="n">
         <f>IF($H$90&gt;0,1-H91/$H$90,0)</f>
@@ -3519,27 +3524,27 @@
       </c>
       <c r="E92" s="145" t="n">
         <f>$G$50/D92</f>
-        <v>2.692307692307692</v>
+        <v>324.11858974358967</v>
       </c>
       <c r="F92" s="136" t="n">
         <f>IF(OR(D92="",E92=""),"",E92/D92)</f>
-        <v>8.456607495069032e-9</v>
+        <v>0.0000010180648011176854</v>
       </c>
       <c r="G92" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F92))),"",F92*$D$55)</f>
-        <v>0.000020987023788759636</v>
+        <v>0.0000010184681144910238</v>
       </c>
       <c r="H92" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F92)),"",F92*$D$45)</f>
-        <v>8.456607495069033</v>
+        <v>1018.0648011176854</v>
       </c>
       <c r="I92" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H92))),"",H92*$D$55)</f>
-        <v>20987.023788759638</v>
+        <v>1018.4681144910238</v>
       </c>
       <c r="J92" s="133" t="n">
         <f>IF($H$90&gt;0,1-H92/$H$90,0)</f>
-        <v>0.5890861275476661</v>
+        <v>0.5890861275476662</v>
       </c>
       <c r="K92" s="130"/>
       <c r="L92" s="130"/>
@@ -3556,27 +3561,27 @@
       </c>
       <c r="E93" s="145" t="n">
         <f>$G$50/D93</f>
-        <v>2.048780487804878</v>
+        <v>246.6463414634146</v>
       </c>
       <c r="F93" s="136" t="n">
         <f>IF(OR(D93="",E93=""),"",E93/D93)</f>
-        <v>4.89708506841166e-9</v>
+        <v>5.895449137418202e-7</v>
       </c>
       <c r="G93" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F93))),"",F93*$D$55)</f>
-        <v>0.000012153247136781787</v>
+        <v>5.897784660143618e-7</v>
       </c>
       <c r="H93" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F93)),"",F93*$D$45)</f>
-        <v>4.89708506841166</v>
+        <v>589.5449137418202</v>
       </c>
       <c r="I93" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H93))),"",H93*$D$55)</f>
-        <v>12153.247136781787</v>
+        <v>589.7784660143618</v>
       </c>
       <c r="J93" s="133" t="n">
         <f>IF($H$90&gt;0,1-H93/$H$90,0)</f>
-        <v>0.7620464009518144</v>
+        <v>0.7620464009518145</v>
       </c>
       <c r="K93" s="130"/>
       <c r="L93" s="130"/>
@@ -3593,27 +3598,27 @@
       </c>
       <c r="E94" s="145" t="n">
         <f>$G$50/D94</f>
-        <v>1.6535433070866141</v>
+        <v>199.06496062992122</v>
       </c>
       <c r="F94" s="136" t="n">
         <f>IF(OR(D94="",E94=""),"",E94/D94)</f>
-        <v>3.189906379812759e-9</v>
+        <v>3.84022955545911e-7</v>
       </c>
       <c r="G94" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F94))),"",F94*$D$55)</f>
-        <v>0.000007916489102288648</v>
+        <v>3.841750888811079e-7</v>
       </c>
       <c r="H94" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F94)),"",F94*$D$45)</f>
-        <v>3.189906379812759</v>
+        <v>384.022955545911</v>
       </c>
       <c r="I94" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H94))),"",H94*$D$55)</f>
-        <v>7916.4891022886495</v>
+        <v>384.17508888110785</v>
       </c>
       <c r="J94" s="133" t="n">
         <f>IF($H$90&gt;0,1-H94/$H$90,0)</f>
-        <v>0.84499968999938</v>
+        <v>0.8449996899993801</v>
       </c>
       <c r="K94" s="130"/>
       <c r="L94" s="130"/>
@@ -3630,23 +3635,23 @@
       </c>
       <c r="E95" s="145" t="n">
         <f>$G$50/D95</f>
-        <v>1.3861386138613863</v>
+        <v>166.87293729372934</v>
       </c>
       <c r="F95" s="136" t="n">
         <f>IF(OR(D95="",E95=""),"",E95/D95)</f>
-        <v>2.2416102996438257e-9</v>
+        <v>2.69860525656526e-7</v>
       </c>
       <c r="G95" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F95))),"",F95*$D$55)</f>
-        <v>0.000005563073456014711</v>
+        <v>2.6996743275989886e-7</v>
       </c>
       <c r="H95" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F95)),"",F95*$D$45)</f>
-        <v>2.241610299643826</v>
+        <v>269.86052565652597</v>
       </c>
       <c r="I95" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H95))),"",H95*$D$55)</f>
-        <v>5563.073456014711</v>
+        <v>269.9674327598989</v>
       </c>
       <c r="J95" s="133" t="n">
         <f>IF($H$90&gt;0,1-H95/$H$90,0)</f>
@@ -3667,27 +3672,27 @@
       </c>
       <c r="E96" s="145" t="n">
         <f>$G$50/D96</f>
-        <v>1.1931818181818181</v>
+        <v>143.64346590909088</v>
       </c>
       <c r="F96" s="136" t="n">
         <f>IF(OR(D96="",E96=""),"",E96/D96)</f>
-        <v>1.6609633264462809e-9</v>
+        <v>1.9995823379390492e-7</v>
       </c>
       <c r="G96" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F96))),"",F96*$D$55)</f>
-        <v>0.000004122063944047444</v>
+        <v>2.0003744862355984e-7</v>
       </c>
       <c r="H96" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F96)),"",F96*$D$45)</f>
-        <v>1.6609633264462809</v>
+        <v>199.95823379390492</v>
       </c>
       <c r="I96" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H96))),"",H96*$D$55)</f>
-        <v>4122.063944047444</v>
+        <v>200.03744862355984</v>
       </c>
       <c r="J96" s="133" t="n">
         <f>IF($H$90&gt;0,1-H96/$H$90,0)</f>
-        <v>0.9192923553719008</v>
+        <v>0.9192923553719009</v>
       </c>
       <c r="K96" s="130"/>
       <c r="L96" s="130"/>
@@ -3704,23 +3709,23 @@
       </c>
       <c r="E97" s="145" t="n">
         <f>$G$50/D97</f>
-        <v>1.0473815461346634</v>
+        <v>126.09102244389025</v>
       </c>
       <c r="F97" s="136" t="n">
         <f>IF(OR(D97="",E97=""),"",E97/D97)</f>
-        <v>1.2798427870473443e-9</v>
+        <v>1.5407631171447936e-7</v>
       </c>
       <c r="G97" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F97))),"",F97*$D$55)</f>
-        <v>0.0000031762253401611592</v>
+        <v>1.5413735010512097e-7</v>
       </c>
       <c r="H97" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F97)),"",F97*$D$45)</f>
-        <v>1.2798427870473443</v>
+        <v>154.07631171447935</v>
       </c>
       <c r="I97" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H97))),"",H97*$D$55)</f>
-        <v>3176.2253401611597</v>
+        <v>154.13735010512096</v>
       </c>
       <c r="J97" s="133" t="n">
         <f>IF($H$90&gt;0,1-H97/$H$90,0)</f>
@@ -3741,23 +3746,23 @@
       </c>
       <c r="E98" s="146" t="n">
         <f>$G$50/D98</f>
-        <v>0.9333333333333333</v>
+        <v>112.3611111111111</v>
       </c>
       <c r="F98" s="137" t="n">
         <f>IF(OR(D98="",E98=""),"",E98/D98)</f>
-        <v>1.0162962962962963e-9</v>
+        <v>1.2234876543209874e-7</v>
       </c>
       <c r="G98" s="137" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F98))),"",F98*$D$55)</f>
-        <v>0.0000025221738811024916</v>
+        <v>1.2239723473705462e-7</v>
       </c>
       <c r="H98" s="146" t="n">
         <f>IF(NOT(ISNUMBER(F98)),"",F98*$D$45)</f>
-        <v>1.0162962962962963</v>
+        <v>122.34876543209874</v>
       </c>
       <c r="I98" s="146" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H98))),"",H98*$D$55)</f>
-        <v>2522.1738811024916</v>
+        <v>122.3972347370546</v>
       </c>
       <c r="J98" s="134" t="n">
         <f>IF($H$90&gt;0,1-H98/$H$90,0)</f>
@@ -3768,7 +3773,7 @@
       </c>
       <c r="L98" s="131" t="n">
         <f>E98</f>
-        <v>0.9333333333333333</v>
+        <v>112.3611111111111</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -4613,7 +4618,7 @@
   </conditionalFormatting>
   <dataValidations count="13">
     <dataValidation type="list" sqref="D7">
-      <formula1>'Quote参数'!$E$9:$E$62</formula1>
+      <formula1>'Quote参数'!$E$9:$E$63</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" sqref="D8">
       <formula1>0</formula1>
@@ -4743,7 +4748,7 @@
       <x:c r="A3" s="2"/>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="6" t="str">
-        <x:v>ETH + 53 个股票 / ETF Quote。股票类参数为 Robinhood Chain 区块 54,430,299 快照；Factory owner 后续可更新新 Launch 参数。</x:v>
+        <x:v>ETH、USDG 与股票 / ETF Quote。USDG 参数取 Factory 区块 68,708,148；已发币以发行时快照为准。</x:v>
       </x:c>
       <x:c r="D3" s="6"/>
       <x:c r="E3" s="6"/>
@@ -4878,9 +4883,11 @@
       <x:c r="F7" s="35"/>
       <x:c r="G7" s="35"/>
       <x:c r="H7" s="35" t="str">
-        <x:v>Snipe 窗口</x:v>
-      </x:c>
-      <x:c r="I7" s="35"/>
+        <x:v>USDG 参数依据</x:v>
+      </x:c>
+      <x:c r="I7" s="35" t="str">
+        <x:v>https://robinhoodchain.blockscout.com/address/0x7eD598BcEf8bd9Edd8C97A195C6d13f40801EC7e?tab=read_contract</x:v>
+      </x:c>
       <x:c r="J7" s="35" t="str">
         <x:v>3 秒（当前 Factory 链上参数）</x:v>
       </x:c>
@@ -8703,6 +8710,73 @@
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="42" customHeight="1">
+      <x:c r="C63" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D63" t="str">
+        <x:v>稳定币</x:v>
+      </x:c>
+      <x:c r="E63" t="str">
+        <x:v>USDG</x:v>
+      </x:c>
+      <x:c r="F63" t="str">
+        <x:v>Global Dollar</x:v>
+      </x:c>
+      <x:c r="G63" t="str">
+        <x:v>​0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</x:v>
+      </x:c>
+      <x:c r="H63" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I63" t="n">
+        <x:v>202.25</x:v>
+      </x:c>
+      <x:c r="J63" t="n">
+        <x:v>505.625</x:v>
+      </x:c>
+      <x:c r="K63" t="n">
+        <x:f>J63/I63</x:f>
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="L63" t="n">
+        <x:f>J63</x:f>
+        <x:v>505.625</x:v>
+      </x:c>
+      <x:c r="M63" t="n">
+        <x:f>1000000000*I63*J63/(I63+J63)^2</x:f>
+        <x:v>204081632.6530612</x:v>
+      </x:c>
+      <x:c r="N63" t="n">
+        <x:f>1000000000*I63^2/(I63+J63)^2</x:f>
+        <x:v>81632653.06122449</x:v>
+      </x:c>
+      <x:c r="O63" t="n">
+        <x:f>1-N63/1000000000</x:f>
+        <x:v>0.9183673469387755</x:v>
+      </x:c>
+      <x:c r="P63" t="n">
+        <x:v>68708148</x:v>
+      </x:c>
+      <x:c r="Q63" t="str">
+        <x:v>Approved / ERC-20</x:v>
+      </x:c>
+      <x:c r="R63" t="str">
+        <x:v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</x:v>
+      </x:c>
+      <x:c r="S63" s="155" t="n">
+        <x:v>1.0003961568781237</x:v>
+      </x:c>
+      <x:c r="T63" s="156" t="n">
+        <x:v>46285.27349457176</x:v>
+      </x:c>
+      <x:c r="U63" t="str">
+        <x:v>https://www.coingecko.com/en/coins/global-dollar</x:v>
+      </x:c>
+      <x:c r="V63" s="157" t="str">
+        <x:v>USDG 按 1 USD 估算；6 位精度；当前 Factory 新发币参数；旧币按发行快照</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R6c70b30a17644365"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R3ed7d1eb6cff4109"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rd7aedc8ed7d34244"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R2337eec321c940d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D18" s="121" t="n">
         <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
-        <v>52441.863942819284</v>
+        <v>689114.8230851085</v>
       </c>
       <c r="E18" s="62" t="str">
         <f>$D$7</f>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="J18" s="121" t="n">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
-        <v>55192.5430935758</v>
+        <v>692117.7246077446</v>
       </c>
       <c r="K18" s="62" t="str">
         <v>USDT</v>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D19" s="122" t="n">
         <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$55&gt;0,$D$18*$D$55,"")),"")</f>
-        <v>52462.63914792186</v>
+        <v>689387.8206620907</v>
       </c>
       <c r="E19" s="106" t="str">
         <v>USDT</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="D22" s="122" t="n">
         <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
-        <v>12456.885932495734</v>
+        <v>199310.17491993174</v>
       </c>
       <c r="E22" s="106" t="str">
         <f>$D$7</f>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="D23" s="122" t="n">
         <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
-        <v>510.7323232323232</v>
+        <v>8171.717171717171</v>
       </c>
       <c r="E23" s="106" t="str">
         <f>$D$7</f>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D24" s="122" t="n">
         <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
-        <v>29477.24568709123</v>
+        <v>471635.93099345965</v>
       </c>
       <c r="E24" s="106" t="str">
         <f>$D$7</f>
@@ -1755,7 +1755,7 @@
       <c r="F37" s="127"/>
       <c r="G37" s="128" t="n">
         <f>E98</f>
-        <v>112.3611111111111</v>
+        <v>1797.7777777777776</v>
       </c>
       <c r="H37" s="127" t="str">
         <f>$D$7</f>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="J41" s="108" t="n">
         <f>IF(1-$G$41-$J$7&gt;0,$G$44/(1-$G$41-$J$7),"")</f>
-        <v>510.7323232323232</v>
+        <v>8171.717171717171</v>
       </c>
       <c r="K41" s="107"/>
       <c r="L41" s="107"/>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="J43" s="108" t="n">
         <f>IF($J$42="","",$G$50/$J$42)</f>
-        <v>12332.317073170776</v>
+        <v>197317.07317073242</v>
       </c>
       <c r="K43" s="107"/>
       <c r="L43" s="107"/>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="G44" s="108" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,6,FALSE)</f>
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="H44" s="107"/>
       <c r="I44" s="107" t="str">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="J44" s="108" t="n">
         <f>IF($J$43="","",MAX(0,$J$43-$G$44))</f>
-        <v>11826.692073170776</v>
+        <v>189227.07317073242</v>
       </c>
       <c r="K44" s="107"/>
       <c r="L44" s="107"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J45" s="108" t="n">
         <f>IF($J$42="","",($J$43-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>11946.15360926341</v>
+        <v>191138.45774821457</v>
       </c>
       <c r="K45" s="107"/>
       <c r="L45" s="107"/>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D46" s="108" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$63,12,FALSE)</f>
-        <v>68708148</v>
+        <v>69045064</v>
       </c>
       <c r="E46" s="107"/>
       <c r="F46" s="107" t="str">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="G46" s="108" t="n">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,5,FALSE)</f>
-        <v>202.25</v>
+        <v>3236</v>
       </c>
       <c r="H46" s="107"/>
       <c r="I46" s="107" t="str">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="J46" s="108" t="n">
         <f>IF($J$43="","",$J$43/$J$42*$D$45)</f>
-        <v>1473862.2843545615</v>
+        <v>23581796.549672984</v>
       </c>
       <c r="K46" s="107"/>
       <c r="L46" s="107"/>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G47" s="114" t="n">
         <f>$G$46*$D$45</f>
-        <v>202250000000</v>
+        <v>3236000000000</v>
       </c>
       <c r="H47" s="107"/>
       <c r="I47" s="107" t="str">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="G49" s="108" t="n">
         <f>$G$44</f>
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="H49" s="107"/>
       <c r="I49" s="107" t="str">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="G50" s="114" t="n">
         <f>$G$48*$G$44</f>
-        <v>103188775510.20407</v>
+        <v>1651020408163.2651</v>
       </c>
       <c r="H50" s="107"/>
       <c r="I50" s="107"/>
@@ -2313,23 +2313,23 @@
       </c>
       <c r="E59" s="144" t="n">
         <f>$G$47/D59</f>
-        <v>202.25</v>
+        <v>3236</v>
       </c>
       <c r="F59" s="135" t="n">
         <f>IF(OR(D59="",E59=""),"",E59/D59)</f>
-        <v>2.0225e-7</v>
+        <v>0.000003236</v>
       </c>
       <c r="G59" s="135" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F59))),"",F59*$D$55)</f>
-        <v>2.0233012272860051e-7</v>
+        <v>0.0000032372819636576082</v>
       </c>
       <c r="H59" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F59)),"",F59*$D$45)</f>
-        <v>202.25</v>
+        <v>3236</v>
       </c>
       <c r="I59" s="144" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H59))),"",H59*$D$55)</f>
-        <v>202.33012272860051</v>
+        <v>3237.2819636576082</v>
       </c>
       <c r="J59" s="144" t="n">
         <f>0</f>
@@ -2356,35 +2356,35 @@
       </c>
       <c r="E60" s="145" t="n">
         <f>$G$47/D60</f>
-        <v>224.72222222222223</v>
+        <v>3595.5555555555557</v>
       </c>
       <c r="F60" s="136" t="n">
         <f>IF(OR(D60="",E60=""),"",E60/D60)</f>
-        <v>2.496913580246914e-7</v>
+        <v>0.000003995061728395062</v>
       </c>
       <c r="G60" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F60))),"",F60*$D$55)</f>
-        <v>2.497902749735809e-7</v>
+        <v>0.000003996644399577294</v>
       </c>
       <c r="H60" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F60)),"",F60*$D$45)</f>
-        <v>249.6913580246914</v>
+        <v>3995.0617283950623</v>
       </c>
       <c r="I60" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H60))),"",H60*$D$55)</f>
-        <v>249.79027497358092</v>
+        <v>3996.6443995772947</v>
       </c>
       <c r="J60" s="145" t="n">
         <f>E60-E59</f>
-        <v>22.47222222222223</v>
+        <v>359.55555555555566</v>
       </c>
       <c r="K60" s="145" t="n">
         <f>J60/(1-$G$41-$J$7)</f>
-        <v>22.69921436588104</v>
+        <v>363.18742985409665</v>
       </c>
       <c r="L60" s="148" t="n">
         <f>SUM($K$59:K60)</f>
-        <v>22.69921436588104</v>
+        <v>363.18742985409665</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2399,35 +2399,35 @@
       </c>
       <c r="E61" s="145" t="n">
         <f>$G$47/D61</f>
-        <v>252.8125</v>
+        <v>4045</v>
       </c>
       <c r="F61" s="136" t="n">
         <f>IF(OR(D61="",E61=""),"",E61/D61)</f>
-        <v>3.16015625e-7</v>
+        <v>0.00000505625</v>
       </c>
       <c r="G61" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F61))),"",F61*$D$55)</f>
-        <v>3.161408167634383e-7</v>
+        <v>0.0000050582530682150125</v>
       </c>
       <c r="H61" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F61)),"",F61*$D$45)</f>
-        <v>316.015625</v>
+        <v>5056.25</v>
       </c>
       <c r="I61" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H61))),"",H61*$D$55)</f>
-        <v>316.1408167634383</v>
+        <v>5058.253068215013</v>
       </c>
       <c r="J61" s="145" t="n">
         <f>E61-E60</f>
-        <v>28.09027777777777</v>
+        <v>449.44444444444434</v>
       </c>
       <c r="K61" s="145" t="n">
         <f>J61/(1-$G$41-$J$7)</f>
-        <v>28.374017957351285</v>
+        <v>453.98428731762056</v>
       </c>
       <c r="L61" s="148" t="n">
         <f>SUM($K$59:K61)</f>
-        <v>51.073232323232325</v>
+        <v>817.1717171717172</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -2442,35 +2442,35 @@
       </c>
       <c r="E62" s="145" t="n">
         <f>$G$47/D62</f>
-        <v>288.92857142857144</v>
+        <v>4622.857142857143</v>
       </c>
       <c r="F62" s="136" t="n">
         <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
-        <v>4.1275510204081637e-7</v>
+        <v>0.000006604081632653062</v>
       </c>
       <c r="G62" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F62))),"",F62*$D$55)</f>
-        <v>4.1291861781347046e-7</v>
+        <v>0.0000066066978850155274</v>
       </c>
       <c r="H62" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$45)</f>
-        <v>412.7551020408164</v>
+        <v>6604.081632653062</v>
       </c>
       <c r="I62" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H62))),"",H62*$D$55)</f>
-        <v>412.91861781347046</v>
+        <v>6606.697885015527</v>
       </c>
       <c r="J62" s="145" t="n">
         <f>E62-E61</f>
-        <v>36.116071428571445</v>
+        <v>577.8571428571431</v>
       </c>
       <c r="K62" s="145" t="n">
         <f>J62/(1-$G$41-$J$7)</f>
-        <v>36.480880230880246</v>
+        <v>583.6940836940839</v>
       </c>
       <c r="L62" s="148" t="n">
         <f>SUM($K$59:K62)</f>
-        <v>87.55411255411258</v>
+        <v>1400.8658008658012</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -2485,35 +2485,35 @@
       </c>
       <c r="E63" s="145" t="n">
         <f>$G$47/D63</f>
-        <v>337.0833333333333</v>
+        <v>5393.333333333333</v>
       </c>
       <c r="F63" s="136" t="n">
         <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
-        <v>5.618055555555556e-7</v>
+        <v>0.000008988888888888889</v>
       </c>
       <c r="G63" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F63))),"",F63*$D$55)</f>
-        <v>5.62028118690557e-7</v>
+        <v>0.000008992449899048911</v>
       </c>
       <c r="H63" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$45)</f>
-        <v>561.8055555555555</v>
+        <v>8988.888888888889</v>
       </c>
       <c r="I63" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H63))),"",H63*$D$55)</f>
-        <v>562.028118690557</v>
+        <v>8992.449899048912</v>
       </c>
       <c r="J63" s="145" t="n">
         <f>E63-E62</f>
-        <v>48.15476190476187</v>
+        <v>770.4761904761899</v>
       </c>
       <c r="K63" s="145" t="n">
         <f>J63/(1-$G$41-$J$7)</f>
-        <v>48.64117364117361</v>
+        <v>778.2587782587777</v>
       </c>
       <c r="L63" s="148" t="n">
         <f>SUM($K$59:K63)</f>
-        <v>136.1952861952862</v>
+        <v>2179.124579124579</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -2528,35 +2528,35 @@
       </c>
       <c r="E64" s="145" t="n">
         <f>$G$47/D64</f>
-        <v>404.5</v>
+        <v>6472</v>
       </c>
       <c r="F64" s="136" t="n">
         <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
-        <v>8.09e-7</v>
+        <v>0.000012944</v>
       </c>
       <c r="G64" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F64))),"",F64*$D$55)</f>
-        <v>8.093204909144021e-7</v>
+        <v>0.000012949127854630433</v>
       </c>
       <c r="H64" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$45)</f>
-        <v>809</v>
+        <v>12944</v>
       </c>
       <c r="I64" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H64))),"",H64*$D$55)</f>
-        <v>809.3204909144021</v>
+        <v>12949.127854630433</v>
       </c>
       <c r="J64" s="145" t="n">
         <f>E64-E63</f>
-        <v>67.41666666666669</v>
+        <v>1078.666666666667</v>
       </c>
       <c r="K64" s="145" t="n">
         <f>J64/(1-$G$41-$J$7)</f>
-        <v>68.09764309764311</v>
+        <v>1089.5622895622898</v>
       </c>
       <c r="L64" s="148" t="n">
         <f>SUM($K$59:K64)</f>
-        <v>204.29292929292933</v>
+        <v>3268.6868686868693</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -2571,35 +2571,35 @@
       </c>
       <c r="E65" s="145" t="n">
         <f>$G$47/D65</f>
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="F65" s="136" t="n">
         <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
-        <v>0.0000012640625</v>
+        <v>0.000020225</v>
       </c>
       <c r="G65" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F65))),"",F65*$D$55)</f>
-        <v>0.0000012645632670537531</v>
+        <v>0.00002023301227286005</v>
       </c>
       <c r="H65" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$45)</f>
-        <v>1264.0625</v>
+        <v>20225</v>
       </c>
       <c r="I65" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H65))),"",H65*$D$55)</f>
-        <v>1264.5632670537532</v>
+        <v>20233.01227286005</v>
       </c>
       <c r="J65" s="145" t="n">
         <f>E65-E64</f>
-        <v>101.125</v>
+        <v>1618</v>
       </c>
       <c r="K65" s="145" t="n">
         <f>J65/(1-$G$41-$J$7)</f>
-        <v>102.14646464646465</v>
+        <v>1634.3434343434344</v>
       </c>
       <c r="L65" s="148" t="n">
         <f>SUM($K$59:K65)</f>
-        <v>306.439393939394</v>
+        <v>4903.030303030304</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -2614,35 +2614,35 @@
       </c>
       <c r="E66" s="145" t="n">
         <f>$G$47/D66</f>
-        <v>674.1666666666665</v>
+        <v>10786.666666666664</v>
       </c>
       <c r="F66" s="136" t="n">
         <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
-        <v>0.0000022472222222222214</v>
+        <v>0.00003595555555555554</v>
       </c>
       <c r="G66" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F66))),"",F66*$D$55)</f>
-        <v>0.000002248112474762227</v>
+        <v>0.00003596979959619563</v>
       </c>
       <c r="H66" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$45)</f>
-        <v>2247.2222222222213</v>
+        <v>35955.55555555554</v>
       </c>
       <c r="I66" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H66))),"",H66*$D$55)</f>
-        <v>2248.112474762227</v>
+        <v>35969.79959619563</v>
       </c>
       <c r="J66" s="145" t="n">
         <f>E66-E65</f>
-        <v>168.54166666666652</v>
+        <v>2696.6666666666642</v>
       </c>
       <c r="K66" s="145" t="n">
         <f>J66/(1-$G$41-$J$7)</f>
-        <v>170.2441077441076</v>
+        <v>2723.9057239057215</v>
       </c>
       <c r="L66" s="148" t="n">
         <f>SUM($K$59:K66)</f>
-        <v>476.6835016835016</v>
+        <v>7626.936026936026</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -2658,35 +2658,35 @@
       </c>
       <c r="E67" s="146" t="n">
         <f>$G$47/D67</f>
-        <v>707.8750000000001</v>
+        <v>11326.000000000002</v>
       </c>
       <c r="F67" s="137" t="n">
         <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
-        <v>0.0000024775625000000006</v>
+        <v>0.00003964100000000001</v>
       </c>
       <c r="G67" s="137" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F67))),"",F67*$D$55)</f>
-        <v>0.0000024785440034253568</v>
+        <v>0.00003965670405480571</v>
       </c>
       <c r="H67" s="146" t="n">
         <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$45)</f>
-        <v>2477.5625000000005</v>
+        <v>39641.00000000001</v>
       </c>
       <c r="I67" s="146" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H67))),"",H67*$D$55)</f>
-        <v>2478.5440034253565</v>
+        <v>39656.704054805705</v>
       </c>
       <c r="J67" s="146" t="n">
         <f>E67-E66</f>
-        <v>33.7083333333336</v>
+        <v>539.3333333333376</v>
       </c>
       <c r="K67" s="146" t="n">
         <f>J67/(1-$G$41-$J$7)</f>
-        <v>34.04882154882182</v>
+        <v>544.7811447811491</v>
       </c>
       <c r="L67" s="149" t="n">
         <f>SUM($K$59:K67)</f>
-        <v>510.73232323232344</v>
+        <v>8171.717171717175</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -2783,23 +2783,23 @@
       </c>
       <c r="E72" s="144" t="n">
         <f>$G$44</f>
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="F72" s="135" t="n">
         <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
-        <v>0.0000024775625</v>
+        <v>0.000039641</v>
       </c>
       <c r="G72" s="135" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F72))),"",F72*$D$55)</f>
-        <v>0.0000024785440034253564</v>
+        <v>0.0000396567040548057</v>
       </c>
       <c r="H72" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$45)</f>
-        <v>2477.5625</v>
+        <v>39641</v>
       </c>
       <c r="I72" s="144" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H72))),"",H72*$D$55)</f>
-        <v>2478.544003425356</v>
+        <v>39656.7040548057</v>
       </c>
       <c r="J72" s="144" t="n">
         <f>0</f>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="L72" s="147" t="n">
         <f>$J$41</f>
-        <v>510.7323232323232</v>
+        <v>8171.717171717171</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2826,35 +2826,35 @@
       </c>
       <c r="E73" s="145" t="n">
         <f>IF(D73="","",$G$50/D73)</f>
-        <v>612.8787878787878</v>
+        <v>9806.060606060604</v>
       </c>
       <c r="F73" s="136" t="n">
         <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
-        <v>0.000003640128558310376</v>
+        <v>0.000058242056932966014</v>
       </c>
       <c r="G73" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F73))),"",F73*$D$55)</f>
-        <v>0.000003641570620276005</v>
+        <v>0.00005826512992441608</v>
       </c>
       <c r="H73" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$45)</f>
-        <v>3640.128558310376</v>
+        <v>58242.056932966014</v>
       </c>
       <c r="I73" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H73))),"",H73*$D$55)</f>
-        <v>3641.570620276005</v>
+        <v>58265.12992441608</v>
       </c>
       <c r="J73" s="145" t="n">
         <f>IF(E73="","",MAX(0,E73-$G$44))</f>
-        <v>107.25378787878776</v>
+        <v>1716.0606060606042</v>
       </c>
       <c r="K73" s="145" t="n">
         <f>IF(D73="","",MAX(0,$G$50/D73-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>108.33715947352299</v>
+        <v>1733.3945515763678</v>
       </c>
       <c r="L73" s="148" t="n">
         <f>IF(K73="","",$J$41+K73)</f>
-        <v>619.0694827058462</v>
+        <v>9905.11172329354</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2869,35 +2869,35 @@
       </c>
       <c r="E74" s="145" t="n">
         <f>IF(D74="","",$G$50/D74)</f>
-        <v>871.7672413793105</v>
+        <v>13948.275862068967</v>
       </c>
       <c r="F74" s="136" t="n">
         <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
-        <v>0.00000736493014268728</v>
+        <v>0.00011783888228299648</v>
       </c>
       <c r="G74" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F74))),"",F74*$D$55)</f>
-        <v>0.000007367847810420206</v>
+        <v>0.0001178855649667233</v>
       </c>
       <c r="H74" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$45)</f>
-        <v>7364.93014268728</v>
+        <v>117838.88228299648</v>
       </c>
       <c r="I74" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H74))),"",H74*$D$55)</f>
-        <v>7367.847810420206</v>
+        <v>117885.5649667233</v>
       </c>
       <c r="J74" s="145" t="n">
         <f>IF(E74="","",MAX(0,E74-$G$44))</f>
-        <v>366.14224137931046</v>
+        <v>5858.275862068967</v>
       </c>
       <c r="K74" s="145" t="n">
         <f>IF(D74="","",MAX(0,$G$50/D74-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>369.84064785788934</v>
+        <v>5917.450365726229</v>
       </c>
       <c r="L74" s="148" t="n">
         <f>IF(K74="","",$J$41+K74)</f>
-        <v>880.5729710902126</v>
+        <v>14089.167537443402</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2912,35 +2912,35 @@
       </c>
       <c r="E75" s="145" t="n">
         <f>IF(D75="","",$G$50/D75)</f>
-        <v>1049.014522821576</v>
+        <v>16784.232365145217</v>
       </c>
       <c r="F75" s="136" t="n">
         <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
-        <v>0.000010664255522459999</v>
+        <v>0.00017062808835935998</v>
       </c>
       <c r="G75" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F75))),"",F75*$D$55)</f>
-        <v>0.000010668480240635289</v>
+        <v>0.00017069568385016462</v>
       </c>
       <c r="H75" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$45)</f>
-        <v>10664.255522459998</v>
+        <v>170628.08835935997</v>
       </c>
       <c r="I75" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H75))),"",H75*$D$55)</f>
-        <v>10668.480240635288</v>
+        <v>170695.6838501646</v>
       </c>
       <c r="J75" s="145" t="n">
         <f>IF(E75="","",MAX(0,E75-$G$44))</f>
-        <v>543.3895228215761</v>
+        <v>8694.232365145217</v>
       </c>
       <c r="K75" s="145" t="n">
         <f>IF(D75="","",MAX(0,$G$50/D75-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>548.8783058803799</v>
+        <v>8782.052894086079</v>
       </c>
       <c r="L75" s="148" t="n">
         <f>IF(K75="","",$J$41+K75)</f>
-        <v>1059.610629112703</v>
+        <v>16953.770065803248</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2955,35 +2955,35 @@
       </c>
       <c r="E76" s="145" t="n">
         <f>IF(D76="","",$G$50/D76)</f>
-        <v>1316.7317708333328</v>
+        <v>21067.708333333325</v>
       </c>
       <c r="F76" s="136" t="n">
         <f>IF(OR(D76="",E76=""),"",E76/D76)</f>
-        <v>0.000016802046034071167</v>
+        <v>0.00026883273654513867</v>
       </c>
       <c r="G76" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F76))),"",F76*$D$55)</f>
-        <v>0.000016808702280174114</v>
+        <v>0.0002689392364827858</v>
       </c>
       <c r="H76" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F76)),"",F76*$D$45)</f>
-        <v>16802.046034071165</v>
+        <v>268832.73654513864</v>
       </c>
       <c r="I76" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H76))),"",H76*$D$55)</f>
-        <v>16808.70228017411</v>
+        <v>268939.2364827858</v>
       </c>
       <c r="J76" s="145" t="n">
         <f>IF(E76="","",MAX(0,E76-$G$44))</f>
-        <v>811.1067708333328</v>
+        <v>12977.708333333325</v>
       </c>
       <c r="K76" s="145" t="n">
         <f>IF(D76="","",MAX(0,$G$50/D76-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>819.299768518518</v>
+        <v>13108.796296296288</v>
       </c>
       <c r="L76" s="148" t="n">
         <f>IF(K76="","",$J$41+K76)</f>
-        <v>1330.0320917508411</v>
+        <v>21280.513468013458</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2998,35 +2998,35 @@
       </c>
       <c r="E77" s="145" t="n">
         <f>IF(D77="","",$G$50/D77)</f>
-        <v>1767.9195804195804</v>
+        <v>28286.713286713286</v>
       </c>
       <c r="F77" s="136" t="n">
         <f>IF(OR(D77="",E77=""),"",E77/D77)</f>
-        <v>0.000030289531272922882</v>
+        <v>0.0004846325003667661</v>
       </c>
       <c r="G77" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F77))),"",F77*$D$55)</f>
-        <v>0.000030301530679071792</v>
+        <v>0.0004848244908651487</v>
       </c>
       <c r="H77" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F77)),"",F77*$D$45)</f>
-        <v>30289.531272922883</v>
+        <v>484632.5003667661</v>
       </c>
       <c r="I77" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H77))),"",H77*$D$55)</f>
-        <v>30301.53067907179</v>
+        <v>484824.49086514866</v>
       </c>
       <c r="J77" s="145" t="n">
         <f>IF(E77="","",MAX(0,E77-$G$44))</f>
-        <v>1262.2945804195804</v>
+        <v>20196.713286713286</v>
       </c>
       <c r="K77" s="145" t="n">
         <f>IF(D77="","",MAX(0,$G$50/D77-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>1275.0450307268488</v>
+        <v>20400.72049162958</v>
       </c>
       <c r="L77" s="148" t="n">
         <f>IF(K77="","",$J$41+K77)</f>
-        <v>1785.7773539591722</v>
+        <v>28572.437663346755</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3041,35 +3041,35 @@
       </c>
       <c r="E78" s="145" t="n">
         <f>IF(D78="","",$G$50/D78)</f>
-        <v>2689.4946808510635</v>
+        <v>43031.91489361702</v>
       </c>
       <c r="F78" s="136" t="n">
         <f>IF(OR(D78="",E78=""),"",E78/D78)</f>
-        <v>0.00007009853157537346</v>
+        <v>0.0011215765052059754</v>
       </c>
       <c r="G78" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F78))),"",F78*$D$55)</f>
-        <v>0.00007012630159080341</v>
+        <v>0.0011220208254528546</v>
       </c>
       <c r="H78" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F78)),"",F78*$D$45)</f>
-        <v>70098.53157537346</v>
+        <v>1121576.5052059754</v>
       </c>
       <c r="I78" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H78))),"",H78*$D$55)</f>
-        <v>70126.30159080341</v>
+        <v>1122020.8254528546</v>
       </c>
       <c r="J78" s="145" t="n">
         <f>IF(E78="","",MAX(0,E78-$G$44))</f>
-        <v>2183.8696808510635</v>
+        <v>34941.91489361702</v>
       </c>
       <c r="K78" s="145" t="n">
         <f>IF(D78="","",MAX(0,$G$50/D78-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>2205.92897055663</v>
+        <v>35294.86352890608</v>
       </c>
       <c r="L78" s="148" t="n">
         <f>IF(K78="","",$J$41+K78)</f>
-        <v>2716.661293788953</v>
+        <v>43466.58070062325</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3084,35 +3084,35 @@
       </c>
       <c r="E79" s="145" t="n">
         <f>IF(D79="","",$G$50/D79)</f>
-        <v>3637.5899280575554</v>
+        <v>58201.43884892089</v>
       </c>
       <c r="F79" s="136" t="n">
         <f>IF(OR(D79="",E79=""),"",E79/D79)</f>
-        <v>0.00012823158739195707</v>
+        <v>0.002051705398271313</v>
       </c>
       <c r="G79" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F79))),"",F79*$D$55)</f>
-        <v>0.0001282823872172951</v>
+        <v>0.0020525181954767218</v>
       </c>
       <c r="H79" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F79)),"",F79*$D$45)</f>
-        <v>128231.58739195707</v>
+        <v>2051705.3982713132</v>
       </c>
       <c r="I79" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H79))),"",H79*$D$55)</f>
-        <v>128282.38721729511</v>
+        <v>2052518.1954767217</v>
       </c>
       <c r="J79" s="145" t="n">
         <f>IF(E79="","",MAX(0,E79-$G$44))</f>
-        <v>3131.9649280575554</v>
+        <v>50111.43884892089</v>
       </c>
       <c r="K79" s="145" t="n">
         <f>IF(D79="","",MAX(0,$G$50/D79-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>3163.600937431874</v>
+        <v>50617.61499890999</v>
       </c>
       <c r="L79" s="148" t="n">
         <f>IF(K79="","",$J$41+K79)</f>
-        <v>3674.3332606641975</v>
+        <v>58789.33217062716</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3127,35 +3127,35 @@
       </c>
       <c r="E80" s="145" t="n">
         <f>IF(D80="","",$G$50/D80)</f>
-        <v>5618.055555555559</v>
+        <v>89888.88888888895</v>
       </c>
       <c r="F80" s="136" t="n">
         <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
-        <v>0.00030587191358024735</v>
+        <v>0.004893950617283958</v>
       </c>
       <c r="G80" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F80))),"",F80*$D$55)</f>
-        <v>0.00030599308684263704</v>
+        <v>0.004895889389482193</v>
       </c>
       <c r="H80" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$45)</f>
-        <v>305871.9135802474</v>
+        <v>4893950.617283958</v>
       </c>
       <c r="I80" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H80))),"",H80*$D$55)</f>
-        <v>305993.08684263704</v>
+        <v>4895889.389482193</v>
       </c>
       <c r="J80" s="145" t="n">
         <f>IF(E80="","",MAX(0,E80-$G$44))</f>
-        <v>5112.430555555559</v>
+        <v>81798.88888888895</v>
       </c>
       <c r="K80" s="145" t="n">
         <f>IF(D80="","",MAX(0,$G$50/D80-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>5164.071268237939</v>
+        <v>82625.14029180702</v>
       </c>
       <c r="L80" s="148" t="n">
         <f>IF(K80="","",$J$41+K80)</f>
-        <v>5674.803591470262</v>
+        <v>90796.8574635242</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3170,35 +3170,35 @@
       </c>
       <c r="E81" s="145" t="n">
         <f>IF(D81="","",$G$50/D81)</f>
-        <v>7719.465648854979</v>
+        <v>123511.45038167966</v>
       </c>
       <c r="F81" s="136" t="n">
         <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
-        <v>0.000577486743196786</v>
+        <v>0.009239787891148576</v>
       </c>
       <c r="G81" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F81))),"",F81*$D$55)</f>
-        <v>0.0005777155185421286</v>
+        <v>0.009243448296674058</v>
       </c>
       <c r="H81" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$45)</f>
-        <v>577486.743196786</v>
+        <v>9239787.891148577</v>
       </c>
       <c r="I81" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H81))),"",H81*$D$55)</f>
-        <v>577715.5185421287</v>
+        <v>9243448.29667406</v>
       </c>
       <c r="J81" s="145" t="n">
         <f>IF(E81="","",MAX(0,E81-$G$44))</f>
-        <v>7213.840648854979</v>
+        <v>115421.45038167966</v>
       </c>
       <c r="K81" s="145" t="n">
         <f>IF(D81="","",MAX(0,$G$50/D81-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>7286.70772611614</v>
+        <v>116587.32361785824</v>
       </c>
       <c r="L81" s="148" t="n">
         <f>IF(K81="","",$J$41+K81)</f>
-        <v>7797.440049348464</v>
+        <v>124759.04078957542</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3213,35 +3213,35 @@
       </c>
       <c r="E82" s="145" t="n">
         <f>IF(D82="","",$G$50/D82)</f>
-        <v>12332.317073170776</v>
+        <v>197317.07317073242</v>
       </c>
       <c r="F82" s="136" t="n">
         <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
-        <v>0.0014738622843545614</v>
+        <v>0.023581796549672983</v>
       </c>
       <c r="G82" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F82))),"",F82*$D$55)</f>
-        <v>0.0014744461650359156</v>
+        <v>0.02359113864057465</v>
       </c>
       <c r="H82" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$45)</f>
-        <v>1473862.2843545615</v>
+        <v>23581796.549672984</v>
       </c>
       <c r="I82" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H82))),"",H82*$D$55)</f>
-        <v>1474446.1650359156</v>
+        <v>23591138.64057465</v>
       </c>
       <c r="J82" s="145" t="n">
         <f>IF(E82="","",MAX(0,E82-$G$44))</f>
-        <v>11826.692073170776</v>
+        <v>189227.07317073242</v>
       </c>
       <c r="K82" s="145" t="n">
         <f>IF(D82="","",MAX(0,$G$50/D82-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>11946.15360926341</v>
+        <v>191138.45774821457</v>
       </c>
       <c r="L82" s="148" t="n">
         <f>IF(K82="","",$J$41+K82)</f>
-        <v>12456.885932495734</v>
+        <v>199310.17491993174</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3256,35 +3256,35 @@
       </c>
       <c r="E83" s="145" t="n">
         <f>IF(D83="","",$G$50/D83)</f>
-        <v>30643.93939393967</v>
+        <v>490303.0303030347</v>
       </c>
       <c r="F83" s="136" t="n">
         <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
-        <v>0.009100321395776104</v>
+        <v>0.14560514233241767</v>
       </c>
       <c r="G83" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F83))),"",F83*$D$55)</f>
-        <v>0.009103926550690178</v>
+        <v>0.14566282481104284</v>
       </c>
       <c r="H83" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$45)</f>
-        <v>9100321.395776104</v>
+        <v>145605142.33241767</v>
       </c>
       <c r="I83" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H83))),"",H83*$D$55)</f>
-        <v>9103926.550690176</v>
+        <v>145662824.81104282</v>
       </c>
       <c r="J83" s="145" t="n">
         <f>IF(E83="","",MAX(0,E83-$G$44))</f>
-        <v>30138.31439393967</v>
+        <v>482213.0303030347</v>
       </c>
       <c r="K83" s="145" t="n">
         <f>IF(D83="","",MAX(0,$G$50/D83-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>30442.74181206027</v>
+        <v>487083.86899296433</v>
       </c>
       <c r="L83" s="148" t="n">
         <f>IF(K83="","",$J$41+K83)</f>
-        <v>30953.474135292592</v>
+        <v>495255.5861646815</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3299,35 +3299,35 @@
       </c>
       <c r="E84" s="145" t="n">
         <f>IF(D84="","",$G$50/D84)</f>
-        <v>280902.7777778124</v>
+        <v>4494444.444444998</v>
       </c>
       <c r="F84" s="136" t="n">
         <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
-        <v>0.7646797839508058</v>
+        <v>12.234876543212893</v>
       </c>
       <c r="G84" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F84))),"",F84*$D$55)</f>
-        <v>0.76498271710678</v>
+        <v>12.23972347370848</v>
       </c>
       <c r="H84" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$45)</f>
-        <v>764679783.9508058</v>
+        <v>12234876543.212893</v>
       </c>
       <c r="I84" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H84))),"",H84*$D$55)</f>
-        <v>764982717.10678</v>
+        <v>12239723473.70848</v>
       </c>
       <c r="J84" s="145" t="n">
         <f>IF(E84="","",MAX(0,E84-$G$44))</f>
-        <v>280397.1527778124</v>
+        <v>4486354.444444998</v>
       </c>
       <c r="K84" s="145" t="n">
         <f>IF(D84="","",MAX(0,$G$50/D84-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
-        <v>283229.44725031557</v>
+        <v>4531671.156005049</v>
       </c>
       <c r="L84" s="148" t="n">
         <f>IF(K84="","",$J$41+K84)</f>
-        <v>283740.1795735479</v>
+        <v>4539842.873176767</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3450,23 +3450,23 @@
       </c>
       <c r="E90" s="144" t="n">
         <f>$G$50/D90</f>
-        <v>505.62500000000006</v>
+        <v>8090.000000000001</v>
       </c>
       <c r="F90" s="135" t="n">
         <f>IF(OR(D90="",E90=""),"",E90/D90)</f>
-        <v>0.000002477562500000001</v>
+        <v>0.000039641000000000016</v>
       </c>
       <c r="G90" s="135" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F90))),"",F90*$D$55)</f>
-        <v>0.000002478544003425357</v>
+        <v>0.000039656704054805715</v>
       </c>
       <c r="H90" s="144" t="n">
         <f>IF(NOT(ISNUMBER(F90)),"",F90*$D$45)</f>
-        <v>2477.562500000001</v>
+        <v>39641.000000000015</v>
       </c>
       <c r="I90" s="144" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H90))),"",H90*$D$55)</f>
-        <v>2478.544003425357</v>
+        <v>39656.70405480571</v>
       </c>
       <c r="J90" s="132" t="n">
         <f>IF($H$90&gt;0,1-H90/$H$90,0)</f>
@@ -3487,23 +3487,23 @@
       </c>
       <c r="E91" s="145" t="n">
         <f>$G$50/D91</f>
-        <v>472.54672897196247</v>
+        <v>7560.7476635513995</v>
       </c>
       <c r="F91" s="136" t="n">
         <f>IF(OR(D91="",E91=""),"",E91/D91)</f>
-        <v>0.0000021639990392173977</v>
+        <v>0.000034623984627478364</v>
       </c>
       <c r="G91" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F91))),"",F91*$D$55)</f>
-        <v>0.000002164856322321037</v>
+        <v>0.00003463770115713659</v>
       </c>
       <c r="H91" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F91)),"",F91*$D$45)</f>
-        <v>2163.9990392173977</v>
+        <v>34623.98462747836</v>
       </c>
       <c r="I91" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H91))),"",H91*$D$55)</f>
-        <v>2164.8563223210367</v>
+        <v>34637.70115713659</v>
       </c>
       <c r="J91" s="133" t="n">
         <f>IF($H$90&gt;0,1-H91/$H$90,0)</f>
@@ -3524,23 +3524,23 @@
       </c>
       <c r="E92" s="145" t="n">
         <f>$G$50/D92</f>
-        <v>324.11858974358967</v>
+        <v>5185.897435897435</v>
       </c>
       <c r="F92" s="136" t="n">
         <f>IF(OR(D92="",E92=""),"",E92/D92)</f>
-        <v>0.0000010180648011176854</v>
+        <v>0.000016289036817882967</v>
       </c>
       <c r="G92" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F92))),"",F92*$D$55)</f>
-        <v>0.0000010184681144910238</v>
+        <v>0.00001629548983185638</v>
       </c>
       <c r="H92" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F92)),"",F92*$D$45)</f>
-        <v>1018.0648011176854</v>
+        <v>16289.036817882967</v>
       </c>
       <c r="I92" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H92))),"",H92*$D$55)</f>
-        <v>1018.4681144910238</v>
+        <v>16295.489831856381</v>
       </c>
       <c r="J92" s="133" t="n">
         <f>IF($H$90&gt;0,1-H92/$H$90,0)</f>
@@ -3561,23 +3561,23 @@
       </c>
       <c r="E93" s="145" t="n">
         <f>$G$50/D93</f>
-        <v>246.6463414634146</v>
+        <v>3946.3414634146334</v>
       </c>
       <c r="F93" s="136" t="n">
         <f>IF(OR(D93="",E93=""),"",E93/D93)</f>
-        <v>5.895449137418202e-7</v>
+        <v>0.000009432718619869124</v>
       </c>
       <c r="G93" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F93))),"",F93*$D$55)</f>
-        <v>5.897784660143618e-7</v>
+        <v>0.00000943645545622979</v>
       </c>
       <c r="H93" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F93)),"",F93*$D$45)</f>
-        <v>589.5449137418202</v>
+        <v>9432.718619869123</v>
       </c>
       <c r="I93" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H93))),"",H93*$D$55)</f>
-        <v>589.7784660143618</v>
+        <v>9436.455456229789</v>
       </c>
       <c r="J93" s="133" t="n">
         <f>IF($H$90&gt;0,1-H93/$H$90,0)</f>
@@ -3598,23 +3598,23 @@
       </c>
       <c r="E94" s="145" t="n">
         <f>$G$50/D94</f>
-        <v>199.06496062992122</v>
+        <v>3185.0393700787395</v>
       </c>
       <c r="F94" s="136" t="n">
         <f>IF(OR(D94="",E94=""),"",E94/D94)</f>
-        <v>3.84022955545911e-7</v>
+        <v>0.000006144367288734576</v>
       </c>
       <c r="G94" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F94))),"",F94*$D$55)</f>
-        <v>3.841750888811079e-7</v>
+        <v>0.000006146801422097726</v>
       </c>
       <c r="H94" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F94)),"",F94*$D$45)</f>
-        <v>384.022955545911</v>
+        <v>6144.367288734576</v>
       </c>
       <c r="I94" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H94))),"",H94*$D$55)</f>
-        <v>384.17508888110785</v>
+        <v>6146.801422097726</v>
       </c>
       <c r="J94" s="133" t="n">
         <f>IF($H$90&gt;0,1-H94/$H$90,0)</f>
@@ -3635,23 +3635,23 @@
       </c>
       <c r="E95" s="145" t="n">
         <f>$G$50/D95</f>
-        <v>166.87293729372934</v>
+        <v>2669.9669966996694</v>
       </c>
       <c r="F95" s="136" t="n">
         <f>IF(OR(D95="",E95=""),"",E95/D95)</f>
-        <v>2.69860525656526e-7</v>
+        <v>0.000004317768410504416</v>
       </c>
       <c r="G95" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F95))),"",F95*$D$55)</f>
-        <v>2.6996743275989886e-7</v>
+        <v>0.000004319478924158382</v>
       </c>
       <c r="H95" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F95)),"",F95*$D$45)</f>
-        <v>269.86052565652597</v>
+        <v>4317.768410504415</v>
       </c>
       <c r="I95" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H95))),"",H95*$D$55)</f>
-        <v>269.9674327598989</v>
+        <v>4319.478924158382</v>
       </c>
       <c r="J95" s="133" t="n">
         <f>IF($H$90&gt;0,1-H95/$H$90,0)</f>
@@ -3672,23 +3672,23 @@
       </c>
       <c r="E96" s="145" t="n">
         <f>$G$50/D96</f>
-        <v>143.64346590909088</v>
+        <v>2298.295454545454</v>
       </c>
       <c r="F96" s="136" t="n">
         <f>IF(OR(D96="",E96=""),"",E96/D96)</f>
-        <v>1.9995823379390492e-7</v>
+        <v>0.0000031993317407024787</v>
       </c>
       <c r="G96" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F96))),"",F96*$D$55)</f>
-        <v>2.0003744862355984e-7</v>
+        <v>0.0000032005991779769574</v>
       </c>
       <c r="H96" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F96)),"",F96*$D$45)</f>
-        <v>199.95823379390492</v>
+        <v>3199.331740702479</v>
       </c>
       <c r="I96" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H96))),"",H96*$D$55)</f>
-        <v>200.03744862355984</v>
+        <v>3200.5991779769574</v>
       </c>
       <c r="J96" s="133" t="n">
         <f>IF($H$90&gt;0,1-H96/$H$90,0)</f>
@@ -3709,23 +3709,23 @@
       </c>
       <c r="E97" s="145" t="n">
         <f>$G$50/D97</f>
-        <v>126.09102244389025</v>
+        <v>2017.456359102244</v>
       </c>
       <c r="F97" s="136" t="n">
         <f>IF(OR(D97="",E97=""),"",E97/D97)</f>
-        <v>1.5407631171447936e-7</v>
+        <v>0.0000024652209874316697</v>
       </c>
       <c r="G97" s="136" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F97))),"",F97*$D$55)</f>
-        <v>1.5413735010512097e-7</v>
+        <v>0.0000024661976016819355</v>
       </c>
       <c r="H97" s="145" t="n">
         <f>IF(NOT(ISNUMBER(F97)),"",F97*$D$45)</f>
-        <v>154.07631171447935</v>
+        <v>2465.2209874316695</v>
       </c>
       <c r="I97" s="145" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H97))),"",H97*$D$55)</f>
-        <v>154.13735010512096</v>
+        <v>2466.1976016819353</v>
       </c>
       <c r="J97" s="133" t="n">
         <f>IF($H$90&gt;0,1-H97/$H$90,0)</f>
@@ -3746,23 +3746,23 @@
       </c>
       <c r="E98" s="146" t="n">
         <f>$G$50/D98</f>
-        <v>112.3611111111111</v>
+        <v>1797.7777777777776</v>
       </c>
       <c r="F98" s="137" t="n">
         <f>IF(OR(D98="",E98=""),"",E98/D98)</f>
-        <v>1.2234876543209874e-7</v>
+        <v>0.00000195758024691358</v>
       </c>
       <c r="G98" s="137" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(F98))),"",F98*$D$55)</f>
-        <v>1.2239723473705462e-7</v>
+        <v>0.000001958355755792874</v>
       </c>
       <c r="H98" s="146" t="n">
         <f>IF(NOT(ISNUMBER(F98)),"",F98*$D$45)</f>
-        <v>122.34876543209874</v>
+        <v>1957.58024691358</v>
       </c>
       <c r="I98" s="146" t="n">
         <f>IF(OR($D$55="",NOT(ISNUMBER(H98))),"",H98*$D$55)</f>
-        <v>122.3972347370546</v>
+        <v>1958.3557557928737</v>
       </c>
       <c r="J98" s="134" t="n">
         <f>IF($H$90&gt;0,1-H98/$H$90,0)</f>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="L98" s="131" t="n">
         <f>E98</f>
-        <v>112.3611111111111</v>
+        <v>1797.7777777777776</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -4748,7 +4748,7 @@
       <x:c r="A3" s="2"/>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="6" t="str">
-        <x:v>ETH、USDG 与股票 / ETF Quote。USDG 参数取 Factory 区块 68,708,148；已发币以发行时快照为准。</x:v>
+        <x:v>ETH、USDG 与股票 / ETF Quote。USDG 采用 TRAIN 发行参数快照，外盘 8,090 USDG；新币参数可变。</x:v>
       </x:c>
       <x:c r="D3" s="6"/>
       <x:c r="E3" s="6"/>
@@ -4886,7 +4886,7 @@
         <x:v>USDG 参数依据</x:v>
       </x:c>
       <x:c r="I7" s="35" t="str">
-        <x:v>https://robinhoodchain.blockscout.com/address/0x7eD598BcEf8bd9Edd8C97A195C6d13f40801EC7e?tab=read_contract</x:v>
+        <x:v>https://robin.etherscan.io/tx/0x387e3237904e4822075066331564561c373b691fd47ad2d52b4f64fb4f398c84#eventlog</x:v>
       </x:c>
       <x:c r="J7" s="35" t="str">
         <x:v>3 秒（当前 Factory 链上参数）</x:v>
@@ -8732,10 +8732,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:v>202.25</x:v>
+        <x:v>3236</x:v>
       </x:c>
       <x:c r="J63" t="n">
-        <x:v>505.625</x:v>
+        <x:v>8090</x:v>
       </x:c>
       <x:c r="K63" t="n">
         <x:f>J63/I63</x:f>
@@ -8743,7 +8743,7 @@
       </x:c>
       <x:c r="L63" t="n">
         <x:f>J63</x:f>
-        <x:v>505.625</x:v>
+        <x:v>8090</x:v>
       </x:c>
       <x:c r="M63" t="n">
         <x:f>1000000000*I63*J63/(I63+J63)^2</x:f>
@@ -8758,10 +8758,10 @@
         <x:v>0.9183673469387755</x:v>
       </x:c>
       <x:c r="P63" t="n">
-        <x:v>68708148</x:v>
+        <x:v>69045064</x:v>
       </x:c>
       <x:c r="Q63" t="str">
-        <x:v>Approved / ERC-20</x:v>
+        <x:v>已发行实例 / ERC-20</x:v>
       </x:c>
       <x:c r="R63" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</x:v>
@@ -8776,7 +8776,7 @@
         <x:v>https://www.coingecko.com/en/coins/global-dollar</x:v>
       </x:c>
       <x:c r="V63" s="157" t="str">
-        <x:v>USDG 按 1 USD 估算；6 位精度；当前 Factory 新发币参数；旧币按发行快照</x:v>
+        <x:v>TRAIN 创建时 phantom 3,236、门槛 8,090 USDG；PERC 迁池同为 8,090。其他币按发行时参数核对。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rd7aedc8ed7d34244"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R2337eec321c940d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R4174b316770c4864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Ra03c4c2a547940c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="J18" s="121" t="n">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
-        <v>692117.7246077446</v>
+        <v>692225.9105456846</v>
       </c>
       <c r="K18" s="62" t="str">
         <v>USDT</v>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G19" s="122" t="n">
         <f>IF($G$18=0,0,IF($J$19="","",$G$18*$J$19))</f>
-        <v>2729.9039456539363</v>
+        <v>2838.0898835939033</v>
       </c>
       <c r="H19" s="106" t="str">
         <v>USDT</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J19" s="123" t="n">
         <f>IF($D$7="ETH",$D$55,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$63,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$63,15,FALSE),""))</f>
-        <v>2481.7308596853964</v>
+        <v>2580.0817123580937</v>
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="106"/>
@@ -1555,7 +1555,7 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="122" t="n">
-        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",0)</f>
+        <f>IF($D$51&lt;&gt;"可达","",0)</f>
         <v>0</v>
       </c>
       <c r="E26" s="106" t="str">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="D27" s="125" t="n">
         <f>$D$8*$J$54</f>
-        <v>0.9</v>
+        <v>0.88209</v>
       </c>
       <c r="E27" s="106"/>
       <c r="F27" s="106"/>
@@ -1595,7 +1595,7 @@
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="107" t="str">
-        <v>补回目标控筹率</v>
+        <v>原目标控筹率</v>
       </c>
       <c r="D28" s="124" t="n">
         <f>$D$8</f>
@@ -1732,7 +1732,7 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="115" t="str">
-        <v>Pons V2 外盘手续费始终按 Quote leg 计收；Hook 某些方向暂存的 Meme 费用会在池内转换回 Quote，属于内部归集路径。按本模型口径不降低 TOKEN 控筹率，因此恢复目标控筹预留为 0。</v>
+        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
       </c>
       <c r="D36" s="115"/>
       <c r="E36" s="115"/>
@@ -2185,8 +2185,8 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="112" t="n">
-        <f>1</f>
-        <v>1</v>
+        <f>MAX(0,1-$J$29)*MAX(0,1-$J$30)</f>
+        <v>0.9801</v>
       </c>
       <c r="K54" s="107"/>
       <c r="L54" s="107"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J56" s="108" t="n">
         <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)</f>
-        <v>18367346.93877548</v>
+        <v>36277346.93877548</v>
       </c>
       <c r="K56" s="107"/>
       <c r="L56" s="107"/>
@@ -4853,7 +4853,7 @@
       </x:c>
       <x:c r="I6" s="153"/>
       <x:c r="J6" s="153" t="str">
-        <x:v>费用始终按 Quote leg 计收；Hook 暂存的 Meme 费用会转换回 Quote。</x:v>
+        <x:v>外盘卖出所得 Quote 用于回买；双边 Hook 与 Creator Tax 降低洗后持币，预留为 0。</x:v>
       </x:c>
       <x:c r="K6" s="153"/>
       <x:c r="L6" s="153"/>
@@ -5025,14 +5025,14 @@
         <x:v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</x:v>
       </x:c>
       <x:c r="S9" s="26">
-        <x:v>2481.7308596853964</x:v>
+        <x:v>2580.0817123580937</x:v>
       </x:c>
       <x:c r="T9" s="29">
-        <x:v>46283.229076828706</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="U9" s="32" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin&amp;vs_currencies=usd</x:t>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
         </x:is>
       </x:c>
       <x:c r="V9" s="32" t="inlineStr">
@@ -5098,10 +5098,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</x:v>
       </x:c>
       <x:c r="S10" s="27">
-        <x:v>336.2102267154778</x:v>
+        <x:v>334.9426372843646</x:v>
       </x:c>
       <x:c r="T10" s="30">
-        <x:v>46283.22877545139</x:v>
+        <x:v>46285.27318768518</x:v>
       </x:c>
       <x:c r="U10" s="33" t="inlineStr">
         <x:is>
@@ -5171,10 +5171,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</x:v>
       </x:c>
       <x:c r="S11" s="27">
-        <x:v>2.7120991647535195</x:v>
+        <x:v>2.6810617004333714</x:v>
       </x:c>
       <x:c r="T11" s="30">
-        <x:v>46283.228781875005</x:v>
+        <x:v>46285.27319353009</x:v>
       </x:c>
       <x:c r="U11" s="33" t="inlineStr">
         <x:is>
@@ -5243,11 +5243,19 @@
       <x:c r="R12" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x86923f96303D656E4aa86D9d42D1e57ad2023fdC</x:v>
       </x:c>
-      <x:c r="S12" s="27"/>
+      <x:c r="S12" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T12" s="30">
-        <x:v>46283.228786747684</x:v>
-      </x:c>
-      <x:c r="U12" s="33"/>
+        <x:v>46285.27319930556</x:v>
+      </x:c>
+      <x:c r="U12" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V12" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -5310,11 +5318,19 @@
       <x:c r="R13" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x12f190a9F9d7D37a250758b26824B97CE941bF54</x:v>
       </x:c>
-      <x:c r="S13" s="27"/>
+      <x:c r="S13" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T13" s="30">
-        <x:v>46283.22879292824</x:v>
-      </x:c>
-      <x:c r="U13" s="33"/>
+        <x:v>46285.273205115736</x:v>
+      </x:c>
+      <x:c r="U13" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V13" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -5377,11 +5393,19 @@
       <x:c r="R14" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xad25ac6c84d497db898fa1e8387bf6af3532a1c4</x:v>
       </x:c>
-      <x:c r="S14" s="27"/>
+      <x:c r="S14" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T14" s="30">
-        <x:v>46283.22879886574</x:v>
-      </x:c>
-      <x:c r="U14" s="33"/>
+        <x:v>46285.27321087963</x:v>
+      </x:c>
+      <x:c r="U14" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V14" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -5444,11 +5468,19 @@
       <x:c r="R15" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x48E39E56aCdbA37b09020C0b734A613C9a2f100A</x:v>
       </x:c>
-      <x:c r="S15" s="27"/>
+      <x:c r="S15" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T15" s="30">
-        <x:v>46283.22880457176</x:v>
-      </x:c>
-      <x:c r="U15" s="33"/>
+        <x:v>46285.27321663194</x:v>
+      </x:c>
+      <x:c r="U15" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V15" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -5511,11 +5543,19 @@
       <x:c r="R16" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x822cc93ffd030293e9842c30bbd678f530701867</x:v>
       </x:c>
-      <x:c r="S16" s="27"/>
+      <x:c r="S16" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T16" s="30">
-        <x:v>46283.228810706016</x:v>
-      </x:c>
-      <x:c r="U16" s="33"/>
+        <x:v>46285.27322246528</x:v>
+      </x:c>
+      <x:c r="U16" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V16" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -5578,11 +5618,19 @@
       <x:c r="R17" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xcef9027c7d6985b85f0ba431125073529a947a68</x:v>
       </x:c>
-      <x:c r="S17" s="27"/>
+      <x:c r="S17" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T17" s="30">
-        <x:v>46283.228815891205</x:v>
-      </x:c>
-      <x:c r="U17" s="33"/>
+        <x:v>46285.273228252314</x:v>
+      </x:c>
+      <x:c r="U17" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V17" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -5646,10 +5694,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</x:v>
       </x:c>
       <x:c r="S18" s="27">
-        <x:v>176.24641472499718</x:v>
+        <x:v>192.1700993593463</x:v>
       </x:c>
       <x:c r="T18" s="30">
-        <x:v>46283.22882157408</x:v>
+        <x:v>46285.273234050925</x:v>
       </x:c>
       <x:c r="U18" s="33" t="inlineStr">
         <x:is>
@@ -5718,11 +5766,19 @@
       <x:c r="R19" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x4EA005168D7F09a7A0Ba9D1DEf21a479950E44C2</x:v>
       </x:c>
-      <x:c r="S19" s="27"/>
+      <x:c r="S19" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T19" s="30">
-        <x:v>46283.2288278588</x:v>
-      </x:c>
-      <x:c r="U19" s="33"/>
+        <x:v>46285.27323954861</x:v>
+      </x:c>
+      <x:c r="U19" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V19" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -5786,10 +5842,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</x:v>
       </x:c>
       <x:c r="S20" s="27">
-        <x:v>86.246754988361</x:v>
+        <x:v>90.91600273708387</x:v>
       </x:c>
       <x:c r="T20" s="30">
-        <x:v>46283.228835625</x:v>
+        <x:v>46285.273245625</x:v>
       </x:c>
       <x:c r="U20" s="33" t="inlineStr">
         <x:is>
@@ -5858,11 +5914,19 @@
       <x:c r="R21" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x941AE714EC6D8130c7B75d67160Ca08f1e7d11Dd</x:v>
       </x:c>
-      <x:c r="S21" s="27"/>
+      <x:c r="S21" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T21" s="30">
-        <x:v>46283.22883954861</x:v>
-      </x:c>
-      <x:c r="U21" s="33"/>
+        <x:v>46285.27325148148</x:v>
+      </x:c>
+      <x:c r="U21" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V21" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -5926,10 +5990,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</x:v>
       </x:c>
       <x:c r="S22" s="27">
-        <x:v>8.766785491970786</x:v>
+        <x:v>8.843502026802613</x:v>
       </x:c>
       <x:c r="T22" s="30">
-        <x:v>46283.228845150465</x:v>
+        <x:v>46285.27325719907</x:v>
       </x:c>
       <x:c r="U22" s="33" t="inlineStr">
         <x:is>
@@ -5998,11 +6062,19 @@
       <x:c r="R23" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x25c288e6d899b9bc30160965ad9644c67e73be0c</x:v>
       </x:c>
-      <x:c r="S23" s="27"/>
+      <x:c r="S23" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T23" s="30">
-        <x:v>46283.22885092592</x:v>
-      </x:c>
-      <x:c r="U23" s="33"/>
+        <x:v>46285.27326297454</x:v>
+      </x:c>
+      <x:c r="U23" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V23" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -6065,11 +6137,19 @@
       <x:c r="R24" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x41F4267525a8AFf329540eF24fD83d9044758B33</x:v>
       </x:c>
-      <x:c r="S24" s="27"/>
+      <x:c r="S24" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T24" s="30">
-        <x:v>46283.228857256945</x:v>
-      </x:c>
-      <x:c r="U24" s="33"/>
+        <x:v>46285.27326883102</x:v>
+      </x:c>
+      <x:c r="U24" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V24" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -6133,10 +6213,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</x:v>
       </x:c>
       <x:c r="S25" s="27">
-        <x:v>402.5115439350057</x:v>
+        <x:v>400.1284508665432</x:v>
       </x:c>
       <x:c r="T25" s="30">
-        <x:v>46283.228863055556</x:v>
+        <x:v>46285.27327459491</x:v>
       </x:c>
       <x:c r="U25" s="33" t="inlineStr">
         <x:is>
@@ -6205,11 +6285,19 @@
       <x:c r="R26" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x1b0E319c6A659F002271B69dB8A7df2F911c153E</x:v>
       </x:c>
-      <x:c r="S26" s="27"/>
+      <x:c r="S26" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T26" s="30">
-        <x:v>46283.22886776621</x:v>
-      </x:c>
-      <x:c r="U26" s="33"/>
+        <x:v>46285.273280092595</x:v>
+      </x:c>
+      <x:c r="U26" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V26" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -6273,10 +6361,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</x:v>
       </x:c>
       <x:c r="S27" s="27">
-        <x:v>349.14023454153516</x:v>
+        <x:v>349.5884370210603</x:v>
       </x:c>
       <x:c r="T27" s="30">
-        <x:v>46283.22887355324</x:v>
+        <x:v>46285.273286157404</x:v>
       </x:c>
       <x:c r="U27" s="33" t="inlineStr">
         <x:is>
@@ -6346,10 +6434,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</x:v>
       </x:c>
       <x:c r="S28" s="27">
-        <x:v>28.281890183001646</x:v>
+        <x:v>27.690965622386464</x:v>
       </x:c>
       <x:c r="T28" s="30">
-        <x:v>46283.228878981485</x:v>
+        <x:v>46285.273291631944</x:v>
       </x:c>
       <x:c r="U28" s="33" t="inlineStr">
         <x:is>
@@ -6418,11 +6506,19 @@
       <x:c r="R29" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x980dcf6766fa79f5cf0c4aadb3ab477ff15a9619</x:v>
       </x:c>
-      <x:c r="S29" s="27"/>
+      <x:c r="S29" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T29" s="30">
-        <x:v>46283.22888631944</x:v>
-      </x:c>
-      <x:c r="U29" s="33"/>
+        <x:v>46285.273297430555</x:v>
+      </x:c>
+      <x:c r="U29" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V29" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -6485,11 +6581,19 @@
       <x:c r="R30" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xacef2e09adb47ad6abebad9ff06689e60615c2b6</x:v>
       </x:c>
-      <x:c r="S30" s="27"/>
+      <x:c r="S30" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T30" s="30">
-        <x:v>46283.22889162037</x:v>
-      </x:c>
-      <x:c r="U30" s="33"/>
+        <x:v>46285.27330356481</x:v>
+      </x:c>
+      <x:c r="U30" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V30" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -6552,11 +6656,19 @@
       <x:c r="R31" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x03DfbBE0AC4E7bCDaFd08eD41A400326B77D8c80</x:v>
       </x:c>
-      <x:c r="S31" s="27"/>
+      <x:c r="S31" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T31" s="30">
-        <x:v>46283.228897395835</x:v>
-      </x:c>
-      <x:c r="U31" s="33"/>
+        <x:v>46285.273309027776</x:v>
+      </x:c>
+      <x:c r="U31" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V31" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -6620,10 +6732,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</x:v>
       </x:c>
       <x:c r="S32" s="27">
-        <x:v>1157.4858940820195</x:v>
+        <x:v>1149.547220699397</x:v>
       </x:c>
       <x:c r="T32" s="30">
-        <x:v>46283.22890365741</x:v>
+        <x:v>46285.27331482639</x:v>
       </x:c>
       <x:c r="U32" s="33" t="inlineStr">
         <x:is>
@@ -6692,11 +6804,19 @@
       <x:c r="R33" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x4e62068525Ab11FE768e29dfD00ef909B9803016</x:v>
       </x:c>
-      <x:c r="S33" s="27"/>
+      <x:c r="S33" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T33" s="30">
-        <x:v>46283.22890925926</x:v>
-      </x:c>
-      <x:c r="U33" s="33"/>
+        <x:v>46285.273321134264</x:v>
+      </x:c>
+      <x:c r="U33" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V33" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -6760,10 +6880,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</x:v>
       </x:c>
       <x:c r="S34" s="27">
-        <x:v>683.7392141517536</x:v>
+        <x:v>669.7652270299038</x:v>
       </x:c>
       <x:c r="T34" s="30">
-        <x:v>46283.228914872685</x:v>
+        <x:v>46285.273326724535</x:v>
       </x:c>
       <x:c r="U34" s="33" t="inlineStr">
         <x:is>
@@ -6832,11 +6952,19 @@
       <x:c r="R35" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x43B07D15cE533bEc5476d70C22a78a1B2B662155</x:v>
       </x:c>
-      <x:c r="S35" s="27"/>
+      <x:c r="S35" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T35" s="30">
-        <x:v>46283.22892003472</x:v>
-      </x:c>
-      <x:c r="U35" s="33"/>
+        <x:v>46285.2733328588</x:v>
+      </x:c>
+      <x:c r="U35" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V35" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -6899,11 +7027,19 @@
       <x:c r="R36" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x62fd0668e10D8B72339BE2DCF7643001688ff13B</x:v>
       </x:c>
-      <x:c r="S36" s="27"/>
+      <x:c r="S36" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T36" s="30">
-        <x:v>46283.22892554398</x:v>
-      </x:c>
-      <x:c r="U36" s="33"/>
+        <x:v>46285.27333861111</x:v>
+      </x:c>
+      <x:c r="U36" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V36" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -6966,11 +7102,19 @@
       <x:c r="R37" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xe93237C50D904957Cf27E7B1133b510C669c2e74</x:v>
       </x:c>
-      <x:c r="S37" s="27"/>
+      <x:c r="S37" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T37" s="30">
-        <x:v>46283.22893216435</x:v>
-      </x:c>
-      <x:c r="U37" s="33"/>
+        <x:v>46285.273344155095</x:v>
+      </x:c>
+      <x:c r="U37" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V37" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -7034,10 +7178,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</x:v>
       </x:c>
       <x:c r="S38" s="27">
-        <x:v>134.80433855804392</x:v>
+        <x:v>154.7412775459082</x:v>
       </x:c>
       <x:c r="T38" s="30">
-        <x:v>46283.22893792824</x:v>
+        <x:v>46285.27334990741</x:v>
       </x:c>
       <x:c r="U38" s="33" t="inlineStr">
         <x:is>
@@ -7107,10 +7251,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</x:v>
       </x:c>
       <x:c r="S39" s="27">
-        <x:v>995.5105251464635</x:v>
+        <x:v>998.9555864122192</x:v>
       </x:c>
       <x:c r="T39" s="30">
-        <x:v>46283.22894375</x:v>
+        <x:v>46285.27335563657</x:v>
       </x:c>
       <x:c r="U39" s="33" t="inlineStr">
         <x:is>
@@ -7179,11 +7323,19 @@
       <x:c r="R40" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xe0444ef8bf4ed74f74fd73686e2ddf4c1c5591e8</x:v>
       </x:c>
-      <x:c r="S40" s="27"/>
+      <x:c r="S40" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T40" s="30">
-        <x:v>46283.22895483796</x:v>
-      </x:c>
-      <x:c r="U40" s="33"/>
+        <x:v>46285.27336726852</x:v>
+      </x:c>
+      <x:c r="U40" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V40" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -7246,11 +7398,19 @@
       <x:c r="R41" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x408c14038a04f7bd235329e26d2bf569ee20e250</x:v>
       </x:c>
-      <x:c r="S41" s="27"/>
+      <x:c r="S41" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T41" s="30">
-        <x:v>46283.2289609838</x:v>
-      </x:c>
-      <x:c r="U41" s="33"/>
+        <x:v>46285.27337311342</x:v>
+      </x:c>
+      <x:c r="U41" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V41" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -7314,10 +7474,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</x:v>
       </x:c>
       <x:c r="S42" s="27">
-        <x:v>220.8209153885107</x:v>
+        <x:v>221.1215641393992</x:v>
       </x:c>
       <x:c r="T42" s="30">
-        <x:v>46283.228949687495</x:v>
+        <x:v>46285.27336118056</x:v>
       </x:c>
       <x:c r="U42" s="33" t="inlineStr">
         <x:is>
@@ -7386,11 +7546,19 @@
       <x:c r="R43" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x7066A64c24e4206CD62E83bf198c1E7EB361F51e</x:v>
       </x:c>
-      <x:c r="S43" s="27"/>
+      <x:c r="S43" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T43" s="30">
-        <x:v>46283.22896710648</x:v>
-      </x:c>
-      <x:c r="U43" s="33"/>
+        <x:v>46285.27337888889</x:v>
+      </x:c>
+      <x:c r="U43" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V43" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -7453,11 +7621,19 @@
       <x:c r="R44" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x894E1EC2D74FFE5AEF8Dc8A9e84686acCB964F2A</x:v>
       </x:c>
-      <x:c r="S44" s="27"/>
+      <x:c r="S44" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T44" s="30">
-        <x:v>46283.22897207176</x:v>
-      </x:c>
-      <x:c r="U44" s="33"/>
+        <x:v>46285.27338466435</x:v>
+      </x:c>
+      <x:c r="U44" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V44" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -7521,10 +7697,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</x:v>
       </x:c>
       <x:c r="S45" s="27">
-        <x:v>717.2751709823403</x:v>
+        <x:v>720.4953161451934</x:v>
       </x:c>
       <x:c r="T45" s="30">
-        <x:v>46283.22897837963</x:v>
+        <x:v>46285.2733905787</x:v>
       </x:c>
       <x:c r="U45" s="33" t="inlineStr">
         <x:is>
@@ -7594,10 +7770,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</x:v>
       </x:c>
       <x:c r="S46" s="27">
-        <x:v>47.88706458799111</x:v>
+        <x:v>47.33874614347281</x:v>
       </x:c>
       <x:c r="T46" s="30">
-        <x:v>46283.22898378472</x:v>
+        <x:v>46285.27339596065</x:v>
       </x:c>
       <x:c r="U46" s="33" t="inlineStr">
         <x:is>
@@ -7667,10 +7843,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</x:v>
       </x:c>
       <x:c r="S47" s="27">
-        <x:v>154.6897298509046</x:v>
+        <x:v>150.76970480310203</x:v>
       </x:c>
       <x:c r="T47" s="30">
-        <x:v>46283.228990069445</x:v>
+        <x:v>46285.273402025465</x:v>
       </x:c>
       <x:c r="U47" s="33" t="inlineStr">
         <x:is>
@@ -7739,11 +7915,19 @@
       <x:c r="R48" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xB1BF26c1D20ff267A4f93550d1E0d06ac40a114B</x:v>
       </x:c>
-      <x:c r="S48" s="27"/>
+      <x:c r="S48" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T48" s="30">
-        <x:v>46283.228996226855</x:v>
-      </x:c>
-      <x:c r="U48" s="33"/>
+        <x:v>46285.27340775463</x:v>
+      </x:c>
+      <x:c r="U48" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V48" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -7807,10 +7991,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</x:v>
       </x:c>
       <x:c r="S49" s="27">
-        <x:v>101.59863734530526</x:v>
+        <x:v>100.73989299762705</x:v>
       </x:c>
       <x:c r="T49" s="30">
-        <x:v>46283.22900111111</x:v>
+        <x:v>46285.273413599534</x:v>
       </x:c>
       <x:c r="U49" s="33" t="inlineStr">
         <x:is>
@@ -7879,11 +8063,19 @@
       <x:c r="R50" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xf53f66751b1eff985311b693531e3290f600c410</x:v>
       </x:c>
-      <x:c r="S50" s="27"/>
+      <x:c r="S50" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T50" s="30">
-        <x:v>46283.22900706019</x:v>
-      </x:c>
-      <x:c r="U50" s="33"/>
+        <x:v>46285.273419351855</x:v>
+      </x:c>
+      <x:c r="U50" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V50" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -7946,11 +8138,19 @@
       <x:c r="R51" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x84CAb63bc87912E71ad199ff14A0bA45de68FeF8</x:v>
       </x:c>
-      <x:c r="S51" s="27"/>
+      <x:c r="S51" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T51" s="30">
-        <x:v>46283.22901306713</x:v>
-      </x:c>
-      <x:c r="U51" s="33"/>
+        <x:v>46285.273425127314</x:v>
+      </x:c>
+      <x:c r="U51" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V51" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -8013,11 +8213,19 @@
       <x:c r="R52" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x411efb0e7f985935daec3d4c3ebaea0d0ad7d89f</x:v>
       </x:c>
-      <x:c r="S52" s="27"/>
+      <x:c r="S52" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T52" s="30">
-        <x:v>46283.229019363425</x:v>
-      </x:c>
-      <x:c r="U52" s="33"/>
+        <x:v>46285.2734309375</x:v>
+      </x:c>
+      <x:c r="U52" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V52" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -8080,11 +8288,19 @@
       <x:c r="R53" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xF6589F11Bc40b669e584073F428B05562F568733</x:v>
       </x:c>
-      <x:c r="S53" s="27"/>
+      <x:c r="S53" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T53" s="30">
-        <x:v>46283.22902486111</x:v>
-      </x:c>
-      <x:c r="U53" s="33"/>
+        <x:v>46285.27343675926</x:v>
+      </x:c>
+      <x:c r="U53" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V53" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -8147,11 +8363,19 @@
       <x:c r="R54" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xB90A19fF0Af67f7779afF50A882A9CfF42446400</x:v>
       </x:c>
-      <x:c r="S54" s="27"/>
+      <x:c r="S54" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T54" s="30">
-        <x:v>46283.22903109954</x:v>
-      </x:c>
-      <x:c r="U54" s="33"/>
+        <x:v>46285.27344251158</x:v>
+      </x:c>
+      <x:c r="U54" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V54" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -8215,10 +8439,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</x:v>
       </x:c>
       <x:c r="S55" s="27">
-        <x:v>155.17810785548014</x:v>
+        <x:v>152.61043373175778</x:v>
       </x:c>
       <x:c r="T55" s="30">
-        <x:v>46283.22903584491</x:v>
+        <x:v>46285.27344795139</x:v>
       </x:c>
       <x:c r="U55" s="33" t="inlineStr">
         <x:is>
@@ -8288,10 +8512,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</x:v>
       </x:c>
       <x:c r="S56" s="27">
-        <x:v>763.9713137968788</x:v>
+        <x:v>764.0325568925294</x:v>
       </x:c>
       <x:c r="T56" s="30">
-        <x:v>46283.229042175924</x:v>
+        <x:v>46285.27345454861</x:v>
       </x:c>
       <x:c r="U56" s="33" t="inlineStr">
         <x:is>
@@ -8361,10 +8585,10 @@
         <x:v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</x:v>
       </x:c>
       <x:c r="S57" s="27">
-        <x:v>368.1749674247868</x:v>
+        <x:v>362.95372967695204</x:v>
       </x:c>
       <x:c r="T57" s="30">
-        <x:v>46283.22904818287</x:v>
+        <x:v>46285.27345984954</x:v>
       </x:c>
       <x:c r="U57" s="33" t="inlineStr">
         <x:is>
@@ -8433,11 +8657,19 @@
       <x:c r="R58" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x58FfE4a942d3885bAa22D7520691F611EF09e7AA</x:v>
       </x:c>
-      <x:c r="S58" s="27"/>
+      <x:c r="S58" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T58" s="30">
-        <x:v>46283.22905378472</x:v>
-      </x:c>
-      <x:c r="U58" s="33"/>
+        <x:v>46285.27346563658</x:v>
+      </x:c>
+      <x:c r="U58" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V58" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -8500,11 +8732,19 @@
       <x:c r="R59" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x5e81213613b6B86EaB4c6c50d718d34359459786</x:v>
       </x:c>
-      <x:c r="S59" s="27"/>
+      <x:c r="S59" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T59" s="30">
-        <x:v>46283.22905945602</x:v>
-      </x:c>
-      <x:c r="U59" s="33"/>
+        <x:v>46285.273471423614</x:v>
+      </x:c>
+      <x:c r="U59" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V59" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -8567,11 +8807,19 @@
       <x:c r="R60" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xf23250dac154d05bb671cb0d0ebef3c635c79ce2</x:v>
       </x:c>
-      <x:c r="S60" s="27"/>
+      <x:c r="S60" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T60" s="30">
-        <x:v>46283.22906563657</x:v>
-      </x:c>
-      <x:c r="U60" s="33"/>
+        <x:v>46285.273477222225</x:v>
+      </x:c>
+      <x:c r="U60" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V60" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -8634,11 +8882,19 @@
       <x:c r="R61" s="33" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0xa30FA36Db767ad9eD3f7a60fC79526fB4d56D344</x:v>
       </x:c>
-      <x:c r="S61" s="27"/>
+      <x:c r="S61" s="27" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T61" s="30">
-        <x:v>46283.229071168986</x:v>
-      </x:c>
-      <x:c r="U61" s="33"/>
+        <x:v>46285.27348305556</x:v>
+      </x:c>
+      <x:c r="U61" s="33" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V61" s="33" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -8701,11 +8957,19 @@
       <x:c r="R62" s="34" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x9e7ABD3C9139D14E4c86DcE0e455AAB7A0C2FB3E</x:v>
       </x:c>
-      <x:c r="S62" s="28"/>
+      <x:c r="S62" s="28" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="T62" s="31">
-        <x:v>46283.229076828706</x:v>
-      </x:c>
-      <x:c r="U62" s="34"/>
+        <x:v>46285.27348880787</x:v>
+      </x:c>
+      <x:c r="U62" s="34" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
       <x:c r="V62" s="34" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">暂无合格池价；可手动输入</x:t>
@@ -8766,17 +9030,21 @@
       <x:c r="R63" t="str">
         <x:v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</x:v>
       </x:c>
-      <x:c r="S63" s="155" t="n">
+      <x:c r="S63" s="155">
         <x:v>1.0003961568781237</x:v>
       </x:c>
-      <x:c r="T63" s="156" t="n">
+      <x:c r="T63" s="156">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="U63" t="str">
-        <x:v>https://www.coingecko.com/en/coins/global-dollar</x:v>
-      </x:c>
-      <x:c r="V63" s="157" t="str">
-        <x:v>TRAIN 创建时 phantom 3,236、门槛 8,090 USDG；PERC 迁池同为 8,090。其他币按发行时参数核对。</x:v>
+      <x:c r="U63" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V63" s="157" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">USDG 按 1 USD 估算；本地可手动更新</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R4174b316770c4864"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Ra03c4c2a547940c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rc186d0e49add41d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R3b11b162cb2c48f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D18" s="121" t="n">
         <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
-        <v>689114.8230851085</v>
+        <v>733940.9157956967</v>
       </c>
       <c r="E18" s="62" t="str">
         <f>$D$7</f>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="J18" s="121" t="n">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
-        <v>692225.9105456846</v>
+        <v>737069.7614212194</v>
       </c>
       <c r="K18" s="62" t="str">
         <v>USDT</v>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D19" s="122" t="n">
         <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$55&gt;0,$D$18*$D$55,"")),"")</f>
-        <v>689387.8206620907</v>
+        <v>734231.6715376255</v>
       </c>
       <c r="E19" s="106" t="str">
         <v>USDT</v>
@@ -1555,8 +1555,8 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="122" t="n">
-        <f>IF($D$51&lt;&gt;"可达","",0)</f>
-        <v>0</v>
+        <f>IF($D$51&lt;&gt;"可达","",IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*(1/(1-$G$42-$J$7))),""))</f>
+        <v>44826.09271058811</v>
       </c>
       <c r="E26" s="106" t="str">
         <f>$D$7</f>
@@ -1732,7 +1732,7 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="115" t="str">
-        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="115"/>
       <c r="E36" s="115"/>
@@ -2214,7 +2214,7 @@
         <v>目标外盘 Pool TOKEN</v>
       </c>
       <c r="J55" s="108" t="n">
-        <f>$G$48-MAX(0,($D$8-$G$43)*$D$45)</f>
+        <f>$G$48-($D$8-$G$43)*$D$45</f>
         <v>18367346.93877548</v>
       </c>
       <c r="K55" s="107"/>
@@ -2242,7 +2242,7 @@
         <v>洗后外盘 Pool TOKEN</v>
       </c>
       <c r="J56" s="108" t="n">
-        <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)</f>
+        <f>$G$48-($D$27-$G$43)*$D$45</f>
         <v>36277346.93877548</v>
       </c>
       <c r="K56" s="107"/>
@@ -4853,7 +4853,7 @@
       </x:c>
       <x:c r="I6" s="153"/>
       <x:c r="J6" s="153" t="str">
-        <x:v>外盘卖出所得 Quote 用于回买；双边 Hook 与 Creator Tax 降低洗后持币，预留为 0。</x:v>
+        <x:v>外盘卖出所得 Quote 用于回买；双边 Hook 与 Creator Tax 降低持币。恢复目标按外盘曲线差额及买入费另列。</x:v>
       </x:c>
       <x:c r="K6" s="153"/>
       <x:c r="L6" s="153"/>

--- a/excel/templates/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/templates/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rc186d0e49add41d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R3b11b162cb2c48f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R29bd439ea94449d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R75525efca1a94dae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="11">
+  <x:numFmts count="12">
     <x:numFmt numFmtId="200" formatCode="@"/>
     <x:numFmt numFmtId="201" formatCode="0"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
@@ -26,6 +26,7 @@
     <x:numFmt numFmtId="208" formatCode="0.00%"/>
     <x:numFmt numFmtId="209" formatCode="0.000000E+00"/>
     <x:numFmt numFmtId="210" formatCode="0.0000000000"/>
+    <x:numFmt numFmtId="211" formatCode=";;;"/>
   </x:numFmts>
   <x:fonts count="12">
     <x:font>
@@ -163,7 +164,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="158">
+  <x:cellXfs count="159">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -625,6 +626,9 @@
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1348,8 +1352,8 @@
         <v>建议 Quote 资金</v>
       </c>
       <c r="D18" s="121" t="n">
-        <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
-        <v>733940.9157956967</v>
+        <f>IF(AND(LEFT($D$51,2)="可达",ISNUMBER($D$22),ISNUMBER($D$23),ISNUMBER($D$25),ISNUMBER($D$26)),SUM($D$22:$D$23,$D$25:$D$26),"")</f>
+        <v>262304.984802237</v>
       </c>
       <c r="E18" s="62" t="str">
         <f>$D$7</f>
@@ -1370,7 +1374,7 @@
       </c>
       <c r="J18" s="121" t="n">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
-        <v>737069.7614212194</v>
+        <v>265246.9886097264</v>
       </c>
       <c r="K18" s="62" t="str">
         <v>USDT</v>
@@ -1385,7 +1389,7 @@
       </c>
       <c r="D19" s="122" t="n">
         <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$55&gt;0,$D$18*$D$55,"")),"")</f>
-        <v>734231.6715376255</v>
+        <v>262408.8987261325</v>
       </c>
       <c r="E19" s="106" t="str">
         <v>USDT</v>
@@ -1494,16 +1498,11 @@
       <c r="K23" s="106"/>
       <c r="L23" s="106"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
+    <row r="24" customHeight="1" hidden="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="107" t="str">
-        <v>洗筹损耗</v>
-      </c>
-      <c r="D24" s="122" t="n">
-        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
-        <v>471635.93099345965</v>
-      </c>
+      <c r="C24" s="107"/>
+      <c r="D24" s="158"/>
       <c r="E24" s="106" t="str">
         <f>$D$7</f>
         <v>USDG</v>
@@ -1732,7 +1731,7 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="115" t="str">
-        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；手续费仅降低洗后持币，不另列资金。洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="115"/>
       <c r="E36" s="115"/>
